--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NLCX3311\Desktop\MES SUIVIS\EXTRACTION\Extraction 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NLCX3311\Desktop\MES SUIVIS\EXTRACTION\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$109</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="592">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -44,10 +44,10 @@
     <t>DATE CREATION DOSSIER</t>
   </si>
   <si>
-    <t>OPERATION TM</t>
-  </si>
-  <si>
-    <t>LOCALISATION</t>
+    <t>TYPE OPERATION TM</t>
+  </si>
+  <si>
+    <t>LOCALISATION GEO</t>
   </si>
   <si>
     <t>DEBIT</t>
@@ -71,33 +71,111 @@
     <t>CARACTERISTIQUE</t>
   </si>
   <si>
+    <t>42090133</t>
+  </si>
+  <si>
+    <t>11/03/2025 19:12:18</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>support</t>
+  </si>
+  <si>
+    <t>ftto</t>
+  </si>
+  <si>
+    <t>fo</t>
+  </si>
+  <si>
+    <t>DOUANES</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/VRIDI SDV-CI</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>VPNLL220026</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>Backup</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie GAIA</t>
+  </si>
+  <si>
+    <t>Responsable Zone: Validation pour intervention</t>
+  </si>
+  <si>
+    <t>Support IP: Config Eq Acces</t>
+  </si>
+  <si>
+    <t>Technicien zone: Survey</t>
+  </si>
+  <si>
+    <t>Technicien zone: Intervention</t>
+  </si>
+  <si>
+    <t>Sauvegardé</t>
+  </si>
+  <si>
+    <t>Responsable Zone: Validation intervention</t>
+  </si>
+  <si>
+    <t>28/08/2025 17:43:52</t>
+  </si>
+  <si>
+    <t>Responsable Zone: Validation Survey</t>
+  </si>
+  <si>
+    <t>Responsable IP: Affectation Ingenieur Delivery</t>
+  </si>
+  <si>
+    <t>SIE: Pilote</t>
+  </si>
+  <si>
+    <t>42085288</t>
+  </si>
+  <si>
+    <t>11/03/2025 17:42:13</t>
+  </si>
+  <si>
+    <t>radio</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/CT 0707630916</t>
+  </si>
+  <si>
+    <t>4M</t>
+  </si>
+  <si>
+    <t>VPNLL220036</t>
+  </si>
+  <si>
+    <t>07/04/2025 18:04:16</t>
+  </si>
+  <si>
+    <t>Offert</t>
+  </si>
+  <si>
     <t>42091025</t>
   </si>
   <si>
     <t>11/03/2025 19:35:08</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Modification</t>
-  </si>
-  <si>
-    <t>fo</t>
-  </si>
-  <si>
-    <t>DOUANES</t>
+    <t>DIRECTION INFORMATIQUE DOUANES</t>
   </si>
   <si>
     <t>VPNLL130143</t>
   </si>
   <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>Backup</t>
-  </si>
-  <si>
     <t>En cours</t>
   </si>
   <si>
@@ -107,9 +185,6 @@
     <t>02/06/2025 14:26:16</t>
   </si>
   <si>
-    <t>Parametrage facturation</t>
-  </si>
-  <si>
     <t>Réassigné</t>
   </si>
   <si>
@@ -131,78 +206,6 @@
     <t>03/04/2025 12:48:56</t>
   </si>
   <si>
-    <t>42085288</t>
-  </si>
-  <si>
-    <t>11/03/2025 17:42:13</t>
-  </si>
-  <si>
-    <t>radio</t>
-  </si>
-  <si>
-    <t>4M</t>
-  </si>
-  <si>
-    <t>VPNLL220036</t>
-  </si>
-  <si>
-    <t>BO Homologation: Saisie GAIA</t>
-  </si>
-  <si>
-    <t>07/04/2025 18:04:16</t>
-  </si>
-  <si>
-    <t>Offert</t>
-  </si>
-  <si>
-    <t>SIE: Pilote</t>
-  </si>
-  <si>
-    <t>42090133</t>
-  </si>
-  <si>
-    <t>11/03/2025 19:12:18</t>
-  </si>
-  <si>
-    <t>ftto</t>
-  </si>
-  <si>
-    <t>PORT BOUET</t>
-  </si>
-  <si>
-    <t>1M</t>
-  </si>
-  <si>
-    <t>VPNLL220026</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Validation pour intervention</t>
-  </si>
-  <si>
-    <t>Support IP: Config Eq Acces</t>
-  </si>
-  <si>
-    <t>Technicien zone: Survey</t>
-  </si>
-  <si>
-    <t>Technicien zone: Intervention</t>
-  </si>
-  <si>
-    <t>Sauvegardé</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Validation intervention</t>
-  </si>
-  <si>
-    <t>28/08/2025 17:43:52</t>
-  </si>
-  <si>
-    <t>Support IP: Correction</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Validation Survey</t>
-  </si>
-  <si>
     <t>Transfert</t>
   </si>
   <si>
@@ -215,7 +218,40 @@
     <t>SIE : Mise en service GAIA</t>
   </si>
   <si>
-    <t>Test et recette</t>
+    <t>44075918</t>
+  </si>
+  <si>
+    <t>30/04/2025 10:09:42</t>
+  </si>
+  <si>
+    <t>fo_virage</t>
+  </si>
+  <si>
+    <t>BANQUE MALIENNE DE SOLIDARITE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>PLATEAU</t>
+  </si>
+  <si>
+    <t>ABIDJAN PLATEAU RUE DU COMMERCE</t>
+  </si>
+  <si>
+    <t>128K</t>
+  </si>
+  <si>
+    <t>2720307380</t>
+  </si>
+  <si>
+    <t>numerique</t>
+  </si>
+  <si>
+    <t>DIE : Preparation Travaux</t>
+  </si>
+  <si>
+    <t>23/09/2025 16:49:09</t>
+  </si>
+  <si>
+    <t>Travaux Suspendu</t>
   </si>
   <si>
     <t>43259257</t>
@@ -227,6 +263,9 @@
     <t>CIMAF</t>
   </si>
   <si>
+    <t>SAN-PEDRO//VOIE INCONNUE/ZONE PORTUAIRE SAN PEDRO</t>
+  </si>
+  <si>
     <t>40M</t>
   </si>
   <si>
@@ -236,40 +275,28 @@
     <t>LSI</t>
   </si>
   <si>
+    <t>BO Homologation : Saisie GAIA LSI</t>
+  </si>
+  <si>
     <t>28/05/2025 15:21:06</t>
   </si>
   <si>
-    <t>44075918</t>
-  </si>
-  <si>
-    <t>30/04/2025 10:09:42</t>
-  </si>
-  <si>
-    <t>fo_virage</t>
-  </si>
-  <si>
-    <t>BANQUE MALIENNE DE SOLIDARITE COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>PLATEAU</t>
-  </si>
-  <si>
-    <t>128K</t>
-  </si>
-  <si>
-    <t>2720307380</t>
-  </si>
-  <si>
-    <t>numerique</t>
-  </si>
-  <si>
-    <t>DIE : Preparation Travaux</t>
-  </si>
-  <si>
-    <t>23/09/2025 16:49:09</t>
-  </si>
-  <si>
-    <t>Travaux Suspendu</t>
+    <t>45306957</t>
+  </si>
+  <si>
+    <t>28/05/2025 14:31:51</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIRIENNE DE BANQUE</t>
+  </si>
+  <si>
+    <t>ABIDJAN YOPOUGON</t>
+  </si>
+  <si>
+    <t>BUVPN230179</t>
+  </si>
+  <si>
+    <t>26/06/2025 13:57:23</t>
   </si>
   <si>
     <t>44431296</t>
@@ -281,7 +308,7 @@
     <t>LOTERIE NATIONALE DE COTE D'IVOIRE</t>
   </si>
   <si>
-    <t>KORHOGO</t>
+    <t>KORHOGO//VOIE INCONNUE/KORHOGO</t>
   </si>
   <si>
     <t>6M</t>
@@ -293,28 +320,68 @@
     <t>13/11/2025 10:12:24</t>
   </si>
   <si>
-    <t>45306957</t>
-  </si>
-  <si>
-    <t>28/05/2025 14:31:51</t>
-  </si>
-  <si>
-    <t>SOCIETE IVOIRIENNE DE BANQUE</t>
-  </si>
-  <si>
-    <t>BUVPN230179</t>
-  </si>
-  <si>
-    <t>26/06/2025 13:57:23</t>
-  </si>
-  <si>
     <t>ftto_virage</t>
   </si>
   <si>
     <t>TREICHVILLE</t>
   </si>
   <si>
-    <t>DIE : Configuration IMS</t>
+    <t>46596937</t>
+  </si>
+  <si>
+    <t>26/06/2025 18:16:26</t>
+  </si>
+  <si>
+    <t>debit</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DU TRESOR ET DE LA COMPTABILITE PUBLIQUE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU
+IMMEUBLE SCIAM</t>
+  </si>
+  <si>
+    <t>SYTHD050048</t>
+  </si>
+  <si>
+    <t>06/11/2025 15:29:33</t>
+  </si>
+  <si>
+    <t>46473005</t>
+  </si>
+  <si>
+    <t>24/06/2025 16:24:21</t>
+  </si>
+  <si>
+    <t>SEGUELA//VOIE INCONNUE/CONTACT 0707003126</t>
+  </si>
+  <si>
+    <t>VPNLL080103</t>
+  </si>
+  <si>
+    <t>06/11/2025 15:30:05</t>
+  </si>
+  <si>
+    <t>46536492</t>
+  </si>
+  <si>
+    <t>25/06/2025 17:16:21</t>
+  </si>
+  <si>
+    <t>cuivre</t>
+  </si>
+  <si>
+    <t>//VOIE INCONNUE/MAIRIE DE SINFRA - TRESOR</t>
+  </si>
+  <si>
+    <t>30M</t>
+  </si>
+  <si>
+    <t>VPNLL090184</t>
+  </si>
+  <si>
+    <t>06/10/2025 15:57:26</t>
   </si>
   <si>
     <t>46532522</t>
@@ -323,7 +390,7 @@
     <t>25/06/2025 16:32:38</t>
   </si>
   <si>
-    <t>DIRECTION GENERALE DU TRESOR ET DE LA COMPTABILITE PUBLIQUE</t>
+    <t>//VOIE INCONNUE/DGTCP,cité financière,Tour B</t>
   </si>
   <si>
     <t>2M</t>
@@ -335,46 +402,88 @@
     <t>06/11/2025 15:30:23</t>
   </si>
   <si>
-    <t>46536492</t>
-  </si>
-  <si>
-    <t>25/06/2025 17:16:21</t>
-  </si>
-  <si>
-    <t>cuivre</t>
-  </si>
-  <si>
-    <t>30M</t>
-  </si>
-  <si>
-    <t>VPNLL090184</t>
-  </si>
-  <si>
-    <t>06/10/2025 15:57:26</t>
-  </si>
-  <si>
-    <t>46473005</t>
-  </si>
-  <si>
-    <t>24/06/2025 16:24:21</t>
-  </si>
-  <si>
-    <t>VPNLL080103</t>
-  </si>
-  <si>
-    <t>06/11/2025 15:30:05</t>
-  </si>
-  <si>
-    <t>46596937</t>
-  </si>
-  <si>
-    <t>26/06/2025 18:16:26</t>
-  </si>
-  <si>
-    <t>SYTHD050048</t>
-  </si>
-  <si>
-    <t>06/11/2025 15:29:33</t>
+    <t>47261410</t>
+  </si>
+  <si>
+    <t>10/07/2025 15:09:58</t>
+  </si>
+  <si>
+    <t>PROJET D'APPUI A LA SECURITE DE L'EAU ET L'ASSAINISSEMENT</t>
+  </si>
+  <si>
+    <t>ABIDJAN COCODY</t>
+  </si>
+  <si>
+    <t>2722228685</t>
+  </si>
+  <si>
+    <t>02/09/2025 18:11:09</t>
+  </si>
+  <si>
+    <t>47658350</t>
+  </si>
+  <si>
+    <t>18/07/2025 13:30:49</t>
+  </si>
+  <si>
+    <t>CAISSE NATIONALE DE PREVOYANCE SOCIALE</t>
+  </si>
+  <si>
+    <t>SAN-PEDRO//VOIE INCONNUE/SAN PEDRO</t>
+  </si>
+  <si>
+    <t>5M</t>
+  </si>
+  <si>
+    <t>SYTHD240176</t>
+  </si>
+  <si>
+    <t>14/08/2025 09:01:02</t>
+  </si>
+  <si>
+    <t>47871834</t>
+  </si>
+  <si>
+    <t>23/07/2025 11:27:13</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY ANGRE DJIBI</t>
+  </si>
+  <si>
+    <t>SYTHD240171</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie BSCS</t>
+  </si>
+  <si>
+    <t>30/10/2025 14:56:28</t>
+  </si>
+  <si>
+    <t>47878019</t>
+  </si>
+  <si>
+    <t>23/07/2025 12:51:35</t>
+  </si>
+  <si>
+    <t>20M</t>
+  </si>
+  <si>
+    <t>BUVPN150600</t>
+  </si>
+  <si>
+    <t>27/08/2025 14:19:45</t>
+  </si>
+  <si>
+    <t>48207282</t>
+  </si>
+  <si>
+    <t>30/07/2025 10:08:29</t>
+  </si>
+  <si>
+    <t>VPNLL220035</t>
+  </si>
+  <si>
+    <t>11/12/2025 09:01:38</t>
   </si>
   <si>
     <t>47653333</t>
@@ -383,30 +492,60 @@
     <t>18/07/2025 12:45:02</t>
   </si>
   <si>
-    <t>CAISSE NATIONALE DE PREVOYANCE SOCIALE</t>
-  </si>
-  <si>
-    <t>20M</t>
-  </si>
-  <si>
     <t>BUVPN150689</t>
   </si>
   <si>
     <t>14/08/2025 09:23:10</t>
   </si>
   <si>
+    <t>47648026</t>
+  </si>
+  <si>
+    <t>18/07/2025 11:14:46</t>
+  </si>
+  <si>
+    <t>SAN PEDRO</t>
+  </si>
+  <si>
+    <t>BUVPN150605</t>
+  </si>
+  <si>
+    <t>01/08/2025 12:49:49</t>
+  </si>
+  <si>
     <t>47885035</t>
   </si>
   <si>
     <t>23/07/2025 14:30:04</t>
   </si>
   <si>
+    <t>COCODY ANGRE DJIBI</t>
+  </si>
+  <si>
     <t>2720305170</t>
   </si>
   <si>
     <t>27/08/2025 15:59:17</t>
   </si>
   <si>
+    <t>48206525</t>
+  </si>
+  <si>
+    <t>30/07/2025 09:58:32</t>
+  </si>
+  <si>
+    <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/TREICHVILLE 0767161532</t>
+  </si>
+  <si>
+    <t>512K</t>
+  </si>
+  <si>
+    <t>VPNLL130015</t>
+  </si>
+  <si>
+    <t>14/01/2026 09:22:01</t>
+  </si>
+  <si>
     <t>47639322</t>
   </si>
   <si>
@@ -419,99 +558,6 @@
     <t>28/08/2025 20:16:23</t>
   </si>
   <si>
-    <t>47261410</t>
-  </si>
-  <si>
-    <t>10/07/2025 15:09:58</t>
-  </si>
-  <si>
-    <t>PROJET D'APPUI A LA SECURITE DE L'EAU ET L'ASSAINISSEMENT</t>
-  </si>
-  <si>
-    <t>2722228685</t>
-  </si>
-  <si>
-    <t>02/09/2025 18:11:09</t>
-  </si>
-  <si>
-    <t>47648026</t>
-  </si>
-  <si>
-    <t>18/07/2025 11:14:46</t>
-  </si>
-  <si>
-    <t>BUVPN150605</t>
-  </si>
-  <si>
-    <t>01/08/2025 12:49:49</t>
-  </si>
-  <si>
-    <t>47878019</t>
-  </si>
-  <si>
-    <t>23/07/2025 12:51:35</t>
-  </si>
-  <si>
-    <t>BUVPN150600</t>
-  </si>
-  <si>
-    <t>27/08/2025 14:19:45</t>
-  </si>
-  <si>
-    <t>48207282</t>
-  </si>
-  <si>
-    <t>30/07/2025 10:08:29</t>
-  </si>
-  <si>
-    <t>VPNLL220035</t>
-  </si>
-  <si>
-    <t>11/12/2025 09:01:38</t>
-  </si>
-  <si>
-    <t>48206525</t>
-  </si>
-  <si>
-    <t>30/07/2025 09:58:32</t>
-  </si>
-  <si>
-    <t>512K</t>
-  </si>
-  <si>
-    <t>VPNLL130015</t>
-  </si>
-  <si>
-    <t>14/01/2026 09:22:01</t>
-  </si>
-  <si>
-    <t>47871834</t>
-  </si>
-  <si>
-    <t>23/07/2025 11:27:13</t>
-  </si>
-  <si>
-    <t>5M</t>
-  </si>
-  <si>
-    <t>SYTHD240171</t>
-  </si>
-  <si>
-    <t>30/10/2025 14:56:28</t>
-  </si>
-  <si>
-    <t>47658350</t>
-  </si>
-  <si>
-    <t>18/07/2025 13:30:49</t>
-  </si>
-  <si>
-    <t>SYTHD240176</t>
-  </si>
-  <si>
-    <t>14/08/2025 09:01:02</t>
-  </si>
-  <si>
     <t>48419891</t>
   </si>
   <si>
@@ -521,6 +567,9 @@
     <t>ECOBANK COTE D'IVOIRE</t>
   </si>
   <si>
+    <t>ABIDJAN ANGRE AGHIEN</t>
+  </si>
+  <si>
     <t>2722526370</t>
   </si>
   <si>
@@ -536,73 +585,103 @@
     <t>MEDLOG COTE D'IVOIRE</t>
   </si>
   <si>
+    <t>TREICHVILLE KM4</t>
+  </si>
+  <si>
     <t>2721216390</t>
   </si>
   <si>
     <t>27/01/2026 11:29:22</t>
   </si>
   <si>
+    <t>51016709</t>
+  </si>
+  <si>
+    <t>24/09/2025 08:43:16</t>
+  </si>
+  <si>
+    <t>ODIENNE//VOIE INCONNUE/ODIENNE</t>
+  </si>
+  <si>
+    <t>VPNLL120010</t>
+  </si>
+  <si>
+    <t>14/10/2025 14:27:35</t>
+  </si>
+  <si>
+    <t>51053195</t>
+  </si>
+  <si>
+    <t>24/09/2025 16:13:20</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES IMPOTS</t>
+  </si>
+  <si>
+    <t>GRAND-LAHOU//VOIE INCONNUE/GRAND LAHOU</t>
+  </si>
+  <si>
+    <t>VPNLL120232</t>
+  </si>
+  <si>
+    <t>10/10/2025 12:19:09</t>
+  </si>
+  <si>
+    <t>50439713</t>
+  </si>
+  <si>
+    <t>12/09/2025 13:43:51</t>
+  </si>
+  <si>
+    <t>SYTHD030257</t>
+  </si>
+  <si>
+    <t>24/10/2025 15:48:07</t>
+  </si>
+  <si>
+    <t>50411465</t>
+  </si>
+  <si>
+    <t>12/09/2025 08:45:30</t>
+  </si>
+  <si>
+    <t>SYTHD070012</t>
+  </si>
+  <si>
+    <t>24/10/2025 16:34:01</t>
+  </si>
+  <si>
     <t>50608489</t>
   </si>
   <si>
     <t>16/09/2025 10:36:49</t>
   </si>
   <si>
+    <t>IMMEUBLE SCIAM</t>
+  </si>
+  <si>
     <t>BUVPN180153</t>
   </si>
   <si>
     <t>26/09/2025 22:47:49</t>
   </si>
   <si>
-    <t>51016709</t>
-  </si>
-  <si>
-    <t>24/09/2025 08:43:16</t>
-  </si>
-  <si>
-    <t>VPNLL120010</t>
-  </si>
-  <si>
-    <t>14/10/2025 14:27:35</t>
-  </si>
-  <si>
-    <t>50411465</t>
-  </si>
-  <si>
-    <t>12/09/2025 08:45:30</t>
-  </si>
-  <si>
-    <t>SYTHD070012</t>
-  </si>
-  <si>
-    <t>24/10/2025 16:34:01</t>
-  </si>
-  <si>
-    <t>50439713</t>
-  </si>
-  <si>
-    <t>12/09/2025 13:43:51</t>
-  </si>
-  <si>
-    <t>SYTHD030257</t>
-  </si>
-  <si>
-    <t>24/10/2025 15:48:07</t>
-  </si>
-  <si>
-    <t>51053195</t>
-  </si>
-  <si>
-    <t>24/09/2025 16:13:20</t>
-  </si>
-  <si>
-    <t>DIRECTION GENERALE DES IMPOTS</t>
-  </si>
-  <si>
-    <t>VPNLL120232</t>
-  </si>
-  <si>
-    <t>10/10/2025 12:19:09</t>
+    <t>52558712</t>
+  </si>
+  <si>
+    <t>24/10/2025 15:03:02</t>
+  </si>
+  <si>
+    <t>FONDS INTERNATIONAL POUR LE DEVELOPPEMENT DE LA RETRAITE ACTIVE</t>
+  </si>
+  <si>
+    <t>50M</t>
+  </si>
+  <si>
+    <t>BUVPN230242</t>
+  </si>
+  <si>
+    <t>11/11/2025 16:40:10</t>
   </si>
   <si>
     <t>51691679</t>
@@ -611,28 +690,31 @@
     <t>07/10/2025 11:10:57</t>
   </si>
   <si>
+    <t>ABIDJAN-PLATEAU//A008 AV NOGUES/PLATEAU AVENUE NOGUES</t>
+  </si>
+  <si>
     <t>SYTHD200123</t>
   </si>
   <si>
     <t>22/10/2025 12:30:17</t>
   </si>
   <si>
-    <t>52558712</t>
-  </si>
-  <si>
-    <t>24/10/2025 15:03:02</t>
-  </si>
-  <si>
-    <t>FONDS INTERNATIONAL POUR LE DEVELOPPEMENT DE LA RETRAITE ACTIVE</t>
-  </si>
-  <si>
-    <t>50M</t>
-  </si>
-  <si>
-    <t>BUVPN230242</t>
-  </si>
-  <si>
-    <t>11/11/2025 16:40:10</t>
+    <t>52090983</t>
+  </si>
+  <si>
+    <t>15/10/2025 14:03:08</t>
+  </si>
+  <si>
+    <t>AVIATION ET COMPAGNIES COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET</t>
+  </si>
+  <si>
+    <t>2721212909</t>
+  </si>
+  <si>
+    <t>26/02/2026 12:37:40</t>
   </si>
   <si>
     <t>52741559</t>
@@ -641,40 +723,31 @@
     <t>29/10/2025 09:10:21</t>
   </si>
   <si>
+    <t>bonoua</t>
+  </si>
+  <si>
     <t>2721300130</t>
   </si>
   <si>
     <t>25/11/2025 12:54:15</t>
   </si>
   <si>
-    <t>52090983</t>
-  </si>
-  <si>
-    <t>15/10/2025 14:03:08</t>
-  </si>
-  <si>
-    <t>AVIATION ET COMPAGNIES COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>2721212909</t>
-  </si>
-  <si>
-    <t>16/10/2025 11:38:30</t>
-  </si>
-  <si>
-    <t>53522780</t>
-  </si>
-  <si>
-    <t>13/11/2025 15:13:08</t>
-  </si>
-  <si>
-    <t>SDMCI/ PROPHARMED INTERNATIONAL</t>
-  </si>
-  <si>
-    <t>2722409380</t>
-  </si>
-  <si>
-    <t>19/02/2026 12:03:50</t>
+    <t>55994930</t>
+  </si>
+  <si>
+    <t>30/12/2025 15:09:31</t>
+  </si>
+  <si>
+    <t>INTELCIA COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/INTELCA CI, COCODY RIVIERA</t>
+  </si>
+  <si>
+    <t>SYTHD170178</t>
+  </si>
+  <si>
+    <t>06/01/2026 19:35:09</t>
   </si>
   <si>
     <t>54442992</t>
@@ -689,39 +762,15 @@
     <t>06/01/2026 19:47:15</t>
   </si>
   <si>
-    <t>55994930</t>
-  </si>
-  <si>
-    <t>30/12/2025 15:09:31</t>
-  </si>
-  <si>
-    <t>INTELCIA COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>SYTHD170178</t>
-  </si>
-  <si>
-    <t>06/01/2026 19:35:09</t>
-  </si>
-  <si>
-    <t>54479742</t>
-  </si>
-  <si>
-    <t>02/12/2025 11:44:39</t>
-  </si>
-  <si>
-    <t>VPNLL100068</t>
-  </si>
-  <si>
-    <t>02/01/2026 12:27:12</t>
-  </si>
-  <si>
     <t>55980750</t>
   </si>
   <si>
     <t>30/12/2025 12:27:06</t>
   </si>
   <si>
+    <t>COCODY RIVIERA PALMERAIE SOCOPRIX ROUTE DE BINGERVILLE</t>
+  </si>
+  <si>
     <t>100M</t>
   </si>
   <si>
@@ -734,28 +783,52 @@
     <t>06/01/2026 19:29:08</t>
   </si>
   <si>
+    <t>55492730</t>
+  </si>
+  <si>
+    <t>19/12/2025 18:59:39</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/FRET AEROPORT</t>
+  </si>
+  <si>
+    <t>VPNLL230023</t>
+  </si>
+  <si>
+    <t>20/01/2026 09:11:56</t>
+  </si>
+  <si>
     <t>54447209</t>
   </si>
   <si>
     <t>01/12/2025 16:36:58</t>
   </si>
   <si>
+    <t>SEGUELA</t>
+  </si>
+  <si>
     <t>BUVPN230217</t>
   </si>
   <si>
     <t>16/01/2026 09:44:03</t>
   </si>
   <si>
-    <t>55492730</t>
-  </si>
-  <si>
-    <t>19/12/2025 18:59:39</t>
-  </si>
-  <si>
-    <t>VPNLL230023</t>
-  </si>
-  <si>
-    <t>20/01/2026 09:11:56</t>
+    <t>54962571</t>
+  </si>
+  <si>
+    <t>11/12/2025 10:06:55</t>
+  </si>
+  <si>
+    <t>DES SOCIETES D'ASSURANCE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>RAXIO VITIB BASSAM</t>
+  </si>
+  <si>
+    <t>2722221750</t>
+  </si>
+  <si>
+    <t>19/12/2025 15:34:19</t>
   </si>
   <si>
     <t>55167162</t>
@@ -767,22 +840,64 @@
     <t>29/12/2025 15:45:51</t>
   </si>
   <si>
-    <t>54962571</t>
-  </si>
-  <si>
-    <t>11/12/2025 10:06:55</t>
-  </si>
-  <si>
-    <t>DES SOCIETES D'ASSURANCE COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>GRAND BASSAM</t>
-  </si>
-  <si>
-    <t>2722221750</t>
-  </si>
-  <si>
-    <t>19/12/2025 15:34:19</t>
+    <t>57100866</t>
+  </si>
+  <si>
+    <t>22/01/2026 14:47:47</t>
+  </si>
+  <si>
+    <t>BANQUE INTERNATIONALE POUR LE COMMERCE ET L'INDUSTRIE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/RIVIERA PALMERAIE</t>
+  </si>
+  <si>
+    <t>8M</t>
+  </si>
+  <si>
+    <t>BICICI</t>
+  </si>
+  <si>
+    <t>BUVPN170123</t>
+  </si>
+  <si>
+    <t>04/02/2026 19:45:44</t>
+  </si>
+  <si>
+    <t>56268044</t>
+  </si>
+  <si>
+    <t>06/01/2026 15:42:28</t>
+  </si>
+  <si>
+    <t>AERIA</t>
+  </si>
+  <si>
+    <t>AEROPORT FHB 0709254454</t>
+  </si>
+  <si>
+    <t>200M</t>
+  </si>
+  <si>
+    <t>SYTHD230156</t>
+  </si>
+  <si>
+    <t>13/02/2026 13:56:52</t>
+  </si>
+  <si>
+    <t>56580353</t>
+  </si>
+  <si>
+    <t>12/01/2026 16:23:44</t>
+  </si>
+  <si>
+    <t>QUIPUX AFRIQUE</t>
+  </si>
+  <si>
+    <t>BUVPN210339</t>
+  </si>
+  <si>
+    <t>03/02/2026 14:22:58</t>
   </si>
   <si>
     <t>56579652</t>
@@ -791,96 +906,12 @@
     <t>12/01/2026 16:17:11</t>
   </si>
   <si>
-    <t>QUIPUX AFRIQUE</t>
-  </si>
-  <si>
-    <t>200M</t>
-  </si>
-  <si>
     <t>BUVPN150333</t>
   </si>
   <si>
     <t>03/02/2026 13:55:35</t>
   </si>
   <si>
-    <t>56268044</t>
-  </si>
-  <si>
-    <t>06/01/2026 15:42:28</t>
-  </si>
-  <si>
-    <t>AERIA</t>
-  </si>
-  <si>
-    <t>SYTHD230156</t>
-  </si>
-  <si>
-    <t>13/02/2026 13:56:52</t>
-  </si>
-  <si>
-    <t>57100866</t>
-  </si>
-  <si>
-    <t>22/01/2026 14:47:47</t>
-  </si>
-  <si>
-    <t>BANQUE INTERNATIONALE POUR LE COMMERCE ET L'INDUSTRIE</t>
-  </si>
-  <si>
-    <t>8M</t>
-  </si>
-  <si>
-    <t>BICICI</t>
-  </si>
-  <si>
-    <t>BUVPN170123</t>
-  </si>
-  <si>
-    <t>04/02/2026 19:45:44</t>
-  </si>
-  <si>
-    <t>56580353</t>
-  </si>
-  <si>
-    <t>12/01/2026 16:23:44</t>
-  </si>
-  <si>
-    <t>BUVPN210339</t>
-  </si>
-  <si>
-    <t>03/02/2026 14:22:58</t>
-  </si>
-  <si>
-    <t>57547928</t>
-  </si>
-  <si>
-    <t>30/01/2026 19:36:51</t>
-  </si>
-  <si>
-    <t>TRANSIT TRANSPORT SERVICES</t>
-  </si>
-  <si>
-    <t>SYTHD250060</t>
-  </si>
-  <si>
-    <t>19/02/2026 16:21:46</t>
-  </si>
-  <si>
-    <t>56916429</t>
-  </si>
-  <si>
-    <t>19/01/2026 14:07:39</t>
-  </si>
-  <si>
-    <t>SODEXAM</t>
-  </si>
-  <si>
-    <t>2721586294</t>
-  </si>
-  <si>
-    <t>19/02/2026 12:21:03</t>
-  </si>
-  <si>
     <t>57114434</t>
   </si>
   <si>
@@ -890,25 +921,561 @@
     <t>BGFIBANK</t>
   </si>
   <si>
+    <t>ABIDJAN-KOUMASSI//VOIE INCONNUE/CT M. MOUSSA TOURE 58513012</t>
+  </si>
+  <si>
     <t>BUVPN200211</t>
   </si>
   <si>
     <t>10/02/2026 13:57:35</t>
   </si>
   <si>
-    <t>56620712</t>
-  </si>
-  <si>
-    <t>13/01/2026 12:59:16</t>
-  </si>
-  <si>
-    <t>SOUBRE</t>
-  </si>
-  <si>
-    <t>BUVPN150291</t>
-  </si>
-  <si>
-    <t>19/02/2026 09:18:37</t>
+    <t>58784245</t>
+  </si>
+  <si>
+    <t>23/02/2026 10:04:29</t>
+  </si>
+  <si>
+    <t>COCODY RIVIERA 2</t>
+  </si>
+  <si>
+    <t>BUVPN240049</t>
+  </si>
+  <si>
+    <t>25/02/2026 11:55:09</t>
+  </si>
+  <si>
+    <t>58480398</t>
+  </si>
+  <si>
+    <t>17/02/2026 15:24:49</t>
+  </si>
+  <si>
+    <t>BANQUE ATLANTIQUE DE COTE D'IVOIRE AGENCE  ( BOUAKE COMMERCE)</t>
+  </si>
+  <si>
+    <t>BOUAKE COMMERCE</t>
+  </si>
+  <si>
+    <t>VPNLL070176</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:45:43</t>
+  </si>
+  <si>
+    <t>58783980</t>
+  </si>
+  <si>
+    <t>23/02/2026 10:02:01</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM</t>
+  </si>
+  <si>
+    <t>400M</t>
+  </si>
+  <si>
+    <t>BUVPN220126</t>
+  </si>
+  <si>
+    <t>25/02/2026 11:54:30</t>
+  </si>
+  <si>
+    <t>58784601</t>
+  </si>
+  <si>
+    <t>23/02/2026 10:09:18</t>
+  </si>
+  <si>
+    <t>ABIDJAN TREICHVILLE</t>
+  </si>
+  <si>
+    <t>BUVPN150481</t>
+  </si>
+  <si>
+    <t>25/02/2026 11:57:12</t>
+  </si>
+  <si>
+    <t>58431947</t>
+  </si>
+  <si>
+    <t>16/02/2026 17:40:46</t>
+  </si>
+  <si>
+    <t>BANQUE ATLANTIQUE DE COTE D'IVOIRE AGENCE PLATEAU</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/CONTACT 02032576</t>
+  </si>
+  <si>
+    <t>BUVPN200286</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:02:46</t>
+  </si>
+  <si>
+    <t>58835120</t>
+  </si>
+  <si>
+    <t>23/02/2026 18:13:23</t>
+  </si>
+  <si>
+    <t>EXCELIAM</t>
+  </si>
+  <si>
+    <t>COCODY RIVIERA 3</t>
+  </si>
+  <si>
+    <t>120M</t>
+  </si>
+  <si>
+    <t>SYTHD220085</t>
+  </si>
+  <si>
+    <t>10/03/2026 11:49:03</t>
+  </si>
+  <si>
+    <t>58783395</t>
+  </si>
+  <si>
+    <t>23/02/2026 09:54:35</t>
+  </si>
+  <si>
+    <t>ABIDJAN PLATEAU COMMERCE</t>
+  </si>
+  <si>
+    <t>BUVPN140002</t>
+  </si>
+  <si>
+    <t>12/03/2026 17:32:47</t>
+  </si>
+  <si>
+    <t>58488142</t>
+  </si>
+  <si>
+    <t>17/02/2026 16:47:06</t>
+  </si>
+  <si>
+    <t>EGLISE METHODISTE UNIE DE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>2720211797</t>
+  </si>
+  <si>
+    <t>18/02/2026 08:29:02</t>
+  </si>
+  <si>
+    <t>58996002</t>
+  </si>
+  <si>
+    <t>26/02/2026 11:30:04</t>
+  </si>
+  <si>
+    <t>2720306611</t>
+  </si>
+  <si>
+    <t>06/03/2026 09:34:12</t>
+  </si>
+  <si>
+    <t>58810120</t>
+  </si>
+  <si>
+    <t>23/02/2026 14:18:42</t>
+  </si>
+  <si>
+    <t>BUVPN210151</t>
+  </si>
+  <si>
+    <t>26/02/2026 09:47:15</t>
+  </si>
+  <si>
+    <t>58783117</t>
+  </si>
+  <si>
+    <t>23/02/2026 09:51:36</t>
+  </si>
+  <si>
+    <t>60M</t>
+  </si>
+  <si>
+    <t>BUVPN200230</t>
+  </si>
+  <si>
+    <t>25/02/2026 11:09:13</t>
+  </si>
+  <si>
+    <t>57702014</t>
+  </si>
+  <si>
+    <t>03/02/2026 11:11:18</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM//VOIE INCONNUE/GRAND BASSAM</t>
+  </si>
+  <si>
+    <t>VPNLL120077</t>
+  </si>
+  <si>
+    <t>27/02/2026 20:07:54</t>
+  </si>
+  <si>
+    <t>18/02/2026 17:59:04</t>
+  </si>
+  <si>
+    <t>18/02/2026 17:58:51</t>
+  </si>
+  <si>
+    <t>58785667</t>
+  </si>
+  <si>
+    <t>23/02/2026 10:21:46</t>
+  </si>
+  <si>
+    <t>YOPOUGON</t>
+  </si>
+  <si>
+    <t>10M</t>
+  </si>
+  <si>
+    <t>25/02/2026 12:00:25</t>
+  </si>
+  <si>
+    <t>58680600</t>
+  </si>
+  <si>
+    <t>20/02/2026 17:01:22</t>
+  </si>
+  <si>
+    <t>GROUPEMENT ORANGE SERVICES</t>
+  </si>
+  <si>
+    <t>Z.FRANCHE GD-BASSAM VITIB.A
+UPGRADE 1GBPS 
+NOEUD ICA 
+GOS VITIB BASSAM</t>
+  </si>
+  <si>
+    <t>1G</t>
+  </si>
+  <si>
+    <t>300M</t>
+  </si>
+  <si>
+    <t>SYTHD120074</t>
+  </si>
+  <si>
+    <t>25/02/2026 16:45:57</t>
+  </si>
+  <si>
+    <t>03/03/2026 12:38:53</t>
+  </si>
+  <si>
+    <t>25/02/2026 16:38:12</t>
+  </si>
+  <si>
+    <t>23/02/2026 13:30:36</t>
+  </si>
+  <si>
+    <t>58804111</t>
+  </si>
+  <si>
+    <t>23/02/2026 13:19:20</t>
+  </si>
+  <si>
+    <t>BUVPN220135</t>
+  </si>
+  <si>
+    <t>26/02/2026 09:40:55</t>
+  </si>
+  <si>
+    <t>58895685</t>
+  </si>
+  <si>
+    <t>24/02/2026 17:06:29</t>
+  </si>
+  <si>
+    <t>STANDARD CHARTERED BANK COTE D'IVOIRE SA</t>
+  </si>
+  <si>
+    <t>GD BASSAM VITIB</t>
+  </si>
+  <si>
+    <t>2720303200</t>
+  </si>
+  <si>
+    <t>28/02/2026 08:34:38</t>
+  </si>
+  <si>
+    <t>58427309</t>
+  </si>
+  <si>
+    <t>16/02/2026 16:43:29</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY RIVIERA 3</t>
+  </si>
+  <si>
+    <t>BUVPN190195</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:11:55</t>
+  </si>
+  <si>
+    <t>58029496</t>
+  </si>
+  <si>
+    <t>09/02/2026 13:44:17</t>
+  </si>
+  <si>
+    <t>AFRICA SOURCING COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>TREICHVILLE RUE DES THONIERS</t>
+  </si>
+  <si>
+    <t>2721358023</t>
+  </si>
+  <si>
+    <t>13/03/2026 12:44:53</t>
+  </si>
+  <si>
+    <t>58805170</t>
+  </si>
+  <si>
+    <t>23/02/2026 13:29:54</t>
+  </si>
+  <si>
+    <t>BUVPN230180</t>
+  </si>
+  <si>
+    <t>26/02/2026 09:41:30</t>
+  </si>
+  <si>
+    <t>59082502</t>
+  </si>
+  <si>
+    <t>27/02/2026 15:19:13</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU</t>
+  </si>
+  <si>
+    <t>VPNLL090098</t>
+  </si>
+  <si>
+    <t>03/03/2026 19:59:32</t>
+  </si>
+  <si>
+    <t>58048251</t>
+  </si>
+  <si>
+    <t>09/02/2026 16:53:27</t>
+  </si>
+  <si>
+    <t>FOREVER LIVING PRODUCT</t>
+  </si>
+  <si>
+    <t>SYTHD180175</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:43:56</t>
+  </si>
+  <si>
+    <t>58680250</t>
+  </si>
+  <si>
+    <t>20/02/2026 16:56:43</t>
+  </si>
+  <si>
+    <t>UPGRADE 1 Gbps 
+ICA</t>
+  </si>
+  <si>
+    <t>SYTHD120073</t>
+  </si>
+  <si>
+    <t>23/02/2026 13:29:41</t>
+  </si>
+  <si>
+    <t>25/02/2026 16:37:43</t>
+  </si>
+  <si>
+    <t>03/03/2026 12:40:11</t>
+  </si>
+  <si>
+    <t>58821317</t>
+  </si>
+  <si>
+    <t>23/02/2026 15:54:43</t>
+  </si>
+  <si>
+    <t>ALTERA INFRASTRUCTURE VOYAGEUR AS</t>
+  </si>
+  <si>
+    <t>ABIDJAN</t>
+  </si>
+  <si>
+    <t>SYTHD240109</t>
+  </si>
+  <si>
+    <t>13/03/2026 10:20:30</t>
+  </si>
+  <si>
+    <t>BO Homologation: Mise en service BSCS</t>
+  </si>
+  <si>
+    <t>BO Homologation: Mise en service GAIA</t>
+  </si>
+  <si>
+    <t>13/03/2026 10:21:05</t>
+  </si>
+  <si>
+    <t>58896886</t>
+  </si>
+  <si>
+    <t>24/02/2026 17:16:44</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM//VOIE INCONNUE/BASSAM VITIB</t>
+  </si>
+  <si>
+    <t>VPNLL120246</t>
+  </si>
+  <si>
+    <t>13/03/2026 10:54:09</t>
+  </si>
+  <si>
+    <t>57670112</t>
+  </si>
+  <si>
+    <t>02/02/2026 16:48:58</t>
+  </si>
+  <si>
+    <t>SOCIETE NATIONALE  DE TELECOM DAKAR</t>
+  </si>
+  <si>
+    <t>EXTR A : ACE CLS 
+EXTR B : BCEAO PLATEAU</t>
+  </si>
+  <si>
+    <t>SYTHD210026</t>
+  </si>
+  <si>
+    <t>10/02/2026 11:22:09</t>
+  </si>
+  <si>
+    <t>57860238</t>
+  </si>
+  <si>
+    <t>05/02/2026 16:21:01</t>
+  </si>
+  <si>
+    <t>BANQUE INTERNATIONALE POUR LE COMMERCE ET L'INDUSTRIE DE CI</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM//VOIE INCONNUE/GRAND BASSAM VITIB</t>
+  </si>
+  <si>
+    <t>SYTHD210187</t>
+  </si>
+  <si>
+    <t>12/02/2026 19:44:21</t>
+  </si>
+  <si>
+    <t>58822007</t>
+  </si>
+  <si>
+    <t>23/02/2026 16:00:58</t>
+  </si>
+  <si>
+    <t>SYTHD240087</t>
+  </si>
+  <si>
+    <t>13/03/2026 10:18:53</t>
+  </si>
+  <si>
+    <t>13/03/2026 10:19:27</t>
+  </si>
+  <si>
+    <t>58417809</t>
+  </si>
+  <si>
+    <t>16/02/2026 15:02:05</t>
+  </si>
+  <si>
+    <t>MARCORY</t>
+  </si>
+  <si>
+    <t>BUVPN180204</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:09:32</t>
+  </si>
+  <si>
+    <t>57711569</t>
+  </si>
+  <si>
+    <t>03/02/2026 12:49:14</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU//VOIE INCONNUE/EXTREMITE  A PLATEAU</t>
+  </si>
+  <si>
+    <t>SYTHD250061</t>
+  </si>
+  <si>
+    <t>18/02/2026 15:55:59</t>
+  </si>
+  <si>
+    <t>18/02/2026 15:56:17</t>
+  </si>
+  <si>
+    <t>28/02/2026 11:00:28</t>
+  </si>
+  <si>
+    <t>57852659</t>
+  </si>
+  <si>
+    <t>05/02/2026 15:07:32</t>
+  </si>
+  <si>
+    <t>COTE D'IVOIRE MULTIMEDIA</t>
+  </si>
+  <si>
+    <t>COMMUNE INCONNUE//VOIE INCONNUE/ AXE ABIDJAN-YAKRO  PK 22</t>
+  </si>
+  <si>
+    <t>SYTHD180109</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:13:44</t>
+  </si>
+  <si>
+    <t>57864191</t>
+  </si>
+  <si>
+    <t>05/02/2026 16:54:42</t>
+  </si>
+  <si>
+    <t>SYTHD230067</t>
+  </si>
+  <si>
+    <t>11/02/2026 19:07:39</t>
+  </si>
+  <si>
+    <t>59011477</t>
+  </si>
+  <si>
+    <t>26/02/2026 14:00:03</t>
+  </si>
+  <si>
+    <t>BRIDGE BANK GROUP</t>
+  </si>
+  <si>
+    <t>2721212910</t>
+  </si>
+  <si>
+    <t>28/02/2026 11:36:47</t>
   </si>
   <si>
     <t>57703033</t>
@@ -917,523 +1484,334 @@
     <t>03/02/2026 11:21:12</t>
   </si>
   <si>
-    <t>BANQUE INTERNATIONALE POUR LE COMMERCE ET L'INDUSTRIE EN CÔTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>60M</t>
+    <t>GRAND-BASSAM//VOIE INCONNUE/</t>
   </si>
   <si>
     <t>VPNLL060028</t>
   </si>
   <si>
+    <t>28/02/2026 10:44:59</t>
+  </si>
+  <si>
     <t>18/02/2026 15:54:47</t>
   </si>
   <si>
-    <t>18/02/2026 17:05:42</t>
-  </si>
-  <si>
     <t>18/02/2026 15:54:31</t>
   </si>
   <si>
-    <t>57702014</t>
-  </si>
-  <si>
-    <t>03/02/2026 11:11:18</t>
-  </si>
-  <si>
-    <t>VPNLL120077</t>
-  </si>
-  <si>
-    <t>18/02/2026 17:59:04</t>
-  </si>
-  <si>
-    <t>18/02/2026 17:58:51</t>
-  </si>
-  <si>
-    <t>18/02/2026 18:07:34</t>
-  </si>
-  <si>
-    <t>58101275</t>
-  </si>
-  <si>
-    <t>10/02/2026 15:16:32</t>
-  </si>
-  <si>
-    <t>SOCIETE D'ETUDE ET DE DEVELOPPEMENT DE LA CULTURE BANANIERE</t>
-  </si>
-  <si>
-    <t>SYTHD200248</t>
-  </si>
-  <si>
-    <t>18/02/2026 11:47:34</t>
-  </si>
-  <si>
-    <t>57795532</t>
-  </si>
-  <si>
-    <t>04/02/2026 16:25:19</t>
-  </si>
-  <si>
-    <t>BANQUE INTERNATIONALE POUR LE COMMERCE ET L'INDUSTRIE DE CI</t>
-  </si>
-  <si>
-    <t>2720242424</t>
-  </si>
-  <si>
-    <t>05/02/2026 10:15:18</t>
-  </si>
-  <si>
-    <t>58488142</t>
-  </si>
-  <si>
-    <t>17/02/2026 16:47:06</t>
-  </si>
-  <si>
-    <t>EGLISE METHODISTE UNIE DE COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>2720211797</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:29:02</t>
-  </si>
-  <si>
-    <t>58004479</t>
-  </si>
-  <si>
-    <t>09/02/2026 08:42:33</t>
-  </si>
-  <si>
-    <t>Huawei Technologies Cote d'Ivoire SAU Abj Plateau 01 BP 3838 Abj 01</t>
-  </si>
-  <si>
-    <t>SYTHD230071</t>
-  </si>
-  <si>
-    <t>16/02/2026 17:08:24</t>
-  </si>
-  <si>
-    <t>58477559</t>
-  </si>
-  <si>
-    <t>17/02/2026 14:56:41</t>
-  </si>
-  <si>
-    <t>MICROFINANCE FOR AFRICA COTE D'IVOIRE  (YAMOUSSOUKRO)</t>
-  </si>
-  <si>
-    <t>BUVPN160219</t>
-  </si>
-  <si>
-    <t>17/02/2026 14:57:05</t>
-  </si>
-  <si>
-    <t>58426696</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:35:56</t>
-  </si>
-  <si>
-    <t>BANQUE ATLANTIQUE DE COTE D'IVOIRE AGENCE PLATEAU</t>
-  </si>
-  <si>
-    <t>VPNLL080233</t>
-  </si>
-  <si>
-    <t>19/02/2026 15:23:42</t>
-  </si>
-  <si>
-    <t>58204995</t>
-  </si>
-  <si>
-    <t>12/02/2026 10:42:45</t>
-  </si>
-  <si>
-    <t>MINISTERE DU COMMERCE</t>
-  </si>
-  <si>
-    <t>2720331555</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:16:30</t>
-  </si>
-  <si>
-    <t>57852659</t>
-  </si>
-  <si>
-    <t>05/02/2026 15:07:32</t>
-  </si>
-  <si>
-    <t>COTE D'IVOIRE MULTIMEDIA</t>
-  </si>
-  <si>
-    <t>SYTHD180109</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:53:10</t>
-  </si>
-  <si>
-    <t>58428242</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:53:18</t>
-  </si>
-  <si>
-    <t>BUVPN190201</t>
-  </si>
-  <si>
-    <t>19/02/2026 17:47:35</t>
-  </si>
-  <si>
-    <t>58154235</t>
-  </si>
-  <si>
-    <t>11/02/2026 13:18:21</t>
-  </si>
-  <si>
-    <t>ORGANISATION INTERNATIONALE POUR LES MIGRATIONS</t>
-  </si>
-  <si>
-    <t>2722528200</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:35:26</t>
-  </si>
-  <si>
-    <t>58428775</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:59:22</t>
-  </si>
-  <si>
-    <t>BUVPN160004</t>
-  </si>
-  <si>
-    <t>19/02/2026 14:14:01</t>
-  </si>
-  <si>
-    <t>58427309</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:43:29</t>
-  </si>
-  <si>
-    <t>BUVPN190195</t>
-  </si>
-  <si>
-    <t>19/02/2026 17:38:36</t>
-  </si>
-  <si>
-    <t>57864191</t>
-  </si>
-  <si>
-    <t>05/02/2026 16:54:42</t>
-  </si>
-  <si>
-    <t>SYTHD230067</t>
-  </si>
-  <si>
-    <t>11/02/2026 19:07:39</t>
-  </si>
-  <si>
-    <t>58584861</t>
-  </si>
-  <si>
-    <t>19/02/2026 10:46:41</t>
-  </si>
-  <si>
-    <t>MOTA-ENGIL COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>SYTHD240400</t>
-  </si>
-  <si>
-    <t>19/02/2026 10:46:50</t>
-  </si>
-  <si>
-    <t>58417809</t>
-  </si>
-  <si>
-    <t>16/02/2026 15:02:05</t>
-  </si>
-  <si>
-    <t>BUVPN180204</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:39:40</t>
-  </si>
-  <si>
-    <t>58425505</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:23:36</t>
-  </si>
-  <si>
-    <t>BUVPN250149</t>
-  </si>
-  <si>
-    <t>19/02/2026 17:38:13</t>
-  </si>
-  <si>
-    <t>58101768</t>
-  </si>
-  <si>
-    <t>10/02/2026 15:22:30</t>
-  </si>
-  <si>
-    <t>SYTHD200279</t>
-  </si>
-  <si>
-    <t>18/02/2026 13:52:51</t>
-  </si>
-  <si>
-    <t>58426192</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:31:52</t>
-  </si>
-  <si>
-    <t>BUVPN170290</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:40:47</t>
-  </si>
-  <si>
-    <t>58048251</t>
-  </si>
-  <si>
-    <t>09/02/2026 16:53:27</t>
-  </si>
-  <si>
-    <t>FOREVER LIVING PRODUCT</t>
-  </si>
-  <si>
-    <t>SYTHD180175</t>
-  </si>
-  <si>
-    <t>19/02/2026 16:29:47</t>
-  </si>
-  <si>
-    <t>57711569</t>
-  </si>
-  <si>
-    <t>03/02/2026 12:49:14</t>
-  </si>
-  <si>
-    <t>SYTHD250061</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:55:59</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:56:17</t>
-  </si>
-  <si>
-    <t>18/02/2026 17:23:15</t>
-  </si>
-  <si>
-    <t>58431947</t>
-  </si>
-  <si>
-    <t>16/02/2026 17:40:46</t>
-  </si>
-  <si>
-    <t>BUVPN200286</t>
-  </si>
-  <si>
-    <t>19/02/2026 17:18:42</t>
-  </si>
-  <si>
-    <t>58424733</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:16:37</t>
-  </si>
-  <si>
-    <t>BUVPN210305</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:42:25</t>
-  </si>
-  <si>
-    <t>58029496</t>
-  </si>
-  <si>
-    <t>09/02/2026 13:44:17</t>
-  </si>
-  <si>
-    <t>AFRICA SOURCING COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>2721358023</t>
-  </si>
-  <si>
-    <t>09/02/2026 14:58:08</t>
-  </si>
-  <si>
-    <t>58425194</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:20:30</t>
-  </si>
-  <si>
-    <t>BUVPN160202</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:41:30</t>
-  </si>
-  <si>
-    <t>58204079</t>
-  </si>
-  <si>
-    <t>12/02/2026 10:31:48</t>
-  </si>
-  <si>
-    <t>2720229528</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:20:09</t>
-  </si>
-  <si>
-    <t>58430178</t>
-  </si>
-  <si>
-    <t>16/02/2026 17:16:32</t>
-  </si>
-  <si>
-    <t>VPNLL080235</t>
-  </si>
-  <si>
-    <t>19/02/2026 17:34:27</t>
-  </si>
-  <si>
-    <t>58425944</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:29:22</t>
-  </si>
-  <si>
-    <t>VPNLL110035</t>
-  </si>
-  <si>
-    <t>18/02/2026 14:56:38</t>
-  </si>
-  <si>
-    <t>58164578</t>
-  </si>
-  <si>
-    <t>11/02/2026 15:13:39</t>
-  </si>
-  <si>
-    <t>VPNLL140112</t>
-  </si>
-  <si>
-    <t>16/02/2026 15:36:35</t>
-  </si>
-  <si>
-    <t>57670112</t>
-  </si>
-  <si>
-    <t>02/02/2026 16:48:58</t>
-  </si>
-  <si>
-    <t>SOCIETE NATIONALE  DE TELECOM DAKAR</t>
-  </si>
-  <si>
-    <t>SYTHD210026</t>
-  </si>
-  <si>
-    <t>10/02/2026 11:22:09</t>
-  </si>
-  <si>
-    <t>58424511</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:13:53</t>
-  </si>
-  <si>
-    <t>VPNLL070247</t>
-  </si>
-  <si>
-    <t>18/02/2026 14:59:13</t>
-  </si>
-  <si>
-    <t>57654864</t>
-  </si>
-  <si>
-    <t>02/02/2026 14:32:29</t>
-  </si>
-  <si>
-    <t>COMPAGNIE DE TRANSFORMATION DU CAOUCHOUC IVOIRIEN</t>
-  </si>
-  <si>
-    <t>BUVPN210050</t>
-  </si>
-  <si>
-    <t>18/02/2026 14:09:21</t>
-  </si>
-  <si>
-    <t>58418528</t>
-  </si>
-  <si>
-    <t>16/02/2026 15:09:27</t>
-  </si>
-  <si>
-    <t>BUVPN160029</t>
-  </si>
-  <si>
-    <t>19/02/2026 17:37:45</t>
-  </si>
-  <si>
-    <t>58480398</t>
-  </si>
-  <si>
-    <t>17/02/2026 15:24:49</t>
-  </si>
-  <si>
-    <t>BANQUE ATLANTIQUE DE COTE D'IVOIRE AGENCE  ( BOUAKE COMMERCE)</t>
-  </si>
-  <si>
-    <t>VPNLL070176</t>
-  </si>
-  <si>
-    <t>17/02/2026 15:24:54</t>
-  </si>
-  <si>
-    <t>58030822</t>
-  </si>
-  <si>
-    <t>09/02/2026 13:59:02</t>
-  </si>
-  <si>
-    <t>09/02/2026 14:59:46</t>
-  </si>
-  <si>
-    <t>58431525</t>
-  </si>
-  <si>
-    <t>16/02/2026 17:34:31</t>
-  </si>
-  <si>
-    <t>VPNLL080241</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:40:14</t>
-  </si>
-  <si>
-    <t>57860238</t>
-  </si>
-  <si>
-    <t>05/02/2026 16:21:01</t>
-  </si>
-  <si>
-    <t>SYTHD210187</t>
-  </si>
-  <si>
-    <t>12/02/2026 19:44:21</t>
-  </si>
-  <si>
-    <t>NOM CLIENT</t>
+    <t>58782956</t>
+  </si>
+  <si>
+    <t>23/02/2026 09:49:42</t>
+  </si>
+  <si>
+    <t>BUVPN220116</t>
+  </si>
+  <si>
+    <t>11/03/2026 14:57:27</t>
+  </si>
+  <si>
+    <t>58783796</t>
+  </si>
+  <si>
+    <t>23/02/2026 09:59:21</t>
+  </si>
+  <si>
+    <t>BUVPN210149</t>
+  </si>
+  <si>
+    <t>11/03/2026 14:59:44</t>
+  </si>
+  <si>
+    <t>58822848</t>
+  </si>
+  <si>
+    <t>23/02/2026 16:08:17</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIRIENNE DE BANQUE (GRAND-BASSAM )</t>
+  </si>
+  <si>
+    <t>BUVPN220110</t>
+  </si>
+  <si>
+    <t>26/02/2026 09:49:46</t>
+  </si>
+  <si>
+    <t>59428182</t>
+  </si>
+  <si>
+    <t>05/03/2026 16:07:54</t>
+  </si>
+  <si>
+    <t>CORIS BANK INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>BD REPUBLIQUE 23 ANGLE RUE</t>
+  </si>
+  <si>
+    <t>BUVPN150629</t>
+  </si>
+  <si>
+    <t>12/03/2026 16:33:33</t>
+  </si>
+  <si>
+    <t>59302434</t>
+  </si>
+  <si>
+    <t>03/03/2026 16:51:42</t>
+  </si>
+  <si>
+    <t>BUVPN230155</t>
+  </si>
+  <si>
+    <t>12/03/2026 12:04:11</t>
+  </si>
+  <si>
+    <t>59323774</t>
+  </si>
+  <si>
+    <t>04/03/2026 09:17:41</t>
+  </si>
+  <si>
+    <t>BRIDGE GROUP WEST AFRICA</t>
+  </si>
+  <si>
+    <t>COCODY RUE CANEBIERRE IMMEUBLE PHEHONE</t>
+  </si>
+  <si>
+    <t>SYTHD250379</t>
+  </si>
+  <si>
+    <t>12/03/2026 12:46:06</t>
+  </si>
+  <si>
+    <t>59470580</t>
+  </si>
+  <si>
+    <t>06/03/2026 11:10:51</t>
+  </si>
+  <si>
+    <t>CIMPOR</t>
+  </si>
+  <si>
+    <t>YOPOUGON ZONE INDUSTRIELLE</t>
+  </si>
+  <si>
+    <t>SYTHD200159</t>
+  </si>
+  <si>
+    <t>12/03/2026 16:51:20</t>
+  </si>
+  <si>
+    <t>59696023</t>
+  </si>
+  <si>
+    <t>10/03/2026 15:33:01</t>
+  </si>
+  <si>
+    <t>BAOBAB COTE D'IVOIRE BOUAFLE</t>
+  </si>
+  <si>
+    <t>SYTHD210072</t>
+  </si>
+  <si>
+    <t>12/03/2026 17:03:36</t>
+  </si>
+  <si>
+    <t>59457854</t>
+  </si>
+  <si>
+    <t>06/03/2026 08:40:21</t>
+  </si>
+  <si>
+    <t>MEDLOG</t>
+  </si>
+  <si>
+    <t>150M</t>
+  </si>
+  <si>
+    <t>SYTHD160040</t>
+  </si>
+  <si>
+    <t>12/03/2026 16:47:41</t>
+  </si>
+  <si>
+    <t>59822523</t>
+  </si>
+  <si>
+    <t>12/03/2026 15:00:46</t>
+  </si>
+  <si>
+    <t>AGENCE OCI 2PLTX  ENA</t>
+  </si>
+  <si>
+    <t>ABIDJAN PLATEAU PIA</t>
+  </si>
+  <si>
+    <t>VPNLL210028</t>
+  </si>
+  <si>
+    <t>12/03/2026 17:05:50</t>
+  </si>
+  <si>
+    <t>59488550</t>
+  </si>
+  <si>
+    <t>06/03/2026 14:31:49</t>
+  </si>
+  <si>
+    <t>CLINIQUE MEDICALE TRADE CENTER</t>
+  </si>
+  <si>
+    <t>MARCORY RESIDENTIEL</t>
+  </si>
+  <si>
+    <t>2720219797</t>
+  </si>
+  <si>
+    <t>12/03/2026 16:54:21</t>
+  </si>
+  <si>
+    <t>59692851</t>
+  </si>
+  <si>
+    <t>10/03/2026 15:03:16</t>
+  </si>
+  <si>
+    <t>BAOBAB COTE D'IVOIRE DABOU</t>
+  </si>
+  <si>
+    <t>SYTHD210080</t>
+  </si>
+  <si>
+    <t>12/03/2026 17:03:11</t>
+  </si>
+  <si>
+    <t>59301236</t>
+  </si>
+  <si>
+    <t>03/03/2026 16:38:39</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES DOUANES</t>
+  </si>
+  <si>
+    <t>SYTHD230225</t>
+  </si>
+  <si>
+    <t>12/03/2026 11:58:44</t>
+  </si>
+  <si>
+    <t>59609074</t>
+  </si>
+  <si>
+    <t>09/03/2026 11:15:22</t>
+  </si>
+  <si>
+    <t>OLAM COCOA PROCESSING CI</t>
+  </si>
+  <si>
+    <t>PORT-BOUET ZONE INDUSTRIELLE DE VRIDI</t>
+  </si>
+  <si>
+    <t>SYTHD070082</t>
+  </si>
+  <si>
+    <t>12/03/2026 16:58:39</t>
+  </si>
+  <si>
+    <t>59698221</t>
+  </si>
+  <si>
+    <t>10/03/2026 15:56:09</t>
+  </si>
+  <si>
+    <t>BAOBAB COTE D'IVOIRE AYAMA</t>
+  </si>
+  <si>
+    <t>SYTHD240187</t>
+  </si>
+  <si>
+    <t>12/03/2026 17:04:14</t>
+  </si>
+  <si>
+    <t>59429267</t>
+  </si>
+  <si>
+    <t>05/03/2026 16:16:19</t>
+  </si>
+  <si>
+    <t>BUVPN150572</t>
+  </si>
+  <si>
+    <t>12/03/2026 14:40:20</t>
+  </si>
+  <si>
+    <t>59805789</t>
+  </si>
+  <si>
+    <t>12/03/2026 11:59:46</t>
+  </si>
+  <si>
+    <t>ORANGE COTE D'IVOIRE S.A</t>
+  </si>
+  <si>
+    <t>HABITA BAT CIT FC HOPITAL P102</t>
+  </si>
+  <si>
+    <t>VPNLL170009</t>
+  </si>
+  <si>
+    <t>12/03/2026 12:43:51</t>
+  </si>
+  <si>
+    <t>59301884</t>
+  </si>
+  <si>
+    <t>03/03/2026 16:45:07</t>
+  </si>
+  <si>
+    <t>SYTHD170144</t>
+  </si>
+  <si>
+    <t>12/03/2026 12:01:20</t>
+  </si>
+  <si>
+    <t>59458389</t>
+  </si>
+  <si>
+    <t>06/03/2026 08:52:02</t>
+  </si>
+  <si>
+    <t>ARTCI</t>
+  </si>
+  <si>
+    <t>2721711800</t>
+  </si>
+  <si>
+    <t>11/03/2026 14:42:45</t>
+  </si>
+  <si>
+    <t>59808510</t>
+  </si>
+  <si>
+    <t>12/03/2026 12:25:09</t>
+  </si>
+  <si>
+    <t>ETABLISSEMENT MULTI SERVICES SORO ZIE</t>
+  </si>
+  <si>
+    <t>COCODY RIVERA ATTOBAN</t>
+  </si>
+  <si>
+    <t>SYTHD210086</t>
+  </si>
+  <si>
+    <t>12/03/2026 17:30:56</t>
+  </si>
+  <si>
+    <t>NOM  CLIENT</t>
   </si>
 </sst>
 </file>
@@ -1810,15 +2188,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="49.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="49.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="44.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="59.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="44.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="25.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="69.75" style="1" customWidth="1"/>
@@ -1843,7 +2221,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>467</v>
+        <v>591</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1887,254 +2265,254 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
         <v>24</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
         <v>23</v>
       </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s">
-        <v>20</v>
-      </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" t="s">
         <v>23</v>
       </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" t="s">
-        <v>20</v>
-      </c>
       <c r="N5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="M6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="M7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2145,3828 +2523,4488 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="J8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K8" t="s">
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
         <v>79</v>
       </c>
-      <c r="J9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" t="s">
-        <v>75</v>
-      </c>
       <c r="M9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K10" t="s">
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K11" t="s">
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K12" t="s">
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="M12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
         <v>101</v>
       </c>
-      <c r="B13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" t="s">
-        <v>97</v>
-      </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="G13" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K13" t="s">
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J14" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="K14" t="s">
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I15" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J15" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K16" t="s">
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="M16" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N16" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="J17" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K17" t="s">
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="M17" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I18" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="K18" t="s">
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="E19" t="s">
         <v>131</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>144</v>
       </c>
       <c r="H19" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="J19" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K19" t="s">
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="N19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J20" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="K20" t="s">
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="M20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N20" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I21" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="J21" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="K21" t="s">
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="M21" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N21" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B22" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="G22" t="s">
-        <v>36</v>
+        <v>144</v>
       </c>
       <c r="H22" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I22" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="K22" t="s">
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="M22" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N22" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>162</v>
       </c>
       <c r="G23" t="s">
-        <v>148</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I23" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="J23" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="K23" t="s">
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="M23" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="G24" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="H24" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="J24" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K24" t="s">
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="M24" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" t="s">
         <v>157</v>
       </c>
-      <c r="C25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" t="s">
-        <v>117</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
       <c r="G25" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I25" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J25" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="K25" t="s">
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="M25" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="C26" t="s">
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>178</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I26" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="J26" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="K26" t="s">
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="M26" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="N26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="F27" t="s">
-        <v>93</v>
+        <v>184</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I27" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="J27" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="K27" t="s">
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="M27" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>189</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="K28" t="s">
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="M28" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="G29" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H29" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J29" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="K29" t="s">
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="M29" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B30" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G30" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="H30" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I30" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J30" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="K30" t="s">
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="M30" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G31" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="H31" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I31" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J31" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="K31" t="s">
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="M31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="B32" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>208</v>
       </c>
       <c r="G32" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="H32" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I32" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J32" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="K32" t="s">
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="M32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="B33" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="F33" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="G33" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="H33" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I33" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J33" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="K33" t="s">
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="M33" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
       </c>
       <c r="E34" t="s">
-        <v>197</v>
+        <v>101</v>
       </c>
       <c r="F34" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="G34" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="H34" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I34" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="K34" t="s">
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="M34" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="E35" t="s">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="K35" t="s">
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="M35" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="N35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E36" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>230</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I36" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J36" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="K36" t="s">
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="M36" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="B37" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>236</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="J37" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="K37" t="s">
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="M37" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="N37" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="B38" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G38" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H38" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I38" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J38" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="K38" t="s">
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="M38" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F39" t="s">
-        <v>15</v>
+        <v>245</v>
       </c>
       <c r="G39" t="s">
-        <v>65</v>
+        <v>246</v>
       </c>
       <c r="H39" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I39" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J39" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="K39" t="s">
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="M39" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N39" t="s">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B40" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="G40" t="s">
-        <v>36</v>
+        <v>214</v>
       </c>
       <c r="H40" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I40" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J40" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="K40" t="s">
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="M40" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="B41" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>221</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>257</v>
       </c>
       <c r="G41" t="s">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="H41" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I41" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J41" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="K41" t="s">
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="M41" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N41" t="s">
-        <v>232</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>262</v>
       </c>
       <c r="F42" t="s">
-        <v>15</v>
+        <v>263</v>
       </c>
       <c r="G42" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I42" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="J42" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="K42" t="s">
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="M42" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="G43" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="H43" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I43" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="J43" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="K43" t="s">
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="M43" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="B44" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>271</v>
       </c>
       <c r="F44" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="G44" t="s">
-        <v>118</v>
+        <v>273</v>
       </c>
       <c r="H44" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I44" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J44" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="K44" t="s">
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="M44" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="B45" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="F45" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>281</v>
       </c>
       <c r="H45" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I45" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="J45" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="K45" t="s">
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="M45" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>251</v>
+        <v>284</v>
       </c>
       <c r="B46" t="s">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="F46" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="G46" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="H46" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I46" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="J46" t="s">
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="K46" t="s">
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="M46" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N46" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="B47" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="G47" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="H47" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I47" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J47" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="K47" t="s">
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="M47" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N47" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="B48" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="F48" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G48" t="s">
-        <v>265</v>
+        <v>40</v>
       </c>
       <c r="H48" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I48" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J48" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="K48" t="s">
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="M48" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="B49" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E49" t="s">
-        <v>253</v>
+        <v>85</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
+        <v>301</v>
       </c>
       <c r="G49" t="s">
-        <v>254</v>
+        <v>120</v>
       </c>
       <c r="H49" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I49" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="J49" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="K49" t="s">
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="M49" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N49" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="B50" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="F50" t="s">
-        <v>15</v>
+        <v>307</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H50" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I50" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J50" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="K50" t="s">
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="M50" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="B51" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D51" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s">
-        <v>280</v>
+        <v>85</v>
       </c>
       <c r="F51" t="s">
-        <v>45</v>
+        <v>312</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>313</v>
       </c>
       <c r="H51" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I51" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J51" t="s">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="K51" t="s">
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
       <c r="M51" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="N51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="B52" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>285</v>
+        <v>85</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="G52" t="s">
-        <v>36</v>
+        <v>313</v>
       </c>
       <c r="H52" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I52" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="J52" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="K52" t="s">
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="M52" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="B53" t="s">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>253</v>
+        <v>323</v>
       </c>
       <c r="F53" t="s">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="G53" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="H53" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I53" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J53" t="s">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="K53" t="s">
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="M53" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="B54" t="s">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E54" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>330</v>
       </c>
       <c r="G54" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="H54" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I54" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="J54" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="K54" t="s">
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="M54" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="B55" t="s">
-        <v>294</v>
+        <v>335</v>
       </c>
       <c r="C55" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
-        <v>295</v>
+        <v>85</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>336</v>
       </c>
       <c r="G55" t="s">
-        <v>296</v>
+        <v>21</v>
       </c>
       <c r="H55" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I55" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="J55" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="K55" t="s">
-        <v>298</v>
+        <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="M55" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E56" t="s">
-        <v>295</v>
+        <v>341</v>
       </c>
       <c r="F56" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G56" t="s">
-        <v>265</v>
+        <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="I56" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J56" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="K56" t="s">
-        <v>304</v>
+        <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="M56" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>301</v>
+        <v>344</v>
       </c>
       <c r="B57" t="s">
-        <v>302</v>
+        <v>345</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="E57" t="s">
-        <v>295</v>
+        <v>101</v>
       </c>
       <c r="F57" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G57" t="s">
-        <v>265</v>
+        <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J57" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="K57" t="s">
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="M57" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="B58" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>309</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>312</v>
       </c>
       <c r="G58" t="s">
-        <v>65</v>
+        <v>313</v>
       </c>
       <c r="H58" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I58" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="J58" t="s">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="K58" t="s">
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="M58" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>312</v>
+        <v>352</v>
       </c>
       <c r="B59" t="s">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="C59" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D59" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E59" t="s">
-        <v>314</v>
+        <v>85</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="H59" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I59" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J59" t="s">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="K59" t="s">
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="M59" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="N59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="B60" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D60" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="F60" t="s">
-        <v>15</v>
+        <v>359</v>
       </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>273</v>
       </c>
       <c r="H60" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I60" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J60" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="K60" t="s">
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="M60" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="N60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>322</v>
+        <v>357</v>
       </c>
       <c r="B61" t="s">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E61" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>359</v>
       </c>
       <c r="G61" t="s">
-        <v>198</v>
+        <v>273</v>
       </c>
       <c r="H61" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I61" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="J61" t="s">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="K61" t="s">
-        <v>15</v>
+        <v>362</v>
       </c>
       <c r="L61" t="s">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="M61" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="B62" t="s">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>329</v>
+        <v>85</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>366</v>
       </c>
       <c r="G62" t="s">
-        <v>36</v>
+        <v>367</v>
       </c>
       <c r="H62" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I62" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J62" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="K62" t="s">
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>330</v>
+        <v>87</v>
       </c>
       <c r="M62" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="B63" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G63" t="s">
-        <v>36</v>
+        <v>373</v>
       </c>
       <c r="H63" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I63" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="J63" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="K63" t="s">
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>335</v>
+        <v>375</v>
       </c>
       <c r="M63" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N63" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="B64" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D64" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="F64" t="s">
-        <v>73</v>
+        <v>372</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>373</v>
       </c>
       <c r="H64" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I64" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J64" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="K64" t="s">
-        <v>15</v>
+        <v>376</v>
       </c>
       <c r="L64" t="s">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="M64" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N64" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="B65" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="F65" t="s">
-        <v>15</v>
+        <v>372</v>
       </c>
       <c r="G65" t="s">
-        <v>198</v>
+        <v>373</v>
       </c>
       <c r="H65" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I65" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="J65" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="K65" t="s">
-        <v>15</v>
+        <v>378</v>
       </c>
       <c r="L65" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="M65" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="N65" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="B66" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>334</v>
+        <v>85</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="G66" t="s">
-        <v>36</v>
+        <v>367</v>
       </c>
       <c r="H66" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I66" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="J66" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="K66" t="s">
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="M66" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="B67" t="s">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D67" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E67" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="F67" t="s">
-        <v>58</v>
+        <v>387</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I67" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J67" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="K67" t="s">
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="M67" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="N67" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="B68" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="F68" t="s">
-        <v>15</v>
+        <v>392</v>
       </c>
       <c r="G68" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H68" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I68" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="J68" t="s">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="K68" t="s">
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>358</v>
+        <v>393</v>
       </c>
       <c r="M68" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="B69" t="s">
-        <v>361</v>
+        <v>396</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D69" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="F69" t="s">
-        <v>15</v>
+        <v>398</v>
       </c>
       <c r="G69" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I69" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J69" t="s">
-        <v>363</v>
+        <v>400</v>
       </c>
       <c r="K69" t="s">
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>362</v>
+        <v>399</v>
       </c>
       <c r="M69" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="B70" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="C70" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E70" t="s">
-        <v>266</v>
+        <v>85</v>
       </c>
       <c r="F70" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="G70" t="s">
-        <v>98</v>
+        <v>367</v>
       </c>
       <c r="H70" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I70" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J70" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="K70" t="s">
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="M70" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="B71" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D71" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E71" t="s">
-        <v>370</v>
+        <v>85</v>
       </c>
       <c r="F71" t="s">
-        <v>15</v>
+        <v>407</v>
       </c>
       <c r="G71" t="s">
-        <v>65</v>
+        <v>313</v>
       </c>
       <c r="H71" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I71" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J71" t="s">
-        <v>372</v>
+        <v>409</v>
       </c>
       <c r="K71" t="s">
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="M71" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N71" t="s">
-        <v>59</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="B72" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>334</v>
+        <v>412</v>
       </c>
       <c r="F72" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="G72" t="s">
-        <v>36</v>
+        <v>144</v>
       </c>
       <c r="H72" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I72" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J72" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="K72" t="s">
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>375</v>
+        <v>413</v>
       </c>
       <c r="M72" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N72" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="B73" t="s">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="F73" t="s">
-        <v>15</v>
+        <v>417</v>
       </c>
       <c r="G73" t="s">
-        <v>36</v>
+        <v>373</v>
       </c>
       <c r="H73" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I73" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="J73" t="s">
-        <v>380</v>
+        <v>421</v>
       </c>
       <c r="K73" t="s">
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>379</v>
+        <v>418</v>
       </c>
       <c r="M73" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N73" t="s">
-        <v>59</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="B74" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>309</v>
+        <v>371</v>
       </c>
       <c r="F74" t="s">
-        <v>15</v>
+        <v>417</v>
       </c>
       <c r="G74" t="s">
-        <v>65</v>
+        <v>373</v>
       </c>
       <c r="H74" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I74" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="J74" t="s">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="K74" t="s">
-        <v>15</v>
+        <v>420</v>
       </c>
       <c r="L74" t="s">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="M74" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="N74" t="s">
-        <v>59</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="B75" t="s">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="F75" t="s">
-        <v>15</v>
+        <v>425</v>
       </c>
       <c r="G75" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="H75" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I75" t="s">
-        <v>55</v>
+        <v>428</v>
       </c>
       <c r="J75" t="s">
-        <v>388</v>
+        <v>427</v>
       </c>
       <c r="K75" t="s">
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
       <c r="M75" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N75" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="B76" t="s">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E76" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="F76" t="s">
-        <v>15</v>
+        <v>425</v>
       </c>
       <c r="G76" t="s">
-        <v>118</v>
+        <v>246</v>
       </c>
       <c r="H76" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I76" t="s">
-        <v>25</v>
+        <v>429</v>
       </c>
       <c r="J76" t="s">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="K76" t="s">
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="M76" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="N76" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="B77" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="C77" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E77" t="s">
-        <v>314</v>
+        <v>386</v>
       </c>
       <c r="F77" t="s">
-        <v>15</v>
+        <v>433</v>
       </c>
       <c r="G77" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="H77" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I77" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J77" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="K77" t="s">
-        <v>398</v>
+        <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="M77" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>394</v>
+        <v>436</v>
       </c>
       <c r="B78" t="s">
-        <v>395</v>
+        <v>437</v>
       </c>
       <c r="C78" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D78" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="F78" t="s">
-        <v>15</v>
+        <v>439</v>
       </c>
       <c r="G78" t="s">
-        <v>36</v>
+        <v>281</v>
       </c>
       <c r="H78" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I78" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="J78" t="s">
-        <v>399</v>
+        <v>441</v>
       </c>
       <c r="K78" t="s">
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>396</v>
+        <v>440</v>
       </c>
       <c r="M78" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>400</v>
+        <v>442</v>
       </c>
       <c r="B79" t="s">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
-        <v>334</v>
+        <v>444</v>
       </c>
       <c r="F79" t="s">
-        <v>15</v>
+        <v>445</v>
       </c>
       <c r="G79" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="H79" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I79" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="J79" t="s">
-        <v>403</v>
+        <v>447</v>
       </c>
       <c r="K79" t="s">
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>402</v>
+        <v>446</v>
       </c>
       <c r="M79" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>404</v>
+        <v>448</v>
       </c>
       <c r="B80" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D80" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="F80" t="s">
-        <v>15</v>
+        <v>425</v>
       </c>
       <c r="G80" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="H80" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I80" t="s">
-        <v>55</v>
+        <v>428</v>
       </c>
       <c r="J80" t="s">
-        <v>407</v>
+        <v>451</v>
       </c>
       <c r="K80" t="s">
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="M80" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="B81" t="s">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="C81" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D81" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E81" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="F81" t="s">
-        <v>15</v>
+        <v>425</v>
       </c>
       <c r="G81" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="H81" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I81" t="s">
-        <v>38</v>
+        <v>429</v>
       </c>
       <c r="J81" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="K81" t="s">
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="M81" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>413</v>
+        <v>453</v>
       </c>
       <c r="B82" t="s">
-        <v>414</v>
+        <v>454</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="F82" t="s">
-        <v>15</v>
+        <v>455</v>
       </c>
       <c r="G82" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H82" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I82" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J82" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="K82" t="s">
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>415</v>
+        <v>456</v>
       </c>
       <c r="M82" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="B83" t="s">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="C83" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D83" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>339</v>
+        <v>444</v>
       </c>
       <c r="F83" t="s">
-        <v>73</v>
+        <v>460</v>
       </c>
       <c r="G83" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H83" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I83" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="J83" t="s">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="K83" t="s">
-        <v>15</v>
+        <v>463</v>
       </c>
       <c r="L83" t="s">
-        <v>419</v>
+        <v>461</v>
       </c>
       <c r="M83" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="N83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="B84" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
       <c r="C84" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D84" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>334</v>
+        <v>444</v>
       </c>
       <c r="F84" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G84" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H84" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I84" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="J84" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="K84" t="s">
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="M84" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>425</v>
+        <v>465</v>
       </c>
       <c r="B85" t="s">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D85" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E85" t="s">
-        <v>334</v>
+        <v>467</v>
       </c>
       <c r="F85" t="s">
-        <v>15</v>
+        <v>468</v>
       </c>
       <c r="G85" t="s">
-        <v>36</v>
+        <v>214</v>
       </c>
       <c r="H85" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I85" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J85" t="s">
-        <v>428</v>
+        <v>470</v>
       </c>
       <c r="K85" t="s">
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>427</v>
+        <v>469</v>
       </c>
       <c r="M85" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N85" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>429</v>
+        <v>471</v>
       </c>
       <c r="B86" t="s">
-        <v>430</v>
+        <v>472</v>
       </c>
       <c r="C86" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E86" t="s">
-        <v>18</v>
+        <v>274</v>
       </c>
       <c r="F86" t="s">
-        <v>15</v>
+        <v>433</v>
       </c>
       <c r="G86" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="H86" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I86" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J86" t="s">
-        <v>432</v>
+        <v>474</v>
       </c>
       <c r="K86" t="s">
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>431</v>
+        <v>473</v>
       </c>
       <c r="M86" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N86" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>433</v>
+        <v>475</v>
       </c>
       <c r="B87" t="s">
-        <v>434</v>
+        <v>476</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E87" t="s">
-        <v>435</v>
+        <v>477</v>
       </c>
       <c r="F87" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="G87" t="s">
-        <v>254</v>
+        <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I87" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J87" t="s">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="K87" t="s">
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>436</v>
+        <v>478</v>
       </c>
       <c r="M87" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N87" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>438</v>
+        <v>480</v>
       </c>
       <c r="B88" t="s">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>334</v>
+        <v>271</v>
       </c>
       <c r="F88" t="s">
-        <v>15</v>
+        <v>482</v>
       </c>
       <c r="G88" t="s">
-        <v>36</v>
+        <v>354</v>
       </c>
       <c r="H88" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I88" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J88" t="s">
-        <v>441</v>
+        <v>484</v>
       </c>
       <c r="K88" t="s">
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="M88" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N88" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="B89" t="s">
-        <v>443</v>
+        <v>481</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D89" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>444</v>
+        <v>271</v>
       </c>
       <c r="F89" t="s">
-        <v>15</v>
+        <v>482</v>
       </c>
       <c r="G89" t="s">
-        <v>118</v>
+        <v>354</v>
       </c>
       <c r="H89" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I89" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J89" t="s">
-        <v>446</v>
+        <v>486</v>
       </c>
       <c r="K89" t="s">
-        <v>15</v>
+        <v>485</v>
       </c>
       <c r="L89" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="M89" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N89" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>447</v>
+        <v>487</v>
       </c>
       <c r="B90" t="s">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E90" t="s">
-        <v>334</v>
+        <v>85</v>
       </c>
       <c r="F90" t="s">
-        <v>15</v>
+        <v>407</v>
       </c>
       <c r="G90" t="s">
-        <v>36</v>
+        <v>367</v>
       </c>
       <c r="H90" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I90" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J90" t="s">
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="K90" t="s">
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>449</v>
+        <v>489</v>
       </c>
       <c r="M90" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N90" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>451</v>
+        <v>491</v>
       </c>
       <c r="B91" t="s">
-        <v>452</v>
+        <v>492</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D91" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E91" t="s">
-        <v>453</v>
+        <v>85</v>
       </c>
       <c r="F91" t="s">
-        <v>15</v>
+        <v>312</v>
       </c>
       <c r="G91" t="s">
-        <v>36</v>
+        <v>374</v>
       </c>
       <c r="H91" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I91" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="J91" t="s">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="K91" t="s">
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>454</v>
+        <v>493</v>
       </c>
       <c r="M91" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N91" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="B92" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="C92" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="D92" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E92" t="s">
-        <v>410</v>
+        <v>497</v>
       </c>
       <c r="F92" t="s">
-        <v>15</v>
+        <v>312</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>367</v>
       </c>
       <c r="H92" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I92" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J92" t="s">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="K92" t="s">
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>411</v>
+        <v>498</v>
       </c>
       <c r="M92" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="N92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="B93" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="C93" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E93" t="s">
-        <v>334</v>
+        <v>502</v>
       </c>
       <c r="F93" t="s">
-        <v>15</v>
+        <v>503</v>
       </c>
       <c r="G93" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H93" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I93" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="J93" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="K93" t="s">
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="M93" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="B94" t="s">
-        <v>464</v>
+        <v>507</v>
       </c>
       <c r="C94" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>314</v>
+        <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="G94" t="s">
-        <v>230</v>
+        <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I94" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J94" t="s">
-        <v>466</v>
+        <v>509</v>
       </c>
       <c r="K94" t="s">
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>465</v>
+        <v>508</v>
       </c>
       <c r="M94" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N94" t="s">
-        <v>59</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>510</v>
+      </c>
+      <c r="B95" t="s">
+        <v>511</v>
+      </c>
+      <c r="C95" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" t="s">
+        <v>512</v>
+      </c>
+      <c r="F95" t="s">
+        <v>513</v>
+      </c>
+      <c r="G95" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" t="s">
+        <v>43</v>
+      </c>
+      <c r="I95" t="s">
+        <v>34</v>
+      </c>
+      <c r="J95" t="s">
+        <v>515</v>
+      </c>
+      <c r="K95" t="s">
+        <v>15</v>
+      </c>
+      <c r="L95" t="s">
+        <v>514</v>
+      </c>
+      <c r="M95" t="s">
+        <v>80</v>
+      </c>
+      <c r="N95" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>516</v>
+      </c>
+      <c r="B96" t="s">
+        <v>517</v>
+      </c>
+      <c r="C96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D96" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96" t="s">
+        <v>518</v>
+      </c>
+      <c r="F96" t="s">
+        <v>519</v>
+      </c>
+      <c r="G96" t="s">
+        <v>214</v>
+      </c>
+      <c r="H96" t="s">
+        <v>43</v>
+      </c>
+      <c r="I96" t="s">
+        <v>34</v>
+      </c>
+      <c r="J96" t="s">
+        <v>521</v>
+      </c>
+      <c r="K96" t="s">
+        <v>15</v>
+      </c>
+      <c r="L96" t="s">
+        <v>520</v>
+      </c>
+      <c r="M96" t="s">
+        <v>80</v>
+      </c>
+      <c r="N96" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>522</v>
+      </c>
+      <c r="B97" t="s">
+        <v>523</v>
+      </c>
+      <c r="C97" t="s">
+        <v>100</v>
+      </c>
+      <c r="D97" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" t="s">
+        <v>524</v>
+      </c>
+      <c r="F97" t="s">
+        <v>524</v>
+      </c>
+      <c r="G97" t="s">
+        <v>367</v>
+      </c>
+      <c r="H97" t="s">
+        <v>43</v>
+      </c>
+      <c r="I97" t="s">
+        <v>34</v>
+      </c>
+      <c r="J97" t="s">
+        <v>526</v>
+      </c>
+      <c r="K97" t="s">
+        <v>15</v>
+      </c>
+      <c r="L97" t="s">
+        <v>525</v>
+      </c>
+      <c r="M97" t="s">
+        <v>80</v>
+      </c>
+      <c r="N97" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>527</v>
+      </c>
+      <c r="B98" t="s">
+        <v>528</v>
+      </c>
+      <c r="C98" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98" t="s">
+        <v>529</v>
+      </c>
+      <c r="F98" t="s">
+        <v>97</v>
+      </c>
+      <c r="G98" t="s">
+        <v>530</v>
+      </c>
+      <c r="H98" t="s">
+        <v>43</v>
+      </c>
+      <c r="I98" t="s">
+        <v>34</v>
+      </c>
+      <c r="J98" t="s">
+        <v>532</v>
+      </c>
+      <c r="K98" t="s">
+        <v>15</v>
+      </c>
+      <c r="L98" t="s">
+        <v>531</v>
+      </c>
+      <c r="M98" t="s">
+        <v>80</v>
+      </c>
+      <c r="N98" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>533</v>
+      </c>
+      <c r="B99" t="s">
+        <v>534</v>
+      </c>
+      <c r="C99" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99" t="s">
+        <v>535</v>
+      </c>
+      <c r="F99" t="s">
+        <v>536</v>
+      </c>
+      <c r="G99" t="s">
+        <v>373</v>
+      </c>
+      <c r="H99" t="s">
+        <v>43</v>
+      </c>
+      <c r="I99" t="s">
+        <v>34</v>
+      </c>
+      <c r="J99" t="s">
+        <v>538</v>
+      </c>
+      <c r="K99" t="s">
+        <v>15</v>
+      </c>
+      <c r="L99" t="s">
+        <v>537</v>
+      </c>
+      <c r="M99" t="s">
+        <v>23</v>
+      </c>
+      <c r="N99" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>539</v>
+      </c>
+      <c r="B100" t="s">
+        <v>540</v>
+      </c>
+      <c r="C100" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" t="s">
+        <v>64</v>
+      </c>
+      <c r="E100" t="s">
+        <v>541</v>
+      </c>
+      <c r="F100" t="s">
+        <v>542</v>
+      </c>
+      <c r="G100" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" t="s">
+        <v>43</v>
+      </c>
+      <c r="I100" t="s">
+        <v>34</v>
+      </c>
+      <c r="J100" t="s">
+        <v>544</v>
+      </c>
+      <c r="K100" t="s">
+        <v>15</v>
+      </c>
+      <c r="L100" t="s">
+        <v>543</v>
+      </c>
+      <c r="M100" t="s">
+        <v>70</v>
+      </c>
+      <c r="N100" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>545</v>
+      </c>
+      <c r="B101" t="s">
+        <v>546</v>
+      </c>
+      <c r="C101" t="s">
+        <v>100</v>
+      </c>
+      <c r="D101" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" t="s">
+        <v>547</v>
+      </c>
+      <c r="F101" t="s">
+        <v>547</v>
+      </c>
+      <c r="G101" t="s">
+        <v>367</v>
+      </c>
+      <c r="H101" t="s">
+        <v>43</v>
+      </c>
+      <c r="I101" t="s">
+        <v>34</v>
+      </c>
+      <c r="J101" t="s">
+        <v>549</v>
+      </c>
+      <c r="K101" t="s">
+        <v>15</v>
+      </c>
+      <c r="L101" t="s">
+        <v>548</v>
+      </c>
+      <c r="M101" t="s">
+        <v>80</v>
+      </c>
+      <c r="N101" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>550</v>
+      </c>
+      <c r="B102" t="s">
+        <v>551</v>
+      </c>
+      <c r="C102" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" t="s">
+        <v>18</v>
+      </c>
+      <c r="E102" t="s">
+        <v>552</v>
+      </c>
+      <c r="F102" t="s">
+        <v>97</v>
+      </c>
+      <c r="G102" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" t="s">
+        <v>43</v>
+      </c>
+      <c r="I102" t="s">
+        <v>34</v>
+      </c>
+      <c r="J102" t="s">
+        <v>554</v>
+      </c>
+      <c r="K102" t="s">
+        <v>15</v>
+      </c>
+      <c r="L102" t="s">
+        <v>553</v>
+      </c>
+      <c r="M102" t="s">
+        <v>80</v>
+      </c>
+      <c r="N102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>555</v>
+      </c>
+      <c r="B103" t="s">
+        <v>556</v>
+      </c>
+      <c r="C103" t="s">
+        <v>100</v>
+      </c>
+      <c r="D103" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" t="s">
+        <v>557</v>
+      </c>
+      <c r="F103" t="s">
+        <v>558</v>
+      </c>
+      <c r="G103" t="s">
+        <v>281</v>
+      </c>
+      <c r="H103" t="s">
+        <v>43</v>
+      </c>
+      <c r="I103" t="s">
+        <v>34</v>
+      </c>
+      <c r="J103" t="s">
+        <v>560</v>
+      </c>
+      <c r="K103" t="s">
+        <v>15</v>
+      </c>
+      <c r="L103" t="s">
+        <v>559</v>
+      </c>
+      <c r="M103" t="s">
+        <v>80</v>
+      </c>
+      <c r="N103" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>561</v>
+      </c>
+      <c r="B104" t="s">
+        <v>562</v>
+      </c>
+      <c r="C104" t="s">
+        <v>100</v>
+      </c>
+      <c r="D104" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" t="s">
+        <v>563</v>
+      </c>
+      <c r="F104" t="s">
+        <v>563</v>
+      </c>
+      <c r="G104" t="s">
+        <v>367</v>
+      </c>
+      <c r="H104" t="s">
+        <v>43</v>
+      </c>
+      <c r="I104" t="s">
+        <v>34</v>
+      </c>
+      <c r="J104" t="s">
+        <v>565</v>
+      </c>
+      <c r="K104" t="s">
+        <v>15</v>
+      </c>
+      <c r="L104" t="s">
+        <v>564</v>
+      </c>
+      <c r="M104" t="s">
+        <v>80</v>
+      </c>
+      <c r="N104" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>566</v>
+      </c>
+      <c r="B105" t="s">
+        <v>567</v>
+      </c>
+      <c r="C105" t="s">
+        <v>100</v>
+      </c>
+      <c r="D105" t="s">
+        <v>18</v>
+      </c>
+      <c r="E105" t="s">
+        <v>502</v>
+      </c>
+      <c r="F105" t="s">
+        <v>503</v>
+      </c>
+      <c r="G105" t="s">
+        <v>78</v>
+      </c>
+      <c r="H105" t="s">
+        <v>43</v>
+      </c>
+      <c r="I105" t="s">
+        <v>34</v>
+      </c>
+      <c r="J105" t="s">
+        <v>569</v>
+      </c>
+      <c r="K105" t="s">
+        <v>15</v>
+      </c>
+      <c r="L105" t="s">
+        <v>568</v>
+      </c>
+      <c r="M105" t="s">
+        <v>23</v>
+      </c>
+      <c r="N105" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>570</v>
+      </c>
+      <c r="B106" t="s">
+        <v>571</v>
+      </c>
+      <c r="C106" t="s">
+        <v>100</v>
+      </c>
+      <c r="D106" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" t="s">
+        <v>572</v>
+      </c>
+      <c r="F106" t="s">
+        <v>573</v>
+      </c>
+      <c r="G106" t="s">
+        <v>373</v>
+      </c>
+      <c r="H106" t="s">
+        <v>43</v>
+      </c>
+      <c r="I106" t="s">
+        <v>34</v>
+      </c>
+      <c r="J106" t="s">
+        <v>575</v>
+      </c>
+      <c r="K106" t="s">
+        <v>15</v>
+      </c>
+      <c r="L106" t="s">
+        <v>574</v>
+      </c>
+      <c r="M106" t="s">
+        <v>23</v>
+      </c>
+      <c r="N106" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>576</v>
+      </c>
+      <c r="B107" t="s">
+        <v>577</v>
+      </c>
+      <c r="C107" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" t="s">
+        <v>97</v>
+      </c>
+      <c r="G107" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" t="s">
+        <v>43</v>
+      </c>
+      <c r="I107" t="s">
+        <v>34</v>
+      </c>
+      <c r="J107" t="s">
+        <v>579</v>
+      </c>
+      <c r="K107" t="s">
+        <v>15</v>
+      </c>
+      <c r="L107" t="s">
+        <v>578</v>
+      </c>
+      <c r="M107" t="s">
+        <v>80</v>
+      </c>
+      <c r="N107" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>580</v>
+      </c>
+      <c r="B108" t="s">
+        <v>581</v>
+      </c>
+      <c r="C108" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" t="s">
+        <v>64</v>
+      </c>
+      <c r="E108" t="s">
+        <v>582</v>
+      </c>
+      <c r="F108" t="s">
+        <v>455</v>
+      </c>
+      <c r="G108" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" t="s">
+        <v>43</v>
+      </c>
+      <c r="I108" t="s">
+        <v>61</v>
+      </c>
+      <c r="J108" t="s">
+        <v>584</v>
+      </c>
+      <c r="K108" t="s">
+        <v>15</v>
+      </c>
+      <c r="L108" t="s">
+        <v>583</v>
+      </c>
+      <c r="M108" t="s">
+        <v>70</v>
+      </c>
+      <c r="N108" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>585</v>
+      </c>
+      <c r="B109" t="s">
+        <v>586</v>
+      </c>
+      <c r="C109" t="s">
+        <v>100</v>
+      </c>
+      <c r="D109" t="s">
+        <v>18</v>
+      </c>
+      <c r="E109" t="s">
+        <v>587</v>
+      </c>
+      <c r="F109" t="s">
+        <v>588</v>
+      </c>
+      <c r="G109" t="s">
+        <v>354</v>
+      </c>
+      <c r="H109" t="s">
+        <v>43</v>
+      </c>
+      <c r="I109" t="s">
+        <v>34</v>
+      </c>
+      <c r="J109" t="s">
+        <v>590</v>
+      </c>
+      <c r="K109" t="s">
+        <v>15</v>
+      </c>
+      <c r="L109" t="s">
+        <v>589</v>
+      </c>
+      <c r="M109" t="s">
+        <v>80</v>
+      </c>
+      <c r="N109" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N94"/>
+  <autoFilter ref="A1:N109"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NLCX3311\Desktop\MES SUIVIS\EXTRACTION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NLCX3311\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$101</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="557">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -71,27 +71,108 @@
     <t>CARACTERISTIQUE</t>
   </si>
   <si>
+    <t>42091025</t>
+  </si>
+  <si>
+    <t>11/03/2025 19:35:08</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>support</t>
+  </si>
+  <si>
+    <t>fo</t>
+  </si>
+  <si>
+    <t>DOUANES</t>
+  </si>
+  <si>
+    <t>DIRECTION INFORMATIQUE DOUANES</t>
+  </si>
+  <si>
+    <t>VPNLL130143</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>Backup</t>
+  </si>
+  <si>
+    <t>En cours</t>
+  </si>
+  <si>
+    <t>Saisie ASCOM</t>
+  </si>
+  <si>
+    <t>02/06/2025 14:26:16</t>
+  </si>
+  <si>
+    <t>Réassigné</t>
+  </si>
+  <si>
+    <t>03/04/2025 12:21:07</t>
+  </si>
+  <si>
+    <t>42090725</t>
+  </si>
+  <si>
+    <t>11/03/2025 19:29:46</t>
+  </si>
+  <si>
+    <t>VPNLL060014</t>
+  </si>
+  <si>
+    <t>02/06/2025 14:26:15</t>
+  </si>
+  <si>
+    <t>03/04/2025 12:48:56</t>
+  </si>
+  <si>
+    <t>42085288</t>
+  </si>
+  <si>
+    <t>11/03/2025 17:42:13</t>
+  </si>
+  <si>
+    <t>radio</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/CT 0707630916</t>
+  </si>
+  <si>
+    <t>4M</t>
+  </si>
+  <si>
+    <t>VPNLL220036</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie GAIA</t>
+  </si>
+  <si>
+    <t>07/04/2025 18:04:16</t>
+  </si>
+  <si>
+    <t>Offert</t>
+  </si>
+  <si>
+    <t>SIE: Pilote</t>
+  </si>
+  <si>
+    <t>Responsable IP: Affectation Ingenieur Delivery</t>
+  </si>
+  <si>
     <t>42090133</t>
   </si>
   <si>
     <t>11/03/2025 19:12:18</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>support</t>
-  </si>
-  <si>
     <t>ftto</t>
   </si>
   <si>
-    <t>fo</t>
-  </si>
-  <si>
-    <t>DOUANES</t>
-  </si>
-  <si>
     <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/VRIDI SDV-CI</t>
   </si>
   <si>
@@ -101,21 +182,9 @@
     <t>VPNLL220026</t>
   </si>
   <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>Backup</t>
-  </si>
-  <si>
-    <t>BO Homologation: Saisie GAIA</t>
-  </si>
-  <si>
     <t>Responsable Zone: Validation pour intervention</t>
   </si>
   <si>
-    <t>Support IP: Config Eq Acces</t>
-  </si>
-  <si>
     <t>Technicien zone: Survey</t>
   </si>
   <si>
@@ -134,78 +203,6 @@
     <t>Responsable Zone: Validation Survey</t>
   </si>
   <si>
-    <t>Responsable IP: Affectation Ingenieur Delivery</t>
-  </si>
-  <si>
-    <t>SIE: Pilote</t>
-  </si>
-  <si>
-    <t>42085288</t>
-  </si>
-  <si>
-    <t>11/03/2025 17:42:13</t>
-  </si>
-  <si>
-    <t>radio</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/CT 0707630916</t>
-  </si>
-  <si>
-    <t>4M</t>
-  </si>
-  <si>
-    <t>VPNLL220036</t>
-  </si>
-  <si>
-    <t>07/04/2025 18:04:16</t>
-  </si>
-  <si>
-    <t>Offert</t>
-  </si>
-  <si>
-    <t>42091025</t>
-  </si>
-  <si>
-    <t>11/03/2025 19:35:08</t>
-  </si>
-  <si>
-    <t>DIRECTION INFORMATIQUE DOUANES</t>
-  </si>
-  <si>
-    <t>VPNLL130143</t>
-  </si>
-  <si>
-    <t>En cours</t>
-  </si>
-  <si>
-    <t>Saisie ASCOM</t>
-  </si>
-  <si>
-    <t>02/06/2025 14:26:16</t>
-  </si>
-  <si>
-    <t>Réassigné</t>
-  </si>
-  <si>
-    <t>03/04/2025 12:21:07</t>
-  </si>
-  <si>
-    <t>42090725</t>
-  </si>
-  <si>
-    <t>11/03/2025 19:29:46</t>
-  </si>
-  <si>
-    <t>VPNLL060014</t>
-  </si>
-  <si>
-    <t>02/06/2025 14:26:15</t>
-  </si>
-  <si>
-    <t>03/04/2025 12:48:56</t>
-  </si>
-  <si>
     <t>Transfert</t>
   </si>
   <si>
@@ -218,6 +215,33 @@
     <t>SIE : Mise en service GAIA</t>
   </si>
   <si>
+    <t>43259257</t>
+  </si>
+  <si>
+    <t>09/04/2025 10:47:35</t>
+  </si>
+  <si>
+    <t>CIMAF</t>
+  </si>
+  <si>
+    <t>SAN-PEDRO//VOIE INCONNUE/ZONE PORTUAIRE SAN PEDRO</t>
+  </si>
+  <si>
+    <t>40M</t>
+  </si>
+  <si>
+    <t>SYTHD170230</t>
+  </si>
+  <si>
+    <t>LSI</t>
+  </si>
+  <si>
+    <t>BO Homologation : Saisie GAIA LSI</t>
+  </si>
+  <si>
+    <t>28/05/2025 15:21:06</t>
+  </si>
+  <si>
     <t>44075918</t>
   </si>
   <si>
@@ -254,31 +278,25 @@
     <t>Travaux Suspendu</t>
   </si>
   <si>
-    <t>43259257</t>
-  </si>
-  <si>
-    <t>09/04/2025 10:47:35</t>
-  </si>
-  <si>
-    <t>CIMAF</t>
-  </si>
-  <si>
-    <t>SAN-PEDRO//VOIE INCONNUE/ZONE PORTUAIRE SAN PEDRO</t>
-  </si>
-  <si>
-    <t>40M</t>
-  </si>
-  <si>
-    <t>SYTHD170230</t>
-  </si>
-  <si>
-    <t>LSI</t>
-  </si>
-  <si>
-    <t>BO Homologation : Saisie GAIA LSI</t>
-  </si>
-  <si>
-    <t>28/05/2025 15:21:06</t>
+    <t>44431296</t>
+  </si>
+  <si>
+    <t>09/05/2025 09:44:34</t>
+  </si>
+  <si>
+    <t>LOTERIE NATIONALE DE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>KORHOGO//VOIE INCONNUE/KORHOGO</t>
+  </si>
+  <si>
+    <t>6M</t>
+  </si>
+  <si>
+    <t>BUVPN200157</t>
+  </si>
+  <si>
+    <t>13/11/2025 10:12:24</t>
   </si>
   <si>
     <t>45306957</t>
@@ -299,43 +317,79 @@
     <t>26/06/2025 13:57:23</t>
   </si>
   <si>
-    <t>44431296</t>
-  </si>
-  <si>
-    <t>09/05/2025 09:44:34</t>
-  </si>
-  <si>
-    <t>LOTERIE NATIONALE DE COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>KORHOGO//VOIE INCONNUE/KORHOGO</t>
-  </si>
-  <si>
-    <t>6M</t>
-  </si>
-  <si>
-    <t>BUVPN200157</t>
-  </si>
-  <si>
-    <t>13/11/2025 10:12:24</t>
-  </si>
-  <si>
     <t>ftto_virage</t>
   </si>
   <si>
     <t>TREICHVILLE</t>
   </si>
   <si>
+    <t>DIE : Configuration IMS</t>
+  </si>
+  <si>
+    <t>46532522</t>
+  </si>
+  <si>
+    <t>25/06/2025 16:32:38</t>
+  </si>
+  <si>
+    <t>debit</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DU TRESOR ET DE LA COMPTABILITE PUBLIQUE</t>
+  </si>
+  <si>
+    <t>//VOIE INCONNUE/DGTCP,cité financière,Tour B</t>
+  </si>
+  <si>
+    <t>2M</t>
+  </si>
+  <si>
+    <t>VPNLL070232</t>
+  </si>
+  <si>
+    <t>06/11/2025 15:30:23</t>
+  </si>
+  <si>
+    <t>46536492</t>
+  </si>
+  <si>
+    <t>25/06/2025 17:16:21</t>
+  </si>
+  <si>
+    <t>cuivre</t>
+  </si>
+  <si>
+    <t>//VOIE INCONNUE/MAIRIE DE SINFRA - TRESOR</t>
+  </si>
+  <si>
+    <t>30M</t>
+  </si>
+  <si>
+    <t>VPNLL090184</t>
+  </si>
+  <si>
+    <t>06/10/2025 15:57:26</t>
+  </si>
+  <si>
+    <t>46473005</t>
+  </si>
+  <si>
+    <t>24/06/2025 16:24:21</t>
+  </si>
+  <si>
+    <t>SEGUELA//VOIE INCONNUE/CONTACT 0707003126</t>
+  </si>
+  <si>
+    <t>VPNLL080103</t>
+  </si>
+  <si>
+    <t>06/11/2025 15:30:05</t>
+  </si>
+  <si>
     <t>46596937</t>
   </si>
   <si>
     <t>26/06/2025 18:16:26</t>
-  </si>
-  <si>
-    <t>debit</t>
-  </si>
-  <si>
-    <t>DIRECTION GENERALE DU TRESOR ET DE LA COMPTABILITE PUBLIQUE</t>
   </si>
   <si>
     <t>ABIDJAN-PLATEAU
@@ -348,58 +402,40 @@
     <t>06/11/2025 15:29:33</t>
   </si>
   <si>
-    <t>46473005</t>
-  </si>
-  <si>
-    <t>24/06/2025 16:24:21</t>
-  </si>
-  <si>
-    <t>SEGUELA//VOIE INCONNUE/CONTACT 0707003126</t>
-  </si>
-  <si>
-    <t>VPNLL080103</t>
-  </si>
-  <si>
-    <t>06/11/2025 15:30:05</t>
-  </si>
-  <si>
-    <t>46536492</t>
-  </si>
-  <si>
-    <t>25/06/2025 17:16:21</t>
-  </si>
-  <si>
-    <t>cuivre</t>
-  </si>
-  <si>
-    <t>//VOIE INCONNUE/MAIRIE DE SINFRA - TRESOR</t>
-  </si>
-  <si>
-    <t>30M</t>
-  </si>
-  <si>
-    <t>VPNLL090184</t>
-  </si>
-  <si>
-    <t>06/10/2025 15:57:26</t>
-  </si>
-  <si>
-    <t>46532522</t>
-  </si>
-  <si>
-    <t>25/06/2025 16:32:38</t>
-  </si>
-  <si>
-    <t>//VOIE INCONNUE/DGTCP,cité financière,Tour B</t>
-  </si>
-  <si>
-    <t>2M</t>
-  </si>
-  <si>
-    <t>VPNLL070232</t>
-  </si>
-  <si>
-    <t>06/11/2025 15:30:23</t>
+    <t>47653333</t>
+  </si>
+  <si>
+    <t>18/07/2025 12:45:02</t>
+  </si>
+  <si>
+    <t>CAISSE NATIONALE DE PREVOYANCE SOCIALE</t>
+  </si>
+  <si>
+    <t>SAN-PEDRO//VOIE INCONNUE/SAN PEDRO</t>
+  </si>
+  <si>
+    <t>20M</t>
+  </si>
+  <si>
+    <t>BUVPN150689</t>
+  </si>
+  <si>
+    <t>14/08/2025 09:23:10</t>
+  </si>
+  <si>
+    <t>47885035</t>
+  </si>
+  <si>
+    <t>23/07/2025 14:30:04</t>
+  </si>
+  <si>
+    <t>COCODY ANGRE DJIBI</t>
+  </si>
+  <si>
+    <t>2720305170</t>
+  </si>
+  <si>
+    <t>27/08/2025 15:59:17</t>
   </si>
   <si>
     <t>47261410</t>
@@ -420,18 +456,84 @@
     <t>02/09/2025 18:11:09</t>
   </si>
   <si>
+    <t>47878019</t>
+  </si>
+  <si>
+    <t>23/07/2025 12:51:35</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY ANGRE DJIBI</t>
+  </si>
+  <si>
+    <t>BUVPN150600</t>
+  </si>
+  <si>
+    <t>27/08/2025 14:19:45</t>
+  </si>
+  <si>
+    <t>47639322</t>
+  </si>
+  <si>
+    <t>18/07/2025 09:46:15</t>
+  </si>
+  <si>
+    <t>SAN PEDRO</t>
+  </si>
+  <si>
+    <t>2734711025</t>
+  </si>
+  <si>
+    <t>28/08/2025 20:16:23</t>
+  </si>
+  <si>
+    <t>48207282</t>
+  </si>
+  <si>
+    <t>30/07/2025 10:08:29</t>
+  </si>
+  <si>
+    <t>VPNLL220035</t>
+  </si>
+  <si>
+    <t>11/12/2025 09:01:38</t>
+  </si>
+  <si>
+    <t>47648026</t>
+  </si>
+  <si>
+    <t>18/07/2025 11:14:46</t>
+  </si>
+  <si>
+    <t>BUVPN150605</t>
+  </si>
+  <si>
+    <t>01/08/2025 12:49:49</t>
+  </si>
+  <si>
+    <t>48206525</t>
+  </si>
+  <si>
+    <t>30/07/2025 09:58:32</t>
+  </si>
+  <si>
+    <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/TREICHVILLE 0767161532</t>
+  </si>
+  <si>
+    <t>512K</t>
+  </si>
+  <si>
+    <t>VPNLL130015</t>
+  </si>
+  <si>
+    <t>14/01/2026 09:22:01</t>
+  </si>
+  <si>
     <t>47658350</t>
   </si>
   <si>
     <t>18/07/2025 13:30:49</t>
   </si>
   <si>
-    <t>CAISSE NATIONALE DE PREVOYANCE SOCIALE</t>
-  </si>
-  <si>
-    <t>SAN-PEDRO//VOIE INCONNUE/SAN PEDRO</t>
-  </si>
-  <si>
     <t>5M</t>
   </si>
   <si>
@@ -447,9 +549,6 @@
     <t>23/07/2025 11:27:13</t>
   </si>
   <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY ANGRE DJIBI</t>
-  </si>
-  <si>
     <t>SYTHD240171</t>
   </si>
   <si>
@@ -459,105 +558,6 @@
     <t>30/10/2025 14:56:28</t>
   </si>
   <si>
-    <t>47878019</t>
-  </si>
-  <si>
-    <t>23/07/2025 12:51:35</t>
-  </si>
-  <si>
-    <t>20M</t>
-  </si>
-  <si>
-    <t>BUVPN150600</t>
-  </si>
-  <si>
-    <t>27/08/2025 14:19:45</t>
-  </si>
-  <si>
-    <t>48207282</t>
-  </si>
-  <si>
-    <t>30/07/2025 10:08:29</t>
-  </si>
-  <si>
-    <t>VPNLL220035</t>
-  </si>
-  <si>
-    <t>11/12/2025 09:01:38</t>
-  </si>
-  <si>
-    <t>47653333</t>
-  </si>
-  <si>
-    <t>18/07/2025 12:45:02</t>
-  </si>
-  <si>
-    <t>BUVPN150689</t>
-  </si>
-  <si>
-    <t>14/08/2025 09:23:10</t>
-  </si>
-  <si>
-    <t>47648026</t>
-  </si>
-  <si>
-    <t>18/07/2025 11:14:46</t>
-  </si>
-  <si>
-    <t>SAN PEDRO</t>
-  </si>
-  <si>
-    <t>BUVPN150605</t>
-  </si>
-  <si>
-    <t>01/08/2025 12:49:49</t>
-  </si>
-  <si>
-    <t>47885035</t>
-  </si>
-  <si>
-    <t>23/07/2025 14:30:04</t>
-  </si>
-  <si>
-    <t>COCODY ANGRE DJIBI</t>
-  </si>
-  <si>
-    <t>2720305170</t>
-  </si>
-  <si>
-    <t>27/08/2025 15:59:17</t>
-  </si>
-  <si>
-    <t>48206525</t>
-  </si>
-  <si>
-    <t>30/07/2025 09:58:32</t>
-  </si>
-  <si>
-    <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/TREICHVILLE 0767161532</t>
-  </si>
-  <si>
-    <t>512K</t>
-  </si>
-  <si>
-    <t>VPNLL130015</t>
-  </si>
-  <si>
-    <t>14/01/2026 09:22:01</t>
-  </si>
-  <si>
-    <t>47639322</t>
-  </si>
-  <si>
-    <t>18/07/2025 09:46:15</t>
-  </si>
-  <si>
-    <t>2734711025</t>
-  </si>
-  <si>
-    <t>28/08/2025 20:16:23</t>
-  </si>
-  <si>
     <t>48419891</t>
   </si>
   <si>
@@ -594,6 +594,21 @@
     <t>27/01/2026 11:29:22</t>
   </si>
   <si>
+    <t>50608489</t>
+  </si>
+  <si>
+    <t>16/09/2025 10:36:49</t>
+  </si>
+  <si>
+    <t>IMMEUBLE SCIAM</t>
+  </si>
+  <si>
+    <t>BUVPN180153</t>
+  </si>
+  <si>
+    <t>26/09/2025 22:47:49</t>
+  </si>
+  <si>
     <t>51016709</t>
   </si>
   <si>
@@ -651,19 +666,22 @@
     <t>24/10/2025 16:34:01</t>
   </si>
   <si>
-    <t>50608489</t>
-  </si>
-  <si>
-    <t>16/09/2025 10:36:49</t>
-  </si>
-  <si>
-    <t>IMMEUBLE SCIAM</t>
-  </si>
-  <si>
-    <t>BUVPN180153</t>
-  </si>
-  <si>
-    <t>26/09/2025 22:47:49</t>
+    <t>52090983</t>
+  </si>
+  <si>
+    <t>15/10/2025 14:03:08</t>
+  </si>
+  <si>
+    <t>AVIATION ET COMPAGNIES COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET</t>
+  </si>
+  <si>
+    <t>2721212909</t>
+  </si>
+  <si>
+    <t>26/02/2026 12:37:40</t>
   </si>
   <si>
     <t>52558712</t>
@@ -684,6 +702,21 @@
     <t>11/11/2025 16:40:10</t>
   </si>
   <si>
+    <t>52741559</t>
+  </si>
+  <si>
+    <t>29/10/2025 09:10:21</t>
+  </si>
+  <si>
+    <t>bonoua</t>
+  </si>
+  <si>
+    <t>2721300130</t>
+  </si>
+  <si>
+    <t>25/11/2025 12:54:15</t>
+  </si>
+  <si>
     <t>51691679</t>
   </si>
   <si>
@@ -699,37 +732,76 @@
     <t>22/10/2025 12:30:17</t>
   </si>
   <si>
-    <t>52090983</t>
-  </si>
-  <si>
-    <t>15/10/2025 14:03:08</t>
-  </si>
-  <si>
-    <t>AVIATION ET COMPAGNIES COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT-BOUET</t>
-  </si>
-  <si>
-    <t>2721212909</t>
-  </si>
-  <si>
-    <t>26/02/2026 12:37:40</t>
-  </si>
-  <si>
-    <t>52741559</t>
-  </si>
-  <si>
-    <t>29/10/2025 09:10:21</t>
-  </si>
-  <si>
-    <t>bonoua</t>
-  </si>
-  <si>
-    <t>2721300130</t>
-  </si>
-  <si>
-    <t>25/11/2025 12:54:15</t>
+    <t>55980750</t>
+  </si>
+  <si>
+    <t>30/12/2025 12:27:06</t>
+  </si>
+  <si>
+    <t>INTELCIA COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>COCODY RIVIERA PALMERAIE SOCOPRIX ROUTE DE BINGERVILLE</t>
+  </si>
+  <si>
+    <t>100M</t>
+  </si>
+  <si>
+    <t>SYTHD170248</t>
+  </si>
+  <si>
+    <t>Principale (avec backup)</t>
+  </si>
+  <si>
+    <t>06/01/2026 19:29:08</t>
+  </si>
+  <si>
+    <t>54447209</t>
+  </si>
+  <si>
+    <t>01/12/2025 16:36:58</t>
+  </si>
+  <si>
+    <t>SEGUELA</t>
+  </si>
+  <si>
+    <t>BUVPN230217</t>
+  </si>
+  <si>
+    <t>16/01/2026 09:44:03</t>
+  </si>
+  <si>
+    <t>55492730</t>
+  </si>
+  <si>
+    <t>19/12/2025 18:59:39</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/FRET AEROPORT</t>
+  </si>
+  <si>
+    <t>VPNLL230023</t>
+  </si>
+  <si>
+    <t>20/01/2026 09:11:56</t>
+  </si>
+  <si>
+    <t>54962571</t>
+  </si>
+  <si>
+    <t>11/12/2025 10:06:55</t>
+  </si>
+  <si>
+    <t>DES SOCIETES D'ASSURANCE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>RAXIO VITIB BASSAM</t>
+  </si>
+  <si>
+    <t>2722221750</t>
+  </si>
+  <si>
+    <t>19/12/2025 15:34:19</t>
   </si>
   <si>
     <t>55994930</t>
@@ -738,9 +810,6 @@
     <t>30/12/2025 15:09:31</t>
   </si>
   <si>
-    <t>INTELCIA COTE D'IVOIRE</t>
-  </si>
-  <si>
     <t>ABIDJAN-COCODY//VOIE INCONNUE/INTELCA CI, COCODY RIVIERA</t>
   </si>
   <si>
@@ -762,75 +831,6 @@
     <t>06/01/2026 19:47:15</t>
   </si>
   <si>
-    <t>55980750</t>
-  </si>
-  <si>
-    <t>30/12/2025 12:27:06</t>
-  </si>
-  <si>
-    <t>COCODY RIVIERA PALMERAIE SOCOPRIX ROUTE DE BINGERVILLE</t>
-  </si>
-  <si>
-    <t>100M</t>
-  </si>
-  <si>
-    <t>SYTHD170248</t>
-  </si>
-  <si>
-    <t>Principale (avec backup)</t>
-  </si>
-  <si>
-    <t>06/01/2026 19:29:08</t>
-  </si>
-  <si>
-    <t>55492730</t>
-  </si>
-  <si>
-    <t>19/12/2025 18:59:39</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/FRET AEROPORT</t>
-  </si>
-  <si>
-    <t>VPNLL230023</t>
-  </si>
-  <si>
-    <t>20/01/2026 09:11:56</t>
-  </si>
-  <si>
-    <t>54447209</t>
-  </si>
-  <si>
-    <t>01/12/2025 16:36:58</t>
-  </si>
-  <si>
-    <t>SEGUELA</t>
-  </si>
-  <si>
-    <t>BUVPN230217</t>
-  </si>
-  <si>
-    <t>16/01/2026 09:44:03</t>
-  </si>
-  <si>
-    <t>54962571</t>
-  </si>
-  <si>
-    <t>11/12/2025 10:06:55</t>
-  </si>
-  <si>
-    <t>DES SOCIETES D'ASSURANCE COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>RAXIO VITIB BASSAM</t>
-  </si>
-  <si>
-    <t>2722221750</t>
-  </si>
-  <si>
-    <t>19/12/2025 15:34:19</t>
-  </si>
-  <si>
     <t>55167162</t>
   </si>
   <si>
@@ -840,6 +840,42 @@
     <t>29/12/2025 15:45:51</t>
   </si>
   <si>
+    <t>56579652</t>
+  </si>
+  <si>
+    <t>12/01/2026 16:17:11</t>
+  </si>
+  <si>
+    <t>QUIPUX AFRIQUE</t>
+  </si>
+  <si>
+    <t>200M</t>
+  </si>
+  <si>
+    <t>BUVPN150333</t>
+  </si>
+  <si>
+    <t>03/02/2026 13:55:35</t>
+  </si>
+  <si>
+    <t>56268044</t>
+  </si>
+  <si>
+    <t>06/01/2026 15:42:28</t>
+  </si>
+  <si>
+    <t>AERIA</t>
+  </si>
+  <si>
+    <t>AEROPORT FHB 0709254454</t>
+  </si>
+  <si>
+    <t>SYTHD230156</t>
+  </si>
+  <si>
+    <t>13/02/2026 13:56:52</t>
+  </si>
+  <si>
     <t>57100866</t>
   </si>
   <si>
@@ -864,52 +900,37 @@
     <t>04/02/2026 19:45:44</t>
   </si>
   <si>
-    <t>56268044</t>
-  </si>
-  <si>
-    <t>06/01/2026 15:42:28</t>
-  </si>
-  <si>
-    <t>AERIA</t>
-  </si>
-  <si>
-    <t>AEROPORT FHB 0709254454</t>
-  </si>
-  <si>
-    <t>200M</t>
-  </si>
-  <si>
-    <t>SYTHD230156</t>
-  </si>
-  <si>
-    <t>13/02/2026 13:56:52</t>
-  </si>
-  <si>
     <t>56580353</t>
   </si>
   <si>
     <t>12/01/2026 16:23:44</t>
   </si>
   <si>
-    <t>QUIPUX AFRIQUE</t>
-  </si>
-  <si>
     <t>BUVPN210339</t>
   </si>
   <si>
     <t>03/02/2026 14:22:58</t>
   </si>
   <si>
-    <t>56579652</t>
-  </si>
-  <si>
-    <t>12/01/2026 16:17:11</t>
-  </si>
-  <si>
-    <t>BUVPN150333</t>
-  </si>
-  <si>
-    <t>03/02/2026 13:55:35</t>
+    <t>56903552</t>
+  </si>
+  <si>
+    <t>19/01/2026 11:52:02</t>
+  </si>
+  <si>
+    <t>ABIDJAN-MARCORY//VOIE INCONNUE/BLHD FHD PREMOTO FACE PLAYCE</t>
+  </si>
+  <si>
+    <t>VPNLL060054</t>
+  </si>
+  <si>
+    <t>03/02/2026 10:25:14</t>
+  </si>
+  <si>
+    <t>17/02/2026 17:07:55</t>
+  </si>
+  <si>
+    <t>18/03/2026 13:49:49</t>
   </si>
   <si>
     <t>57114434</t>
@@ -930,19 +951,97 @@
     <t>10/02/2026 13:57:35</t>
   </si>
   <si>
-    <t>58784245</t>
-  </si>
-  <si>
-    <t>23/02/2026 10:04:29</t>
-  </si>
-  <si>
-    <t>COCODY RIVIERA 2</t>
-  </si>
-  <si>
-    <t>BUVPN240049</t>
-  </si>
-  <si>
-    <t>25/02/2026 11:55:09</t>
+    <t>58431947</t>
+  </si>
+  <si>
+    <t>16/02/2026 17:40:46</t>
+  </si>
+  <si>
+    <t>BANQUE ATLANTIQUE DE COTE D'IVOIRE AGENCE PLATEAU</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/CONTACT 02032576</t>
+  </si>
+  <si>
+    <t>BUVPN200286</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:02:46</t>
+  </si>
+  <si>
+    <t>58996002</t>
+  </si>
+  <si>
+    <t>26/02/2026 11:30:04</t>
+  </si>
+  <si>
+    <t>2720306611</t>
+  </si>
+  <si>
+    <t>18/03/2026 10:19:10</t>
+  </si>
+  <si>
+    <t>57703033</t>
+  </si>
+  <si>
+    <t>03/02/2026 11:21:12</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM//VOIE INCONNUE/</t>
+  </si>
+  <si>
+    <t>60M</t>
+  </si>
+  <si>
+    <t>VPNLL060028</t>
+  </si>
+  <si>
+    <t>28/02/2026 10:44:59</t>
+  </si>
+  <si>
+    <t>18/02/2026 15:54:47</t>
+  </si>
+  <si>
+    <t>18/02/2026 15:54:31</t>
+  </si>
+  <si>
+    <t>58822848</t>
+  </si>
+  <si>
+    <t>23/02/2026 16:08:17</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIRIENNE DE BANQUE (GRAND-BASSAM )</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM</t>
+  </si>
+  <si>
+    <t>10M</t>
+  </si>
+  <si>
+    <t>BUVPN220110</t>
+  </si>
+  <si>
+    <t>24/03/2026 16:08:50</t>
+  </si>
+  <si>
+    <t>58029496</t>
+  </si>
+  <si>
+    <t>09/02/2026 13:44:17</t>
+  </si>
+  <si>
+    <t>AFRICA SOURCING COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>TREICHVILLE RUE DES THONIERS</t>
+  </si>
+  <si>
+    <t>2721358023</t>
+  </si>
+  <si>
+    <t>16/03/2026 22:18:50</t>
   </si>
   <si>
     <t>58480398</t>
@@ -963,55 +1062,49 @@
     <t>03/03/2026 09:45:43</t>
   </si>
   <si>
-    <t>58783980</t>
-  </si>
-  <si>
-    <t>23/02/2026 10:02:01</t>
-  </si>
-  <si>
-    <t>GRAND-BASSAM</t>
+    <t>58804111</t>
+  </si>
+  <si>
+    <t>23/02/2026 13:19:20</t>
+  </si>
+  <si>
+    <t>BUVPN220135</t>
+  </si>
+  <si>
+    <t>26/02/2026 09:40:55</t>
+  </si>
+  <si>
+    <t>58784601</t>
+  </si>
+  <si>
+    <t>23/02/2026 10:09:18</t>
+  </si>
+  <si>
+    <t>ABIDJAN TREICHVILLE</t>
   </si>
   <si>
     <t>400M</t>
   </si>
   <si>
-    <t>BUVPN220126</t>
-  </si>
-  <si>
-    <t>25/02/2026 11:54:30</t>
-  </si>
-  <si>
-    <t>58784601</t>
-  </si>
-  <si>
-    <t>23/02/2026 10:09:18</t>
-  </si>
-  <si>
-    <t>ABIDJAN TREICHVILLE</t>
-  </si>
-  <si>
     <t>BUVPN150481</t>
   </si>
   <si>
-    <t>25/02/2026 11:57:12</t>
-  </si>
-  <si>
-    <t>58431947</t>
-  </si>
-  <si>
-    <t>16/02/2026 17:40:46</t>
-  </si>
-  <si>
-    <t>BANQUE ATLANTIQUE DE COTE D'IVOIRE AGENCE PLATEAU</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/CONTACT 02032576</t>
-  </si>
-  <si>
-    <t>BUVPN200286</t>
-  </si>
-  <si>
-    <t>03/03/2026 09:02:46</t>
+    <t>19/03/2026 11:11:26</t>
+  </si>
+  <si>
+    <t>59011477</t>
+  </si>
+  <si>
+    <t>26/02/2026 14:00:03</t>
+  </si>
+  <si>
+    <t>BRIDGE BANK GROUP</t>
+  </si>
+  <si>
+    <t>2721212910</t>
+  </si>
+  <si>
+    <t>25/03/2026 15:30:49</t>
   </si>
   <si>
     <t>58835120</t>
@@ -1035,19 +1128,240 @@
     <t>10/03/2026 11:49:03</t>
   </si>
   <si>
-    <t>58783395</t>
-  </si>
-  <si>
-    <t>23/02/2026 09:54:35</t>
-  </si>
-  <si>
-    <t>ABIDJAN PLATEAU COMMERCE</t>
-  </si>
-  <si>
-    <t>BUVPN140002</t>
-  </si>
-  <si>
-    <t>12/03/2026 17:32:47</t>
+    <t>58417809</t>
+  </si>
+  <si>
+    <t>16/02/2026 15:02:05</t>
+  </si>
+  <si>
+    <t>MARCORY</t>
+  </si>
+  <si>
+    <t>BUVPN180204</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:09:32</t>
+  </si>
+  <si>
+    <t>57711569</t>
+  </si>
+  <si>
+    <t>03/02/2026 12:49:14</t>
+  </si>
+  <si>
+    <t>BANQUE INTERNATIONALE POUR LE COMMERCE ET L'INDUSTRIE DE CI</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU//VOIE INCONNUE/EXTREMITE  A PLATEAU</t>
+  </si>
+  <si>
+    <t>SYTHD250061</t>
+  </si>
+  <si>
+    <t>18/02/2026 15:55:59</t>
+  </si>
+  <si>
+    <t>18/02/2026 15:56:17</t>
+  </si>
+  <si>
+    <t>28/02/2026 11:00:28</t>
+  </si>
+  <si>
+    <t>58427309</t>
+  </si>
+  <si>
+    <t>16/02/2026 16:43:29</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY RIVIERA 3</t>
+  </si>
+  <si>
+    <t>BUVPN190195</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:11:55</t>
+  </si>
+  <si>
+    <t>57852659</t>
+  </si>
+  <si>
+    <t>05/02/2026 15:07:32</t>
+  </si>
+  <si>
+    <t>COTE D'IVOIRE MULTIMEDIA</t>
+  </si>
+  <si>
+    <t>COMMUNE INCONNUE//VOIE INCONNUE/ AXE ABIDJAN-YAKRO  PK 22</t>
+  </si>
+  <si>
+    <t>SYTHD180109</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:13:44</t>
+  </si>
+  <si>
+    <t>58783117</t>
+  </si>
+  <si>
+    <t>23/02/2026 09:51:36</t>
+  </si>
+  <si>
+    <t>BUVPN200230</t>
+  </si>
+  <si>
+    <t>25/02/2026 11:09:13</t>
+  </si>
+  <si>
+    <t>57702014</t>
+  </si>
+  <si>
+    <t>03/02/2026 11:11:18</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM//VOIE INCONNUE/GRAND BASSAM</t>
+  </si>
+  <si>
+    <t>VPNLL120077</t>
+  </si>
+  <si>
+    <t>27/02/2026 20:07:54</t>
+  </si>
+  <si>
+    <t>18/02/2026 17:59:04</t>
+  </si>
+  <si>
+    <t>18/02/2026 17:58:51</t>
+  </si>
+  <si>
+    <t>58805170</t>
+  </si>
+  <si>
+    <t>23/02/2026 13:29:54</t>
+  </si>
+  <si>
+    <t>BUVPN230180</t>
+  </si>
+  <si>
+    <t>26/02/2026 09:41:30</t>
+  </si>
+  <si>
+    <t>58896886</t>
+  </si>
+  <si>
+    <t>24/02/2026 17:16:44</t>
+  </si>
+  <si>
+    <t>STANDARD CHARTERED BANK COTE D'IVOIRE SA</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM//VOIE INCONNUE/BASSAM VITIB</t>
+  </si>
+  <si>
+    <t>VPNLL120246</t>
+  </si>
+  <si>
+    <t>13/03/2026 10:54:09</t>
+  </si>
+  <si>
+    <t>58810120</t>
+  </si>
+  <si>
+    <t>23/02/2026 14:18:42</t>
+  </si>
+  <si>
+    <t>BUVPN210151</t>
+  </si>
+  <si>
+    <t>26/02/2026 09:47:15</t>
+  </si>
+  <si>
+    <t>57864191</t>
+  </si>
+  <si>
+    <t>05/02/2026 16:54:42</t>
+  </si>
+  <si>
+    <t>SYTHD230067</t>
+  </si>
+  <si>
+    <t>11/02/2026 19:07:39</t>
+  </si>
+  <si>
+    <t>58048251</t>
+  </si>
+  <si>
+    <t>09/02/2026 16:53:27</t>
+  </si>
+  <si>
+    <t>FOREVER LIVING PRODUCT</t>
+  </si>
+  <si>
+    <t>SYTHD180175</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:43:56</t>
+  </si>
+  <si>
+    <t>58680250</t>
+  </si>
+  <si>
+    <t>20/02/2026 16:56:43</t>
+  </si>
+  <si>
+    <t>GROUPEMENT ORANGE SERVICES</t>
+  </si>
+  <si>
+    <t>UPGRADE 1 Gbps 
+ICA</t>
+  </si>
+  <si>
+    <t>1G</t>
+  </si>
+  <si>
+    <t>SYTHD120073</t>
+  </si>
+  <si>
+    <t>23/02/2026 13:29:41</t>
+  </si>
+  <si>
+    <t>25/02/2026 16:37:43</t>
+  </si>
+  <si>
+    <t>03/03/2026 12:40:11</t>
+  </si>
+  <si>
+    <t>57670112</t>
+  </si>
+  <si>
+    <t>02/02/2026 16:48:58</t>
+  </si>
+  <si>
+    <t>SOCIETE NATIONALE  DE TELECOM DAKAR</t>
+  </si>
+  <si>
+    <t>EXTR A : ACE CLS 
+EXTR B : BCEAO PLATEAU</t>
+  </si>
+  <si>
+    <t>SYTHD210026</t>
+  </si>
+  <si>
+    <t>10/02/2026 11:22:09</t>
+  </si>
+  <si>
+    <t>59082502</t>
+  </si>
+  <si>
+    <t>27/02/2026 15:19:13</t>
+  </si>
+  <si>
+    <t>//VOIE INCONNUE/AGENCE SIB PLATEAU IMMEUBLE</t>
+  </si>
+  <si>
+    <t>VPNLL090098</t>
+  </si>
+  <si>
+    <t>24/03/2026 16:04:38</t>
   </si>
   <si>
     <t>58488142</t>
@@ -1062,91 +1376,13 @@
     <t>2720211797</t>
   </si>
   <si>
-    <t>18/02/2026 08:29:02</t>
-  </si>
-  <si>
-    <t>58996002</t>
-  </si>
-  <si>
-    <t>26/02/2026 11:30:04</t>
-  </si>
-  <si>
-    <t>2720306611</t>
-  </si>
-  <si>
-    <t>06/03/2026 09:34:12</t>
-  </si>
-  <si>
-    <t>58810120</t>
-  </si>
-  <si>
-    <t>23/02/2026 14:18:42</t>
-  </si>
-  <si>
-    <t>BUVPN210151</t>
-  </si>
-  <si>
-    <t>26/02/2026 09:47:15</t>
-  </si>
-  <si>
-    <t>58783117</t>
-  </si>
-  <si>
-    <t>23/02/2026 09:51:36</t>
-  </si>
-  <si>
-    <t>60M</t>
-  </si>
-  <si>
-    <t>BUVPN200230</t>
-  </si>
-  <si>
-    <t>25/02/2026 11:09:13</t>
-  </si>
-  <si>
-    <t>57702014</t>
-  </si>
-  <si>
-    <t>03/02/2026 11:11:18</t>
-  </si>
-  <si>
-    <t>GRAND-BASSAM//VOIE INCONNUE/GRAND BASSAM</t>
-  </si>
-  <si>
-    <t>VPNLL120077</t>
-  </si>
-  <si>
-    <t>27/02/2026 20:07:54</t>
-  </si>
-  <si>
-    <t>18/02/2026 17:59:04</t>
-  </si>
-  <si>
-    <t>18/02/2026 17:58:51</t>
-  </si>
-  <si>
-    <t>58785667</t>
-  </si>
-  <si>
-    <t>23/02/2026 10:21:46</t>
-  </si>
-  <si>
-    <t>YOPOUGON</t>
-  </si>
-  <si>
-    <t>10M</t>
-  </si>
-  <si>
-    <t>25/02/2026 12:00:25</t>
+    <t>19/03/2026 11:42:27</t>
   </si>
   <si>
     <t>58680600</t>
   </si>
   <si>
     <t>20/02/2026 17:01:22</t>
-  </si>
-  <si>
-    <t>GROUPEMENT ORANGE SERVICES</t>
   </si>
   <si>
     <t>Z.FRANCHE GD-BASSAM VITIB.A
@@ -1155,12 +1391,6 @@
 GOS VITIB BASSAM</t>
   </si>
   <si>
-    <t>1G</t>
-  </si>
-  <si>
-    <t>300M</t>
-  </si>
-  <si>
     <t>SYTHD120074</t>
   </si>
   <si>
@@ -1176,27 +1406,12 @@
     <t>23/02/2026 13:30:36</t>
   </si>
   <si>
-    <t>58804111</t>
-  </si>
-  <si>
-    <t>23/02/2026 13:19:20</t>
-  </si>
-  <si>
-    <t>BUVPN220135</t>
-  </si>
-  <si>
-    <t>26/02/2026 09:40:55</t>
-  </si>
-  <si>
     <t>58895685</t>
   </si>
   <si>
     <t>24/02/2026 17:06:29</t>
   </si>
   <si>
-    <t>STANDARD CHARTERED BANK COTE D'IVOIRE SA</t>
-  </si>
-  <si>
     <t>GD BASSAM VITIB</t>
   </si>
   <si>
@@ -1206,173 +1421,12 @@
     <t>28/02/2026 08:34:38</t>
   </si>
   <si>
-    <t>58427309</t>
-  </si>
-  <si>
-    <t>16/02/2026 16:43:29</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY RIVIERA 3</t>
-  </si>
-  <si>
-    <t>BUVPN190195</t>
-  </si>
-  <si>
-    <t>03/03/2026 09:11:55</t>
-  </si>
-  <si>
-    <t>58029496</t>
-  </si>
-  <si>
-    <t>09/02/2026 13:44:17</t>
-  </si>
-  <si>
-    <t>AFRICA SOURCING COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>TREICHVILLE RUE DES THONIERS</t>
-  </si>
-  <si>
-    <t>2721358023</t>
-  </si>
-  <si>
-    <t>13/03/2026 12:44:53</t>
-  </si>
-  <si>
-    <t>58805170</t>
-  </si>
-  <si>
-    <t>23/02/2026 13:29:54</t>
-  </si>
-  <si>
-    <t>BUVPN230180</t>
-  </si>
-  <si>
-    <t>26/02/2026 09:41:30</t>
-  </si>
-  <si>
-    <t>59082502</t>
-  </si>
-  <si>
-    <t>27/02/2026 15:19:13</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU</t>
-  </si>
-  <si>
-    <t>VPNLL090098</t>
-  </si>
-  <si>
-    <t>03/03/2026 19:59:32</t>
-  </si>
-  <si>
-    <t>58048251</t>
-  </si>
-  <si>
-    <t>09/02/2026 16:53:27</t>
-  </si>
-  <si>
-    <t>FOREVER LIVING PRODUCT</t>
-  </si>
-  <si>
-    <t>SYTHD180175</t>
-  </si>
-  <si>
-    <t>03/03/2026 09:43:56</t>
-  </si>
-  <si>
-    <t>58680250</t>
-  </si>
-  <si>
-    <t>20/02/2026 16:56:43</t>
-  </si>
-  <si>
-    <t>UPGRADE 1 Gbps 
-ICA</t>
-  </si>
-  <si>
-    <t>SYTHD120073</t>
-  </si>
-  <si>
-    <t>23/02/2026 13:29:41</t>
-  </si>
-  <si>
-    <t>25/02/2026 16:37:43</t>
-  </si>
-  <si>
-    <t>03/03/2026 12:40:11</t>
-  </si>
-  <si>
-    <t>58821317</t>
-  </si>
-  <si>
-    <t>23/02/2026 15:54:43</t>
-  </si>
-  <si>
-    <t>ALTERA INFRASTRUCTURE VOYAGEUR AS</t>
-  </si>
-  <si>
-    <t>ABIDJAN</t>
-  </si>
-  <si>
-    <t>SYTHD240109</t>
-  </si>
-  <si>
-    <t>13/03/2026 10:20:30</t>
-  </si>
-  <si>
-    <t>BO Homologation: Mise en service BSCS</t>
-  </si>
-  <si>
-    <t>BO Homologation: Mise en service GAIA</t>
-  </si>
-  <si>
-    <t>13/03/2026 10:21:05</t>
-  </si>
-  <si>
-    <t>58896886</t>
-  </si>
-  <si>
-    <t>24/02/2026 17:16:44</t>
-  </si>
-  <si>
-    <t>GRAND-BASSAM//VOIE INCONNUE/BASSAM VITIB</t>
-  </si>
-  <si>
-    <t>VPNLL120246</t>
-  </si>
-  <si>
-    <t>13/03/2026 10:54:09</t>
-  </si>
-  <si>
-    <t>57670112</t>
-  </si>
-  <si>
-    <t>02/02/2026 16:48:58</t>
-  </si>
-  <si>
-    <t>SOCIETE NATIONALE  DE TELECOM DAKAR</t>
-  </si>
-  <si>
-    <t>EXTR A : ACE CLS 
-EXTR B : BCEAO PLATEAU</t>
-  </si>
-  <si>
-    <t>SYTHD210026</t>
-  </si>
-  <si>
-    <t>10/02/2026 11:22:09</t>
-  </si>
-  <si>
     <t>57860238</t>
   </si>
   <si>
     <t>05/02/2026 16:21:01</t>
   </si>
   <si>
-    <t>BANQUE INTERNATIONALE POUR LE COMMERCE ET L'INDUSTRIE DE CI</t>
-  </si>
-  <si>
     <t>GRAND-BASSAM//VOIE INCONNUE/GRAND BASSAM VITIB</t>
   </si>
   <si>
@@ -1382,166 +1436,247 @@
     <t>12/02/2026 19:44:21</t>
   </si>
   <si>
-    <t>58822007</t>
-  </si>
-  <si>
-    <t>23/02/2026 16:00:58</t>
-  </si>
-  <si>
-    <t>SYTHD240087</t>
-  </si>
-  <si>
-    <t>13/03/2026 10:18:53</t>
-  </si>
-  <si>
-    <t>13/03/2026 10:19:27</t>
-  </si>
-  <si>
-    <t>58417809</t>
-  </si>
-  <si>
-    <t>16/02/2026 15:02:05</t>
-  </si>
-  <si>
-    <t>MARCORY</t>
-  </si>
-  <si>
-    <t>BUVPN180204</t>
-  </si>
-  <si>
-    <t>03/03/2026 09:09:32</t>
-  </si>
-  <si>
-    <t>57711569</t>
-  </si>
-  <si>
-    <t>03/02/2026 12:49:14</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU//VOIE INCONNUE/EXTREMITE  A PLATEAU</t>
-  </si>
-  <si>
-    <t>SYTHD250061</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:55:59</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:56:17</t>
-  </si>
-  <si>
-    <t>28/02/2026 11:00:28</t>
-  </si>
-  <si>
-    <t>57852659</t>
-  </si>
-  <si>
-    <t>05/02/2026 15:07:32</t>
-  </si>
-  <si>
-    <t>COTE D'IVOIRE MULTIMEDIA</t>
-  </si>
-  <si>
-    <t>COMMUNE INCONNUE//VOIE INCONNUE/ AXE ABIDJAN-YAKRO  PK 22</t>
-  </si>
-  <si>
-    <t>SYTHD180109</t>
-  </si>
-  <si>
-    <t>03/03/2026 09:13:44</t>
-  </si>
-  <si>
-    <t>57864191</t>
-  </si>
-  <si>
-    <t>05/02/2026 16:54:42</t>
-  </si>
-  <si>
-    <t>SYTHD230067</t>
-  </si>
-  <si>
-    <t>11/02/2026 19:07:39</t>
-  </si>
-  <si>
-    <t>59011477</t>
-  </si>
-  <si>
-    <t>26/02/2026 14:00:03</t>
-  </si>
-  <si>
-    <t>BRIDGE BANK GROUP</t>
-  </si>
-  <si>
-    <t>2721212910</t>
-  </si>
-  <si>
-    <t>28/02/2026 11:36:47</t>
-  </si>
-  <si>
-    <t>57703033</t>
-  </si>
-  <si>
-    <t>03/02/2026 11:21:12</t>
-  </si>
-  <si>
-    <t>GRAND-BASSAM//VOIE INCONNUE/</t>
-  </si>
-  <si>
-    <t>VPNLL060028</t>
-  </si>
-  <si>
-    <t>28/02/2026 10:44:59</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:54:47</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:54:31</t>
-  </si>
-  <si>
-    <t>58782956</t>
-  </si>
-  <si>
-    <t>23/02/2026 09:49:42</t>
-  </si>
-  <si>
-    <t>BUVPN220116</t>
-  </si>
-  <si>
-    <t>11/03/2026 14:57:27</t>
-  </si>
-  <si>
-    <t>58783796</t>
-  </si>
-  <si>
-    <t>23/02/2026 09:59:21</t>
-  </si>
-  <si>
-    <t>BUVPN210149</t>
-  </si>
-  <si>
-    <t>11/03/2026 14:59:44</t>
-  </si>
-  <si>
-    <t>58822848</t>
-  </si>
-  <si>
-    <t>23/02/2026 16:08:17</t>
-  </si>
-  <si>
-    <t>SOCIETE IVOIRIENNE DE BANQUE (GRAND-BASSAM )</t>
-  </si>
-  <si>
-    <t>BUVPN220110</t>
-  </si>
-  <si>
-    <t>26/02/2026 09:49:46</t>
-  </si>
-  <si>
-    <t>59428182</t>
-  </si>
-  <si>
-    <t>05/03/2026 16:07:54</t>
+    <t>58783980</t>
+  </si>
+  <si>
+    <t>23/02/2026 10:02:01</t>
+  </si>
+  <si>
+    <t>BUVPN220126</t>
+  </si>
+  <si>
+    <t>25/02/2026 11:54:30</t>
+  </si>
+  <si>
+    <t>59302434</t>
+  </si>
+  <si>
+    <t>03/03/2026 16:51:42</t>
+  </si>
+  <si>
+    <t>BUVPN230155</t>
+  </si>
+  <si>
+    <t>26/03/2026 16:30:25</t>
+  </si>
+  <si>
+    <t>59805789</t>
+  </si>
+  <si>
+    <t>12/03/2026 11:59:46</t>
+  </si>
+  <si>
+    <t>ORANGE COTE D'IVOIRE S.A</t>
+  </si>
+  <si>
+    <t>HABITA BAT CIT FC HOPITAL P102</t>
+  </si>
+  <si>
+    <t>VPNLL170009</t>
+  </si>
+  <si>
+    <t>19/03/2026 13:30:49</t>
+  </si>
+  <si>
+    <t>60126667</t>
+  </si>
+  <si>
+    <t>18/03/2026 15:09:23</t>
+  </si>
+  <si>
+    <t>STE CEDERAC</t>
+  </si>
+  <si>
+    <t>PK 44 AUTOROUTE DU NORD</t>
+  </si>
+  <si>
+    <t>SYTHD150313</t>
+  </si>
+  <si>
+    <t>26/03/2026 10:57:20</t>
+  </si>
+  <si>
+    <t>60040794</t>
+  </si>
+  <si>
+    <t>17/03/2026 11:32:25</t>
+  </si>
+  <si>
+    <t>AFRICA GLOBAL LOGISTICS</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/VRIDI</t>
+  </si>
+  <si>
+    <t>BUVPN170223</t>
+  </si>
+  <si>
+    <t>24/03/2026 16:11:10</t>
+  </si>
+  <si>
+    <t>59301884</t>
+  </si>
+  <si>
+    <t>03/03/2026 16:45:07</t>
+  </si>
+  <si>
+    <t>SYTHD170144</t>
+  </si>
+  <si>
+    <t>26/03/2026 17:43:13</t>
+  </si>
+  <si>
+    <t>60121462</t>
+  </si>
+  <si>
+    <t>18/03/2026 14:09:33</t>
+  </si>
+  <si>
+    <t>MOTA-ENGIL COTE D'IVOIRE HIRIE AGBAOU</t>
+  </si>
+  <si>
+    <t>SYTHD250188</t>
+  </si>
+  <si>
+    <t>24/03/2026 15:58:34</t>
+  </si>
+  <si>
+    <t>60361274</t>
+  </si>
+  <si>
+    <t>23/03/2026 15:47:41</t>
+  </si>
+  <si>
+    <t>GMA</t>
+  </si>
+  <si>
+    <t>150M</t>
+  </si>
+  <si>
+    <t>SYTHD190266</t>
+  </si>
+  <si>
+    <t>27/03/2026 15:05:51</t>
+  </si>
+  <si>
+    <t>60165030</t>
+  </si>
+  <si>
+    <t>19/03/2026 10:25:48</t>
+  </si>
+  <si>
+    <t>EGLISE DE JESUS CHRIST DES SAINTS DES DERNIERS JOURS</t>
+  </si>
+  <si>
+    <t>SYTHD240106</t>
+  </si>
+  <si>
+    <t>25/03/2026 17:30:16</t>
+  </si>
+  <si>
+    <t>60117848</t>
+  </si>
+  <si>
+    <t>18/03/2026 13:25:57</t>
+  </si>
+  <si>
+    <t>MOTA-ENGIL COTE D'IVOIRE SEGUELA</t>
+  </si>
+  <si>
+    <t>40G</t>
+  </si>
+  <si>
+    <t>SYTHD230111</t>
+  </si>
+  <si>
+    <t>24/03/2026 15:57:52</t>
+  </si>
+  <si>
+    <t>60166789</t>
+  </si>
+  <si>
+    <t>19/03/2026 10:45:13</t>
+  </si>
+  <si>
+    <t>SYTHD240107</t>
+  </si>
+  <si>
+    <t>25/03/2026 17:30:59</t>
+  </si>
+  <si>
+    <t>59488550</t>
+  </si>
+  <si>
+    <t>06/03/2026 14:31:49</t>
+  </si>
+  <si>
+    <t>CLINIQUE MEDICALE TRADE CENTER</t>
+  </si>
+  <si>
+    <t>MARCORY RESIDENTIEL</t>
+  </si>
+  <si>
+    <t>2720219797</t>
+  </si>
+  <si>
+    <t>24/03/2026 16:03:38</t>
+  </si>
+  <si>
+    <t>59822523</t>
+  </si>
+  <si>
+    <t>12/03/2026 15:00:46</t>
+  </si>
+  <si>
+    <t>AGENCE OCI 2PLTX  ENA</t>
+  </si>
+  <si>
+    <t>ABIDJAN PLATEAU PIA</t>
+  </si>
+  <si>
+    <t>VPNLL210028</t>
+  </si>
+  <si>
+    <t>24/03/2026 16:05:01</t>
+  </si>
+  <si>
+    <t>59301236</t>
+  </si>
+  <si>
+    <t>03/03/2026 16:38:39</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES DOUANES</t>
+  </si>
+  <si>
+    <t>SYTHD230225</t>
+  </si>
+  <si>
+    <t>26/03/2026 16:49:44</t>
+  </si>
+  <si>
+    <t>59323774</t>
+  </si>
+  <si>
+    <t>04/03/2026 09:17:41</t>
+  </si>
+  <si>
+    <t>BRIDGE GROUP WEST AFRICA</t>
+  </si>
+  <si>
+    <t>COCODY RUE CANEBIERRE IMMEUBLE PHEHONE</t>
+  </si>
+  <si>
+    <t>SYTHD250379</t>
+  </si>
+  <si>
+    <t>24/03/2026 16:09:57</t>
+  </si>
+  <si>
+    <t>59429267</t>
+  </si>
+  <si>
+    <t>05/03/2026 16:16:19</t>
   </si>
   <si>
     <t>CORIS BANK INTERNATIONAL</t>
@@ -1550,232 +1685,10 @@
     <t>BD REPUBLIQUE 23 ANGLE RUE</t>
   </si>
   <si>
-    <t>BUVPN150629</t>
-  </si>
-  <si>
-    <t>12/03/2026 16:33:33</t>
-  </si>
-  <si>
-    <t>59302434</t>
-  </si>
-  <si>
-    <t>03/03/2026 16:51:42</t>
-  </si>
-  <si>
-    <t>BUVPN230155</t>
-  </si>
-  <si>
-    <t>12/03/2026 12:04:11</t>
-  </si>
-  <si>
-    <t>59323774</t>
-  </si>
-  <si>
-    <t>04/03/2026 09:17:41</t>
-  </si>
-  <si>
-    <t>BRIDGE GROUP WEST AFRICA</t>
-  </si>
-  <si>
-    <t>COCODY RUE CANEBIERRE IMMEUBLE PHEHONE</t>
-  </si>
-  <si>
-    <t>SYTHD250379</t>
-  </si>
-  <si>
-    <t>12/03/2026 12:46:06</t>
-  </si>
-  <si>
-    <t>59470580</t>
-  </si>
-  <si>
-    <t>06/03/2026 11:10:51</t>
-  </si>
-  <si>
-    <t>CIMPOR</t>
-  </si>
-  <si>
-    <t>YOPOUGON ZONE INDUSTRIELLE</t>
-  </si>
-  <si>
-    <t>SYTHD200159</t>
-  </si>
-  <si>
-    <t>12/03/2026 16:51:20</t>
-  </si>
-  <si>
-    <t>59696023</t>
-  </si>
-  <si>
-    <t>10/03/2026 15:33:01</t>
-  </si>
-  <si>
-    <t>BAOBAB COTE D'IVOIRE BOUAFLE</t>
-  </si>
-  <si>
-    <t>SYTHD210072</t>
-  </si>
-  <si>
-    <t>12/03/2026 17:03:36</t>
-  </si>
-  <si>
-    <t>59457854</t>
-  </si>
-  <si>
-    <t>06/03/2026 08:40:21</t>
-  </si>
-  <si>
-    <t>MEDLOG</t>
-  </si>
-  <si>
-    <t>150M</t>
-  </si>
-  <si>
-    <t>SYTHD160040</t>
-  </si>
-  <si>
-    <t>12/03/2026 16:47:41</t>
-  </si>
-  <si>
-    <t>59822523</t>
-  </si>
-  <si>
-    <t>12/03/2026 15:00:46</t>
-  </si>
-  <si>
-    <t>AGENCE OCI 2PLTX  ENA</t>
-  </si>
-  <si>
-    <t>ABIDJAN PLATEAU PIA</t>
-  </si>
-  <si>
-    <t>VPNLL210028</t>
-  </si>
-  <si>
-    <t>12/03/2026 17:05:50</t>
-  </si>
-  <si>
-    <t>59488550</t>
-  </si>
-  <si>
-    <t>06/03/2026 14:31:49</t>
-  </si>
-  <si>
-    <t>CLINIQUE MEDICALE TRADE CENTER</t>
-  </si>
-  <si>
-    <t>MARCORY RESIDENTIEL</t>
-  </si>
-  <si>
-    <t>2720219797</t>
-  </si>
-  <si>
-    <t>12/03/2026 16:54:21</t>
-  </si>
-  <si>
-    <t>59692851</t>
-  </si>
-  <si>
-    <t>10/03/2026 15:03:16</t>
-  </si>
-  <si>
-    <t>BAOBAB COTE D'IVOIRE DABOU</t>
-  </si>
-  <si>
-    <t>SYTHD210080</t>
-  </si>
-  <si>
-    <t>12/03/2026 17:03:11</t>
-  </si>
-  <si>
-    <t>59301236</t>
-  </si>
-  <si>
-    <t>03/03/2026 16:38:39</t>
-  </si>
-  <si>
-    <t>DIRECTION GENERALE DES DOUANES</t>
-  </si>
-  <si>
-    <t>SYTHD230225</t>
-  </si>
-  <si>
-    <t>12/03/2026 11:58:44</t>
-  </si>
-  <si>
-    <t>59609074</t>
-  </si>
-  <si>
-    <t>09/03/2026 11:15:22</t>
-  </si>
-  <si>
-    <t>OLAM COCOA PROCESSING CI</t>
-  </si>
-  <si>
-    <t>PORT-BOUET ZONE INDUSTRIELLE DE VRIDI</t>
-  </si>
-  <si>
-    <t>SYTHD070082</t>
-  </si>
-  <si>
-    <t>12/03/2026 16:58:39</t>
-  </si>
-  <si>
-    <t>59698221</t>
-  </si>
-  <si>
-    <t>10/03/2026 15:56:09</t>
-  </si>
-  <si>
-    <t>BAOBAB COTE D'IVOIRE AYAMA</t>
-  </si>
-  <si>
-    <t>SYTHD240187</t>
-  </si>
-  <si>
-    <t>12/03/2026 17:04:14</t>
-  </si>
-  <si>
-    <t>59429267</t>
-  </si>
-  <si>
-    <t>05/03/2026 16:16:19</t>
-  </si>
-  <si>
     <t>BUVPN150572</t>
   </si>
   <si>
-    <t>12/03/2026 14:40:20</t>
-  </si>
-  <si>
-    <t>59805789</t>
-  </si>
-  <si>
-    <t>12/03/2026 11:59:46</t>
-  </si>
-  <si>
-    <t>ORANGE COTE D'IVOIRE S.A</t>
-  </si>
-  <si>
-    <t>HABITA BAT CIT FC HOPITAL P102</t>
-  </si>
-  <si>
-    <t>VPNLL170009</t>
-  </si>
-  <si>
-    <t>12/03/2026 12:43:51</t>
-  </si>
-  <si>
-    <t>59301884</t>
-  </si>
-  <si>
-    <t>03/03/2026 16:45:07</t>
-  </si>
-  <si>
-    <t>SYTHD170144</t>
-  </si>
-  <si>
-    <t>12/03/2026 12:01:20</t>
+    <t>19/03/2026 09:05:15</t>
   </si>
   <si>
     <t>59458389</t>
@@ -1791,24 +1704,6 @@
   </si>
   <si>
     <t>11/03/2026 14:42:45</t>
-  </si>
-  <si>
-    <t>59808510</t>
-  </si>
-  <si>
-    <t>12/03/2026 12:25:09</t>
-  </si>
-  <si>
-    <t>ETABLISSEMENT MULTI SERVICES SORO ZIE</t>
-  </si>
-  <si>
-    <t>COCODY RIVERA ATTOBAN</t>
-  </si>
-  <si>
-    <t>SYTHD210086</t>
-  </si>
-  <si>
-    <t>12/03/2026 17:30:56</t>
   </si>
   <si>
     <t>NOM  CLIENT</t>
@@ -2188,7 +2083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -2221,7 +2116,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -2265,371 +2160,371 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
+      <c r="M2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
-        <v>46</v>
-      </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
-        <v>46</v>
-      </c>
       <c r="G5" t="s">
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
       </c>
       <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
       <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" t="s">
         <v>49</v>
       </c>
-      <c r="J7" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" t="s">
-        <v>55</v>
-      </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
         <v>62</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
         <v>63</v>
       </c>
-      <c r="C8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>64</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>65</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" t="s">
         <v>67</v>
       </c>
-      <c r="G8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" t="s">
-        <v>70</v>
-      </c>
       <c r="N8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" t="s">
         <v>75</v>
       </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>76</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
         <v>77</v>
       </c>
-      <c r="G9" t="s">
+      <c r="M9" t="s">
         <v>78</v>
       </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" t="s">
-        <v>79</v>
-      </c>
-      <c r="M9" t="s">
-        <v>80</v>
-      </c>
       <c r="N9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
         <v>83</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
         <v>84</v>
       </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>85</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>86</v>
       </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="J10" t="s">
         <v>88</v>
@@ -2641,10 +2536,10 @@
         <v>87</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2655,7 +2550,7 @@
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -2667,28 +2562,28 @@
         <v>92</v>
       </c>
       <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" t="s">
         <v>93</v>
       </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" t="s">
-        <v>95</v>
-      </c>
-      <c r="K11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" t="s">
-        <v>94</v>
-      </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2702,7 +2597,7 @@
         <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
         <v>101</v>
@@ -2711,145 +2606,145 @@
         <v>102</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J12" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s">
         <v>104</v>
       </c>
-      <c r="K12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" t="s">
-        <v>103</v>
-      </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K13" t="s">
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
         <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
         <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G14" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="H14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J14" t="s">
+        <v>117</v>
+      </c>
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" t="s">
         <v>116</v>
       </c>
-      <c r="K14" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" t="s">
-        <v>115</v>
-      </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
         <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J15" t="s">
         <v>122</v>
@@ -2861,10 +2756,10 @@
         <v>121</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -2875,10 +2770,10 @@
         <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>125</v>
@@ -2887,104 +2782,104 @@
         <v>126</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I16" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="J16" t="s">
+        <v>129</v>
+      </c>
+      <c r="K16" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
         <v>128</v>
       </c>
-      <c r="K16" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" t="s">
-        <v>127</v>
-      </c>
       <c r="M16" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F17" t="s">
         <v>132</v>
       </c>
       <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" t="s">
+        <v>134</v>
+      </c>
+      <c r="K17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" t="s">
         <v>133</v>
       </c>
-      <c r="H17" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" t="s">
-        <v>135</v>
-      </c>
-      <c r="K17" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" t="s">
-        <v>134</v>
-      </c>
       <c r="M17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" t="s">
         <v>136</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s">
         <v>137</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" t="s">
-        <v>131</v>
       </c>
       <c r="F18" t="s">
         <v>138</v>
       </c>
       <c r="G18" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="J18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K18" t="s">
         <v>15</v>
@@ -2993,83 +2888,83 @@
         <v>139</v>
       </c>
       <c r="M18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" t="s">
         <v>142</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" t="s">
         <v>143</v>
       </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" t="s">
-        <v>131</v>
-      </c>
-      <c r="F19" t="s">
-        <v>138</v>
-      </c>
       <c r="G19" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" t="s">
+        <v>145</v>
+      </c>
+      <c r="K19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" t="s">
         <v>144</v>
       </c>
-      <c r="H19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" t="s">
-        <v>146</v>
-      </c>
-      <c r="K19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L19" t="s">
-        <v>145</v>
-      </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" t="s">
         <v>147</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" t="s">
         <v>148</v>
       </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>46</v>
-      </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I20" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J20" t="s">
         <v>150</v>
@@ -3081,10 +2976,10 @@
         <v>149</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="N20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -3095,25 +2990,25 @@
         <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>144</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I21" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J21" t="s">
         <v>154</v>
@@ -3125,10 +3020,10 @@
         <v>153</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -3139,69 +3034,69 @@
         <v>156</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F22" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" t="s">
+        <v>158</v>
+      </c>
+      <c r="K22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s">
         <v>157</v>
       </c>
-      <c r="G22" t="s">
-        <v>144</v>
-      </c>
-      <c r="H22" t="s">
-        <v>48</v>
-      </c>
-      <c r="I22" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" t="s">
-        <v>159</v>
-      </c>
-      <c r="K22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" t="s">
-        <v>158</v>
-      </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" t="s">
         <v>160</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" t="s">
         <v>161</v>
       </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>162</v>
       </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
       <c r="H23" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I23" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="J23" t="s">
         <v>164</v>
@@ -3213,10 +3108,10 @@
         <v>163</v>
       </c>
       <c r="M23" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="N23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -3227,69 +3122,69 @@
         <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="F24" t="s">
+        <v>126</v>
+      </c>
+      <c r="G24" t="s">
         <v>167</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" t="s">
+        <v>169</v>
+      </c>
+      <c r="K24" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" t="s">
         <v>168</v>
       </c>
-      <c r="H24" t="s">
-        <v>43</v>
-      </c>
-      <c r="I24" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24" t="s">
-        <v>170</v>
-      </c>
-      <c r="K24" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24" t="s">
-        <v>169</v>
-      </c>
       <c r="M24" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" t="s">
         <v>171</v>
       </c>
-      <c r="B25" t="s">
-        <v>172</v>
-      </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F25" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="H25" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I25" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J25" t="s">
         <v>174</v>
@@ -3298,13 +3193,13 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -3318,7 +3213,7 @@
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E26" t="s">
         <v>177</v>
@@ -3330,10 +3225,10 @@
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="I26" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="J26" t="s">
         <v>180</v>
@@ -3345,10 +3240,10 @@
         <v>179</v>
       </c>
       <c r="M26" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="N26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -3359,10 +3254,10 @@
         <v>182</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
         <v>183</v>
@@ -3374,10 +3269,10 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="J27" t="s">
         <v>186</v>
@@ -3389,10 +3284,10 @@
         <v>185</v>
       </c>
       <c r="M27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -3403,25 +3298,25 @@
         <v>188</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="F28" t="s">
         <v>189</v>
       </c>
       <c r="G28" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="H28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I28" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="J28" t="s">
         <v>191</v>
@@ -3433,10 +3328,10 @@
         <v>190</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -3447,157 +3342,157 @@
         <v>193</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
         <v>18</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>194</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H29" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" t="s">
+        <v>50</v>
+      </c>
+      <c r="J29" t="s">
+        <v>196</v>
+      </c>
+      <c r="K29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" t="s">
         <v>195</v>
       </c>
-      <c r="G29" t="s">
-        <v>40</v>
-      </c>
-      <c r="H29" t="s">
-        <v>43</v>
-      </c>
-      <c r="I29" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" t="s">
-        <v>197</v>
-      </c>
-      <c r="K29" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" t="s">
-        <v>196</v>
-      </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>197</v>
+      </c>
+      <c r="B30" t="s">
         <v>198</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
         <v>199</v>
       </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" t="s">
-        <v>101</v>
-      </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="G30" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J30" t="s">
+        <v>202</v>
+      </c>
+      <c r="K30" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" t="s">
         <v>201</v>
       </c>
-      <c r="K30" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30" t="s">
-        <v>200</v>
-      </c>
       <c r="M30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C31" t="s">
         <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E31" t="s">
         <v>101</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="H31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I31" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J31" t="s">
+        <v>206</v>
+      </c>
+      <c r="K31" t="s">
+        <v>15</v>
+      </c>
+      <c r="L31" t="s">
         <v>205</v>
       </c>
-      <c r="K31" t="s">
-        <v>15</v>
-      </c>
-      <c r="L31" t="s">
-        <v>204</v>
-      </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C32" t="s">
         <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E32" t="s">
         <v>101</v>
       </c>
       <c r="F32" t="s">
-        <v>208</v>
+        <v>74</v>
       </c>
       <c r="G32" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="H32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J32" t="s">
         <v>210</v>
@@ -3609,10 +3504,10 @@
         <v>209</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -3623,25 +3518,25 @@
         <v>212</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
         <v>213</v>
       </c>
       <c r="F33" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="G33" t="s">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J33" t="s">
         <v>216</v>
@@ -3653,10 +3548,10 @@
         <v>215</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="N33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -3667,57 +3562,57 @@
         <v>218</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
       </c>
       <c r="E34" t="s">
-        <v>101</v>
+        <v>219</v>
       </c>
       <c r="F34" t="s">
-        <v>219</v>
+        <v>138</v>
       </c>
       <c r="G34" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="H34" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I34" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="J34" t="s">
+        <v>222</v>
+      </c>
+      <c r="K34" t="s">
+        <v>15</v>
+      </c>
+      <c r="L34" t="s">
         <v>221</v>
       </c>
-      <c r="K34" t="s">
-        <v>15</v>
-      </c>
-      <c r="L34" t="s">
-        <v>220</v>
-      </c>
       <c r="M34" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="E35" t="s">
-        <v>224</v>
+        <v>125</v>
       </c>
       <c r="F35" t="s">
         <v>225</v>
@@ -3726,10 +3621,10 @@
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I35" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="J35" t="s">
         <v>227</v>
@@ -3741,10 +3636,10 @@
         <v>226</v>
       </c>
       <c r="M35" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="N35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -3755,25 +3650,25 @@
         <v>229</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="F36" t="s">
         <v>230</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H36" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J36" t="s">
         <v>232</v>
@@ -3785,10 +3680,10 @@
         <v>231</v>
       </c>
       <c r="M36" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -3802,7 +3697,7 @@
         <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E37" t="s">
         <v>235</v>
@@ -3811,233 +3706,233 @@
         <v>236</v>
       </c>
       <c r="G37" t="s">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="H37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I37" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J37" t="s">
+        <v>240</v>
+      </c>
+      <c r="K37" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" t="s">
         <v>238</v>
       </c>
-      <c r="K37" t="s">
-        <v>15</v>
-      </c>
-      <c r="L37" t="s">
-        <v>237</v>
-      </c>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N37" t="s">
-        <v>24</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B38" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C38" t="s">
         <v>100</v>
       </c>
       <c r="D38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" t="s">
         <v>18</v>
       </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
       <c r="F38" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="G38" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J38" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K38" t="s">
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
       </c>
       <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s">
         <v>18</v>
       </c>
-      <c r="E39" t="s">
-        <v>235</v>
-      </c>
       <c r="F39" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G39" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="H39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J39" t="s">
+        <v>250</v>
+      </c>
+      <c r="K39" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s">
         <v>249</v>
       </c>
-      <c r="K39" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39" t="s">
-        <v>247</v>
-      </c>
       <c r="M39" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N39" t="s">
-        <v>248</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B40" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="F40" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G40" t="s">
-        <v>214</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="J40" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K40" t="s">
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M40" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="N40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B41" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C41" t="s">
         <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>235</v>
       </c>
       <c r="F41" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G41" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K41" t="s">
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B42" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>263</v>
+        <v>19</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H42" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I42" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="J42" t="s">
         <v>265</v>
@@ -4049,10 +3944,10 @@
         <v>264</v>
       </c>
       <c r="M42" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -4063,25 +3958,25 @@
         <v>267</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" t="s">
         <v>18</v>
       </c>
-      <c r="E43" t="s">
-        <v>19</v>
-      </c>
       <c r="F43" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G43" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="H43" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I43" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J43" t="s">
         <v>268</v>
@@ -4090,13 +3985,13 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="M43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -4110,110 +4005,110 @@
         <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E44" t="s">
         <v>271</v>
       </c>
       <c r="F44" t="s">
+        <v>96</v>
+      </c>
+      <c r="G44" t="s">
         <v>272</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
+        <v>41</v>
+      </c>
+      <c r="I44" t="s">
+        <v>60</v>
+      </c>
+      <c r="J44" t="s">
+        <v>274</v>
+      </c>
+      <c r="K44" t="s">
+        <v>15</v>
+      </c>
+      <c r="L44" t="s">
         <v>273</v>
       </c>
-      <c r="H44" t="s">
-        <v>43</v>
-      </c>
-      <c r="I44" t="s">
-        <v>33</v>
-      </c>
-      <c r="J44" t="s">
-        <v>276</v>
-      </c>
-      <c r="K44" t="s">
-        <v>15</v>
-      </c>
-      <c r="L44" t="s">
-        <v>275</v>
-      </c>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B45" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C45" t="s">
         <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E45" t="s">
+        <v>277</v>
+      </c>
+      <c r="F45" t="s">
+        <v>278</v>
+      </c>
+      <c r="G45" t="s">
+        <v>272</v>
+      </c>
+      <c r="H45" t="s">
+        <v>41</v>
+      </c>
+      <c r="I45" t="s">
+        <v>56</v>
+      </c>
+      <c r="J45" t="s">
+        <v>280</v>
+      </c>
+      <c r="K45" t="s">
+        <v>15</v>
+      </c>
+      <c r="L45" t="s">
         <v>279</v>
       </c>
-      <c r="F45" t="s">
-        <v>280</v>
-      </c>
-      <c r="G45" t="s">
-        <v>281</v>
-      </c>
-      <c r="H45" t="s">
-        <v>43</v>
-      </c>
-      <c r="I45" t="s">
-        <v>33</v>
-      </c>
-      <c r="J45" t="s">
-        <v>283</v>
-      </c>
-      <c r="K45" t="s">
-        <v>15</v>
-      </c>
-      <c r="L45" t="s">
-        <v>282</v>
-      </c>
       <c r="M45" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B46" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C46" t="s">
         <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F46" t="s">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="G46" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="H46" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I46" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="J46" t="s">
         <v>288</v>
@@ -4225,10 +4120,10 @@
         <v>287</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N46" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -4242,22 +4137,22 @@
         <v>100</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E47" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="F47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G47" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="H47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I47" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J47" t="s">
         <v>292</v>
@@ -4269,10 +4164,10 @@
         <v>291</v>
       </c>
       <c r="M47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N47" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -4283,1037 +4178,1037 @@
         <v>294</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" t="s">
         <v>18</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>295</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
+        <v>37</v>
+      </c>
+      <c r="H48" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" t="s">
+        <v>50</v>
+      </c>
+      <c r="J48" t="s">
+        <v>297</v>
+      </c>
+      <c r="K48" t="s">
+        <v>298</v>
+      </c>
+      <c r="L48" t="s">
         <v>296</v>
       </c>
-      <c r="G48" t="s">
-        <v>40</v>
-      </c>
-      <c r="H48" t="s">
-        <v>43</v>
-      </c>
-      <c r="I48" t="s">
-        <v>33</v>
-      </c>
-      <c r="J48" t="s">
-        <v>298</v>
-      </c>
-      <c r="K48" t="s">
-        <v>15</v>
-      </c>
-      <c r="L48" t="s">
-        <v>297</v>
-      </c>
       <c r="M48" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>293</v>
+      </c>
+      <c r="B49" t="s">
+        <v>294</v>
+      </c>
+      <c r="C49" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" t="s">
+        <v>295</v>
+      </c>
+      <c r="G49" t="s">
+        <v>37</v>
+      </c>
+      <c r="H49" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" t="s">
+        <v>52</v>
+      </c>
+      <c r="J49" t="s">
         <v>299</v>
       </c>
-      <c r="B49" t="s">
-        <v>300</v>
-      </c>
-      <c r="C49" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" t="s">
-        <v>85</v>
-      </c>
-      <c r="F49" t="s">
-        <v>301</v>
-      </c>
-      <c r="G49" t="s">
-        <v>120</v>
-      </c>
-      <c r="H49" t="s">
-        <v>43</v>
-      </c>
-      <c r="I49" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49" t="s">
-        <v>303</v>
-      </c>
       <c r="K49" t="s">
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="M49" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B50" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C50" t="s">
         <v>100</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E50" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F50" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G50" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I50" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J50" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K50" t="s">
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C51" t="s">
         <v>100</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>308</v>
       </c>
       <c r="F51" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G51" t="s">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="H51" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I51" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="J51" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K51" t="s">
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M51" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B52" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="E52" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F52" t="s">
-        <v>318</v>
+        <v>74</v>
       </c>
       <c r="G52" t="s">
-        <v>313</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I52" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="J52" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="K52" t="s">
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="M52" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="N52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>316</v>
+      </c>
+      <c r="B53" t="s">
+        <v>317</v>
+      </c>
+      <c r="C53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" t="s">
+        <v>283</v>
+      </c>
+      <c r="F53" t="s">
+        <v>318</v>
+      </c>
+      <c r="G53" t="s">
+        <v>319</v>
+      </c>
+      <c r="H53" t="s">
+        <v>41</v>
+      </c>
+      <c r="I53" t="s">
+        <v>42</v>
+      </c>
+      <c r="J53" t="s">
         <v>321</v>
       </c>
-      <c r="B53" t="s">
-        <v>322</v>
-      </c>
-      <c r="C53" t="s">
-        <v>100</v>
-      </c>
-      <c r="D53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" t="s">
-        <v>323</v>
-      </c>
-      <c r="F53" t="s">
-        <v>324</v>
-      </c>
-      <c r="G53" t="s">
-        <v>40</v>
-      </c>
-      <c r="H53" t="s">
-        <v>43</v>
-      </c>
-      <c r="I53" t="s">
-        <v>33</v>
-      </c>
-      <c r="J53" t="s">
-        <v>326</v>
-      </c>
       <c r="K53" t="s">
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="B54" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="C54" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E54" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
       <c r="F54" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="G54" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="H54" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I54" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="J54" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="K54" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="L54" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="M54" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B55" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C55" t="s">
         <v>100</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E55" t="s">
-        <v>85</v>
+        <v>326</v>
       </c>
       <c r="F55" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G55" t="s">
+        <v>328</v>
+      </c>
+      <c r="H55" t="s">
+        <v>41</v>
+      </c>
+      <c r="I55" t="s">
+        <v>50</v>
+      </c>
+      <c r="J55" t="s">
+        <v>330</v>
+      </c>
+      <c r="K55" t="s">
+        <v>15</v>
+      </c>
+      <c r="L55" t="s">
+        <v>329</v>
+      </c>
+      <c r="M55" t="s">
         <v>21</v>
       </c>
-      <c r="H55" t="s">
-        <v>43</v>
-      </c>
-      <c r="I55" t="s">
-        <v>61</v>
-      </c>
-      <c r="J55" t="s">
-        <v>338</v>
-      </c>
-      <c r="K55" t="s">
-        <v>15</v>
-      </c>
-      <c r="L55" t="s">
-        <v>337</v>
-      </c>
-      <c r="M55" t="s">
-        <v>23</v>
-      </c>
       <c r="N55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B56" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D56" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="E56" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F56" t="s">
-        <v>66</v>
+        <v>334</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I56" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J56" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="K56" t="s">
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="M56" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="N56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B57" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="E57" t="s">
-        <v>101</v>
+        <v>339</v>
       </c>
       <c r="F57" t="s">
-        <v>66</v>
+        <v>340</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H57" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I57" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="J57" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="K57" t="s">
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="M57" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B58" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C58" t="s">
         <v>100</v>
       </c>
       <c r="D58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E58" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F58" t="s">
-        <v>312</v>
+        <v>96</v>
       </c>
       <c r="G58" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="H58" t="s">
+        <v>41</v>
+      </c>
+      <c r="I58" t="s">
         <v>43</v>
       </c>
-      <c r="I58" t="s">
-        <v>34</v>
-      </c>
       <c r="J58" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="K58" t="s">
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C59" t="s">
         <v>100</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F59" t="s">
-        <v>66</v>
+        <v>349</v>
       </c>
       <c r="G59" t="s">
-        <v>246</v>
+        <v>350</v>
       </c>
       <c r="H59" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I59" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J59" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="K59" t="s">
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>353</v>
+      </c>
+      <c r="B60" t="s">
+        <v>354</v>
+      </c>
+      <c r="C60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" t="s">
+        <v>95</v>
+      </c>
+      <c r="E60" t="s">
+        <v>355</v>
+      </c>
+      <c r="F60" t="s">
+        <v>96</v>
+      </c>
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" t="s">
+        <v>51</v>
+      </c>
+      <c r="J60" t="s">
         <v>357</v>
       </c>
-      <c r="B60" t="s">
-        <v>358</v>
-      </c>
-      <c r="C60" t="s">
-        <v>58</v>
-      </c>
-      <c r="D60" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" t="s">
-        <v>271</v>
-      </c>
-      <c r="F60" t="s">
-        <v>359</v>
-      </c>
-      <c r="G60" t="s">
-        <v>273</v>
-      </c>
-      <c r="H60" t="s">
-        <v>43</v>
-      </c>
-      <c r="I60" t="s">
-        <v>35</v>
-      </c>
-      <c r="J60" t="s">
-        <v>361</v>
-      </c>
       <c r="K60" t="s">
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="M60" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="N60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B61" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C61" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E61" t="s">
-        <v>271</v>
+        <v>360</v>
       </c>
       <c r="F61" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G61" t="s">
-        <v>273</v>
+        <v>362</v>
       </c>
       <c r="H61" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I61" t="s">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="J61" t="s">
+        <v>364</v>
+      </c>
+      <c r="K61" t="s">
+        <v>15</v>
+      </c>
+      <c r="L61" t="s">
         <v>363</v>
       </c>
-      <c r="K61" t="s">
-        <v>362</v>
-      </c>
-      <c r="L61" t="s">
-        <v>360</v>
-      </c>
       <c r="M61" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B62" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C62" t="s">
         <v>100</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E62" t="s">
-        <v>85</v>
+        <v>308</v>
       </c>
       <c r="F62" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G62" t="s">
-        <v>367</v>
+        <v>37</v>
       </c>
       <c r="H62" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I62" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="J62" t="s">
+        <v>369</v>
+      </c>
+      <c r="K62" t="s">
+        <v>15</v>
+      </c>
+      <c r="L62" t="s">
         <v>368</v>
       </c>
-      <c r="K62" t="s">
-        <v>15</v>
-      </c>
-      <c r="L62" t="s">
-        <v>87</v>
-      </c>
       <c r="M62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B63" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C63" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E63" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F63" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G63" t="s">
-        <v>373</v>
+        <v>37</v>
       </c>
       <c r="H63" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="I63" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="J63" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K63" t="s">
-        <v>15</v>
+        <v>376</v>
       </c>
       <c r="L63" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="M63" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B64" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C64" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E64" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F64" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G64" t="s">
-        <v>373</v>
+        <v>37</v>
       </c>
       <c r="H64" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I64" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="J64" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K64" t="s">
-        <v>376</v>
+        <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="M64" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N64" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B65" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C65" t="s">
         <v>100</v>
       </c>
       <c r="D65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E65" t="s">
-        <v>371</v>
+        <v>308</v>
       </c>
       <c r="F65" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="G65" t="s">
-        <v>373</v>
+        <v>37</v>
       </c>
       <c r="H65" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I65" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="J65" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="K65" t="s">
-        <v>378</v>
+        <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="M65" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B66" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C66" t="s">
         <v>100</v>
       </c>
       <c r="D66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>385</v>
       </c>
       <c r="F66" t="s">
-        <v>97</v>
+        <v>386</v>
       </c>
       <c r="G66" t="s">
-        <v>367</v>
+        <v>220</v>
       </c>
       <c r="H66" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I66" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="J66" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="K66" t="s">
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="M66" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B67" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C67" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D67" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="E67" t="s">
-        <v>386</v>
+        <v>91</v>
       </c>
       <c r="F67" t="s">
-        <v>387</v>
+        <v>74</v>
       </c>
       <c r="G67" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="H67" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I67" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="J67" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K67" t="s">
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M67" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="N67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B68" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C68" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E68" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
       <c r="F68" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G68" t="s">
-        <v>40</v>
+        <v>285</v>
       </c>
       <c r="H68" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I68" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J68" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K68" t="s">
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M68" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N68" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>393</v>
+      </c>
+      <c r="B69" t="s">
+        <v>394</v>
+      </c>
+      <c r="C69" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" t="s">
+        <v>283</v>
+      </c>
+      <c r="F69" t="s">
         <v>395</v>
       </c>
-      <c r="B69" t="s">
+      <c r="G69" t="s">
+        <v>285</v>
+      </c>
+      <c r="H69" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" t="s">
+        <v>39</v>
+      </c>
+      <c r="J69" t="s">
+        <v>399</v>
+      </c>
+      <c r="K69" t="s">
+        <v>398</v>
+      </c>
+      <c r="L69" t="s">
         <v>396</v>
       </c>
-      <c r="C69" t="s">
-        <v>58</v>
-      </c>
-      <c r="D69" t="s">
-        <v>96</v>
-      </c>
-      <c r="E69" t="s">
-        <v>397</v>
-      </c>
-      <c r="F69" t="s">
-        <v>398</v>
-      </c>
-      <c r="G69" t="s">
-        <v>15</v>
-      </c>
-      <c r="H69" t="s">
-        <v>43</v>
-      </c>
-      <c r="I69" t="s">
-        <v>27</v>
-      </c>
-      <c r="J69" t="s">
-        <v>400</v>
-      </c>
-      <c r="K69" t="s">
-        <v>15</v>
-      </c>
-      <c r="L69" t="s">
-        <v>399</v>
-      </c>
       <c r="M69" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="N69" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>400</v>
+      </c>
+      <c r="B70" t="s">
         <v>401</v>
-      </c>
-      <c r="B70" t="s">
-        <v>402</v>
       </c>
       <c r="C70" t="s">
         <v>100</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E70" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G70" t="s">
-        <v>367</v>
+        <v>328</v>
       </c>
       <c r="H70" t="s">
+        <v>41</v>
+      </c>
+      <c r="I70" t="s">
         <v>43</v>
       </c>
-      <c r="I70" t="s">
-        <v>34</v>
-      </c>
       <c r="J70" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K70" t="s">
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M70" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>404</v>
+      </c>
+      <c r="B71" t="s">
         <v>405</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
+        <v>57</v>
+      </c>
+      <c r="D71" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" t="s">
         <v>406</v>
-      </c>
-      <c r="C71" t="s">
-        <v>100</v>
-      </c>
-      <c r="D71" t="s">
-        <v>18</v>
-      </c>
-      <c r="E71" t="s">
-        <v>85</v>
       </c>
       <c r="F71" t="s">
         <v>407</v>
       </c>
       <c r="G71" t="s">
-        <v>313</v>
+        <v>103</v>
       </c>
       <c r="H71" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I71" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J71" t="s">
         <v>409</v>
@@ -5325,10 +5220,10 @@
         <v>408</v>
       </c>
       <c r="M71" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N71" t="s">
-        <v>248</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -5342,330 +5237,330 @@
         <v>100</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E72" t="s">
+        <v>91</v>
+      </c>
+      <c r="F72" t="s">
+        <v>327</v>
+      </c>
+      <c r="G72" t="s">
+        <v>350</v>
+      </c>
+      <c r="H72" t="s">
+        <v>41</v>
+      </c>
+      <c r="I72" t="s">
+        <v>43</v>
+      </c>
+      <c r="J72" t="s">
+        <v>413</v>
+      </c>
+      <c r="K72" t="s">
+        <v>15</v>
+      </c>
+      <c r="L72" t="s">
         <v>412</v>
       </c>
-      <c r="F72" t="s">
-        <v>59</v>
-      </c>
-      <c r="G72" t="s">
-        <v>144</v>
-      </c>
-      <c r="H72" t="s">
-        <v>43</v>
-      </c>
-      <c r="I72" t="s">
-        <v>33</v>
-      </c>
-      <c r="J72" t="s">
-        <v>414</v>
-      </c>
-      <c r="K72" t="s">
-        <v>15</v>
-      </c>
-      <c r="L72" t="s">
-        <v>413</v>
-      </c>
       <c r="M72" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N72" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>414</v>
+      </c>
+      <c r="B73" t="s">
         <v>415</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
+        <v>57</v>
+      </c>
+      <c r="D73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" t="s">
+        <v>286</v>
+      </c>
+      <c r="F73" t="s">
+        <v>407</v>
+      </c>
+      <c r="G73" t="s">
+        <v>103</v>
+      </c>
+      <c r="H73" t="s">
+        <v>41</v>
+      </c>
+      <c r="I73" t="s">
+        <v>42</v>
+      </c>
+      <c r="J73" t="s">
+        <v>417</v>
+      </c>
+      <c r="K73" t="s">
+        <v>15</v>
+      </c>
+      <c r="L73" t="s">
         <v>416</v>
       </c>
-      <c r="C73" t="s">
-        <v>100</v>
-      </c>
-      <c r="D73" t="s">
-        <v>18</v>
-      </c>
-      <c r="E73" t="s">
-        <v>371</v>
-      </c>
-      <c r="F73" t="s">
-        <v>417</v>
-      </c>
-      <c r="G73" t="s">
-        <v>373</v>
-      </c>
-      <c r="H73" t="s">
-        <v>43</v>
-      </c>
-      <c r="I73" t="s">
-        <v>140</v>
-      </c>
-      <c r="J73" t="s">
-        <v>421</v>
-      </c>
-      <c r="K73" t="s">
-        <v>15</v>
-      </c>
-      <c r="L73" t="s">
-        <v>418</v>
-      </c>
       <c r="M73" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N73" t="s">
-        <v>248</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B74" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C74" t="s">
         <v>100</v>
       </c>
       <c r="D74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E74" t="s">
-        <v>371</v>
+        <v>420</v>
       </c>
       <c r="F74" t="s">
-        <v>417</v>
+        <v>58</v>
       </c>
       <c r="G74" t="s">
-        <v>373</v>
+        <v>127</v>
       </c>
       <c r="H74" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I74" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="J74" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K74" t="s">
-        <v>420</v>
+        <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M74" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N74" t="s">
-        <v>248</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B75" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C75" t="s">
         <v>100</v>
       </c>
       <c r="D75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E75" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F75" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G75" t="s">
-        <v>246</v>
+        <v>427</v>
       </c>
       <c r="H75" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I75" t="s">
+        <v>173</v>
+      </c>
+      <c r="J75" t="s">
+        <v>431</v>
+      </c>
+      <c r="K75" t="s">
+        <v>15</v>
+      </c>
+      <c r="L75" t="s">
         <v>428</v>
       </c>
-      <c r="J75" t="s">
-        <v>427</v>
-      </c>
-      <c r="K75" t="s">
-        <v>15</v>
-      </c>
-      <c r="L75" t="s">
-        <v>426</v>
-      </c>
       <c r="M75" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N75" t="s">
-        <v>24</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B76" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C76" t="s">
         <v>100</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E76" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F76" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G76" t="s">
-        <v>246</v>
+        <v>427</v>
       </c>
       <c r="H76" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="I76" t="s">
+        <v>68</v>
+      </c>
+      <c r="J76" t="s">
         <v>429</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>430</v>
       </c>
-      <c r="K76" t="s">
-        <v>15</v>
-      </c>
       <c r="L76" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M76" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N76" t="s">
-        <v>24</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B77" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C77" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E77" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="F77" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G77" t="s">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="H77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I77" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J77" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K77" t="s">
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M77" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N77" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B78" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C78" t="s">
         <v>100</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E78" t="s">
-        <v>438</v>
+        <v>91</v>
       </c>
       <c r="F78" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G78" t="s">
-        <v>281</v>
+        <v>350</v>
       </c>
       <c r="H78" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I78" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="J78" t="s">
+        <v>442</v>
+      </c>
+      <c r="K78" t="s">
+        <v>15</v>
+      </c>
+      <c r="L78" t="s">
         <v>441</v>
       </c>
-      <c r="K78" t="s">
-        <v>15</v>
-      </c>
-      <c r="L78" t="s">
-        <v>440</v>
-      </c>
       <c r="M78" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N78" t="s">
-        <v>60</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B79" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D79" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E79" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F79" t="s">
-        <v>445</v>
+        <v>74</v>
       </c>
       <c r="G79" t="s">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I79" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J79" t="s">
         <v>447</v>
@@ -5677,10 +5572,10 @@
         <v>446</v>
       </c>
       <c r="M79" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
@@ -5694,37 +5589,37 @@
         <v>100</v>
       </c>
       <c r="D80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E80" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F80" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G80" t="s">
-        <v>246</v>
+        <v>427</v>
       </c>
       <c r="H80" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I80" t="s">
-        <v>428</v>
+        <v>173</v>
       </c>
       <c r="J80" t="s">
+        <v>453</v>
+      </c>
+      <c r="K80" t="s">
+        <v>15</v>
+      </c>
+      <c r="L80" t="s">
         <v>451</v>
       </c>
-      <c r="K80" t="s">
-        <v>15</v>
-      </c>
-      <c r="L80" t="s">
-        <v>450</v>
-      </c>
       <c r="M80" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N80" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
@@ -5738,286 +5633,286 @@
         <v>100</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E81" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F81" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G81" t="s">
-        <v>246</v>
+        <v>427</v>
       </c>
       <c r="H81" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="I81" t="s">
-        <v>429</v>
+        <v>68</v>
       </c>
       <c r="J81" t="s">
+        <v>454</v>
+      </c>
+      <c r="K81" t="s">
         <v>452</v>
       </c>
-      <c r="K81" t="s">
-        <v>15</v>
-      </c>
       <c r="L81" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M81" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N81" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B82" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C82" t="s">
         <v>100</v>
       </c>
       <c r="D82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E82" t="s">
-        <v>323</v>
+        <v>425</v>
       </c>
       <c r="F82" t="s">
+        <v>450</v>
+      </c>
+      <c r="G82" t="s">
+        <v>427</v>
+      </c>
+      <c r="H82" t="s">
+        <v>26</v>
+      </c>
+      <c r="I82" t="s">
+        <v>68</v>
+      </c>
+      <c r="J82" t="s">
         <v>455</v>
       </c>
-      <c r="G82" t="s">
-        <v>40</v>
-      </c>
-      <c r="H82" t="s">
-        <v>43</v>
-      </c>
-      <c r="I82" t="s">
-        <v>33</v>
-      </c>
-      <c r="J82" t="s">
-        <v>457</v>
-      </c>
       <c r="K82" t="s">
-        <v>15</v>
+        <v>454</v>
       </c>
       <c r="L82" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="M82" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N82" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>456</v>
+      </c>
+      <c r="B83" t="s">
+        <v>457</v>
+      </c>
+      <c r="C83" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83" t="s">
+        <v>95</v>
+      </c>
+      <c r="E83" t="s">
+        <v>406</v>
+      </c>
+      <c r="F83" t="s">
         <v>458</v>
       </c>
-      <c r="B83" t="s">
+      <c r="G83" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" t="s">
+        <v>51</v>
+      </c>
+      <c r="J83" t="s">
+        <v>460</v>
+      </c>
+      <c r="K83" t="s">
+        <v>15</v>
+      </c>
+      <c r="L83" t="s">
         <v>459</v>
       </c>
-      <c r="C83" t="s">
-        <v>58</v>
-      </c>
-      <c r="D83" t="s">
-        <v>18</v>
-      </c>
-      <c r="E83" t="s">
-        <v>444</v>
-      </c>
-      <c r="F83" t="s">
-        <v>460</v>
-      </c>
-      <c r="G83" t="s">
-        <v>40</v>
-      </c>
-      <c r="H83" t="s">
-        <v>51</v>
-      </c>
-      <c r="I83" t="s">
-        <v>25</v>
-      </c>
-      <c r="J83" t="s">
-        <v>462</v>
-      </c>
-      <c r="K83" t="s">
-        <v>463</v>
-      </c>
-      <c r="L83" t="s">
-        <v>461</v>
-      </c>
       <c r="M83" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="N83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B84" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E84" t="s">
-        <v>444</v>
+        <v>372</v>
       </c>
       <c r="F84" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="G84" t="s">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="H84" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I84" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J84" t="s">
+        <v>465</v>
+      </c>
+      <c r="K84" t="s">
+        <v>15</v>
+      </c>
+      <c r="L84" t="s">
         <v>464</v>
       </c>
-      <c r="K84" t="s">
-        <v>15</v>
-      </c>
-      <c r="L84" t="s">
-        <v>461</v>
-      </c>
       <c r="M84" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N84" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B85" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C85" t="s">
         <v>100</v>
       </c>
       <c r="D85" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E85" t="s">
-        <v>467</v>
+        <v>91</v>
       </c>
       <c r="F85" t="s">
+        <v>327</v>
+      </c>
+      <c r="G85" t="s">
+        <v>350</v>
+      </c>
+      <c r="H85" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" t="s">
+        <v>469</v>
+      </c>
+      <c r="K85" t="s">
+        <v>15</v>
+      </c>
+      <c r="L85" t="s">
         <v>468</v>
       </c>
-      <c r="G85" t="s">
-        <v>214</v>
-      </c>
-      <c r="H85" t="s">
-        <v>43</v>
-      </c>
-      <c r="I85" t="s">
-        <v>33</v>
-      </c>
-      <c r="J85" t="s">
-        <v>470</v>
-      </c>
-      <c r="K85" t="s">
-        <v>15</v>
-      </c>
-      <c r="L85" t="s">
-        <v>469</v>
-      </c>
       <c r="M85" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>470</v>
+      </c>
+      <c r="B86" t="s">
         <v>471</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" t="s">
+        <v>96</v>
+      </c>
+      <c r="G86" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" t="s">
+        <v>52</v>
+      </c>
+      <c r="J86" t="s">
+        <v>473</v>
+      </c>
+      <c r="K86" t="s">
+        <v>15</v>
+      </c>
+      <c r="L86" t="s">
         <v>472</v>
       </c>
-      <c r="C86" t="s">
-        <v>58</v>
-      </c>
-      <c r="D86" t="s">
-        <v>18</v>
-      </c>
-      <c r="E86" t="s">
-        <v>274</v>
-      </c>
-      <c r="F86" t="s">
-        <v>433</v>
-      </c>
-      <c r="G86" t="s">
-        <v>120</v>
-      </c>
-      <c r="H86" t="s">
-        <v>43</v>
-      </c>
-      <c r="I86" t="s">
-        <v>35</v>
-      </c>
-      <c r="J86" t="s">
-        <v>474</v>
-      </c>
-      <c r="K86" t="s">
-        <v>15</v>
-      </c>
-      <c r="L86" t="s">
-        <v>473</v>
-      </c>
       <c r="M86" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N86" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>474</v>
+      </c>
+      <c r="B87" t="s">
         <v>475</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" t="s">
         <v>476</v>
       </c>
-      <c r="C87" t="s">
-        <v>58</v>
-      </c>
-      <c r="D87" t="s">
-        <v>64</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>477</v>
       </c>
-      <c r="F87" t="s">
-        <v>97</v>
-      </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>427</v>
       </c>
       <c r="H87" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I87" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J87" t="s">
         <v>479</v>
@@ -6029,10 +5924,10 @@
         <v>478</v>
       </c>
       <c r="M87" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="N87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
@@ -6043,968 +5938,616 @@
         <v>481</v>
       </c>
       <c r="C88" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E88" t="s">
-        <v>271</v>
+        <v>482</v>
       </c>
       <c r="F88" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G88" t="s">
-        <v>354</v>
+        <v>15</v>
       </c>
       <c r="H88" t="s">
+        <v>41</v>
+      </c>
+      <c r="I88" t="s">
         <v>43</v>
       </c>
-      <c r="I88" t="s">
-        <v>35</v>
-      </c>
       <c r="J88" t="s">
+        <v>485</v>
+      </c>
+      <c r="K88" t="s">
+        <v>15</v>
+      </c>
+      <c r="L88" t="s">
         <v>484</v>
       </c>
-      <c r="K88" t="s">
-        <v>15</v>
-      </c>
-      <c r="L88" t="s">
-        <v>483</v>
-      </c>
       <c r="M88" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N88" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B89" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C89" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E89" t="s">
-        <v>271</v>
+        <v>488</v>
       </c>
       <c r="F89" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="G89" t="s">
-        <v>354</v>
+        <v>37</v>
       </c>
       <c r="H89" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I89" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J89" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="K89" t="s">
-        <v>485</v>
+        <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="M89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N89" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B90" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C90" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" t="s">
         <v>18</v>
       </c>
-      <c r="E90" t="s">
-        <v>85</v>
-      </c>
       <c r="F90" t="s">
-        <v>407</v>
+        <v>96</v>
       </c>
       <c r="G90" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I90" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="J90" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="K90" t="s">
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M90" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N90" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B91" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C91" t="s">
         <v>100</v>
       </c>
       <c r="D91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E91" t="s">
-        <v>85</v>
+        <v>498</v>
       </c>
       <c r="F91" t="s">
-        <v>312</v>
+        <v>498</v>
       </c>
       <c r="G91" t="s">
-        <v>374</v>
+        <v>65</v>
       </c>
       <c r="H91" t="s">
+        <v>41</v>
+      </c>
+      <c r="I91" t="s">
         <v>43</v>
       </c>
-      <c r="I91" t="s">
-        <v>61</v>
-      </c>
       <c r="J91" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="K91" t="s">
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="M91" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N91" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B92" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C92" t="s">
         <v>100</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E92" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="F92" t="s">
-        <v>312</v>
+        <v>96</v>
       </c>
       <c r="G92" t="s">
-        <v>367</v>
+        <v>504</v>
       </c>
       <c r="H92" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I92" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J92" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="K92" t="s">
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="M92" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N92" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B93" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C93" t="s">
         <v>100</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E93" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F93" t="s">
-        <v>503</v>
+        <v>58</v>
       </c>
       <c r="G93" t="s">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="H93" t="s">
+        <v>41</v>
+      </c>
+      <c r="I93" t="s">
         <v>43</v>
       </c>
-      <c r="I93" t="s">
-        <v>34</v>
-      </c>
       <c r="J93" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="K93" t="s">
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="M93" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N93" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B94" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D94" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>514</v>
       </c>
       <c r="F94" t="s">
-        <v>97</v>
+        <v>514</v>
       </c>
       <c r="G94" t="s">
-        <v>15</v>
+        <v>515</v>
       </c>
       <c r="H94" t="s">
+        <v>41</v>
+      </c>
+      <c r="I94" t="s">
         <v>43</v>
       </c>
-      <c r="I94" t="s">
-        <v>34</v>
-      </c>
       <c r="J94" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="K94" t="s">
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="M94" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N94" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B95" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D95" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E95" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F95" t="s">
-        <v>513</v>
+        <v>58</v>
       </c>
       <c r="G95" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="H95" t="s">
+        <v>41</v>
+      </c>
+      <c r="I95" t="s">
         <v>43</v>
       </c>
-      <c r="I95" t="s">
-        <v>34</v>
-      </c>
       <c r="J95" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="K95" t="s">
         <v>15</v>
       </c>
       <c r="L95" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="M95" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N95" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B96" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E96" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F96" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="G96" t="s">
-        <v>214</v>
+        <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I96" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J96" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K96" t="s">
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="M96" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N96" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B97" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C97" t="s">
         <v>100</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E97" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="F97" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G97" t="s">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="H97" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I97" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J97" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="K97" t="s">
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="M97" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="N97" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="B98" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="C98" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E98" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F98" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G98" t="s">
-        <v>530</v>
+        <v>15</v>
       </c>
       <c r="H98" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I98" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="J98" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="K98" t="s">
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="M98" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N98" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B99" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C99" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E99" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F99" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="G99" t="s">
-        <v>373</v>
+        <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I99" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="J99" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="K99" t="s">
         <v>15</v>
       </c>
       <c r="L99" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="M99" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N99" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B100" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C100" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D100" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="E100" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="F100" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="G100" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H100" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I100" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="J100" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="K100" t="s">
         <v>15</v>
       </c>
       <c r="L100" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="M100" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="N100" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E101" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="F101" t="s">
-        <v>547</v>
+        <v>367</v>
       </c>
       <c r="G101" t="s">
-        <v>367</v>
+        <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I101" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J101" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="K101" t="s">
         <v>15</v>
       </c>
       <c r="L101" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="M101" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N101" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>550</v>
-      </c>
-      <c r="B102" t="s">
-        <v>551</v>
-      </c>
-      <c r="C102" t="s">
-        <v>16</v>
-      </c>
-      <c r="D102" t="s">
-        <v>18</v>
-      </c>
-      <c r="E102" t="s">
-        <v>552</v>
-      </c>
-      <c r="F102" t="s">
-        <v>97</v>
-      </c>
-      <c r="G102" t="s">
-        <v>15</v>
-      </c>
-      <c r="H102" t="s">
-        <v>43</v>
-      </c>
-      <c r="I102" t="s">
-        <v>34</v>
-      </c>
-      <c r="J102" t="s">
-        <v>554</v>
-      </c>
-      <c r="K102" t="s">
-        <v>15</v>
-      </c>
-      <c r="L102" t="s">
-        <v>553</v>
-      </c>
-      <c r="M102" t="s">
-        <v>80</v>
-      </c>
-      <c r="N102" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>555</v>
-      </c>
-      <c r="B103" t="s">
-        <v>556</v>
-      </c>
-      <c r="C103" t="s">
-        <v>100</v>
-      </c>
-      <c r="D103" t="s">
-        <v>18</v>
-      </c>
-      <c r="E103" t="s">
-        <v>557</v>
-      </c>
-      <c r="F103" t="s">
-        <v>558</v>
-      </c>
-      <c r="G103" t="s">
-        <v>281</v>
-      </c>
-      <c r="H103" t="s">
-        <v>43</v>
-      </c>
-      <c r="I103" t="s">
-        <v>34</v>
-      </c>
-      <c r="J103" t="s">
-        <v>560</v>
-      </c>
-      <c r="K103" t="s">
-        <v>15</v>
-      </c>
-      <c r="L103" t="s">
-        <v>559</v>
-      </c>
-      <c r="M103" t="s">
-        <v>80</v>
-      </c>
-      <c r="N103" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>561</v>
-      </c>
-      <c r="B104" t="s">
-        <v>562</v>
-      </c>
-      <c r="C104" t="s">
-        <v>100</v>
-      </c>
-      <c r="D104" t="s">
-        <v>18</v>
-      </c>
-      <c r="E104" t="s">
-        <v>563</v>
-      </c>
-      <c r="F104" t="s">
-        <v>563</v>
-      </c>
-      <c r="G104" t="s">
-        <v>367</v>
-      </c>
-      <c r="H104" t="s">
-        <v>43</v>
-      </c>
-      <c r="I104" t="s">
-        <v>34</v>
-      </c>
-      <c r="J104" t="s">
-        <v>565</v>
-      </c>
-      <c r="K104" t="s">
-        <v>15</v>
-      </c>
-      <c r="L104" t="s">
-        <v>564</v>
-      </c>
-      <c r="M104" t="s">
-        <v>80</v>
-      </c>
-      <c r="N104" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>566</v>
-      </c>
-      <c r="B105" t="s">
-        <v>567</v>
-      </c>
-      <c r="C105" t="s">
-        <v>100</v>
-      </c>
-      <c r="D105" t="s">
-        <v>18</v>
-      </c>
-      <c r="E105" t="s">
-        <v>502</v>
-      </c>
-      <c r="F105" t="s">
-        <v>503</v>
-      </c>
-      <c r="G105" t="s">
-        <v>78</v>
-      </c>
-      <c r="H105" t="s">
-        <v>43</v>
-      </c>
-      <c r="I105" t="s">
-        <v>34</v>
-      </c>
-      <c r="J105" t="s">
-        <v>569</v>
-      </c>
-      <c r="K105" t="s">
-        <v>15</v>
-      </c>
-      <c r="L105" t="s">
-        <v>568</v>
-      </c>
-      <c r="M105" t="s">
-        <v>23</v>
-      </c>
-      <c r="N105" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>570</v>
-      </c>
-      <c r="B106" t="s">
-        <v>571</v>
-      </c>
-      <c r="C106" t="s">
-        <v>100</v>
-      </c>
-      <c r="D106" t="s">
-        <v>18</v>
-      </c>
-      <c r="E106" t="s">
-        <v>572</v>
-      </c>
-      <c r="F106" t="s">
-        <v>573</v>
-      </c>
-      <c r="G106" t="s">
-        <v>373</v>
-      </c>
-      <c r="H106" t="s">
-        <v>43</v>
-      </c>
-      <c r="I106" t="s">
-        <v>34</v>
-      </c>
-      <c r="J106" t="s">
-        <v>575</v>
-      </c>
-      <c r="K106" t="s">
-        <v>15</v>
-      </c>
-      <c r="L106" t="s">
-        <v>574</v>
-      </c>
-      <c r="M106" t="s">
-        <v>23</v>
-      </c>
-      <c r="N106" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>576</v>
-      </c>
-      <c r="B107" t="s">
-        <v>577</v>
-      </c>
-      <c r="C107" t="s">
-        <v>16</v>
-      </c>
-      <c r="D107" t="s">
-        <v>18</v>
-      </c>
-      <c r="E107" t="s">
-        <v>19</v>
-      </c>
-      <c r="F107" t="s">
-        <v>97</v>
-      </c>
-      <c r="G107" t="s">
-        <v>15</v>
-      </c>
-      <c r="H107" t="s">
-        <v>43</v>
-      </c>
-      <c r="I107" t="s">
-        <v>34</v>
-      </c>
-      <c r="J107" t="s">
-        <v>579</v>
-      </c>
-      <c r="K107" t="s">
-        <v>15</v>
-      </c>
-      <c r="L107" t="s">
-        <v>578</v>
-      </c>
-      <c r="M107" t="s">
-        <v>80</v>
-      </c>
-      <c r="N107" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>580</v>
-      </c>
-      <c r="B108" t="s">
-        <v>581</v>
-      </c>
-      <c r="C108" t="s">
-        <v>16</v>
-      </c>
-      <c r="D108" t="s">
-        <v>64</v>
-      </c>
-      <c r="E108" t="s">
-        <v>582</v>
-      </c>
-      <c r="F108" t="s">
-        <v>455</v>
-      </c>
-      <c r="G108" t="s">
-        <v>15</v>
-      </c>
-      <c r="H108" t="s">
-        <v>43</v>
-      </c>
-      <c r="I108" t="s">
-        <v>61</v>
-      </c>
-      <c r="J108" t="s">
-        <v>584</v>
-      </c>
-      <c r="K108" t="s">
-        <v>15</v>
-      </c>
-      <c r="L108" t="s">
-        <v>583</v>
-      </c>
-      <c r="M108" t="s">
-        <v>70</v>
-      </c>
-      <c r="N108" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>585</v>
-      </c>
-      <c r="B109" t="s">
-        <v>586</v>
-      </c>
-      <c r="C109" t="s">
-        <v>100</v>
-      </c>
-      <c r="D109" t="s">
-        <v>18</v>
-      </c>
-      <c r="E109" t="s">
-        <v>587</v>
-      </c>
-      <c r="F109" t="s">
-        <v>588</v>
-      </c>
-      <c r="G109" t="s">
-        <v>354</v>
-      </c>
-      <c r="H109" t="s">
-        <v>43</v>
-      </c>
-      <c r="I109" t="s">
-        <v>34</v>
-      </c>
-      <c r="J109" t="s">
-        <v>590</v>
-      </c>
-      <c r="K109" t="s">
-        <v>15</v>
-      </c>
-      <c r="L109" t="s">
-        <v>589</v>
-      </c>
-      <c r="M109" t="s">
-        <v>80</v>
-      </c>
-      <c r="N109" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N109"/>
+  <autoFilter ref="A1:N101"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NLCX3311\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NLCX3311\Pictures\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$95</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="527">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -110,6 +110,9 @@
     <t>02/06/2025 14:26:16</t>
   </si>
   <si>
+    <t>Parametrage facturation</t>
+  </si>
+  <si>
     <t>Réassigné</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
     <t>07/04/2025 18:04:16</t>
   </si>
   <si>
+    <t>IP Delivery: Validation information</t>
+  </si>
+  <si>
     <t>Offert</t>
   </si>
   <si>
@@ -200,6 +206,9 @@
     <t>28/08/2025 17:43:52</t>
   </si>
   <si>
+    <t>Support IP: Correction</t>
+  </si>
+  <si>
     <t>Responsable Zone: Validation Survey</t>
   </si>
   <si>
@@ -321,9 +330,6 @@
   </si>
   <si>
     <t>TREICHVILLE</t>
-  </si>
-  <si>
-    <t>DIE : Configuration IMS</t>
   </si>
   <si>
     <t>46532522</t>
@@ -402,160 +408,115 @@
     <t>06/11/2025 15:29:33</t>
   </si>
   <si>
-    <t>47653333</t>
-  </si>
-  <si>
-    <t>18/07/2025 12:45:02</t>
+    <t>47885035</t>
+  </si>
+  <si>
+    <t>23/07/2025 14:30:04</t>
   </si>
   <si>
     <t>CAISSE NATIONALE DE PREVOYANCE SOCIALE</t>
   </si>
   <si>
+    <t>COCODY ANGRE DJIBI</t>
+  </si>
+  <si>
+    <t>2720305170</t>
+  </si>
+  <si>
+    <t>31/03/2026 10:15:08</t>
+  </si>
+  <si>
+    <t>47658350</t>
+  </si>
+  <si>
+    <t>18/07/2025 13:30:49</t>
+  </si>
+  <si>
     <t>SAN-PEDRO//VOIE INCONNUE/SAN PEDRO</t>
   </si>
   <si>
+    <t>5M</t>
+  </si>
+  <si>
+    <t>SYTHD240176</t>
+  </si>
+  <si>
+    <t>07/04/2026 09:30:05</t>
+  </si>
+  <si>
+    <t>BO Homologation: Mise en service BSCS</t>
+  </si>
+  <si>
+    <t>07/04/2026 09:30:07</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie BSCS</t>
+  </si>
+  <si>
+    <t>BO Homologation: Mise en service GAIA</t>
+  </si>
+  <si>
+    <t>47261410</t>
+  </si>
+  <si>
+    <t>10/07/2025 15:09:58</t>
+  </si>
+  <si>
+    <t>PROJET D'APPUI A LA SECURITE DE L'EAU ET L'ASSAINISSEMENT</t>
+  </si>
+  <si>
+    <t>ABIDJAN COCODY</t>
+  </si>
+  <si>
+    <t>2722228685</t>
+  </si>
+  <si>
+    <t>02/09/2025 18:11:09</t>
+  </si>
+  <si>
+    <t>47648026</t>
+  </si>
+  <si>
+    <t>18/07/2025 11:14:46</t>
+  </si>
+  <si>
+    <t>SAN PEDRO</t>
+  </si>
+  <si>
     <t>20M</t>
   </si>
   <si>
-    <t>BUVPN150689</t>
-  </si>
-  <si>
-    <t>14/08/2025 09:23:10</t>
-  </si>
-  <si>
-    <t>47885035</t>
-  </si>
-  <si>
-    <t>23/07/2025 14:30:04</t>
-  </si>
-  <si>
-    <t>COCODY ANGRE DJIBI</t>
-  </si>
-  <si>
-    <t>2720305170</t>
-  </si>
-  <si>
-    <t>27/08/2025 15:59:17</t>
-  </si>
-  <si>
-    <t>47261410</t>
-  </si>
-  <si>
-    <t>10/07/2025 15:09:58</t>
-  </si>
-  <si>
-    <t>PROJET D'APPUI A LA SECURITE DE L'EAU ET L'ASSAINISSEMENT</t>
-  </si>
-  <si>
-    <t>ABIDJAN COCODY</t>
-  </si>
-  <si>
-    <t>2722228685</t>
-  </si>
-  <si>
-    <t>02/09/2025 18:11:09</t>
-  </si>
-  <si>
-    <t>47878019</t>
-  </si>
-  <si>
-    <t>23/07/2025 12:51:35</t>
+    <t>BUVPN150605</t>
+  </si>
+  <si>
+    <t>01/08/2025 12:49:49</t>
+  </si>
+  <si>
+    <t>48207282</t>
+  </si>
+  <si>
+    <t>30/07/2025 10:08:29</t>
+  </si>
+  <si>
+    <t>VPNLL220035</t>
+  </si>
+  <si>
+    <t>11/12/2025 09:01:38</t>
+  </si>
+  <si>
+    <t>47871834</t>
+  </si>
+  <si>
+    <t>23/07/2025 11:27:13</t>
   </si>
   <si>
     <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY ANGRE DJIBI</t>
   </si>
   <si>
-    <t>BUVPN150600</t>
-  </si>
-  <si>
-    <t>27/08/2025 14:19:45</t>
-  </si>
-  <si>
-    <t>47639322</t>
-  </si>
-  <si>
-    <t>18/07/2025 09:46:15</t>
-  </si>
-  <si>
-    <t>SAN PEDRO</t>
-  </si>
-  <si>
-    <t>2734711025</t>
-  </si>
-  <si>
-    <t>28/08/2025 20:16:23</t>
-  </si>
-  <si>
-    <t>48207282</t>
-  </si>
-  <si>
-    <t>30/07/2025 10:08:29</t>
-  </si>
-  <si>
-    <t>VPNLL220035</t>
-  </si>
-  <si>
-    <t>11/12/2025 09:01:38</t>
-  </si>
-  <si>
-    <t>47648026</t>
-  </si>
-  <si>
-    <t>18/07/2025 11:14:46</t>
-  </si>
-  <si>
-    <t>BUVPN150605</t>
-  </si>
-  <si>
-    <t>01/08/2025 12:49:49</t>
-  </si>
-  <si>
-    <t>48206525</t>
-  </si>
-  <si>
-    <t>30/07/2025 09:58:32</t>
-  </si>
-  <si>
-    <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/TREICHVILLE 0767161532</t>
-  </si>
-  <si>
-    <t>512K</t>
-  </si>
-  <si>
-    <t>VPNLL130015</t>
-  </si>
-  <si>
-    <t>14/01/2026 09:22:01</t>
-  </si>
-  <si>
-    <t>47658350</t>
-  </si>
-  <si>
-    <t>18/07/2025 13:30:49</t>
-  </si>
-  <si>
-    <t>5M</t>
-  </si>
-  <si>
-    <t>SYTHD240176</t>
-  </si>
-  <si>
-    <t>14/08/2025 09:01:02</t>
-  </si>
-  <si>
-    <t>47871834</t>
-  </si>
-  <si>
-    <t>23/07/2025 11:27:13</t>
-  </si>
-  <si>
     <t>SYTHD240171</t>
   </si>
   <si>
-    <t>BO Homologation: Saisie BSCS</t>
-  </si>
-  <si>
-    <t>30/10/2025 14:56:28</t>
+    <t>31/03/2026 19:02:23</t>
   </si>
   <si>
     <t>48419891</t>
@@ -594,6 +555,21 @@
     <t>27/01/2026 11:29:22</t>
   </si>
   <si>
+    <t>51016709</t>
+  </si>
+  <si>
+    <t>24/09/2025 08:43:16</t>
+  </si>
+  <si>
+    <t>ODIENNE//VOIE INCONNUE/ODIENNE</t>
+  </si>
+  <si>
+    <t>VPNLL120010</t>
+  </si>
+  <si>
+    <t>31/03/2026 10:43:05</t>
+  </si>
+  <si>
     <t>50608489</t>
   </si>
   <si>
@@ -609,37 +585,16 @@
     <t>26/09/2025 22:47:49</t>
   </si>
   <si>
-    <t>51016709</t>
-  </si>
-  <si>
-    <t>24/09/2025 08:43:16</t>
-  </si>
-  <si>
-    <t>ODIENNE//VOIE INCONNUE/ODIENNE</t>
-  </si>
-  <si>
-    <t>VPNLL120010</t>
-  </si>
-  <si>
-    <t>14/10/2025 14:27:35</t>
-  </si>
-  <si>
-    <t>51053195</t>
-  </si>
-  <si>
-    <t>24/09/2025 16:13:20</t>
-  </si>
-  <si>
-    <t>DIRECTION GENERALE DES IMPOTS</t>
-  </si>
-  <si>
-    <t>GRAND-LAHOU//VOIE INCONNUE/GRAND LAHOU</t>
-  </si>
-  <si>
-    <t>VPNLL120232</t>
-  </si>
-  <si>
-    <t>10/10/2025 12:19:09</t>
+    <t>50411465</t>
+  </si>
+  <si>
+    <t>12/09/2025 08:45:30</t>
+  </si>
+  <si>
+    <t>SYTHD070012</t>
+  </si>
+  <si>
+    <t>24/10/2025 16:34:01</t>
   </si>
   <si>
     <t>50439713</t>
@@ -654,16 +609,37 @@
     <t>24/10/2025 15:48:07</t>
   </si>
   <si>
-    <t>50411465</t>
-  </si>
-  <si>
-    <t>12/09/2025 08:45:30</t>
-  </si>
-  <si>
-    <t>SYTHD070012</t>
-  </si>
-  <si>
-    <t>24/10/2025 16:34:01</t>
+    <t>51691679</t>
+  </si>
+  <si>
+    <t>07/10/2025 11:10:57</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU//A008 AV NOGUES/PLATEAU AVENUE NOGUES</t>
+  </si>
+  <si>
+    <t>SYTHD200123</t>
+  </si>
+  <si>
+    <t>22/10/2025 12:30:17</t>
+  </si>
+  <si>
+    <t>52558712</t>
+  </si>
+  <si>
+    <t>24/10/2025 15:03:02</t>
+  </si>
+  <si>
+    <t>FONDS INTERNATIONAL POUR LE DEVELOPPEMENT DE LA RETRAITE ACTIVE</t>
+  </si>
+  <si>
+    <t>50M</t>
+  </si>
+  <si>
+    <t>BUVPN230242</t>
+  </si>
+  <si>
+    <t>11/11/2025 16:40:10</t>
   </si>
   <si>
     <t>52090983</t>
@@ -681,55 +657,28 @@
     <t>2721212909</t>
   </si>
   <si>
-    <t>26/02/2026 12:37:40</t>
-  </si>
-  <si>
-    <t>52558712</t>
-  </si>
-  <si>
-    <t>24/10/2025 15:03:02</t>
-  </si>
-  <si>
-    <t>FONDS INTERNATIONAL POUR LE DEVELOPPEMENT DE LA RETRAITE ACTIVE</t>
-  </si>
-  <si>
-    <t>50M</t>
-  </si>
-  <si>
-    <t>BUVPN230242</t>
-  </si>
-  <si>
-    <t>11/11/2025 16:40:10</t>
-  </si>
-  <si>
-    <t>52741559</t>
-  </si>
-  <si>
-    <t>29/10/2025 09:10:21</t>
-  </si>
-  <si>
-    <t>bonoua</t>
-  </si>
-  <si>
-    <t>2721300130</t>
-  </si>
-  <si>
-    <t>25/11/2025 12:54:15</t>
-  </si>
-  <si>
-    <t>51691679</t>
-  </si>
-  <si>
-    <t>07/10/2025 11:10:57</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU//A008 AV NOGUES/PLATEAU AVENUE NOGUES</t>
-  </si>
-  <si>
-    <t>SYTHD200123</t>
-  </si>
-  <si>
-    <t>22/10/2025 12:30:17</t>
+    <t>31/03/2026 16:06:34</t>
+  </si>
+  <si>
+    <t>55994930</t>
+  </si>
+  <si>
+    <t>30/12/2025 15:09:31</t>
+  </si>
+  <si>
+    <t>INTELCIA COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/INTELCA CI, COCODY RIVIERA</t>
+  </si>
+  <si>
+    <t>90M</t>
+  </si>
+  <si>
+    <t>SYTHD170178</t>
+  </si>
+  <si>
+    <t>06/01/2026 19:35:09</t>
   </si>
   <si>
     <t>55980750</t>
@@ -738,9 +687,6 @@
     <t>30/12/2025 12:27:06</t>
   </si>
   <si>
-    <t>INTELCIA COTE D'IVOIRE</t>
-  </si>
-  <si>
     <t>COCODY RIVIERA PALMERAIE SOCOPRIX ROUTE DE BINGERVILLE</t>
   </si>
   <si>
@@ -786,6 +732,18 @@
     <t>20/01/2026 09:11:56</t>
   </si>
   <si>
+    <t>54442992</t>
+  </si>
+  <si>
+    <t>01/12/2025 15:54:10</t>
+  </si>
+  <si>
+    <t>VPNLL150028</t>
+  </si>
+  <si>
+    <t>01/04/2026 09:35:20</t>
+  </si>
+  <si>
     <t>54962571</t>
   </si>
   <si>
@@ -804,42 +762,6 @@
     <t>19/12/2025 15:34:19</t>
   </si>
   <si>
-    <t>55994930</t>
-  </si>
-  <si>
-    <t>30/12/2025 15:09:31</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/INTELCA CI, COCODY RIVIERA</t>
-  </si>
-  <si>
-    <t>SYTHD170178</t>
-  </si>
-  <si>
-    <t>06/01/2026 19:35:09</t>
-  </si>
-  <si>
-    <t>54442992</t>
-  </si>
-  <si>
-    <t>01/12/2025 15:54:10</t>
-  </si>
-  <si>
-    <t>VPNLL150028</t>
-  </si>
-  <si>
-    <t>06/01/2026 19:47:15</t>
-  </si>
-  <si>
-    <t>55167162</t>
-  </si>
-  <si>
-    <t>15/12/2025 09:14:53</t>
-  </si>
-  <si>
-    <t>29/12/2025 15:45:51</t>
-  </si>
-  <si>
     <t>56579652</t>
   </si>
   <si>
@@ -969,18 +891,6 @@
     <t>03/03/2026 09:02:46</t>
   </si>
   <si>
-    <t>58996002</t>
-  </si>
-  <si>
-    <t>26/02/2026 11:30:04</t>
-  </si>
-  <si>
-    <t>2720306611</t>
-  </si>
-  <si>
-    <t>18/03/2026 10:19:10</t>
-  </si>
-  <si>
     <t>57703033</t>
   </si>
   <si>
@@ -1005,6 +915,84 @@
     <t>18/02/2026 15:54:31</t>
   </si>
   <si>
+    <t>57711569</t>
+  </si>
+  <si>
+    <t>03/02/2026 12:49:14</t>
+  </si>
+  <si>
+    <t>BANQUE INTERNATIONALE POUR LE COMMERCE ET L'INDUSTRIE DE CI</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU//VOIE INCONNUE/EXTREMITE  A PLATEAU</t>
+  </si>
+  <si>
+    <t>SYTHD250061</t>
+  </si>
+  <si>
+    <t>18/02/2026 15:55:59</t>
+  </si>
+  <si>
+    <t>18/02/2026 15:56:17</t>
+  </si>
+  <si>
+    <t>28/02/2026 11:00:28</t>
+  </si>
+  <si>
+    <t>58835120</t>
+  </si>
+  <si>
+    <t>23/02/2026 18:13:23</t>
+  </si>
+  <si>
+    <t>EXCELIAM</t>
+  </si>
+  <si>
+    <t>COCODY RIVIERA 3</t>
+  </si>
+  <si>
+    <t>120M</t>
+  </si>
+  <si>
+    <t>SYTHD220085</t>
+  </si>
+  <si>
+    <t>31/03/2026 11:06:07</t>
+  </si>
+  <si>
+    <t>58417809</t>
+  </si>
+  <si>
+    <t>16/02/2026 15:02:05</t>
+  </si>
+  <si>
+    <t>MARCORY</t>
+  </si>
+  <si>
+    <t>BUVPN180204</t>
+  </si>
+  <si>
+    <t>03/03/2026 09:09:32</t>
+  </si>
+  <si>
+    <t>58784601</t>
+  </si>
+  <si>
+    <t>23/02/2026 10:09:18</t>
+  </si>
+  <si>
+    <t>ABIDJAN TREICHVILLE</t>
+  </si>
+  <si>
+    <t>400M</t>
+  </si>
+  <si>
+    <t>BUVPN150481</t>
+  </si>
+  <si>
+    <t>19/03/2026 11:11:26</t>
+  </si>
+  <si>
     <t>58822848</t>
   </si>
   <si>
@@ -1026,24 +1014,6 @@
     <t>24/03/2026 16:08:50</t>
   </si>
   <si>
-    <t>58029496</t>
-  </si>
-  <si>
-    <t>09/02/2026 13:44:17</t>
-  </si>
-  <si>
-    <t>AFRICA SOURCING COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>TREICHVILLE RUE DES THONIERS</t>
-  </si>
-  <si>
-    <t>2721358023</t>
-  </si>
-  <si>
-    <t>16/03/2026 22:18:50</t>
-  </si>
-  <si>
     <t>58480398</t>
   </si>
   <si>
@@ -1062,109 +1032,19 @@
     <t>03/03/2026 09:45:43</t>
   </si>
   <si>
-    <t>58804111</t>
-  </si>
-  <si>
-    <t>23/02/2026 13:19:20</t>
-  </si>
-  <si>
-    <t>BUVPN220135</t>
-  </si>
-  <si>
-    <t>26/02/2026 09:40:55</t>
-  </si>
-  <si>
-    <t>58784601</t>
-  </si>
-  <si>
-    <t>23/02/2026 10:09:18</t>
-  </si>
-  <si>
-    <t>ABIDJAN TREICHVILLE</t>
-  </si>
-  <si>
-    <t>400M</t>
-  </si>
-  <si>
-    <t>BUVPN150481</t>
-  </si>
-  <si>
-    <t>19/03/2026 11:11:26</t>
-  </si>
-  <si>
-    <t>59011477</t>
-  </si>
-  <si>
-    <t>26/02/2026 14:00:03</t>
-  </si>
-  <si>
-    <t>BRIDGE BANK GROUP</t>
-  </si>
-  <si>
-    <t>2721212910</t>
-  </si>
-  <si>
-    <t>25/03/2026 15:30:49</t>
-  </si>
-  <si>
-    <t>58835120</t>
-  </si>
-  <si>
-    <t>23/02/2026 18:13:23</t>
-  </si>
-  <si>
-    <t>EXCELIAM</t>
-  </si>
-  <si>
-    <t>COCODY RIVIERA 3</t>
-  </si>
-  <si>
-    <t>120M</t>
-  </si>
-  <si>
-    <t>SYTHD220085</t>
-  </si>
-  <si>
-    <t>10/03/2026 11:49:03</t>
-  </si>
-  <si>
-    <t>58417809</t>
-  </si>
-  <si>
-    <t>16/02/2026 15:02:05</t>
-  </si>
-  <si>
-    <t>MARCORY</t>
-  </si>
-  <si>
-    <t>BUVPN180204</t>
-  </si>
-  <si>
-    <t>03/03/2026 09:09:32</t>
-  </si>
-  <si>
-    <t>57711569</t>
-  </si>
-  <si>
-    <t>03/02/2026 12:49:14</t>
-  </si>
-  <si>
-    <t>BANQUE INTERNATIONALE POUR LE COMMERCE ET L'INDUSTRIE DE CI</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU//VOIE INCONNUE/EXTREMITE  A PLATEAU</t>
-  </si>
-  <si>
-    <t>SYTHD250061</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:55:59</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:56:17</t>
-  </si>
-  <si>
-    <t>28/02/2026 11:00:28</t>
+    <t>57864191</t>
+  </si>
+  <si>
+    <t>05/02/2026 16:54:42</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM//VOIE INCONNUE/BASSAM VITIB</t>
+  </si>
+  <si>
+    <t>SYTHD230067</t>
+  </si>
+  <si>
+    <t>11/02/2026 19:07:39</t>
   </si>
   <si>
     <t>58427309</t>
@@ -1233,60 +1113,6 @@
     <t>18/02/2026 17:58:51</t>
   </si>
   <si>
-    <t>58805170</t>
-  </si>
-  <si>
-    <t>23/02/2026 13:29:54</t>
-  </si>
-  <si>
-    <t>BUVPN230180</t>
-  </si>
-  <si>
-    <t>26/02/2026 09:41:30</t>
-  </si>
-  <si>
-    <t>58896886</t>
-  </si>
-  <si>
-    <t>24/02/2026 17:16:44</t>
-  </si>
-  <si>
-    <t>STANDARD CHARTERED BANK COTE D'IVOIRE SA</t>
-  </si>
-  <si>
-    <t>GRAND-BASSAM//VOIE INCONNUE/BASSAM VITIB</t>
-  </si>
-  <si>
-    <t>VPNLL120246</t>
-  </si>
-  <si>
-    <t>13/03/2026 10:54:09</t>
-  </si>
-  <si>
-    <t>58810120</t>
-  </si>
-  <si>
-    <t>23/02/2026 14:18:42</t>
-  </si>
-  <si>
-    <t>BUVPN210151</t>
-  </si>
-  <si>
-    <t>26/02/2026 09:47:15</t>
-  </si>
-  <si>
-    <t>57864191</t>
-  </si>
-  <si>
-    <t>05/02/2026 16:54:42</t>
-  </si>
-  <si>
-    <t>SYTHD230067</t>
-  </si>
-  <si>
-    <t>11/02/2026 19:07:39</t>
-  </si>
-  <si>
     <t>58048251</t>
   </si>
   <si>
@@ -1300,6 +1126,18 @@
   </si>
   <si>
     <t>03/03/2026 09:43:56</t>
+  </si>
+  <si>
+    <t>58783980</t>
+  </si>
+  <si>
+    <t>23/02/2026 10:02:01</t>
+  </si>
+  <si>
+    <t>BUVPN220126</t>
+  </si>
+  <si>
+    <t>31/03/2026 13:10:14</t>
   </si>
   <si>
     <t>58680250</t>
@@ -1330,6 +1168,48 @@
     <t>03/03/2026 12:40:11</t>
   </si>
   <si>
+    <t>58810120</t>
+  </si>
+  <si>
+    <t>23/02/2026 14:18:42</t>
+  </si>
+  <si>
+    <t>BUVPN210151</t>
+  </si>
+  <si>
+    <t>07/04/2026 10:05:29</t>
+  </si>
+  <si>
+    <t>59011477</t>
+  </si>
+  <si>
+    <t>26/02/2026 14:00:03</t>
+  </si>
+  <si>
+    <t>BRIDGE BANK GROUP</t>
+  </si>
+  <si>
+    <t>2721212910</t>
+  </si>
+  <si>
+    <t>02/04/2026 10:51:34</t>
+  </si>
+  <si>
+    <t>58896886</t>
+  </si>
+  <si>
+    <t>24/02/2026 17:16:44</t>
+  </si>
+  <si>
+    <t>STANDARD CHARTERED BANK COTE D'IVOIRE SA</t>
+  </si>
+  <si>
+    <t>VPNLL120246</t>
+  </si>
+  <si>
+    <t>13/03/2026 10:54:09</t>
+  </si>
+  <si>
     <t>57670112</t>
   </si>
   <si>
@@ -1347,36 +1227,6 @@
   </si>
   <si>
     <t>10/02/2026 11:22:09</t>
-  </si>
-  <si>
-    <t>59082502</t>
-  </si>
-  <si>
-    <t>27/02/2026 15:19:13</t>
-  </si>
-  <si>
-    <t>//VOIE INCONNUE/AGENCE SIB PLATEAU IMMEUBLE</t>
-  </si>
-  <si>
-    <t>VPNLL090098</t>
-  </si>
-  <si>
-    <t>24/03/2026 16:04:38</t>
-  </si>
-  <si>
-    <t>58488142</t>
-  </si>
-  <si>
-    <t>17/02/2026 16:47:06</t>
-  </si>
-  <si>
-    <t>EGLISE METHODISTE UNIE DE COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>2720211797</t>
-  </si>
-  <si>
-    <t>19/03/2026 11:42:27</t>
   </si>
   <si>
     <t>58680600</t>
@@ -1406,6 +1256,18 @@
     <t>23/02/2026 13:30:36</t>
   </si>
   <si>
+    <t>58805170</t>
+  </si>
+  <si>
+    <t>23/02/2026 13:29:54</t>
+  </si>
+  <si>
+    <t>BUVPN230180</t>
+  </si>
+  <si>
+    <t>07/04/2026 09:06:22</t>
+  </si>
+  <si>
     <t>58895685</t>
   </si>
   <si>
@@ -1436,16 +1298,193 @@
     <t>12/02/2026 19:44:21</t>
   </si>
   <si>
-    <t>58783980</t>
-  </si>
-  <si>
-    <t>23/02/2026 10:02:01</t>
-  </si>
-  <si>
-    <t>BUVPN220126</t>
-  </si>
-  <si>
-    <t>25/02/2026 11:54:30</t>
+    <t>60126667</t>
+  </si>
+  <si>
+    <t>18/03/2026 15:09:23</t>
+  </si>
+  <si>
+    <t>STE CEDERAC</t>
+  </si>
+  <si>
+    <t>PK 44 AUTOROUTE DU NORD</t>
+  </si>
+  <si>
+    <t>SYTHD150313</t>
+  </si>
+  <si>
+    <t>30/03/2026 16:39:27</t>
+  </si>
+  <si>
+    <t>60117848</t>
+  </si>
+  <si>
+    <t>18/03/2026 13:25:57</t>
+  </si>
+  <si>
+    <t>MOTA-ENGIL COTE D'IVOIRE SEGUELA</t>
+  </si>
+  <si>
+    <t>40G</t>
+  </si>
+  <si>
+    <t>SYTHD230111</t>
+  </si>
+  <si>
+    <t>07/04/2026 10:08:40</t>
+  </si>
+  <si>
+    <t>59805789</t>
+  </si>
+  <si>
+    <t>12/03/2026 11:59:46</t>
+  </si>
+  <si>
+    <t>ORANGE COTE D'IVOIRE S.A</t>
+  </si>
+  <si>
+    <t>HABITA BAT CIT FC HOPITAL P102</t>
+  </si>
+  <si>
+    <t>VPNLL170009</t>
+  </si>
+  <si>
+    <t>19/03/2026 13:30:49</t>
+  </si>
+  <si>
+    <t>60747953</t>
+  </si>
+  <si>
+    <t>30/03/2026 12:10:09</t>
+  </si>
+  <si>
+    <t>Bassam Vitib</t>
+  </si>
+  <si>
+    <t>2720201600</t>
+  </si>
+  <si>
+    <t>31/03/2026 12:44:44</t>
+  </si>
+  <si>
+    <t>60757807</t>
+  </si>
+  <si>
+    <t>30/03/2026 13:56:52</t>
+  </si>
+  <si>
+    <t>2720242424</t>
+  </si>
+  <si>
+    <t>07/04/2026 09:25:02</t>
+  </si>
+  <si>
+    <t>60121462</t>
+  </si>
+  <si>
+    <t>18/03/2026 14:09:33</t>
+  </si>
+  <si>
+    <t>MOTA-ENGIL COTE D'IVOIRE HIRIE AGBAOU</t>
+  </si>
+  <si>
+    <t>SYTHD250188</t>
+  </si>
+  <si>
+    <t>02/04/2026 12:22:45</t>
+  </si>
+  <si>
+    <t>60040794</t>
+  </si>
+  <si>
+    <t>17/03/2026 11:32:25</t>
+  </si>
+  <si>
+    <t>AFRICA GLOBAL LOGISTICS</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/VRIDI</t>
+  </si>
+  <si>
+    <t>BUVPN170223</t>
+  </si>
+  <si>
+    <t>24/03/2026 16:11:10</t>
+  </si>
+  <si>
+    <t>60166789</t>
+  </si>
+  <si>
+    <t>19/03/2026 10:45:13</t>
+  </si>
+  <si>
+    <t>EGLISE DE JESUS CHRIST DES SAINTS DES DERNIERS JOURS</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/SARAKA KOUAKOU 0584573633</t>
+  </si>
+  <si>
+    <t>SYTHD240107</t>
+  </si>
+  <si>
+    <t>07/04/2026 08:58:12</t>
+  </si>
+  <si>
+    <t>07/04/2026 08:58:09</t>
+  </si>
+  <si>
+    <t>60745864</t>
+  </si>
+  <si>
+    <t>30/03/2026 11:50:48</t>
+  </si>
+  <si>
+    <t>ECOTI SA</t>
+  </si>
+  <si>
+    <t>YOPOUGON</t>
+  </si>
+  <si>
+    <t>SYTHD190109</t>
+  </si>
+  <si>
+    <t>07/04/2026 09:14:15</t>
+  </si>
+  <si>
+    <t>60842944</t>
+  </si>
+  <si>
+    <t>31/03/2026 17:20:35</t>
+  </si>
+  <si>
+    <t>PIXAGILITY AFRIQUE</t>
+  </si>
+  <si>
+    <t>2PLATEAUX-VALLONS</t>
+  </si>
+  <si>
+    <t>SYTHD180207</t>
+  </si>
+  <si>
+    <t>01/04/2026 09:01:59</t>
+  </si>
+  <si>
+    <t>59323774</t>
+  </si>
+  <si>
+    <t>04/03/2026 09:17:41</t>
+  </si>
+  <si>
+    <t>BRIDGE GROUP WEST AFRICA</t>
+  </si>
+  <si>
+    <t>COCODY RUE CANEBIERRE IMMEUBLE PHEHONE</t>
+  </si>
+  <si>
+    <t>SYTHD250379</t>
+  </si>
+  <si>
+    <t>24/03/2026 16:09:57</t>
   </si>
   <si>
     <t>59302434</t>
@@ -1457,106 +1496,7 @@
     <t>BUVPN230155</t>
   </si>
   <si>
-    <t>26/03/2026 16:30:25</t>
-  </si>
-  <si>
-    <t>59805789</t>
-  </si>
-  <si>
-    <t>12/03/2026 11:59:46</t>
-  </si>
-  <si>
-    <t>ORANGE COTE D'IVOIRE S.A</t>
-  </si>
-  <si>
-    <t>HABITA BAT CIT FC HOPITAL P102</t>
-  </si>
-  <si>
-    <t>VPNLL170009</t>
-  </si>
-  <si>
-    <t>19/03/2026 13:30:49</t>
-  </si>
-  <si>
-    <t>60126667</t>
-  </si>
-  <si>
-    <t>18/03/2026 15:09:23</t>
-  </si>
-  <si>
-    <t>STE CEDERAC</t>
-  </si>
-  <si>
-    <t>PK 44 AUTOROUTE DU NORD</t>
-  </si>
-  <si>
-    <t>SYTHD150313</t>
-  </si>
-  <si>
-    <t>26/03/2026 10:57:20</t>
-  </si>
-  <si>
-    <t>60040794</t>
-  </si>
-  <si>
-    <t>17/03/2026 11:32:25</t>
-  </si>
-  <si>
-    <t>AFRICA GLOBAL LOGISTICS</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/VRIDI</t>
-  </si>
-  <si>
-    <t>BUVPN170223</t>
-  </si>
-  <si>
-    <t>24/03/2026 16:11:10</t>
-  </si>
-  <si>
-    <t>59301884</t>
-  </si>
-  <si>
-    <t>03/03/2026 16:45:07</t>
-  </si>
-  <si>
-    <t>SYTHD170144</t>
-  </si>
-  <si>
-    <t>26/03/2026 17:43:13</t>
-  </si>
-  <si>
-    <t>60121462</t>
-  </si>
-  <si>
-    <t>18/03/2026 14:09:33</t>
-  </si>
-  <si>
-    <t>MOTA-ENGIL COTE D'IVOIRE HIRIE AGBAOU</t>
-  </si>
-  <si>
-    <t>SYTHD250188</t>
-  </si>
-  <si>
-    <t>24/03/2026 15:58:34</t>
-  </si>
-  <si>
-    <t>60361274</t>
-  </si>
-  <si>
-    <t>23/03/2026 15:47:41</t>
-  </si>
-  <si>
-    <t>GMA</t>
-  </si>
-  <si>
-    <t>150M</t>
-  </si>
-  <si>
-    <t>SYTHD190266</t>
-  </si>
-  <si>
-    <t>27/03/2026 15:05:51</t>
+    <t>30/03/2026 09:04:54</t>
   </si>
   <si>
     <t>60165030</t>
@@ -1565,112 +1505,34 @@
     <t>19/03/2026 10:25:48</t>
   </si>
   <si>
-    <t>EGLISE DE JESUS CHRIST DES SAINTS DES DERNIERS JOURS</t>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/ATTOBAN 0584573633</t>
   </si>
   <si>
     <t>SYTHD240106</t>
   </si>
   <si>
-    <t>25/03/2026 17:30:16</t>
-  </si>
-  <si>
-    <t>60117848</t>
-  </si>
-  <si>
-    <t>18/03/2026 13:25:57</t>
-  </si>
-  <si>
-    <t>MOTA-ENGIL COTE D'IVOIRE SEGUELA</t>
-  </si>
-  <si>
-    <t>40G</t>
-  </si>
-  <si>
-    <t>SYTHD230111</t>
-  </si>
-  <si>
-    <t>24/03/2026 15:57:52</t>
-  </si>
-  <si>
-    <t>60166789</t>
-  </si>
-  <si>
-    <t>19/03/2026 10:45:13</t>
-  </si>
-  <si>
-    <t>SYTHD240107</t>
-  </si>
-  <si>
-    <t>25/03/2026 17:30:59</t>
-  </si>
-  <si>
-    <t>59488550</t>
-  </si>
-  <si>
-    <t>06/03/2026 14:31:49</t>
-  </si>
-  <si>
-    <t>CLINIQUE MEDICALE TRADE CENTER</t>
-  </si>
-  <si>
-    <t>MARCORY RESIDENTIEL</t>
-  </si>
-  <si>
-    <t>2720219797</t>
-  </si>
-  <si>
-    <t>24/03/2026 16:03:38</t>
-  </si>
-  <si>
-    <t>59822523</t>
-  </si>
-  <si>
-    <t>12/03/2026 15:00:46</t>
-  </si>
-  <si>
-    <t>AGENCE OCI 2PLTX  ENA</t>
-  </si>
-  <si>
-    <t>ABIDJAN PLATEAU PIA</t>
-  </si>
-  <si>
-    <t>VPNLL210028</t>
-  </si>
-  <si>
-    <t>24/03/2026 16:05:01</t>
-  </si>
-  <si>
-    <t>59301236</t>
-  </si>
-  <si>
-    <t>03/03/2026 16:38:39</t>
-  </si>
-  <si>
-    <t>DIRECTION GENERALE DES DOUANES</t>
-  </si>
-  <si>
-    <t>SYTHD230225</t>
-  </si>
-  <si>
-    <t>26/03/2026 16:49:44</t>
-  </si>
-  <si>
-    <t>59323774</t>
-  </si>
-  <si>
-    <t>04/03/2026 09:17:41</t>
-  </si>
-  <si>
-    <t>BRIDGE GROUP WEST AFRICA</t>
-  </si>
-  <si>
-    <t>COCODY RUE CANEBIERRE IMMEUBLE PHEHONE</t>
-  </si>
-  <si>
-    <t>SYTHD250379</t>
-  </si>
-  <si>
-    <t>24/03/2026 16:09:57</t>
+    <t>07/04/2026 08:56:58</t>
+  </si>
+  <si>
+    <t>07/04/2026 08:56:56</t>
+  </si>
+  <si>
+    <t>60757744</t>
+  </si>
+  <si>
+    <t>30/03/2026 13:56:23</t>
+  </si>
+  <si>
+    <t>MEDITERRANIEN SHIPPING COMPAGNY COTE d'IVOIRE</t>
+  </si>
+  <si>
+    <t>TREICHVILLE ZONE 3</t>
+  </si>
+  <si>
+    <t>2721756666</t>
+  </si>
+  <si>
+    <t>03/04/2026 08:32:06</t>
   </si>
   <si>
     <t>59429267</t>
@@ -1691,19 +1553,68 @@
     <t>19/03/2026 09:05:15</t>
   </si>
   <si>
-    <t>59458389</t>
-  </si>
-  <si>
-    <t>06/03/2026 08:52:02</t>
-  </si>
-  <si>
-    <t>ARTCI</t>
-  </si>
-  <si>
-    <t>2721711800</t>
-  </si>
-  <si>
-    <t>11/03/2026 14:42:45</t>
+    <t>61152139</t>
+  </si>
+  <si>
+    <t>07/04/2026 10:26:52</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES IMPOTS</t>
+  </si>
+  <si>
+    <t>JACQUEVILLE AU SEIN DE LA MAIRIE NON LOIN HOTEL PALM SUD.</t>
+  </si>
+  <si>
+    <t>VPNLL130294</t>
+  </si>
+  <si>
+    <t>07/04/2026 10:27:05</t>
+  </si>
+  <si>
+    <t>60874276</t>
+  </si>
+  <si>
+    <t>01/04/2026 11:32:51</t>
+  </si>
+  <si>
+    <t>ALIWAX</t>
+  </si>
+  <si>
+    <t>COCODY-ANGRE
+DJOROBITE</t>
+  </si>
+  <si>
+    <t>2722229530</t>
+  </si>
+  <si>
+    <t>01/04/2026 16:13:38</t>
+  </si>
+  <si>
+    <t>61019484</t>
+  </si>
+  <si>
+    <t>03/04/2026 15:11:12</t>
+  </si>
+  <si>
+    <t>SINOAFRIK AUTO SARL</t>
+  </si>
+  <si>
+    <t>COCODY 2 PLATEAUX</t>
+  </si>
+  <si>
+    <t>2722229765</t>
+  </si>
+  <si>
+    <t>03/04/2026 15:11:20</t>
+  </si>
+  <si>
+    <t>61021684</t>
+  </si>
+  <si>
+    <t>03/04/2026 15:44:13</t>
+  </si>
+  <si>
+    <t>07/04/2026 09:12:26</t>
   </si>
   <si>
     <t>NOM  CLIENT</t>
@@ -2083,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -2116,7 +2027,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -2213,13 +2124,13 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
         <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
         <v>25</v>
@@ -2236,10 +2147,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -2263,13 +2174,13 @@
         <v>24</v>
       </c>
       <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
         <v>31</v>
-      </c>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
@@ -2280,10 +2191,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
@@ -2301,19 +2212,19 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5" t="s">
         <v>24</v>
       </c>
       <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
         <v>32</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>31</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
@@ -2324,10 +2235,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
@@ -2339,25 +2250,25 @@
         <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s">
         <v>41</v>
       </c>
-      <c r="I6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" t="s">
-        <v>40</v>
-      </c>
       <c r="K6" t="s">
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
@@ -2368,40 +2279,40 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
@@ -2412,142 +2323,142 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" t="s">
         <v>69</v>
       </c>
-      <c r="K8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" t="s">
-        <v>66</v>
-      </c>
       <c r="M8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
+        <v>84</v>
+      </c>
+      <c r="J9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M9" t="s">
         <v>81</v>
       </c>
-      <c r="J9" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" t="s">
-        <v>77</v>
-      </c>
-      <c r="M9" t="s">
-        <v>78</v>
-      </c>
       <c r="N9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K10" t="s">
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M10" t="s">
         <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
@@ -2556,342 +2467,342 @@
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K11" t="s">
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s">
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K12" t="s">
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M12" t="s">
         <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K13" t="s">
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M13" t="s">
         <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K14" t="s">
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M14" t="s">
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M15" t="s">
         <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G16" t="s">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I16" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="J16" t="s">
+        <v>130</v>
+      </c>
+      <c r="K16" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
         <v>129</v>
       </c>
-      <c r="K16" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" t="s">
-        <v>128</v>
-      </c>
       <c r="M16" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="N16" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="H17" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="J17" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K17" t="s">
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M17" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" t="s">
+        <v>133</v>
+      </c>
+      <c r="G18" t="s">
+        <v>134</v>
+      </c>
+      <c r="H18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" t="s">
+        <v>140</v>
+      </c>
+      <c r="J18" t="s">
+        <v>136</v>
+      </c>
+      <c r="K18" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" t="s">
         <v>135</v>
       </c>
-      <c r="B18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F18" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" t="s">
-        <v>79</v>
-      </c>
-      <c r="J18" t="s">
-        <v>140</v>
-      </c>
-      <c r="K18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" t="s">
-        <v>139</v>
-      </c>
       <c r="M18" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -2902,95 +2813,95 @@
         <v>142</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="F19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s">
+        <v>146</v>
+      </c>
+      <c r="K19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" t="s">
         <v>145</v>
       </c>
-      <c r="K19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L19" t="s">
-        <v>144</v>
-      </c>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="N19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="H20" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K20" t="s">
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M20" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
         <v>17</v>
@@ -3002,321 +2913,321 @@
         <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J21" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K21" t="s">
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M21" t="s">
         <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F22" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="G22" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H22" t="s">
         <v>23</v>
       </c>
       <c r="I22" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="J22" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K22" t="s">
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M22" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N22" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F23" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G23" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J23" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K23" t="s">
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M23" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="N23" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="F24" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="G24" t="s">
-        <v>167</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I24" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="J24" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K24" t="s">
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="M24" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="N24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G25" t="s">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="H25" t="s">
         <v>23</v>
       </c>
       <c r="I25" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J25" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K25" t="s">
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="M25" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="N25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B26" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="H26" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I26" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J26" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K26" t="s">
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M26" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="N26" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B27" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I27" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J27" t="s">
+        <v>187</v>
+      </c>
+      <c r="K27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" t="s">
         <v>186</v>
-      </c>
-      <c r="K27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L27" t="s">
-        <v>185</v>
       </c>
       <c r="M27" t="s">
         <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J28" t="s">
         <v>191</v>
@@ -3331,7 +3242,7 @@
         <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -3342,25 +3253,25 @@
         <v>193</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s">
         <v>194</v>
       </c>
       <c r="G29" t="s">
-        <v>37</v>
+        <v>150</v>
       </c>
       <c r="H29" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J29" t="s">
         <v>196</v>
@@ -3372,10 +3283,10 @@
         <v>195</v>
       </c>
       <c r="M29" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N29" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -3386,7 +3297,7 @@
         <v>198</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -3395,16 +3306,16 @@
         <v>199</v>
       </c>
       <c r="F30" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="G30" t="s">
-        <v>37</v>
+        <v>150</v>
       </c>
       <c r="H30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I30" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J30" t="s">
         <v>202</v>
@@ -3419,7 +3330,7 @@
         <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -3430,474 +3341,474 @@
         <v>204</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>206</v>
       </c>
       <c r="G31" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K31" t="s">
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M31" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="N31" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
       </c>
       <c r="E32" t="s">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="F32" t="s">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="G32" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="H32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I32" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J32" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K32" t="s">
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="M32" t="s">
         <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>216</v>
+      </c>
+      <c r="B33" t="s">
+        <v>217</v>
+      </c>
+      <c r="C33" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
         <v>211</v>
       </c>
-      <c r="B33" t="s">
-        <v>212</v>
-      </c>
-      <c r="C33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" t="s">
-        <v>46</v>
-      </c>
-      <c r="E33" t="s">
-        <v>213</v>
-      </c>
       <c r="F33" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="H33" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J33" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="K33" t="s">
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M33" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N33" t="s">
-        <v>59</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B34" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
       </c>
       <c r="E34" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>138</v>
+        <v>225</v>
       </c>
       <c r="G34" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="H34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I34" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J34" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K34" t="s">
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="M34" t="s">
         <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B35" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="E35" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="H35" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J35" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K35" t="s">
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="M35" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B36" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="H36" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J36" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K36" t="s">
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="M36" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="N36" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B37" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="E37" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F37" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G37" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J37" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K37" t="s">
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M37" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="N37" t="s">
-        <v>239</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B38" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>245</v>
       </c>
       <c r="F38" t="s">
-        <v>243</v>
+        <v>99</v>
       </c>
       <c r="G38" t="s">
-        <v>37</v>
+        <v>246</v>
       </c>
       <c r="H38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I38" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J38" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K38" t="s">
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M38" t="s">
         <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>249</v>
+      </c>
+      <c r="B39" t="s">
+        <v>250</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s">
+        <v>251</v>
+      </c>
+      <c r="F39" t="s">
+        <v>252</v>
+      </c>
+      <c r="G39" t="s">
         <v>246</v>
       </c>
-      <c r="B39" t="s">
-        <v>247</v>
-      </c>
-      <c r="C39" t="s">
-        <v>100</v>
-      </c>
-      <c r="D39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" t="s">
-        <v>248</v>
-      </c>
-      <c r="G39" t="s">
-        <v>220</v>
-      </c>
       <c r="H39" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I39" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J39" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K39" t="s">
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="M39" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N39" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F40" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="H40" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I40" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J40" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="K40" t="s">
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="M40" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F41" t="s">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="G41" t="s">
-        <v>65</v>
+        <v>246</v>
       </c>
       <c r="H41" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I41" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J41" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K41" t="s">
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="M41" t="s">
         <v>21</v>
@@ -3908,794 +3819,794 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B42" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
         <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>269</v>
       </c>
       <c r="G42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H42" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I42" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J42" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="K42" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="L42" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="M42" t="s">
         <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B43" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E43" t="s">
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="G43" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="H43" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="J43" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K43" t="s">
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="M43" t="s">
         <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B44" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c r="G44" t="s">
-        <v>272</v>
+        <v>38</v>
       </c>
       <c r="H44" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J44" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K44" t="s">
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M44" t="s">
         <v>21</v>
       </c>
       <c r="N44" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B45" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F45" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G45" t="s">
-        <v>272</v>
+        <v>38</v>
       </c>
       <c r="H45" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I45" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J45" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K45" t="s">
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="N45" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B46" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F46" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G46" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H46" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I46" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="J46" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K46" t="s">
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M46" t="s">
         <v>21</v>
       </c>
       <c r="N46" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>286</v>
+      </c>
+      <c r="B47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" t="s">
+        <v>257</v>
+      </c>
+      <c r="F47" t="s">
+        <v>288</v>
+      </c>
+      <c r="G47" t="s">
         <v>289</v>
       </c>
-      <c r="B47" t="s">
+      <c r="H47" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" t="s">
+        <v>40</v>
+      </c>
+      <c r="J47" t="s">
+        <v>293</v>
+      </c>
+      <c r="K47" t="s">
+        <v>292</v>
+      </c>
+      <c r="L47" t="s">
         <v>290</v>
-      </c>
-      <c r="C47" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" t="s">
-        <v>271</v>
-      </c>
-      <c r="F47" t="s">
-        <v>96</v>
-      </c>
-      <c r="G47" t="s">
-        <v>272</v>
-      </c>
-      <c r="H47" t="s">
-        <v>41</v>
-      </c>
-      <c r="I47" t="s">
-        <v>56</v>
-      </c>
-      <c r="J47" t="s">
-        <v>292</v>
-      </c>
-      <c r="K47" t="s">
-        <v>15</v>
-      </c>
-      <c r="L47" t="s">
-        <v>291</v>
       </c>
       <c r="M47" t="s">
         <v>21</v>
       </c>
       <c r="N47" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B48" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E48" t="s">
-        <v>18</v>
+        <v>296</v>
       </c>
       <c r="F48" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I48" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J48" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K48" t="s">
+        <v>300</v>
+      </c>
+      <c r="L48" t="s">
         <v>298</v>
-      </c>
-      <c r="L48" t="s">
-        <v>296</v>
       </c>
       <c r="M48" t="s">
         <v>21</v>
       </c>
       <c r="N48" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B49" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C49" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E49" t="s">
-        <v>18</v>
+        <v>296</v>
       </c>
       <c r="F49" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H49" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I49" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J49" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K49" t="s">
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M49" t="s">
         <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
       </c>
       <c r="E50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F50" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G50" t="s">
-        <v>37</v>
+        <v>306</v>
       </c>
       <c r="H50" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I50" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="J50" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="K50" t="s">
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M50" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N50" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B51" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
       </c>
       <c r="E51" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="F51" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H51" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I51" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K51" t="s">
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M51" t="s">
         <v>21</v>
       </c>
       <c r="N51" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B52" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="E52" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F52" t="s">
-        <v>74</v>
+        <v>316</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="H52" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I52" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="J52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="K52" t="s">
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="M52" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="N52" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B53" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
       <c r="F53" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G53" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="H53" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I53" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J53" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K53" t="s">
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="M53" t="s">
         <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B54" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D54" t="s">
         <v>17</v>
       </c>
       <c r="E54" t="s">
-        <v>283</v>
+        <v>329</v>
       </c>
       <c r="F54" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="G54" t="s">
-        <v>319</v>
+        <v>38</v>
       </c>
       <c r="H54" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I54" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="J54" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="K54" t="s">
-        <v>322</v>
+        <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="M54" t="s">
         <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="B55" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C55" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
         <v>17</v>
       </c>
       <c r="E55" t="s">
-        <v>326</v>
+        <v>260</v>
       </c>
       <c r="F55" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="G55" t="s">
-        <v>328</v>
+        <v>105</v>
       </c>
       <c r="H55" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I55" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J55" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="K55" t="s">
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N55" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D56" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="E56" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="F56" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G56" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H56" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I56" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J56" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="K56" t="s">
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
       </c>
       <c r="E57" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="F57" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="G57" t="s">
-        <v>37</v>
+        <v>200</v>
       </c>
       <c r="H57" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J57" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="K57" t="s">
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="M57" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N57" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C58" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
       </c>
       <c r="E58" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F58" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s">
-        <v>328</v>
+        <v>219</v>
       </c>
       <c r="H58" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I58" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J58" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="K58" t="s">
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="M58" t="s">
         <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B59" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C59" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
       </c>
       <c r="E59" t="s">
-        <v>91</v>
+        <v>257</v>
       </c>
       <c r="F59" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="G59" t="s">
-        <v>350</v>
+        <v>259</v>
       </c>
       <c r="H59" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I59" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J59" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="K59" t="s">
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M59" t="s">
         <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -4706,69 +4617,69 @@
         <v>354</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D60" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="E60" t="s">
+        <v>257</v>
+      </c>
+      <c r="F60" t="s">
         <v>355</v>
       </c>
-      <c r="F60" t="s">
-        <v>96</v>
-      </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="H60" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I60" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J60" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K60" t="s">
-        <v>15</v>
+        <v>358</v>
       </c>
       <c r="L60" t="s">
         <v>356</v>
       </c>
       <c r="M60" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="N60" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B61" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C61" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D61" t="s">
         <v>17</v>
       </c>
       <c r="E61" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F61" t="s">
-        <v>361</v>
+        <v>61</v>
       </c>
       <c r="G61" t="s">
-        <v>362</v>
+        <v>150</v>
       </c>
       <c r="H61" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I61" t="s">
-        <v>173</v>
+        <v>59</v>
       </c>
       <c r="J61" t="s">
         <v>364</v>
@@ -4780,10 +4691,10 @@
         <v>363</v>
       </c>
       <c r="M61" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N61" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -4794,128 +4705,128 @@
         <v>366</v>
       </c>
       <c r="C62" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D62" t="s">
         <v>17</v>
       </c>
       <c r="E62" t="s">
-        <v>308</v>
+        <v>94</v>
       </c>
       <c r="F62" t="s">
+        <v>323</v>
+      </c>
+      <c r="G62" t="s">
+        <v>317</v>
+      </c>
+      <c r="H62" t="s">
+        <v>43</v>
+      </c>
+      <c r="I62" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" t="s">
+        <v>368</v>
+      </c>
+      <c r="K62" t="s">
+        <v>15</v>
+      </c>
+      <c r="L62" t="s">
         <v>367</v>
-      </c>
-      <c r="G62" t="s">
-        <v>37</v>
-      </c>
-      <c r="H62" t="s">
-        <v>41</v>
-      </c>
-      <c r="I62" t="s">
-        <v>56</v>
-      </c>
-      <c r="J62" t="s">
-        <v>369</v>
-      </c>
-      <c r="K62" t="s">
-        <v>15</v>
-      </c>
-      <c r="L62" t="s">
-        <v>368</v>
       </c>
       <c r="M62" t="s">
         <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>369</v>
+      </c>
+      <c r="B63" t="s">
         <v>370</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
+        <v>102</v>
+      </c>
+      <c r="D63" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" t="s">
         <v>371</v>
       </c>
-      <c r="C63" t="s">
-        <v>57</v>
-      </c>
-      <c r="D63" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>372</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>373</v>
       </c>
-      <c r="G63" t="s">
-        <v>37</v>
-      </c>
       <c r="H63" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I63" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="J63" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K63" t="s">
-        <v>376</v>
+        <v>15</v>
       </c>
       <c r="L63" t="s">
         <v>374</v>
       </c>
       <c r="M63" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N63" t="s">
-        <v>59</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>369</v>
+      </c>
+      <c r="B64" t="s">
         <v>370</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
+        <v>102</v>
+      </c>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" t="s">
         <v>371</v>
       </c>
-      <c r="C64" t="s">
-        <v>57</v>
-      </c>
-      <c r="D64" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>372</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>373</v>
       </c>
-      <c r="G64" t="s">
-        <v>37</v>
-      </c>
       <c r="H64" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="I64" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="J64" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K64" t="s">
-        <v>15</v>
+        <v>376</v>
       </c>
       <c r="L64" t="s">
         <v>374</v>
       </c>
       <c r="M64" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N64" t="s">
-        <v>59</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -4926,157 +4837,157 @@
         <v>379</v>
       </c>
       <c r="C65" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D65" t="s">
         <v>17</v>
       </c>
       <c r="E65" t="s">
-        <v>308</v>
+        <v>94</v>
       </c>
       <c r="F65" t="s">
+        <v>323</v>
+      </c>
+      <c r="G65" t="s">
+        <v>317</v>
+      </c>
+      <c r="H65" t="s">
+        <v>43</v>
+      </c>
+      <c r="I65" t="s">
+        <v>40</v>
+      </c>
+      <c r="J65" t="s">
+        <v>381</v>
+      </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+      <c r="L65" t="s">
         <v>380</v>
-      </c>
-      <c r="G65" t="s">
-        <v>37</v>
-      </c>
-      <c r="H65" t="s">
-        <v>41</v>
-      </c>
-      <c r="I65" t="s">
-        <v>56</v>
-      </c>
-      <c r="J65" t="s">
-        <v>382</v>
-      </c>
-      <c r="K65" t="s">
-        <v>15</v>
-      </c>
-      <c r="L65" t="s">
-        <v>381</v>
       </c>
       <c r="M65" t="s">
         <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>382</v>
+      </c>
+      <c r="B66" t="s">
         <v>383</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" t="s">
+        <v>98</v>
+      </c>
+      <c r="E66" t="s">
         <v>384</v>
       </c>
-      <c r="C66" t="s">
-        <v>100</v>
-      </c>
-      <c r="D66" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
+        <v>99</v>
+      </c>
+      <c r="G66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>43</v>
+      </c>
+      <c r="I66" t="s">
+        <v>54</v>
+      </c>
+      <c r="J66" t="s">
+        <v>386</v>
+      </c>
+      <c r="K66" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" t="s">
         <v>385</v>
       </c>
-      <c r="F66" t="s">
-        <v>386</v>
-      </c>
-      <c r="G66" t="s">
-        <v>220</v>
-      </c>
-      <c r="H66" t="s">
-        <v>41</v>
-      </c>
-      <c r="I66" t="s">
-        <v>56</v>
-      </c>
-      <c r="J66" t="s">
-        <v>388</v>
-      </c>
-      <c r="K66" t="s">
-        <v>15</v>
-      </c>
-      <c r="L66" t="s">
-        <v>387</v>
-      </c>
       <c r="M66" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="N66" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>387</v>
+      </c>
+      <c r="B67" t="s">
+        <v>388</v>
+      </c>
+      <c r="C67" t="s">
+        <v>60</v>
+      </c>
+      <c r="D67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" t="s">
         <v>389</v>
       </c>
-      <c r="B67" t="s">
+      <c r="F67" t="s">
+        <v>335</v>
+      </c>
+      <c r="G67" t="s">
+        <v>105</v>
+      </c>
+      <c r="H67" t="s">
+        <v>43</v>
+      </c>
+      <c r="I67" t="s">
+        <v>44</v>
+      </c>
+      <c r="J67" t="s">
+        <v>391</v>
+      </c>
+      <c r="K67" t="s">
+        <v>15</v>
+      </c>
+      <c r="L67" t="s">
         <v>390</v>
-      </c>
-      <c r="C67" t="s">
-        <v>100</v>
-      </c>
-      <c r="D67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" t="s">
-        <v>91</v>
-      </c>
-      <c r="F67" t="s">
-        <v>74</v>
-      </c>
-      <c r="G67" t="s">
-        <v>237</v>
-      </c>
-      <c r="H67" t="s">
-        <v>23</v>
-      </c>
-      <c r="I67" t="s">
-        <v>43</v>
-      </c>
-      <c r="J67" t="s">
-        <v>392</v>
-      </c>
-      <c r="K67" t="s">
-        <v>15</v>
-      </c>
-      <c r="L67" t="s">
-        <v>391</v>
       </c>
       <c r="M67" t="s">
         <v>21</v>
       </c>
       <c r="N67" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>392</v>
+      </c>
+      <c r="B68" t="s">
         <v>393</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
+        <v>102</v>
+      </c>
+      <c r="D68" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" t="s">
         <v>394</v>
-      </c>
-      <c r="C68" t="s">
-        <v>57</v>
-      </c>
-      <c r="D68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" t="s">
-        <v>283</v>
       </c>
       <c r="F68" t="s">
         <v>395</v>
       </c>
       <c r="G68" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="H68" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I68" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J68" t="s">
         <v>397</v>
@@ -5091,359 +5002,359 @@
         <v>21</v>
       </c>
       <c r="N68" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B69" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C69" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D69" t="s">
         <v>17</v>
       </c>
       <c r="E69" t="s">
-        <v>283</v>
+        <v>371</v>
       </c>
       <c r="F69" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G69" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="H69" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I69" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="J69" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K69" t="s">
-        <v>398</v>
+        <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="M69" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N69" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>398</v>
+      </c>
+      <c r="B70" t="s">
+        <v>399</v>
+      </c>
+      <c r="C70" t="s">
+        <v>102</v>
+      </c>
+      <c r="D70" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" t="s">
+        <v>371</v>
+      </c>
+      <c r="F70" t="s">
         <v>400</v>
       </c>
-      <c r="B70" t="s">
+      <c r="G70" t="s">
+        <v>373</v>
+      </c>
+      <c r="H70" t="s">
+        <v>27</v>
+      </c>
+      <c r="I70" t="s">
+        <v>71</v>
+      </c>
+      <c r="J70" t="s">
+        <v>404</v>
+      </c>
+      <c r="K70" t="s">
+        <v>402</v>
+      </c>
+      <c r="L70" t="s">
         <v>401</v>
       </c>
-      <c r="C70" t="s">
-        <v>100</v>
-      </c>
-      <c r="D70" t="s">
-        <v>17</v>
-      </c>
-      <c r="E70" t="s">
-        <v>91</v>
-      </c>
-      <c r="F70" t="s">
-        <v>58</v>
-      </c>
-      <c r="G70" t="s">
-        <v>328</v>
-      </c>
-      <c r="H70" t="s">
-        <v>41</v>
-      </c>
-      <c r="I70" t="s">
-        <v>43</v>
-      </c>
-      <c r="J70" t="s">
-        <v>403</v>
-      </c>
-      <c r="K70" t="s">
-        <v>15</v>
-      </c>
-      <c r="L70" t="s">
-        <v>402</v>
-      </c>
       <c r="M70" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N70" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>398</v>
+      </c>
+      <c r="B71" t="s">
+        <v>399</v>
+      </c>
+      <c r="C71" t="s">
+        <v>102</v>
+      </c>
+      <c r="D71" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" t="s">
+        <v>371</v>
+      </c>
+      <c r="F71" t="s">
+        <v>400</v>
+      </c>
+      <c r="G71" t="s">
+        <v>373</v>
+      </c>
+      <c r="H71" t="s">
+        <v>27</v>
+      </c>
+      <c r="I71" t="s">
+        <v>71</v>
+      </c>
+      <c r="J71" t="s">
+        <v>405</v>
+      </c>
+      <c r="K71" t="s">
         <v>404</v>
       </c>
-      <c r="B71" t="s">
-        <v>405</v>
-      </c>
-      <c r="C71" t="s">
-        <v>57</v>
-      </c>
-      <c r="D71" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" t="s">
-        <v>406</v>
-      </c>
-      <c r="F71" t="s">
-        <v>407</v>
-      </c>
-      <c r="G71" t="s">
-        <v>103</v>
-      </c>
-      <c r="H71" t="s">
-        <v>41</v>
-      </c>
-      <c r="I71" t="s">
-        <v>42</v>
-      </c>
-      <c r="J71" t="s">
-        <v>409</v>
-      </c>
-      <c r="K71" t="s">
-        <v>15</v>
-      </c>
       <c r="L71" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="M71" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N71" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B72" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C72" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D72" t="s">
         <v>17</v>
       </c>
       <c r="E72" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F72" t="s">
-        <v>327</v>
+        <v>61</v>
       </c>
       <c r="G72" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="H72" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I72" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J72" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="K72" t="s">
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="M72" t="s">
         <v>21</v>
       </c>
       <c r="N72" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>410</v>
+      </c>
+      <c r="B73" t="s">
+        <v>411</v>
+      </c>
+      <c r="C73" t="s">
+        <v>60</v>
+      </c>
+      <c r="D73" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" t="s">
+        <v>389</v>
+      </c>
+      <c r="F73" t="s">
+        <v>412</v>
+      </c>
+      <c r="G73" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" t="s">
+        <v>53</v>
+      </c>
+      <c r="J73" t="s">
         <v>414</v>
       </c>
-      <c r="B73" t="s">
-        <v>415</v>
-      </c>
-      <c r="C73" t="s">
-        <v>57</v>
-      </c>
-      <c r="D73" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" t="s">
-        <v>286</v>
-      </c>
-      <c r="F73" t="s">
-        <v>407</v>
-      </c>
-      <c r="G73" t="s">
-        <v>103</v>
-      </c>
-      <c r="H73" t="s">
-        <v>41</v>
-      </c>
-      <c r="I73" t="s">
-        <v>42</v>
-      </c>
-      <c r="J73" t="s">
-        <v>417</v>
-      </c>
       <c r="K73" t="s">
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="M73" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="N73" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>415</v>
+      </c>
+      <c r="B74" t="s">
+        <v>416</v>
+      </c>
+      <c r="C74" t="s">
+        <v>60</v>
+      </c>
+      <c r="D74" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" t="s">
+        <v>296</v>
+      </c>
+      <c r="F74" t="s">
+        <v>417</v>
+      </c>
+      <c r="G74" t="s">
+        <v>219</v>
+      </c>
+      <c r="H74" t="s">
+        <v>43</v>
+      </c>
+      <c r="I74" t="s">
+        <v>44</v>
+      </c>
+      <c r="J74" t="s">
+        <v>419</v>
+      </c>
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
+      <c r="L74" t="s">
         <v>418</v>
       </c>
-      <c r="B74" t="s">
-        <v>419</v>
-      </c>
-      <c r="C74" t="s">
-        <v>100</v>
-      </c>
-      <c r="D74" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" t="s">
-        <v>420</v>
-      </c>
-      <c r="F74" t="s">
-        <v>58</v>
-      </c>
-      <c r="G74" t="s">
-        <v>127</v>
-      </c>
-      <c r="H74" t="s">
-        <v>41</v>
-      </c>
-      <c r="I74" t="s">
-        <v>56</v>
-      </c>
-      <c r="J74" t="s">
-        <v>422</v>
-      </c>
-      <c r="K74" t="s">
-        <v>15</v>
-      </c>
-      <c r="L74" t="s">
-        <v>421</v>
-      </c>
       <c r="M74" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N74" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>420</v>
+      </c>
+      <c r="B75" t="s">
+        <v>421</v>
+      </c>
+      <c r="C75" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" t="s">
+        <v>422</v>
+      </c>
+      <c r="F75" t="s">
         <v>423</v>
       </c>
-      <c r="B75" t="s">
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" t="s">
+        <v>26</v>
+      </c>
+      <c r="J75" t="s">
+        <v>425</v>
+      </c>
+      <c r="K75" t="s">
+        <v>15</v>
+      </c>
+      <c r="L75" t="s">
         <v>424</v>
       </c>
-      <c r="C75" t="s">
-        <v>100</v>
-      </c>
-      <c r="D75" t="s">
-        <v>17</v>
-      </c>
-      <c r="E75" t="s">
-        <v>425</v>
-      </c>
-      <c r="F75" t="s">
-        <v>426</v>
-      </c>
-      <c r="G75" t="s">
-        <v>427</v>
-      </c>
-      <c r="H75" t="s">
-        <v>41</v>
-      </c>
-      <c r="I75" t="s">
-        <v>173</v>
-      </c>
-      <c r="J75" t="s">
-        <v>431</v>
-      </c>
-      <c r="K75" t="s">
-        <v>15</v>
-      </c>
-      <c r="L75" t="s">
-        <v>428</v>
-      </c>
       <c r="M75" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N75" t="s">
-        <v>239</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B76" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D76" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E76" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F76" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G76" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H76" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I76" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J76" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K76" t="s">
+        <v>15</v>
+      </c>
+      <c r="L76" t="s">
         <v>430</v>
       </c>
-      <c r="L76" t="s">
-        <v>428</v>
-      </c>
       <c r="M76" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N76" t="s">
-        <v>239</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
@@ -5454,7 +5365,7 @@
         <v>433</v>
       </c>
       <c r="C77" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D77" t="s">
         <v>17</v>
@@ -5466,13 +5377,13 @@
         <v>435</v>
       </c>
       <c r="G77" t="s">
-        <v>272</v>
+        <v>373</v>
       </c>
       <c r="H77" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I77" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="J77" t="s">
         <v>437</v>
@@ -5487,7 +5398,7 @@
         <v>21</v>
       </c>
       <c r="N77" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -5498,25 +5409,25 @@
         <v>439</v>
       </c>
       <c r="C78" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D78" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E78" t="s">
-        <v>91</v>
+        <v>296</v>
       </c>
       <c r="F78" t="s">
         <v>440</v>
       </c>
       <c r="G78" t="s">
-        <v>350</v>
+        <v>15</v>
       </c>
       <c r="H78" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I78" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="J78" t="s">
         <v>442</v>
@@ -5528,10 +5439,10 @@
         <v>441</v>
       </c>
       <c r="M78" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="N78" t="s">
-        <v>239</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
@@ -5542,169 +5453,169 @@
         <v>444</v>
       </c>
       <c r="C79" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D79" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E79" t="s">
+        <v>296</v>
+      </c>
+      <c r="F79" t="s">
+        <v>440</v>
+      </c>
+      <c r="G79" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" t="s">
+        <v>40</v>
+      </c>
+      <c r="J79" t="s">
+        <v>446</v>
+      </c>
+      <c r="K79" t="s">
+        <v>15</v>
+      </c>
+      <c r="L79" t="s">
         <v>445</v>
       </c>
-      <c r="F79" t="s">
-        <v>74</v>
-      </c>
-      <c r="G79" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" t="s">
-        <v>41</v>
-      </c>
-      <c r="I79" t="s">
-        <v>42</v>
-      </c>
-      <c r="J79" t="s">
-        <v>447</v>
-      </c>
-      <c r="K79" t="s">
-        <v>15</v>
-      </c>
-      <c r="L79" t="s">
-        <v>446</v>
-      </c>
       <c r="M79" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N79" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>447</v>
+      </c>
+      <c r="B80" t="s">
         <v>448</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
+        <v>102</v>
+      </c>
+      <c r="D80" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" t="s">
         <v>449</v>
       </c>
-      <c r="C80" t="s">
-        <v>100</v>
-      </c>
-      <c r="D80" t="s">
-        <v>17</v>
-      </c>
-      <c r="E80" t="s">
-        <v>425</v>
-      </c>
       <c r="F80" t="s">
+        <v>449</v>
+      </c>
+      <c r="G80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H80" t="s">
+        <v>43</v>
+      </c>
+      <c r="I80" t="s">
+        <v>26</v>
+      </c>
+      <c r="J80" t="s">
+        <v>451</v>
+      </c>
+      <c r="K80" t="s">
+        <v>15</v>
+      </c>
+      <c r="L80" t="s">
         <v>450</v>
       </c>
-      <c r="G80" t="s">
-        <v>427</v>
-      </c>
-      <c r="H80" t="s">
-        <v>41</v>
-      </c>
-      <c r="I80" t="s">
-        <v>173</v>
-      </c>
-      <c r="J80" t="s">
-        <v>453</v>
-      </c>
-      <c r="K80" t="s">
-        <v>15</v>
-      </c>
-      <c r="L80" t="s">
-        <v>451</v>
-      </c>
       <c r="M80" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N80" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B81" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C81" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D81" t="s">
         <v>17</v>
       </c>
       <c r="E81" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="F81" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="G81" t="s">
-        <v>427</v>
+        <v>38</v>
       </c>
       <c r="H81" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I81" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="J81" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K81" t="s">
-        <v>452</v>
+        <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="M81" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="N81" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B82" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="C82" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D82" t="s">
         <v>17</v>
       </c>
       <c r="E82" t="s">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="F82" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="G82" t="s">
-        <v>427</v>
+        <v>219</v>
       </c>
       <c r="H82" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I82" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="J82" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="K82" t="s">
-        <v>454</v>
+        <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="M82" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N82" t="s">
         <v>22</v>
@@ -5712,142 +5623,142 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B83" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C83" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D83" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="E83" t="s">
-        <v>406</v>
+        <v>460</v>
       </c>
       <c r="F83" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G83" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="H83" t="s">
         <v>23</v>
       </c>
       <c r="I83" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="J83" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="K83" t="s">
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M83" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N83" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B84" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C84" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="D84" t="s">
         <v>17</v>
       </c>
       <c r="E84" t="s">
-        <v>372</v>
+        <v>467</v>
       </c>
       <c r="F84" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="G84" t="s">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="H84" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I84" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="J84" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="K84" t="s">
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="M84" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N84" t="s">
-        <v>59</v>
+        <v>221</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B85" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D85" t="s">
         <v>17</v>
       </c>
       <c r="E85" t="s">
-        <v>91</v>
+        <v>473</v>
       </c>
       <c r="F85" t="s">
-        <v>327</v>
+        <v>474</v>
       </c>
       <c r="G85" t="s">
-        <v>350</v>
+        <v>213</v>
       </c>
       <c r="H85" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J85" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="K85" t="s">
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="M85" t="s">
         <v>21</v>
       </c>
       <c r="N85" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B86" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C86" t="s">
         <v>16</v>
@@ -5856,154 +5767,154 @@
         <v>17</v>
       </c>
       <c r="E86" t="s">
-        <v>18</v>
+        <v>479</v>
       </c>
       <c r="F86" t="s">
-        <v>96</v>
+        <v>480</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I86" t="s">
         <v>52</v>
       </c>
       <c r="J86" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="K86" t="s">
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="M86" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N86" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="B87" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="C87" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D87" t="s">
         <v>17</v>
       </c>
       <c r="E87" t="s">
-        <v>476</v>
+        <v>18</v>
       </c>
       <c r="F87" t="s">
-        <v>477</v>
+        <v>99</v>
       </c>
       <c r="G87" t="s">
-        <v>427</v>
+        <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I87" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="J87" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="K87" t="s">
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="M87" t="s">
         <v>21</v>
       </c>
       <c r="N87" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B88" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="D88" t="s">
         <v>17</v>
       </c>
       <c r="E88" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="F88" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="G88" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="H88" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I88" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="J88" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="K88" t="s">
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="M88" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N88" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B89" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="D89" t="s">
         <v>17</v>
       </c>
       <c r="E89" t="s">
-        <v>488</v>
+        <v>460</v>
       </c>
       <c r="F89" t="s">
         <v>489</v>
       </c>
       <c r="G89" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="H89" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I89" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="J89" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K89" t="s">
         <v>15</v>
@@ -6012,542 +5923,278 @@
         <v>490</v>
       </c>
       <c r="M89" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="N89" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B90" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D90" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E90" t="s">
-        <v>18</v>
+        <v>495</v>
       </c>
       <c r="F90" t="s">
-        <v>96</v>
+        <v>496</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I90" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J90" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K90" t="s">
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="M90" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="N90" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B91" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C91" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D91" t="s">
         <v>17</v>
       </c>
       <c r="E91" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F91" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="G91" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H91" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I91" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="J91" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K91" t="s">
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="M91" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="N91" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B92" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C92" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D92" t="s">
         <v>17</v>
       </c>
       <c r="E92" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F92" t="s">
-        <v>96</v>
+        <v>508</v>
       </c>
       <c r="G92" t="s">
-        <v>504</v>
+        <v>38</v>
       </c>
       <c r="H92" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I92" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J92" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K92" t="s">
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="M92" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="N92" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B93" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C93" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D93" t="s">
         <v>17</v>
       </c>
       <c r="E93" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F93" t="s">
-        <v>58</v>
+        <v>514</v>
       </c>
       <c r="G93" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="H93" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I93" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J93" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K93" t="s">
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="M93" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="N93" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B94" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C94" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E94" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F94" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="G94" t="s">
-        <v>515</v>
+        <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I94" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J94" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="K94" t="s">
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="M94" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="N94" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B95" t="s">
+        <v>524</v>
+      </c>
+      <c r="C95" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" t="s">
+        <v>75</v>
+      </c>
+      <c r="E95" t="s">
         <v>519</v>
       </c>
-      <c r="C95" t="s">
-        <v>100</v>
-      </c>
-      <c r="D95" t="s">
-        <v>17</v>
-      </c>
-      <c r="E95" t="s">
-        <v>509</v>
-      </c>
       <c r="F95" t="s">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="G95" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I95" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J95" t="s">
+        <v>525</v>
+      </c>
+      <c r="K95" t="s">
+        <v>15</v>
+      </c>
+      <c r="L95" t="s">
         <v>521</v>
       </c>
-      <c r="K95" t="s">
-        <v>15</v>
-      </c>
-      <c r="L95" t="s">
-        <v>520</v>
-      </c>
       <c r="M95" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="N95" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>522</v>
-      </c>
-      <c r="B96" t="s">
-        <v>523</v>
-      </c>
-      <c r="C96" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" t="s">
-        <v>72</v>
-      </c>
-      <c r="E96" t="s">
-        <v>524</v>
-      </c>
-      <c r="F96" t="s">
-        <v>525</v>
-      </c>
-      <c r="G96" t="s">
-        <v>15</v>
-      </c>
-      <c r="H96" t="s">
-        <v>41</v>
-      </c>
-      <c r="I96" t="s">
-        <v>60</v>
-      </c>
-      <c r="J96" t="s">
-        <v>527</v>
-      </c>
-      <c r="K96" t="s">
-        <v>15</v>
-      </c>
-      <c r="L96" t="s">
-        <v>526</v>
-      </c>
-      <c r="M96" t="s">
-        <v>78</v>
-      </c>
-      <c r="N96" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>528</v>
-      </c>
-      <c r="B97" t="s">
-        <v>529</v>
-      </c>
-      <c r="C97" t="s">
-        <v>100</v>
-      </c>
-      <c r="D97" t="s">
-        <v>17</v>
-      </c>
-      <c r="E97" t="s">
-        <v>530</v>
-      </c>
-      <c r="F97" t="s">
-        <v>531</v>
-      </c>
-      <c r="G97" t="s">
-        <v>427</v>
-      </c>
-      <c r="H97" t="s">
-        <v>41</v>
-      </c>
-      <c r="I97" t="s">
-        <v>60</v>
-      </c>
-      <c r="J97" t="s">
-        <v>533</v>
-      </c>
-      <c r="K97" t="s">
-        <v>15</v>
-      </c>
-      <c r="L97" t="s">
-        <v>532</v>
-      </c>
-      <c r="M97" t="s">
-        <v>21</v>
-      </c>
-      <c r="N97" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>534</v>
-      </c>
-      <c r="B98" t="s">
-        <v>535</v>
-      </c>
-      <c r="C98" t="s">
-        <v>16</v>
-      </c>
-      <c r="D98" t="s">
-        <v>17</v>
-      </c>
-      <c r="E98" t="s">
-        <v>536</v>
-      </c>
-      <c r="F98" t="s">
-        <v>96</v>
-      </c>
-      <c r="G98" t="s">
-        <v>15</v>
-      </c>
-      <c r="H98" t="s">
-        <v>23</v>
-      </c>
-      <c r="I98" t="s">
-        <v>52</v>
-      </c>
-      <c r="J98" t="s">
-        <v>538</v>
-      </c>
-      <c r="K98" t="s">
-        <v>15</v>
-      </c>
-      <c r="L98" t="s">
-        <v>537</v>
-      </c>
-      <c r="M98" t="s">
-        <v>67</v>
-      </c>
-      <c r="N98" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>539</v>
-      </c>
-      <c r="B99" t="s">
-        <v>540</v>
-      </c>
-      <c r="C99" t="s">
-        <v>16</v>
-      </c>
-      <c r="D99" t="s">
-        <v>17</v>
-      </c>
-      <c r="E99" t="s">
-        <v>541</v>
-      </c>
-      <c r="F99" t="s">
-        <v>542</v>
-      </c>
-      <c r="G99" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" t="s">
-        <v>41</v>
-      </c>
-      <c r="I99" t="s">
-        <v>50</v>
-      </c>
-      <c r="J99" t="s">
-        <v>544</v>
-      </c>
-      <c r="K99" t="s">
-        <v>15</v>
-      </c>
-      <c r="L99" t="s">
-        <v>543</v>
-      </c>
-      <c r="M99" t="s">
-        <v>67</v>
-      </c>
-      <c r="N99" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>545</v>
-      </c>
-      <c r="B100" t="s">
-        <v>546</v>
-      </c>
-      <c r="C100" t="s">
-        <v>100</v>
-      </c>
-      <c r="D100" t="s">
-        <v>17</v>
-      </c>
-      <c r="E100" t="s">
-        <v>547</v>
-      </c>
-      <c r="F100" t="s">
-        <v>548</v>
-      </c>
-      <c r="G100" t="s">
-        <v>65</v>
-      </c>
-      <c r="H100" t="s">
-        <v>41</v>
-      </c>
-      <c r="I100" t="s">
-        <v>56</v>
-      </c>
-      <c r="J100" t="s">
-        <v>550</v>
-      </c>
-      <c r="K100" t="s">
-        <v>15</v>
-      </c>
-      <c r="L100" t="s">
-        <v>549</v>
-      </c>
-      <c r="M100" t="s">
-        <v>21</v>
-      </c>
-      <c r="N100" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>551</v>
-      </c>
-      <c r="B101" t="s">
-        <v>552</v>
-      </c>
-      <c r="C101" t="s">
-        <v>16</v>
-      </c>
-      <c r="D101" t="s">
-        <v>72</v>
-      </c>
-      <c r="E101" t="s">
-        <v>553</v>
-      </c>
-      <c r="F101" t="s">
-        <v>367</v>
-      </c>
-      <c r="G101" t="s">
-        <v>15</v>
-      </c>
-      <c r="H101" t="s">
-        <v>41</v>
-      </c>
-      <c r="I101" t="s">
-        <v>60</v>
-      </c>
-      <c r="J101" t="s">
-        <v>555</v>
-      </c>
-      <c r="K101" t="s">
-        <v>15</v>
-      </c>
-      <c r="L101" t="s">
-        <v>554</v>
-      </c>
-      <c r="M101" t="s">
-        <v>78</v>
-      </c>
-      <c r="N101" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N101"/>
+  <autoFilter ref="A1:N95"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$90</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="501">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -125,9 +125,6 @@
     <t>11/06/2026 14:22:02</t>
   </si>
   <si>
-    <t>__expression_step_184_</t>
-  </si>
-  <si>
     <t>BO Homologation: Saisie GAIA</t>
   </si>
   <si>
@@ -494,9 +491,6 @@
     <t>27/06/2026 17:05:02</t>
   </si>
   <si>
-    <t>__expression_step_181_</t>
-  </si>
-  <si>
     <t>64766439</t>
   </si>
   <si>
@@ -734,9 +728,6 @@
     <t>23/06/2026 15:47:28</t>
   </si>
   <si>
-    <t>17/06/2026 16:47:14</t>
-  </si>
-  <si>
     <t>65040167</t>
   </si>
   <si>
@@ -764,9 +755,6 @@
     <t>17/06/2026 12:56:35</t>
   </si>
   <si>
-    <t>BGFIBANK / MARCORY</t>
-  </si>
-  <si>
     <t>AGENCE BGFI BANK DE MARCORY</t>
   </si>
   <si>
@@ -782,9 +770,6 @@
     <t>17/06/2026 13:03:46</t>
   </si>
   <si>
-    <t>BGFIBANK / PLATEAU</t>
-  </si>
-  <si>
     <t>AGENCE BGFI BANK DU PLATEAU</t>
   </si>
   <si>
@@ -965,9 +950,6 @@
     <t>17/06/2026 14:40:25</t>
   </si>
   <si>
-    <t>BGFIBANK / RIVIERA YAYA</t>
-  </si>
-  <si>
     <t>AGENCE BGFI BANK DE RIVIERA FAYA</t>
   </si>
   <si>
@@ -1166,15 +1148,9 @@
     <t>2721712130</t>
   </si>
   <si>
-    <t>22/06/2026 11:45:01</t>
-  </si>
-  <si>
     <t>22/06/2026 13:56:57</t>
   </si>
   <si>
-    <t>22/06/2026 12:31:56</t>
-  </si>
-  <si>
     <t>65283747</t>
   </si>
   <si>
@@ -1515,9 +1491,6 @@
   </si>
   <si>
     <t>27/06/2026 14:10:39</t>
-  </si>
-  <si>
-    <t>BGFI</t>
   </si>
   <si>
     <t>SYTHD190141</t>
@@ -1936,7 +1909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -2045,10 +2018,10 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -2060,39 +2033,39 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
         <v>35</v>
       </c>
-      <c r="G3" t="s">
-        <v>36</v>
-      </c>
       <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
         <v>40</v>
       </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>41</v>
-      </c>
       <c r="K3" t="s">
         <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M3" t="s">
         <v>24</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
         <v>43</v>
-      </c>
-      <c r="B4" t="s">
-        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -2104,39 +2077,39 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
         <v>28</v>
       </c>
       <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
         <v>48</v>
       </c>
-      <c r="J4" t="s">
-        <v>49</v>
-      </c>
       <c r="K4" t="s">
         <v>16</v>
       </c>
       <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" t="s">
         <v>46</v>
       </c>
-      <c r="M4" t="s">
-        <v>47</v>
-      </c>
       <c r="N4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
         <v>51</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -2148,25 +2121,25 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K5" t="s">
         <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M5" t="s">
         <v>24</v>
@@ -2177,524 +2150,524 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
         <v>56</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
         <v>57</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>58</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>59</v>
-      </c>
-      <c r="G6" t="s">
-        <v>60</v>
       </c>
       <c r="H6" t="s">
         <v>28</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K6" t="s">
         <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
         <v>64</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
         <v>65</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>66</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>67</v>
       </c>
-      <c r="G7" t="s">
-        <v>68</v>
-      </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" t="s">
         <v>29</v>
       </c>
       <c r="J7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M7" t="s">
         <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
         <v>72</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" t="s">
         <v>73</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" t="s">
-        <v>74</v>
-      </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" t="s">
         <v>29</v>
       </c>
       <c r="J8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K8" t="s">
         <v>16</v>
       </c>
       <c r="L8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M8" t="s">
         <v>24</v>
       </c>
       <c r="N8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
         <v>78</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>79</v>
-      </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
         <v>29</v>
       </c>
       <c r="J9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K9" t="s">
         <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M9" t="s">
         <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
         <v>82</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
         <v>83</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>84</v>
       </c>
-      <c r="F10" t="s">
-        <v>85</v>
-      </c>
       <c r="G10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K10" t="s">
         <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M10" t="s">
         <v>24</v>
       </c>
       <c r="N10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
         <v>89</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" t="s">
         <v>90</v>
       </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" t="s">
-        <v>91</v>
-      </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H11" t="s">
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s">
         <v>16</v>
       </c>
       <c r="L11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M11" t="s">
         <v>24</v>
       </c>
       <c r="N11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" t="s">
         <v>94</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
         <v>95</v>
       </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" t="s">
-        <v>96</v>
-      </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I12" t="s">
         <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K12" t="s">
         <v>16</v>
       </c>
       <c r="L12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M12" t="s">
         <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" t="s">
         <v>100</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
         <v>101</v>
       </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" t="s">
-        <v>102</v>
-      </c>
       <c r="G13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I13" t="s">
         <v>29</v>
       </c>
       <c r="J13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K13" t="s">
         <v>16</v>
       </c>
       <c r="L13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M13" t="s">
         <v>24</v>
       </c>
       <c r="N13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" t="s">
         <v>105</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" t="s">
         <v>106</v>
       </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F14" t="s">
-        <v>107</v>
-      </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I14" t="s">
         <v>29</v>
       </c>
       <c r="J14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K14" t="s">
         <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M14" t="s">
         <v>24</v>
       </c>
       <c r="N14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" t="s">
         <v>110</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
         <v>111</v>
       </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>112</v>
       </c>
-      <c r="F15" t="s">
-        <v>113</v>
-      </c>
       <c r="G15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
         <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K15" t="s">
         <v>16</v>
       </c>
       <c r="L15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M15" t="s">
         <v>24</v>
       </c>
       <c r="N15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" t="s">
         <v>117</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" t="s">
         <v>118</v>
       </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" t="s">
-        <v>119</v>
-      </c>
       <c r="G16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I16" t="s">
         <v>29</v>
       </c>
       <c r="J16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K16" t="s">
         <v>16</v>
       </c>
       <c r="L16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M16" t="s">
         <v>24</v>
       </c>
       <c r="N16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" t="s">
         <v>122</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" t="s">
         <v>123</v>
       </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" t="s">
-        <v>124</v>
-      </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I17" t="s">
         <v>29</v>
       </c>
       <c r="J17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K17" t="s">
         <v>16</v>
       </c>
       <c r="L17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M17" t="s">
         <v>24</v>
@@ -2705,55 +2678,55 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" t="s">
         <v>127</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
         <v>128</v>
       </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>129</v>
       </c>
-      <c r="F18" t="s">
-        <v>130</v>
-      </c>
       <c r="G18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" t="s">
+        <v>133</v>
+      </c>
+      <c r="J18" t="s">
         <v>134</v>
       </c>
-      <c r="J18" t="s">
-        <v>135</v>
-      </c>
       <c r="K18" t="s">
         <v>16</v>
       </c>
       <c r="L18" t="s">
+        <v>131</v>
+      </c>
+      <c r="M18" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" t="s">
         <v>132</v>
-      </c>
-      <c r="M18" t="s">
-        <v>47</v>
-      </c>
-      <c r="N18" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" t="s">
         <v>136</v>
       </c>
-      <c r="B19" t="s">
-        <v>137</v>
-      </c>
       <c r="C19" t="s">
         <v>17</v>
       </c>
@@ -2761,75 +2734,75 @@
         <v>18</v>
       </c>
       <c r="E19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" t="s">
         <v>129</v>
       </c>
-      <c r="F19" t="s">
-        <v>130</v>
-      </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s">
         <v>28</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K19" t="s">
         <v>16</v>
       </c>
       <c r="L19" t="s">
+        <v>131</v>
+      </c>
+      <c r="M19" t="s">
+        <v>46</v>
+      </c>
+      <c r="N19" t="s">
         <v>132</v>
-      </c>
-      <c r="M19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N19" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s">
         <v>139</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" t="s">
         <v>140</v>
       </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>129</v>
-      </c>
-      <c r="F20" t="s">
-        <v>141</v>
-      </c>
       <c r="G20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H20" t="s">
         <v>28</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K20" t="s">
         <v>16</v>
       </c>
       <c r="L20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N20" t="s">
         <v>25</v>
@@ -2837,98 +2810,98 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" t="s">
         <v>146</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>147</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
         <v>148</v>
       </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>149</v>
-      </c>
-      <c r="F21" t="s">
-        <v>150</v>
       </c>
       <c r="G21" t="s">
         <v>22</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I21" t="s">
+        <v>151</v>
+      </c>
+      <c r="J21" t="s">
         <v>152</v>
       </c>
-      <c r="J21" t="s">
-        <v>153</v>
-      </c>
       <c r="K21" t="s">
         <v>16</v>
       </c>
       <c r="L21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s">
         <v>24</v>
       </c>
       <c r="N21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" t="s">
         <v>155</v>
-      </c>
-      <c r="B22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" t="s">
-        <v>145</v>
-      </c>
-      <c r="E22" t="s">
-        <v>149</v>
-      </c>
-      <c r="F22" t="s">
-        <v>157</v>
       </c>
       <c r="G22" t="s">
         <v>22</v>
       </c>
       <c r="H22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I22" t="s">
         <v>29</v>
       </c>
       <c r="J22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K22" t="s">
         <v>16</v>
       </c>
       <c r="L22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M22" t="s">
         <v>24</v>
       </c>
       <c r="N22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -2940,39 +2913,39 @@
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I23" t="s">
         <v>29</v>
       </c>
       <c r="J23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K23" t="s">
         <v>16</v>
       </c>
       <c r="L23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M23" t="s">
         <v>24</v>
       </c>
       <c r="N23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -2987,36 +2960,36 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H24" t="s">
         <v>28</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K24" t="s">
         <v>16</v>
       </c>
       <c r="L24" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M24" t="s">
         <v>24</v>
       </c>
       <c r="N24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -3028,39 +3001,39 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I25" t="s">
         <v>29</v>
       </c>
       <c r="J25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K25" t="s">
         <v>16</v>
       </c>
       <c r="L25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M25" t="s">
         <v>24</v>
       </c>
       <c r="N25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
@@ -3072,39 +3045,39 @@
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I26" t="s">
         <v>29</v>
       </c>
       <c r="J26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K26" t="s">
         <v>16</v>
       </c>
       <c r="L26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M26" t="s">
         <v>24</v>
       </c>
       <c r="N26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
@@ -3119,36 +3092,36 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I27" t="s">
         <v>29</v>
       </c>
       <c r="J27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K27" t="s">
         <v>16</v>
       </c>
       <c r="L27" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s">
         <v>24</v>
       </c>
       <c r="N27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -3163,36 +3136,36 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H28" t="s">
         <v>28</v>
       </c>
       <c r="I28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K28" t="s">
         <v>16</v>
       </c>
       <c r="L28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M28" t="s">
         <v>24</v>
       </c>
       <c r="N28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
@@ -3204,39 +3177,39 @@
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I29" t="s">
         <v>29</v>
       </c>
       <c r="J29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K29" t="s">
         <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s">
         <v>24</v>
       </c>
       <c r="N29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
@@ -3248,347 +3221,347 @@
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I30" t="s">
         <v>29</v>
       </c>
       <c r="J30" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K30" t="s">
         <v>16</v>
       </c>
       <c r="L30" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M30" t="s">
         <v>24</v>
       </c>
       <c r="N30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>191</v>
+      </c>
+      <c r="B31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
         <v>193</v>
       </c>
-      <c r="B31" t="s">
+      <c r="F31" t="s">
         <v>194</v>
       </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>195</v>
-      </c>
-      <c r="F31" t="s">
-        <v>196</v>
-      </c>
-      <c r="G31" t="s">
-        <v>197</v>
       </c>
       <c r="H31" t="s">
         <v>28</v>
       </c>
       <c r="I31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J31" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K31" t="s">
         <v>16</v>
       </c>
       <c r="L31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>198</v>
+      </c>
+      <c r="B32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" t="s">
         <v>200</v>
-      </c>
-      <c r="B32" t="s">
-        <v>201</v>
-      </c>
-      <c r="C32" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" t="s">
-        <v>195</v>
-      </c>
-      <c r="F32" t="s">
-        <v>196</v>
-      </c>
-      <c r="G32" t="s">
-        <v>202</v>
       </c>
       <c r="H32" t="s">
         <v>28</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J32" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K32" t="s">
         <v>16</v>
       </c>
       <c r="L32" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
         <v>205</v>
       </c>
-      <c r="B33" t="s">
+      <c r="F33" t="s">
         <v>206</v>
       </c>
-      <c r="C33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" t="s">
-        <v>207</v>
-      </c>
-      <c r="F33" t="s">
-        <v>208</v>
-      </c>
       <c r="G33" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H33" t="s">
         <v>28</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K33" t="s">
         <v>16</v>
       </c>
       <c r="L33" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>209</v>
+      </c>
+      <c r="B34" t="s">
+        <v>210</v>
+      </c>
+      <c r="C34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" t="s">
         <v>211</v>
       </c>
-      <c r="B34" t="s">
+      <c r="E34" t="s">
         <v>212</v>
       </c>
-      <c r="C34" t="s">
-        <v>144</v>
-      </c>
-      <c r="D34" t="s">
-        <v>213</v>
-      </c>
-      <c r="E34" t="s">
-        <v>214</v>
-      </c>
       <c r="F34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G34" t="s">
         <v>16</v>
       </c>
       <c r="H34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I34" t="s">
         <v>29</v>
       </c>
       <c r="J34" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K34" t="s">
         <v>16</v>
       </c>
       <c r="L34" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M34" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>216</v>
+      </c>
+      <c r="B35" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s">
         <v>218</v>
       </c>
-      <c r="B35" t="s">
+      <c r="F35" t="s">
         <v>219</v>
       </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" t="s">
-        <v>220</v>
-      </c>
-      <c r="F35" t="s">
-        <v>221</v>
-      </c>
       <c r="G35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I35" t="s">
         <v>29</v>
       </c>
       <c r="J35" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K35" t="s">
         <v>16</v>
       </c>
       <c r="L35" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M35" t="s">
         <v>24</v>
       </c>
       <c r="N35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>218</v>
+      </c>
+      <c r="F36" t="s">
         <v>224</v>
-      </c>
-      <c r="B36" t="s">
-        <v>225</v>
-      </c>
-      <c r="C36" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" t="s">
-        <v>220</v>
-      </c>
-      <c r="F36" t="s">
-        <v>226</v>
       </c>
       <c r="G36" t="s">
         <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I36" t="s">
         <v>29</v>
       </c>
       <c r="J36" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K36" t="s">
         <v>16</v>
       </c>
       <c r="L36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M36" t="s">
         <v>24</v>
       </c>
       <c r="N36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" t="s">
+        <v>228</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>218</v>
+      </c>
+      <c r="F37" t="s">
         <v>229</v>
       </c>
-      <c r="B37" t="s">
-        <v>230</v>
-      </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" t="s">
-        <v>220</v>
-      </c>
-      <c r="F37" t="s">
-        <v>231</v>
-      </c>
       <c r="G37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I37" t="s">
         <v>29</v>
       </c>
       <c r="J37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K37" t="s">
         <v>16</v>
       </c>
       <c r="L37" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M37" t="s">
         <v>24</v>
       </c>
       <c r="N37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B38" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
@@ -3597,86 +3570,86 @@
         <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F38" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G38" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J38" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="K38" t="s">
-        <v>234</v>
+        <v>16</v>
       </c>
       <c r="L38" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M38" t="s">
         <v>24</v>
       </c>
       <c r="N38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" t="s">
+        <v>233</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>218</v>
+      </c>
+      <c r="F39" t="s">
+        <v>234</v>
+      </c>
+      <c r="G39" t="s">
+        <v>60</v>
+      </c>
+      <c r="H39" t="s">
+        <v>41</v>
+      </c>
+      <c r="I39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J39" t="s">
+        <v>237</v>
+      </c>
+      <c r="K39" t="s">
+        <v>236</v>
+      </c>
+      <c r="L39" t="s">
         <v>235</v>
       </c>
-      <c r="B39" t="s">
-        <v>236</v>
-      </c>
-      <c r="C39" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" t="s">
-        <v>220</v>
-      </c>
-      <c r="F39" t="s">
-        <v>237</v>
-      </c>
-      <c r="G39" t="s">
-        <v>61</v>
-      </c>
-      <c r="H39" t="s">
-        <v>40</v>
-      </c>
-      <c r="I39" t="s">
-        <v>29</v>
-      </c>
-      <c r="J39" t="s">
-        <v>241</v>
-      </c>
-      <c r="K39" t="s">
-        <v>16</v>
-      </c>
-      <c r="L39" t="s">
-        <v>238</v>
-      </c>
       <c r="M39" t="s">
         <v>24</v>
       </c>
       <c r="N39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B40" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
@@ -3685,42 +3658,42 @@
         <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F40" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="G40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H40" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J40" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K40" t="s">
-        <v>239</v>
+        <v>16</v>
       </c>
       <c r="L40" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M40" t="s">
         <v>24</v>
       </c>
       <c r="N40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B41" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
@@ -3729,42 +3702,42 @@
         <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="F41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G41" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="H41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I41" t="s">
         <v>29</v>
       </c>
       <c r="J41" t="s">
+        <v>248</v>
+      </c>
+      <c r="K41" t="s">
+        <v>16</v>
+      </c>
+      <c r="L41" t="s">
         <v>247</v>
       </c>
-      <c r="K41" t="s">
-        <v>16</v>
-      </c>
-      <c r="L41" t="s">
-        <v>246</v>
-      </c>
       <c r="M41" t="s">
         <v>24</v>
       </c>
       <c r="N41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B42" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
@@ -3773,7 +3746,7 @@
         <v>18</v>
       </c>
       <c r="E42" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="F42" t="s">
         <v>251</v>
@@ -3782,7 +3755,7 @@
         <v>21</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I42" t="s">
         <v>29</v>
@@ -3800,7 +3773,7 @@
         <v>24</v>
       </c>
       <c r="N42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
@@ -3817,7 +3790,7 @@
         <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F43" t="s">
         <v>256</v>
@@ -3826,7 +3799,7 @@
         <v>21</v>
       </c>
       <c r="H43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I43" t="s">
         <v>29</v>
@@ -3844,7 +3817,7 @@
         <v>24</v>
       </c>
       <c r="N43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
@@ -3861,7 +3834,7 @@
         <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F44" t="s">
         <v>261</v>
@@ -3870,7 +3843,7 @@
         <v>21</v>
       </c>
       <c r="H44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I44" t="s">
         <v>29</v>
@@ -3888,7 +3861,7 @@
         <v>24</v>
       </c>
       <c r="N44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
@@ -3905,16 +3878,16 @@
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F45" t="s">
         <v>266</v>
       </c>
       <c r="G45" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I45" t="s">
         <v>29</v>
@@ -3932,7 +3905,7 @@
         <v>24</v>
       </c>
       <c r="N45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
@@ -3949,16 +3922,16 @@
         <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F46" t="s">
         <v>271</v>
       </c>
       <c r="G46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I46" t="s">
         <v>29</v>
@@ -3976,7 +3949,7 @@
         <v>24</v>
       </c>
       <c r="N46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
@@ -3993,16 +3966,16 @@
         <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F47" t="s">
         <v>276</v>
       </c>
       <c r="G47" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="H47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I47" t="s">
         <v>29</v>
@@ -4020,7 +3993,7 @@
         <v>24</v>
       </c>
       <c r="N47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -4037,16 +4010,16 @@
         <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F48" t="s">
         <v>281</v>
       </c>
       <c r="G48" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I48" t="s">
         <v>29</v>
@@ -4064,7 +4037,7 @@
         <v>24</v>
       </c>
       <c r="N48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
@@ -4081,16 +4054,16 @@
         <v>18</v>
       </c>
       <c r="E49" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F49" t="s">
         <v>286</v>
       </c>
       <c r="G49" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="H49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I49" t="s">
         <v>29</v>
@@ -4108,7 +4081,7 @@
         <v>24</v>
       </c>
       <c r="N49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
@@ -4125,16 +4098,16 @@
         <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F50" t="s">
         <v>291</v>
       </c>
       <c r="G50" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I50" t="s">
         <v>29</v>
@@ -4152,7 +4125,7 @@
         <v>24</v>
       </c>
       <c r="N50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
@@ -4169,16 +4142,16 @@
         <v>18</v>
       </c>
       <c r="E51" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F51" t="s">
         <v>296</v>
       </c>
       <c r="G51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I51" t="s">
         <v>29</v>
@@ -4196,7 +4169,7 @@
         <v>24</v>
       </c>
       <c r="N51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
@@ -4213,16 +4186,16 @@
         <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F52" t="s">
         <v>301</v>
       </c>
       <c r="G52" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="H52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I52" t="s">
         <v>29</v>
@@ -4240,7 +4213,7 @@
         <v>24</v>
       </c>
       <c r="N52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
@@ -4257,16 +4230,16 @@
         <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F53" t="s">
         <v>306</v>
       </c>
       <c r="G53" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I53" t="s">
         <v>29</v>
@@ -4284,7 +4257,7 @@
         <v>24</v>
       </c>
       <c r="N53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
@@ -4301,104 +4274,104 @@
         <v>18</v>
       </c>
       <c r="E54" t="s">
+        <v>218</v>
+      </c>
+      <c r="F54" t="s">
         <v>311</v>
       </c>
-      <c r="F54" t="s">
-        <v>312</v>
-      </c>
       <c r="G54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I54" t="s">
         <v>29</v>
       </c>
       <c r="J54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K54" t="s">
         <v>16</v>
       </c>
       <c r="L54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M54" t="s">
         <v>24</v>
       </c>
       <c r="N54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>314</v>
+      </c>
+      <c r="B55" t="s">
         <v>315</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" t="s">
+        <v>218</v>
+      </c>
+      <c r="F55" t="s">
         <v>316</v>
       </c>
-      <c r="C55" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" t="s">
-        <v>220</v>
-      </c>
-      <c r="F55" t="s">
-        <v>317</v>
-      </c>
       <c r="G55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I55" t="s">
         <v>29</v>
       </c>
       <c r="J55" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K55" t="s">
         <v>16</v>
       </c>
       <c r="L55" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M55" t="s">
         <v>24</v>
       </c>
       <c r="N55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>319</v>
+      </c>
+      <c r="B56" t="s">
         <v>320</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" t="s">
+        <v>218</v>
+      </c>
+      <c r="F56" t="s">
         <v>321</v>
       </c>
-      <c r="C56" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" t="s">
-        <v>220</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>322</v>
       </c>
-      <c r="G56" t="s">
-        <v>86</v>
-      </c>
       <c r="H56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I56" t="s">
         <v>29</v>
@@ -4416,7 +4389,7 @@
         <v>24</v>
       </c>
       <c r="N56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
@@ -4433,239 +4406,239 @@
         <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F57" t="s">
         <v>327</v>
       </c>
       <c r="G57" t="s">
-        <v>328</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I57" t="s">
         <v>29</v>
       </c>
       <c r="J57" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K57" t="s">
         <v>16</v>
       </c>
       <c r="L57" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M57" t="s">
         <v>24</v>
       </c>
       <c r="N57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>330</v>
+      </c>
+      <c r="B58" t="s">
         <v>331</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" t="s">
+        <v>218</v>
+      </c>
+      <c r="F58" t="s">
         <v>332</v>
       </c>
-      <c r="C58" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" t="s">
-        <v>220</v>
-      </c>
-      <c r="F58" t="s">
-        <v>333</v>
-      </c>
       <c r="G58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I58" t="s">
         <v>29</v>
       </c>
       <c r="J58" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K58" t="s">
         <v>16</v>
       </c>
       <c r="L58" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M58" t="s">
         <v>24</v>
       </c>
       <c r="N58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>335</v>
+      </c>
+      <c r="B59" t="s">
         <v>336</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>218</v>
+      </c>
+      <c r="F59" t="s">
         <v>337</v>
       </c>
-      <c r="C59" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" t="s">
-        <v>220</v>
-      </c>
-      <c r="F59" t="s">
-        <v>338</v>
-      </c>
       <c r="G59" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="H59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I59" t="s">
         <v>29</v>
       </c>
       <c r="J59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K59" t="s">
         <v>16</v>
       </c>
       <c r="L59" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M59" t="s">
         <v>24</v>
       </c>
       <c r="N59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>340</v>
+      </c>
+      <c r="B60" t="s">
         <v>341</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" t="s">
+        <v>218</v>
+      </c>
+      <c r="F60" t="s">
         <v>342</v>
       </c>
-      <c r="C60" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" t="s">
-        <v>220</v>
-      </c>
-      <c r="F60" t="s">
-        <v>343</v>
-      </c>
       <c r="G60" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="H60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I60" t="s">
         <v>29</v>
       </c>
       <c r="J60" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K60" t="s">
         <v>16</v>
       </c>
       <c r="L60" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="M60" t="s">
         <v>24</v>
       </c>
       <c r="N60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
+        <v>345</v>
+      </c>
+      <c r="B61" t="s">
         <v>346</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" t="s">
+        <v>218</v>
+      </c>
+      <c r="F61" t="s">
         <v>347</v>
       </c>
-      <c r="C61" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" t="s">
-        <v>220</v>
-      </c>
-      <c r="F61" t="s">
-        <v>348</v>
-      </c>
       <c r="G61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I61" t="s">
         <v>29</v>
       </c>
       <c r="J61" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K61" t="s">
         <v>16</v>
       </c>
       <c r="L61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M61" t="s">
         <v>24</v>
       </c>
       <c r="N61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>350</v>
+      </c>
+      <c r="B62" t="s">
         <v>351</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
+        <v>218</v>
+      </c>
+      <c r="F62" t="s">
         <v>352</v>
       </c>
-      <c r="C62" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" t="s">
-        <v>220</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>353</v>
       </c>
-      <c r="G62" t="s">
-        <v>86</v>
-      </c>
       <c r="H62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I62" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J62" t="s">
         <v>355</v>
@@ -4680,7 +4653,7 @@
         <v>24</v>
       </c>
       <c r="N62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
@@ -4697,16 +4670,16 @@
         <v>18</v>
       </c>
       <c r="E63" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F63" t="s">
         <v>358</v>
       </c>
       <c r="G63" t="s">
-        <v>359</v>
+        <v>60</v>
       </c>
       <c r="H63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I63" t="s">
         <v>26</v>
@@ -4724,7 +4697,7 @@
         <v>24</v>
       </c>
       <c r="N63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
@@ -4741,63 +4714,63 @@
         <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F64" t="s">
         <v>364</v>
       </c>
       <c r="G64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H64" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I64" t="s">
         <v>26</v>
       </c>
       <c r="J64" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K64" t="s">
         <v>16</v>
       </c>
       <c r="L64" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M64" t="s">
         <v>24</v>
       </c>
       <c r="N64" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>367</v>
+      </c>
+      <c r="B65" t="s">
         <v>368</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
+        <v>147</v>
+      </c>
+      <c r="D65" t="s">
+        <v>211</v>
+      </c>
+      <c r="E65" t="s">
         <v>369</v>
-      </c>
-      <c r="C65" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" t="s">
-        <v>220</v>
       </c>
       <c r="F65" t="s">
         <v>370</v>
       </c>
       <c r="G65" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="H65" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I65" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="J65" t="s">
         <v>372</v>
@@ -4809,10 +4782,10 @@
         <v>371</v>
       </c>
       <c r="M65" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="N65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
@@ -4823,10 +4796,10 @@
         <v>374</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D66" t="s">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="E66" t="s">
         <v>375</v>
@@ -4835,16 +4808,16 @@
         <v>376</v>
       </c>
       <c r="G66" t="s">
-        <v>16</v>
+        <v>359</v>
       </c>
       <c r="H66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I66" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="J66" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K66" t="s">
         <v>16</v>
@@ -4853,259 +4826,259 @@
         <v>377</v>
       </c>
       <c r="M66" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="N66" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B67" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="E67" t="s">
-        <v>375</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="G67" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="H67" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I67" t="s">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="J67" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="K67" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="L67" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="M67" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="N67" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B68" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F68" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G68" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I68" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J68" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K68" t="s">
         <v>16</v>
       </c>
       <c r="L68" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="M68" t="s">
         <v>24</v>
       </c>
       <c r="N68" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B69" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C69" t="s">
         <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>394</v>
       </c>
       <c r="F69" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G69" t="s">
-        <v>61</v>
+        <v>396</v>
       </c>
       <c r="H69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I69" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J69" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K69" t="s">
         <v>16</v>
       </c>
       <c r="L69" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="M69" t="s">
         <v>24</v>
       </c>
       <c r="N69" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B70" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="E70" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F70" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="G70" t="s">
-        <v>397</v>
+        <v>16</v>
       </c>
       <c r="H70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I70" t="s">
-        <v>32</v>
+        <v>404</v>
       </c>
       <c r="J70" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="K70" t="s">
         <v>16</v>
       </c>
       <c r="L70" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="M70" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="N70" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B71" t="s">
+        <v>407</v>
+      </c>
+      <c r="C71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71" t="s">
+        <v>211</v>
+      </c>
+      <c r="E71" t="s">
         <v>401</v>
       </c>
-      <c r="C71" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" t="s">
-        <v>18</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>402</v>
       </c>
-      <c r="F71" t="s">
-        <v>403</v>
-      </c>
       <c r="G71" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" t="s">
+        <v>39</v>
+      </c>
+      <c r="I71" t="s">
         <v>404</v>
       </c>
-      <c r="H71" t="s">
-        <v>40</v>
-      </c>
-      <c r="I71" t="s">
-        <v>26</v>
-      </c>
       <c r="J71" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="K71" t="s">
         <v>16</v>
       </c>
       <c r="L71" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M71" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="N71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B72" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C72" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D72" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E72" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="F72" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="G72" t="s">
         <v>16</v>
       </c>
       <c r="H72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I72" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="J72" t="s">
         <v>413</v>
@@ -5114,13 +5087,13 @@
         <v>16</v>
       </c>
       <c r="L72" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M72" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N72" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
@@ -5131,113 +5104,113 @@
         <v>415</v>
       </c>
       <c r="C73" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D73" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E73" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="F73" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="G73" t="s">
         <v>16</v>
       </c>
       <c r="H73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I73" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="J73" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K73" t="s">
         <v>16</v>
       </c>
       <c r="L73" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M73" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N73" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B74" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D74" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E74" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="F74" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="G74" t="s">
         <v>16</v>
       </c>
       <c r="H74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I74" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="J74" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K74" t="s">
         <v>16</v>
       </c>
       <c r="L74" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M74" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N74" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B75" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C75" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E75" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="F75" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="G75" t="s">
         <v>16</v>
       </c>
       <c r="H75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I75" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="J75" t="s">
         <v>427</v>
@@ -5249,10 +5222,10 @@
         <v>426</v>
       </c>
       <c r="M75" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N75" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
@@ -5263,550 +5236,550 @@
         <v>429</v>
       </c>
       <c r="C76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D76" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E76" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="F76" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G76" t="s">
         <v>16</v>
       </c>
       <c r="H76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I76" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="J76" t="s">
+        <v>432</v>
+      </c>
+      <c r="K76" t="s">
+        <v>16</v>
+      </c>
+      <c r="L76" t="s">
         <v>431</v>
       </c>
-      <c r="K76" t="s">
-        <v>16</v>
-      </c>
-      <c r="L76" t="s">
-        <v>430</v>
-      </c>
       <c r="M76" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B77" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C77" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D77" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E77" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="F77" t="s">
-        <v>425</v>
+        <v>34</v>
       </c>
       <c r="G77" t="s">
         <v>16</v>
       </c>
       <c r="H77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I77" t="s">
-        <v>412</v>
+        <v>29</v>
       </c>
       <c r="J77" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K77" t="s">
         <v>16</v>
       </c>
       <c r="L77" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M77" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N77" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B78" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C78" t="s">
+        <v>147</v>
+      </c>
+      <c r="D78" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" t="s">
         <v>148</v>
       </c>
-      <c r="D78" t="s">
-        <v>213</v>
-      </c>
-      <c r="E78" t="s">
-        <v>409</v>
-      </c>
       <c r="F78" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G78" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I78" t="s">
-        <v>412</v>
+        <v>26</v>
       </c>
       <c r="J78" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K78" t="s">
         <v>16</v>
       </c>
       <c r="L78" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M78" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="N78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B79" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C79" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D79" t="s">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
-        <v>443</v>
+        <v>148</v>
       </c>
       <c r="F79" t="s">
-        <v>35</v>
+        <v>440</v>
       </c>
       <c r="G79" t="s">
-        <v>16</v>
+        <v>382</v>
       </c>
       <c r="H79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I79" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J79" t="s">
+        <v>446</v>
+      </c>
+      <c r="K79" t="s">
+        <v>16</v>
+      </c>
+      <c r="L79" t="s">
         <v>445</v>
       </c>
-      <c r="K79" t="s">
-        <v>16</v>
-      </c>
-      <c r="L79" t="s">
-        <v>444</v>
-      </c>
       <c r="M79" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="N79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B80" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C80" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>149</v>
+        <v>449</v>
       </c>
       <c r="F80" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G80" t="s">
         <v>21</v>
       </c>
       <c r="H80" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I80" t="s">
         <v>26</v>
       </c>
       <c r="J80" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K80" t="s">
         <v>16</v>
       </c>
       <c r="L80" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M80" t="s">
         <v>24</v>
       </c>
       <c r="N80" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B81" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C81" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
       </c>
       <c r="E81" t="s">
-        <v>149</v>
+        <v>455</v>
       </c>
       <c r="F81" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="G81" t="s">
-        <v>390</v>
+        <v>67</v>
       </c>
       <c r="H81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I81" t="s">
         <v>26</v>
       </c>
       <c r="J81" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="K81" t="s">
         <v>16</v>
       </c>
       <c r="L81" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="M81" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="N81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B82" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C82" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>457</v>
+        <v>401</v>
       </c>
       <c r="F82" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I82" t="s">
         <v>26</v>
       </c>
       <c r="J82" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K82" t="s">
         <v>16</v>
       </c>
       <c r="L82" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M82" t="s">
         <v>24</v>
       </c>
       <c r="N82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B83" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C83" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="F83" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G83" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="H83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I83" t="s">
         <v>26</v>
       </c>
       <c r="J83" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K83" t="s">
         <v>16</v>
       </c>
       <c r="L83" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B84" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="F84" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G84" t="s">
-        <v>36</v>
+        <v>472</v>
       </c>
       <c r="H84" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I84" t="s">
         <v>26</v>
       </c>
       <c r="J84" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K84" t="s">
         <v>16</v>
       </c>
       <c r="L84" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M84" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="N84" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>475</v>
+      </c>
+      <c r="B85" t="s">
+        <v>476</v>
+      </c>
+      <c r="C85" t="s">
+        <v>147</v>
+      </c>
+      <c r="D85" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" t="s">
+        <v>401</v>
+      </c>
+      <c r="F85" t="s">
+        <v>466</v>
+      </c>
+      <c r="G85" t="s">
         <v>472</v>
       </c>
-      <c r="B85" t="s">
-        <v>473</v>
-      </c>
-      <c r="C85" t="s">
-        <v>148</v>
-      </c>
-      <c r="D85" t="s">
-        <v>18</v>
-      </c>
-      <c r="E85" t="s">
-        <v>409</v>
-      </c>
-      <c r="F85" t="s">
-        <v>474</v>
-      </c>
-      <c r="G85" t="s">
-        <v>114</v>
-      </c>
       <c r="H85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I85" t="s">
         <v>26</v>
       </c>
       <c r="J85" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K85" t="s">
         <v>16</v>
       </c>
       <c r="L85" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M85" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N85" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
       </c>
       <c r="E86" t="s">
-        <v>409</v>
+        <v>481</v>
       </c>
       <c r="F86" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="G86" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I86" t="s">
         <v>26</v>
       </c>
       <c r="J86" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K86" t="s">
         <v>16</v>
       </c>
       <c r="L86" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M86" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N86" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B87" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C87" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>409</v>
+        <v>218</v>
       </c>
       <c r="F87" t="s">
-        <v>474</v>
+        <v>34</v>
       </c>
       <c r="G87" t="s">
-        <v>480</v>
+        <v>130</v>
       </c>
       <c r="H87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I87" t="s">
         <v>26</v>
       </c>
       <c r="J87" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K87" t="s">
         <v>16</v>
       </c>
       <c r="L87" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C88" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>489</v>
+        <v>401</v>
       </c>
       <c r="F88" t="s">
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="G88" t="s">
-        <v>490</v>
+        <v>35</v>
       </c>
       <c r="H88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I88" t="s">
         <v>26</v>
@@ -5821,10 +5794,10 @@
         <v>491</v>
       </c>
       <c r="M88" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="N88" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
@@ -5835,176 +5808,88 @@
         <v>494</v>
       </c>
       <c r="C89" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>495</v>
+        <v>401</v>
       </c>
       <c r="F89" t="s">
-        <v>35</v>
+        <v>402</v>
       </c>
       <c r="G89" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="H89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I89" t="s">
         <v>26</v>
       </c>
       <c r="J89" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K89" t="s">
         <v>16</v>
       </c>
       <c r="L89" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M89" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="N89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
+        <v>497</v>
+      </c>
+      <c r="B90" t="s">
         <v>498</v>
       </c>
-      <c r="B90" t="s">
-        <v>499</v>
-      </c>
       <c r="C90" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
       </c>
       <c r="E90" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="F90" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="G90" t="s">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="H90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I90" t="s">
         <v>26</v>
       </c>
       <c r="J90" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K90" t="s">
         <v>16</v>
       </c>
       <c r="L90" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M90" t="s">
         <v>24</v>
       </c>
       <c r="N90" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>502</v>
-      </c>
-      <c r="B91" t="s">
-        <v>503</v>
-      </c>
-      <c r="C91" t="s">
-        <v>148</v>
-      </c>
-      <c r="D91" t="s">
-        <v>18</v>
-      </c>
-      <c r="E91" t="s">
-        <v>409</v>
-      </c>
-      <c r="F91" t="s">
-        <v>410</v>
-      </c>
-      <c r="G91" t="s">
-        <v>114</v>
-      </c>
-      <c r="H91" t="s">
-        <v>40</v>
-      </c>
-      <c r="I91" t="s">
-        <v>26</v>
-      </c>
-      <c r="J91" t="s">
-        <v>505</v>
-      </c>
-      <c r="K91" t="s">
-        <v>16</v>
-      </c>
-      <c r="L91" t="s">
-        <v>504</v>
-      </c>
-      <c r="M91" t="s">
-        <v>24</v>
-      </c>
-      <c r="N91" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>506</v>
-      </c>
-      <c r="B92" t="s">
-        <v>507</v>
-      </c>
-      <c r="C92" t="s">
-        <v>148</v>
-      </c>
-      <c r="D92" t="s">
-        <v>18</v>
-      </c>
-      <c r="E92" t="s">
-        <v>409</v>
-      </c>
-      <c r="F92" t="s">
-        <v>410</v>
-      </c>
-      <c r="G92" t="s">
-        <v>114</v>
-      </c>
-      <c r="H92" t="s">
-        <v>40</v>
-      </c>
-      <c r="I92" t="s">
-        <v>26</v>
-      </c>
-      <c r="J92" t="s">
-        <v>509</v>
-      </c>
-      <c r="K92" t="s">
-        <v>16</v>
-      </c>
-      <c r="L92" t="s">
-        <v>508</v>
-      </c>
-      <c r="M92" t="s">
-        <v>24</v>
-      </c>
-      <c r="N92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N92"/>
+  <autoFilter ref="A1:N90"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$N$55</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="334">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -41,9 +41,6 @@
     <t>SUPPORT</t>
   </si>
   <si>
-    <t>PRODUIT</t>
-  </si>
-  <si>
     <t>DATE CREATION DOSSIER</t>
   </si>
   <si>
@@ -59,21 +56,30 @@
     <t>DEBIT</t>
   </si>
   <si>
-    <t>DEBIT INITIAL</t>
-  </si>
-  <si>
     <t>ETAT TACHE</t>
   </si>
   <si>
     <t>ETAPE</t>
   </si>
   <si>
+    <t>DATE DEBUT</t>
+  </si>
+  <si>
+    <t>DATE FIN</t>
+  </si>
+  <si>
     <t>REFERENCE</t>
   </si>
   <si>
     <t>CARACTERISTIQUE</t>
   </si>
   <si>
+    <t>65047687</t>
+  </si>
+  <si>
+    <t>17/06/2026 14:20:06</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -83,30 +89,132 @@
     <t>fo</t>
   </si>
   <si>
+    <t>BGFIBANK</t>
+  </si>
+  <si>
+    <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/CARRE D'OR</t>
+  </si>
+  <si>
+    <t>6M</t>
+  </si>
+  <si>
+    <t>2M</t>
+  </si>
+  <si>
+    <t>BUVPN250006</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>Nominale</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie GAIA</t>
+  </si>
+  <si>
+    <t>Parametrage facturation</t>
+  </si>
+  <si>
+    <t>En cours</t>
+  </si>
+  <si>
+    <t>Support IP: Correction</t>
+  </si>
+  <si>
+    <t>26/06/2026 16:33:59</t>
+  </si>
+  <si>
+    <t>64552630</t>
+  </si>
+  <si>
+    <t>08/06/2026 16:32:15</t>
+  </si>
+  <si>
+    <t>DREAM COSMETICS</t>
+  </si>
+  <si>
+    <t>YOPOUGON ZONE INDUSTRIELLE</t>
+  </si>
+  <si>
+    <t>100M</t>
+  </si>
+  <si>
+    <t>80M</t>
+  </si>
+  <si>
+    <t>SYTHD200265</t>
+  </si>
+  <si>
+    <t>LSI</t>
+  </si>
+  <si>
+    <t>Backup</t>
+  </si>
+  <si>
+    <t>Offert</t>
+  </si>
+  <si>
+    <t>30/06/2026 19:52:08</t>
+  </si>
+  <si>
+    <t>65548064</t>
+  </si>
+  <si>
+    <t>26/06/2026 17:03:19</t>
+  </si>
+  <si>
+    <t>TERMINAL DE SAN PEDRO</t>
+  </si>
+  <si>
+    <t>SAN PEDRO</t>
+  </si>
+  <si>
+    <t>120M</t>
+  </si>
+  <si>
+    <t>SYTHD170002</t>
+  </si>
+  <si>
+    <t>26/06/2026 17:03:26</t>
+  </si>
+  <si>
+    <t>65395686</t>
+  </si>
+  <si>
+    <t>24/06/2026 11:38:13</t>
+  </si>
+  <si>
+    <t>Transfert</t>
+  </si>
+  <si>
+    <t>fo_virage</t>
+  </si>
+  <si>
+    <t>BANQUE NATIONALE D'INVESTISSEMENT</t>
+  </si>
+  <si>
+    <t>PLATEAU</t>
+  </si>
+  <si>
+    <t>2720209800</t>
+  </si>
+  <si>
+    <t>numerique</t>
+  </si>
+  <si>
+    <t>Ingenieur Projet: Suspension Travaux DOB</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:21:02</t>
+  </si>
+  <si>
     <t>20M</t>
   </si>
   <si>
     <t>10M</t>
   </si>
   <si>
-    <t>BUVPN</t>
-  </si>
-  <si>
-    <t>LS</t>
-  </si>
-  <si>
-    <t>Nominale</t>
-  </si>
-  <si>
-    <t>Support IP: Correction</t>
-  </si>
-  <si>
-    <t>BO Homologation: Saisie GAIA</t>
-  </si>
-  <si>
-    <t>Parametrage facturation</t>
-  </si>
-  <si>
     <t>Support IP: Config Eq Acces</t>
   </si>
   <si>
@@ -125,22 +233,82 @@
     <t>500M</t>
   </si>
   <si>
-    <t>100M</t>
-  </si>
-  <si>
     <t>SYTHD150306</t>
   </si>
   <si>
-    <t>SYTRAN</t>
-  </si>
-  <si>
-    <t>LSI</t>
-  </si>
-  <si>
     <t>Principale (avec backup)</t>
   </si>
   <si>
-    <t>Offert</t>
+    <t>01/07/2026 12:26:20</t>
+  </si>
+  <si>
+    <t>4M</t>
+  </si>
+  <si>
+    <t>65530820</t>
+  </si>
+  <si>
+    <t>26/06/2026 13:54:57</t>
+  </si>
+  <si>
+    <t>TRANSFERT DE LIGNE AU PLATEAU SIEGE DE LA BNI</t>
+  </si>
+  <si>
+    <t>200M</t>
+  </si>
+  <si>
+    <t>VPNLL060103</t>
+  </si>
+  <si>
+    <t>06/07/2026 09:41:35</t>
+  </si>
+  <si>
+    <t>65411444</t>
+  </si>
+  <si>
+    <t>24/06/2026 14:51:50</t>
+  </si>
+  <si>
+    <t>PLATEAU SIEGE BNI</t>
+  </si>
+  <si>
+    <t>2720303000</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:35:28</t>
+  </si>
+  <si>
+    <t>65038851</t>
+  </si>
+  <si>
+    <t>17/06/2026 12:36:07</t>
+  </si>
+  <si>
+    <t>SAN-PEDRO//VOIE INCONNUE/AGENCE BGFI SAN PEDRO</t>
+  </si>
+  <si>
+    <t>BUVPN150100</t>
+  </si>
+  <si>
+    <t>06/07/2026 12:05:15</t>
+  </si>
+  <si>
+    <t>64827598</t>
+  </si>
+  <si>
+    <t>13/06/2026 11:24:03</t>
+  </si>
+  <si>
+    <t>AFRICA GLOBAL LOGISTICS</t>
+  </si>
+  <si>
+    <t>SAN-PEDRO</t>
+  </si>
+  <si>
+    <t>BUVPN240066</t>
+  </si>
+  <si>
+    <t>01/07/2026 15:16:51</t>
   </si>
   <si>
     <t>65587331</t>
@@ -149,28 +317,13 @@
     <t>27/06/2026 14:44:12</t>
   </si>
   <si>
-    <t>Transfert</t>
-  </si>
-  <si>
-    <t>BANQUE NATIONALE D'INVESTISSEMENT</t>
-  </si>
-  <si>
-    <t>PLATEAU</t>
-  </si>
-  <si>
     <t>ABIDJAN-PLATEAU//VOIE INCONNUE/SIEGE BNI PLATEAU</t>
   </si>
   <si>
-    <t>2M</t>
-  </si>
-  <si>
     <t>VPNLL120082</t>
   </si>
   <si>
-    <t>IP Connect LL</t>
-  </si>
-  <si>
-    <t>Ingenieur Projet: Suspension Travaux DOB</t>
+    <t>06/07/2026 09:03:44</t>
   </si>
   <si>
     <t>65087283</t>
@@ -179,52 +332,37 @@
     <t>18/06/2026 10:18:41</t>
   </si>
   <si>
-    <t>BGFIBANK</t>
-  </si>
-  <si>
     <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY RIRIERA PALMERAIE</t>
   </si>
   <si>
     <t>15M</t>
   </si>
   <si>
-    <t>6M</t>
-  </si>
-  <si>
     <t>BUVPN240112</t>
   </si>
   <si>
-    <t>65395686</t>
-  </si>
-  <si>
-    <t>24/06/2026 11:38:13</t>
-  </si>
-  <si>
-    <t>fo_virage</t>
-  </si>
-  <si>
-    <t>2720209800</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>numerique</t>
-  </si>
-  <si>
-    <t>4M</t>
-  </si>
-  <si>
-    <t>65411444</t>
-  </si>
-  <si>
-    <t>24/06/2026 14:51:50</t>
-  </si>
-  <si>
-    <t>PLATEAU SIEGE BNI</t>
-  </si>
-  <si>
-    <t>2720303000</t>
+    <t>03/07/2026 08:45:33</t>
+  </si>
+  <si>
+    <t>64303259</t>
+  </si>
+  <si>
+    <t>03/06/2026 17:36:32</t>
+  </si>
+  <si>
+    <t>PROJET COHESION SOCIALE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/ANGRE 7ème TRANCHE 0707128808</t>
+  </si>
+  <si>
+    <t>30M</t>
+  </si>
+  <si>
+    <t>SYTHD230135</t>
+  </si>
+  <si>
+    <t>30/06/2026 18:59:04</t>
   </si>
   <si>
     <t>support</t>
@@ -233,138 +371,129 @@
     <t>ftto</t>
   </si>
   <si>
-    <t>AFRICA GLOBAL LOGISTICS</t>
-  </si>
-  <si>
-    <t>En cours</t>
-  </si>
-  <si>
-    <t>65047687</t>
-  </si>
-  <si>
-    <t>17/06/2026 14:20:06</t>
-  </si>
-  <si>
-    <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/CARRE D'OR</t>
-  </si>
-  <si>
-    <t>BUVPN250006</t>
-  </si>
-  <si>
-    <t>64827598</t>
-  </si>
-  <si>
-    <t>13/06/2026 11:24:03</t>
-  </si>
-  <si>
-    <t>SAN-PEDRO</t>
-  </si>
-  <si>
-    <t>1M</t>
-  </si>
-  <si>
-    <t>BUVPN240066</t>
+    <t>65584992</t>
+  </si>
+  <si>
+    <t>27/06/2026 14:10:39</t>
+  </si>
+  <si>
+    <t>BGFI</t>
+  </si>
+  <si>
+    <t>MARCORY</t>
+  </si>
+  <si>
+    <t>SYTHD190141</t>
+  </si>
+  <si>
+    <t>27/06/2026 14:10:51</t>
+  </si>
+  <si>
+    <t>64825700</t>
+  </si>
+  <si>
+    <t>13/06/2026 10:54:39</t>
+  </si>
+  <si>
+    <t>BUVPN240003</t>
+  </si>
+  <si>
+    <t>01/07/2026 15:14:01</t>
+  </si>
+  <si>
+    <t>65400923</t>
+  </si>
+  <si>
+    <t>24/06/2026 12:37:44</t>
+  </si>
+  <si>
+    <t>BNI GESTION</t>
+  </si>
+  <si>
+    <t>SIEGE BNI PLATEAU</t>
+  </si>
+  <si>
+    <t>2720208110</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:59:53</t>
+  </si>
+  <si>
+    <t>64766439</t>
+  </si>
+  <si>
+    <t>12/06/2026 10:11:53</t>
+  </si>
+  <si>
+    <t>DOUANES</t>
+  </si>
+  <si>
+    <t>TREICHVILLE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-MARCORY//VOIE INCONNUE/ZONE3</t>
+  </si>
+  <si>
+    <t>VPNLL080017</t>
+  </si>
+  <si>
+    <t>02/07/2026 09:27:19</t>
+  </si>
+  <si>
+    <t>64551824</t>
+  </si>
+  <si>
+    <t>08/06/2026 16:23:42</t>
+  </si>
+  <si>
+    <t>//VOIE INCONNUE/</t>
+  </si>
+  <si>
+    <t>SYTHD130143</t>
+  </si>
+  <si>
+    <t>30/06/2026 19:44:04</t>
+  </si>
+  <si>
+    <t>64976030</t>
+  </si>
+  <si>
+    <t>16/06/2026 12:23:55</t>
+  </si>
+  <si>
+    <t>AEROPORT INTERNATIONAL ABIDJAN</t>
+  </si>
+  <si>
+    <t>PORT BOUET AEROPORT.</t>
+  </si>
+  <si>
+    <t>SYTHD150307</t>
+  </si>
+  <si>
+    <t>02/07/2026 15:26:02</t>
+  </si>
+  <si>
+    <t>64383567</t>
+  </si>
+  <si>
+    <t>05/06/2026 11:29:03</t>
+  </si>
+  <si>
+    <t>STE AGENCE OCI/ MILLENIUM</t>
+  </si>
+  <si>
+    <t>COCODY GOLF</t>
   </si>
   <si>
     <t>1G</t>
   </si>
   <si>
-    <t>Backup</t>
-  </si>
-  <si>
-    <t>64552630</t>
-  </si>
-  <si>
-    <t>08/06/2026 16:32:15</t>
-  </si>
-  <si>
-    <t>DREAM COSMETICS</t>
-  </si>
-  <si>
-    <t>YOPOUGON ZONE INDUSTRIELLE</t>
-  </si>
-  <si>
-    <t>80M</t>
-  </si>
-  <si>
-    <t>SYTHD200265</t>
-  </si>
-  <si>
-    <t>65548064</t>
-  </si>
-  <si>
-    <t>26/06/2026 17:03:19</t>
-  </si>
-  <si>
-    <t>TERMINAL DE SAN PEDRO</t>
-  </si>
-  <si>
-    <t>SAN PEDRO</t>
-  </si>
-  <si>
-    <t>120M</t>
-  </si>
-  <si>
-    <t>SYTHD170002</t>
-  </si>
-  <si>
-    <t>65584992</t>
-  </si>
-  <si>
-    <t>27/06/2026 14:10:39</t>
-  </si>
-  <si>
-    <t>BGFI</t>
-  </si>
-  <si>
-    <t>MARCORY</t>
-  </si>
-  <si>
-    <t>40M</t>
-  </si>
-  <si>
-    <t>SYTHD190141</t>
-  </si>
-  <si>
-    <t>64825700</t>
-  </si>
-  <si>
-    <t>13/06/2026 10:54:39</t>
-  </si>
-  <si>
-    <t>BUVPN240003</t>
-  </si>
-  <si>
-    <t>64976030</t>
-  </si>
-  <si>
-    <t>16/06/2026 12:23:55</t>
-  </si>
-  <si>
-    <t>AEROPORT INTERNATIONAL ABIDJAN</t>
-  </si>
-  <si>
-    <t>PORT BOUET AEROPORT.</t>
-  </si>
-  <si>
-    <t>SYTHD150307</t>
-  </si>
-  <si>
-    <t>64383567</t>
-  </si>
-  <si>
-    <t>05/06/2026 11:29:03</t>
-  </si>
-  <si>
-    <t>STE AGENCE OCI/ MILLENIUM</t>
-  </si>
-  <si>
-    <t>COCODY GOLF</t>
-  </si>
-  <si>
     <t>SYTHD140217</t>
   </si>
   <si>
+    <t>02/07/2026 15:17:54</t>
+  </si>
+  <si>
     <t>65514648</t>
   </si>
   <si>
@@ -386,6 +515,9 @@
     <t>BBF : Prerequis Etude</t>
   </si>
   <si>
+    <t>06/07/2026 09:29:52</t>
+  </si>
+  <si>
     <t>65534223</t>
   </si>
   <si>
@@ -398,7 +530,7 @@
     <t>SYTHD250263</t>
   </si>
   <si>
-    <t>LIAISON SPECIALISEE</t>
+    <t>06/07/2026 09:58:36</t>
   </si>
   <si>
     <t>65587639</t>
@@ -410,19 +542,61 @@
     <t>VPNLL070228</t>
   </si>
   <si>
+    <t>06/07/2026 09:05:11</t>
+  </si>
+  <si>
+    <t>65532924</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:21:48</t>
+  </si>
+  <si>
+    <t>SYTHD120096</t>
+  </si>
+  <si>
+    <t>06/07/2026 09:42:13</t>
+  </si>
+  <si>
+    <t>65081673</t>
+  </si>
+  <si>
+    <t>18/06/2026 09:01:44</t>
+  </si>
+  <si>
+    <t>PLATEAU CAMP GALLIENI</t>
+  </si>
+  <si>
+    <t>8M</t>
+  </si>
+  <si>
+    <t>BUVPN210162</t>
+  </si>
+  <si>
+    <t>01/07/2026 14:38:33</t>
+  </si>
+  <si>
+    <t>64826325</t>
+  </si>
+  <si>
+    <t>13/06/2026 11:03:35</t>
+  </si>
+  <si>
+    <t>BUVPN230259</t>
+  </si>
+  <si>
+    <t>29/06/2026 15:41:51</t>
+  </si>
+  <si>
     <t>65401420</t>
   </si>
   <si>
     <t>24/06/2026 12:44:36</t>
   </si>
   <si>
-    <t>SIEGE BNI PLATEAU</t>
-  </si>
-  <si>
     <t>2720310777</t>
   </si>
   <si>
-    <t>T0</t>
+    <t>26/06/2026 14:26:10</t>
   </si>
   <si>
     <t>65120181</t>
@@ -437,76 +611,79 @@
     <t>CHICKEN NATION ZONE 4</t>
   </si>
   <si>
-    <t>TREICHVILLE</t>
-  </si>
-  <si>
     <t>MARCORY PRES DU RESTO PETIT CAFE</t>
   </si>
   <si>
     <t>2721712130</t>
   </si>
   <si>
-    <t>DOUANES</t>
-  </si>
-  <si>
-    <t>65532924</t>
-  </si>
-  <si>
-    <t>26/06/2026 14:21:48</t>
-  </si>
-  <si>
-    <t>SYTHD120096</t>
-  </si>
-  <si>
-    <t>65081673</t>
-  </si>
-  <si>
-    <t>18/06/2026 09:01:44</t>
-  </si>
-  <si>
-    <t>PLATEAU CAMP GALLIENI</t>
-  </si>
-  <si>
-    <t>8M</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>BUVPN210162</t>
-  </si>
-  <si>
-    <t>64826325</t>
-  </si>
-  <si>
-    <t>13/06/2026 11:03:35</t>
-  </si>
-  <si>
-    <t>BUVPN230259</t>
-  </si>
-  <si>
-    <t>65400923</t>
-  </si>
-  <si>
-    <t>24/06/2026 12:37:44</t>
-  </si>
-  <si>
-    <t>BNI GESTION</t>
-  </si>
-  <si>
-    <t>2720208110</t>
-  </si>
-  <si>
-    <t>64766439</t>
-  </si>
-  <si>
-    <t>12/06/2026 10:11:53</t>
-  </si>
-  <si>
-    <t>ABIDJAN-MARCORY//VOIE INCONNUE/ZONE3</t>
-  </si>
-  <si>
-    <t>VPNLL080017</t>
+    <t>03/07/2026 17:38:01</t>
+  </si>
+  <si>
+    <t>65442117</t>
+  </si>
+  <si>
+    <t>25/06/2026 08:37:15</t>
+  </si>
+  <si>
+    <t>AEROPORT FRET DOUANES</t>
+  </si>
+  <si>
+    <t>50M</t>
+  </si>
+  <si>
+    <t>VPNLL230023</t>
+  </si>
+  <si>
+    <t>25/06/2026 08:37:36</t>
+  </si>
+  <si>
+    <t>65344048</t>
+  </si>
+  <si>
+    <t>23/06/2026 12:05:41</t>
+  </si>
+  <si>
+    <t>NSIA BANQUE</t>
+  </si>
+  <si>
+    <t>COCODY VALLON</t>
+  </si>
+  <si>
+    <t>16M</t>
+  </si>
+  <si>
+    <t>BUVPN180214</t>
+  </si>
+  <si>
+    <t>23/06/2026 12:05:48</t>
+  </si>
+  <si>
+    <t>65418027</t>
+  </si>
+  <si>
+    <t>24/06/2026 15:43:38</t>
+  </si>
+  <si>
+    <t>MAIRIE DE MARCORY</t>
+  </si>
+  <si>
+    <t>2721710160</t>
+  </si>
+  <si>
+    <t>06/07/2026 12:18:15</t>
+  </si>
+  <si>
+    <t>65402557</t>
+  </si>
+  <si>
+    <t>24/06/2026 12:58:18</t>
+  </si>
+  <si>
+    <t>2720312270</t>
+  </si>
+  <si>
+    <t>26/06/2026 14:55:41</t>
   </si>
   <si>
     <t>65089564</t>
@@ -521,19 +698,19 @@
     <t>BUVPN190189</t>
   </si>
   <si>
+    <t>01/07/2026 14:36:30</t>
+  </si>
+  <si>
     <t>65441446</t>
   </si>
   <si>
     <t>25/06/2026 08:18:23</t>
   </si>
   <si>
-    <t>AEROPORT FRET DOUANES</t>
-  </si>
-  <si>
     <t>VPNLL050188</t>
   </si>
   <si>
-    <t>VPNLL</t>
+    <t>25/06/2026 08:18:38</t>
   </si>
   <si>
     <t>65586906</t>
@@ -542,12 +719,12 @@
     <t>27/06/2026 14:36:57</t>
   </si>
   <si>
-    <t>200M</t>
-  </si>
-  <si>
     <t>VPNLL100132</t>
   </si>
   <si>
+    <t>06/07/2026 09:11:13</t>
+  </si>
+  <si>
     <t>65290949</t>
   </si>
   <si>
@@ -557,37 +734,10 @@
     <t>YOPOUGON</t>
   </si>
   <si>
-    <t>50M</t>
-  </si>
-  <si>
     <t>BUVPN170232</t>
   </si>
   <si>
-    <t>65038851</t>
-  </si>
-  <si>
-    <t>17/06/2026 12:36:07</t>
-  </si>
-  <si>
-    <t>SAN-PEDRO//VOIE INCONNUE/AGENCE BGFI SAN PEDRO</t>
-  </si>
-  <si>
-    <t>7M</t>
-  </si>
-  <si>
-    <t>BUVPN150100</t>
-  </si>
-  <si>
-    <t>65040167</t>
-  </si>
-  <si>
-    <t>17/06/2026 12:49:29</t>
-  </si>
-  <si>
-    <t>ABIDJAN-KOUMASSI//VOIE INCONNUE/CENTRAL KOUMASSI</t>
-  </si>
-  <si>
-    <t>BUVPN200211</t>
+    <t>02/07/2026 11:55:36</t>
   </si>
   <si>
     <t>65395290</t>
@@ -599,6 +749,9 @@
     <t>2720209900</t>
   </si>
   <si>
+    <t>26/06/2026 14:30:26</t>
+  </si>
+  <si>
     <t>65084584</t>
   </si>
   <si>
@@ -611,58 +764,7 @@
     <t>BUVPN140220</t>
   </si>
   <si>
-    <t>65442117</t>
-  </si>
-  <si>
-    <t>25/06/2026 08:37:15</t>
-  </si>
-  <si>
-    <t>VPNLL230023</t>
-  </si>
-  <si>
-    <t>65344048</t>
-  </si>
-  <si>
-    <t>23/06/2026 12:05:41</t>
-  </si>
-  <si>
-    <t>NSIA BANQUE</t>
-  </si>
-  <si>
-    <t>COCODY VALLON</t>
-  </si>
-  <si>
-    <t>16M</t>
-  </si>
-  <si>
-    <t>BUVPN180214</t>
-  </si>
-  <si>
-    <t>65402557</t>
-  </si>
-  <si>
-    <t>24/06/2026 12:58:18</t>
-  </si>
-  <si>
-    <t>2720312270</t>
-  </si>
-  <si>
-    <t>64303259</t>
-  </si>
-  <si>
-    <t>03/06/2026 17:36:32</t>
-  </si>
-  <si>
-    <t>PROJET COHESION SOCIALE</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/ANGRE 7ème TRANCHE 0707128808</t>
-  </si>
-  <si>
-    <t>30M</t>
-  </si>
-  <si>
-    <t>SYTHD230135</t>
+    <t>01/07/2026 14:37:01</t>
   </si>
   <si>
     <t>65532025</t>
@@ -677,6 +779,9 @@
     <t>SYTHD160199</t>
   </si>
   <si>
+    <t>06/07/2026 09:46:18</t>
+  </si>
+  <si>
     <t>64975214</t>
   </si>
   <si>
@@ -689,6 +794,9 @@
     <t>SYTHD230156</t>
   </si>
   <si>
+    <t>02/07/2026 19:17:16</t>
+  </si>
+  <si>
     <t>65337758</t>
   </si>
   <si>
@@ -704,15 +812,15 @@
     <t>130M</t>
   </si>
   <si>
-    <t>110M</t>
-  </si>
-  <si>
     <t>SYTHD180206</t>
   </si>
   <si>
     <t>Saisie ASCOM</t>
   </si>
   <si>
+    <t>06/07/2026 09:23:49</t>
+  </si>
+  <si>
     <t>65394128</t>
   </si>
   <si>
@@ -722,6 +830,9 @@
     <t>2720316600</t>
   </si>
   <si>
+    <t>26/06/2026 14:08:59</t>
+  </si>
+  <si>
     <t>64827269</t>
   </si>
   <si>
@@ -731,6 +842,9 @@
     <t>BUVPN240065</t>
   </si>
   <si>
+    <t>01/07/2026 15:16:10</t>
+  </si>
+  <si>
     <t>65088465</t>
   </si>
   <si>
@@ -743,16 +857,7 @@
     <t>BUVPN150015</t>
   </si>
   <si>
-    <t>65036621</t>
-  </si>
-  <si>
-    <t>17/06/2026 12:16:19</t>
-  </si>
-  <si>
-    <t>GRAND-BASSAM//VOIE INCONNUE/CENTRAL MODESTE</t>
-  </si>
-  <si>
-    <t>BUVPN210009</t>
+    <t>03/07/2026 08:20:08</t>
   </si>
   <si>
     <t>64206190</t>
@@ -764,6 +869,9 @@
     <t>BUVPN220077</t>
   </si>
   <si>
+    <t>25/06/2026 17:12:17</t>
+  </si>
+  <si>
     <t>65085655</t>
   </si>
   <si>
@@ -776,6 +884,9 @@
     <t>BUVPN230172</t>
   </si>
   <si>
+    <t>01/07/2026 14:37:22</t>
+  </si>
+  <si>
     <t>65514856</t>
   </si>
   <si>
@@ -788,28 +899,7 @@
     <t>SYTHD220197</t>
   </si>
   <si>
-    <t>65047487</t>
-  </si>
-  <si>
-    <t>17/06/2026 14:17:27</t>
-  </si>
-  <si>
-    <t>60M</t>
-  </si>
-  <si>
-    <t>BUVPN150014</t>
-  </si>
-  <si>
-    <t>65418027</t>
-  </si>
-  <si>
-    <t>24/06/2026 15:43:38</t>
-  </si>
-  <si>
-    <t>MAIRIE DE MARCORY</t>
-  </si>
-  <si>
-    <t>2721710160</t>
+    <t>26/06/2026 10:42:44</t>
   </si>
   <si>
     <t>64388621</t>
@@ -827,6 +917,9 @@
     <t>VPNLL080113</t>
   </si>
   <si>
+    <t>02/07/2026 17:04:17</t>
+  </si>
+  <si>
     <t>64824601</t>
   </si>
   <si>
@@ -836,6 +929,9 @@
     <t>BUVPN230260</t>
   </si>
   <si>
+    <t>01/07/2026 15:18:28</t>
+  </si>
+  <si>
     <t>64551757</t>
   </si>
   <si>
@@ -845,40 +941,44 @@
     <t>YOPOUGON ZONE INDUSTRIELLE.</t>
   </si>
   <si>
-    <t>SYTHD130143</t>
-  </si>
-  <si>
-    <t>65530820</t>
-  </si>
-  <si>
-    <t>26/06/2026 13:54:57</t>
-  </si>
-  <si>
-    <t>TRANSFERT DE LIGNE AU PLATEAU SIEGE DE LA BNI</t>
-  </si>
-  <si>
-    <t>VPNLL060103</t>
-  </si>
-  <si>
-    <t>65046091</t>
-  </si>
-  <si>
-    <t>17/06/2026 14:02:54</t>
-  </si>
-  <si>
-    <t>///CONTACT:57776000</t>
-  </si>
-  <si>
-    <t>BUVPN250103</t>
-  </si>
-  <si>
-    <t>64551824</t>
-  </si>
-  <si>
-    <t>08/06/2026 16:23:42</t>
-  </si>
-  <si>
-    <t>//VOIE INCONNUE/</t>
+    <t>25/06/2026 13:29:07</t>
+  </si>
+  <si>
+    <t>65780721</t>
+  </si>
+  <si>
+    <t>01/07/2026 15:51:44</t>
+  </si>
+  <si>
+    <t>SOCIETE CARGILL COCOA SARL</t>
+  </si>
+  <si>
+    <t>ZONE INDUSTRIELLE DE YOPOUGON
+0707037814</t>
+  </si>
+  <si>
+    <t>2721221350</t>
+  </si>
+  <si>
+    <t>01/07/2026 18:53:37</t>
+  </si>
+  <si>
+    <t>65867272</t>
+  </si>
+  <si>
+    <t>03/07/2026 11:02:52</t>
+  </si>
+  <si>
+    <t>SGCI</t>
+  </si>
+  <si>
+    <t>COCODY ATTOBAN</t>
+  </si>
+  <si>
+    <t>BUVPN190115</t>
+  </si>
+  <si>
+    <t>06/07/2026 12:40:07</t>
   </si>
   <si>
     <t>65811580</t>
@@ -899,38 +999,43 @@
     <t>SYTHD210090</t>
   </si>
   <si>
-    <t>65867272</t>
-  </si>
-  <si>
-    <t>03/07/2026 11:02:52</t>
-  </si>
-  <si>
-    <t>SGCI</t>
-  </si>
-  <si>
-    <t>COCODY ATTOBAN</t>
-  </si>
-  <si>
-    <t>512K</t>
-  </si>
-  <si>
-    <t>BUVPN190115</t>
-  </si>
-  <si>
-    <t>65780721</t>
-  </si>
-  <si>
-    <t>01/07/2026 15:51:44</t>
-  </si>
-  <si>
-    <t>SOCIETE CARGILL COCOA SARL</t>
-  </si>
-  <si>
-    <t>ZONE INDUSTRIELLE DE YOPOUGON
-0707037814</t>
-  </si>
-  <si>
-    <t>2721221350</t>
+    <t>02/07/2026 12:19:08</t>
+  </si>
+  <si>
+    <t>66040814</t>
+  </si>
+  <si>
+    <t>06/07/2026 12:54:46</t>
+  </si>
+  <si>
+    <t>STE AGL CI</t>
+  </si>
+  <si>
+    <t>TREEICHVILLE AV CHRISTIANI AU SIEGE DE AGL -CI</t>
+  </si>
+  <si>
+    <t>SYTHD190031</t>
+  </si>
+  <si>
+    <t>06/07/2026 12:54:53</t>
+  </si>
+  <si>
+    <t>66040156</t>
+  </si>
+  <si>
+    <t>06/07/2026 12:48:24</t>
+  </si>
+  <si>
+    <t>STE AGL</t>
+  </si>
+  <si>
+    <t>TREICHVILLE AV CHRISTIANI AU SIEGE DE LA STE AGL</t>
+  </si>
+  <si>
+    <t>SYTHD190030</t>
+  </si>
+  <si>
+    <t>06/07/2026 12:48:40</t>
   </si>
 </sst>
 </file>
@@ -1307,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -1317,11 +1422,11 @@
     <col min="5" max="5" width="49.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="59.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="44.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="69.83203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="35" style="1" customWidth="1"/>
-    <col min="12" max="12" width="37.9140625" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="69.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="35.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="33" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35" style="1" customWidth="1"/>
     <col min="13" max="13" width="39.9140625" customWidth="1"/>
     <col min="14" max="14" width="48.58203125" customWidth="1"/>
   </cols>
@@ -1331,37 +1436,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>1</v>
@@ -1372,442 +1477,442 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" t="s">
+      <c r="M3" t="s">
         <v>38</v>
       </c>
-      <c r="C3" t="s">
+      <c r="N3" t="s">
         <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" t="s">
         <v>47</v>
       </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" t="s">
-        <v>45</v>
-      </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s">
         <v>54</v>
       </c>
-      <c r="B5" t="s">
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" t="s">
         <v>55</v>
       </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="M5" t="s">
         <v>56</v>
       </c>
-      <c r="E5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" t="s">
-        <v>57</v>
-      </c>
-      <c r="L5" t="s">
-        <v>58</v>
-      </c>
-      <c r="M5" t="s">
-        <v>59</v>
-      </c>
       <c r="N5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="M6" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="K7" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="M7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="K8" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="M8" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="N8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J9" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="K9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" t="s">
         <v>85</v>
       </c>
-      <c r="L9" t="s">
-        <v>33</v>
-      </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K10" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" t="s">
+        <v>91</v>
+      </c>
+      <c r="M10" t="s">
         <v>24</v>
       </c>
-      <c r="K10" t="s">
-        <v>91</v>
-      </c>
-      <c r="L10" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" t="s">
-        <v>34</v>
-      </c>
       <c r="N10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="F11" t="s">
         <v>95</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" t="s">
+        <v>97</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" t="s">
         <v>96</v>
       </c>
-      <c r="I11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
         <v>24</v>
       </c>
-      <c r="K11" t="s">
-        <v>97</v>
-      </c>
-      <c r="L11" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" t="s">
-        <v>34</v>
-      </c>
       <c r="N11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -1818,2024 +1923,1936 @@
         <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="K12" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="M12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J13" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="K13" t="s">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="L13" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N13" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J14" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="K14" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="M14" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I15" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K15" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="L15" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="M15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J16" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="K16" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
       <c r="L16" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="N16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I17" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J17" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="K17" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="L17" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="M17" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" t="s">
+        <v>140</v>
+      </c>
+      <c r="K18" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" t="s">
+        <v>139</v>
+      </c>
+      <c r="M18" t="s">
+        <v>38</v>
+      </c>
+      <c r="N18" t="s">
         <v>68</v>
-      </c>
-      <c r="J18" t="s">
-        <v>46</v>
-      </c>
-      <c r="K18" t="s">
-        <v>129</v>
-      </c>
-      <c r="L18" t="s">
-        <v>130</v>
-      </c>
-      <c r="M18" t="s">
-        <v>59</v>
-      </c>
-      <c r="N18" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F19" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I19" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J19" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="K19" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="L19" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="N19" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I20" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J20" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="K20" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="L20" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="M20" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="F21" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="G21" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="H21" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="I21" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="J21" t="s">
-        <v>25</v>
+        <v>161</v>
       </c>
       <c r="K21" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="L21" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="M21" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="G22" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="H22" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="I22" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J22" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="K22" t="s">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="M22" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J23" t="s">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="K23" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="L23" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="M23" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="N23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="B24" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
         <v>157</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I24" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J24" t="s">
-        <v>25</v>
+        <v>174</v>
       </c>
       <c r="K24" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="L24" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="M24" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I25" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="K25" t="s">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c r="L25" t="s">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="M25" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="B26" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I26" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="J26" t="s">
+        <v>184</v>
+      </c>
+      <c r="K26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" t="s">
+        <v>183</v>
+      </c>
+      <c r="M26" t="s">
         <v>24</v>
       </c>
-      <c r="K26" t="s">
-        <v>166</v>
-      </c>
-      <c r="L26" t="s">
-        <v>167</v>
-      </c>
-      <c r="M26" t="s">
-        <v>20</v>
-      </c>
       <c r="N26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="G27" t="s">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I27" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J27" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="K27" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="L27" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="M27" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="N27" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="I28" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J28" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="K28" t="s">
-        <v>176</v>
+        <v>16</v>
       </c>
       <c r="L28" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="M28" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="N28" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B29" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="F29" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="H29" t="s">
-        <v>180</v>
+        <v>28</v>
       </c>
       <c r="I29" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J29" t="s">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="K29" t="s">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="M29" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="F30" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="H30" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="I30" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J30" t="s">
-        <v>22</v>
+        <v>208</v>
       </c>
       <c r="K30" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="L30" t="s">
-        <v>45</v>
+        <v>207</v>
       </c>
       <c r="M30" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
+        <v>211</v>
+      </c>
+      <c r="F31" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
+        <v>40</v>
+      </c>
+      <c r="I31" t="s">
+        <v>61</v>
+      </c>
+      <c r="J31" t="s">
+        <v>213</v>
+      </c>
+      <c r="K31" t="s">
+        <v>16</v>
+      </c>
+      <c r="L31" t="s">
+        <v>212</v>
+      </c>
+      <c r="M31" t="s">
         <v>56</v>
       </c>
-      <c r="E31" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J31" t="s">
-        <v>46</v>
-      </c>
-      <c r="K31" t="s">
-        <v>188</v>
-      </c>
-      <c r="L31" t="s">
-        <v>58</v>
-      </c>
-      <c r="M31" t="s">
-        <v>59</v>
-      </c>
       <c r="N31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="F32" t="s">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="G32" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="I32" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J32" t="s">
-        <v>25</v>
+        <v>217</v>
       </c>
       <c r="K32" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c r="L32" t="s">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="M32" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="N32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="B33" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="G33" t="s">
-        <v>175</v>
+        <v>60</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I33" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="J33" t="s">
+        <v>222</v>
+      </c>
+      <c r="K33" t="s">
+        <v>16</v>
+      </c>
+      <c r="L33" t="s">
+        <v>221</v>
+      </c>
+      <c r="M33" t="s">
         <v>24</v>
       </c>
-      <c r="K33" t="s">
-        <v>195</v>
-      </c>
-      <c r="L33" t="s">
-        <v>167</v>
-      </c>
-      <c r="M33" t="s">
-        <v>20</v>
-      </c>
       <c r="N33" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E34" t="s">
+        <v>131</v>
+      </c>
+      <c r="F34" t="s">
         <v>198</v>
       </c>
-      <c r="F34" t="s">
-        <v>199</v>
-      </c>
       <c r="G34" t="s">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="H34" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="I34" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="J34" t="s">
+        <v>226</v>
+      </c>
+      <c r="K34" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" t="s">
+        <v>225</v>
+      </c>
+      <c r="M34" t="s">
         <v>24</v>
       </c>
-      <c r="K34" t="s">
-        <v>201</v>
-      </c>
-      <c r="L34" t="s">
-        <v>19</v>
-      </c>
-      <c r="M34" t="s">
-        <v>20</v>
-      </c>
       <c r="N34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="B35" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I35" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J35" t="s">
-        <v>46</v>
+        <v>230</v>
       </c>
       <c r="K35" t="s">
-        <v>204</v>
+        <v>16</v>
       </c>
       <c r="L35" t="s">
-        <v>130</v>
+        <v>229</v>
       </c>
       <c r="M35" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="N35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E36" t="s">
-        <v>207</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="G36" t="s">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I36" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J36" t="s">
-        <v>22</v>
+        <v>235</v>
       </c>
       <c r="K36" t="s">
-        <v>210</v>
+        <v>16</v>
       </c>
       <c r="L36" t="s">
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="M36" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N36" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="B37" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>213</v>
+        <v>54</v>
       </c>
       <c r="G37" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H37" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I37" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J37" t="s">
-        <v>46</v>
+        <v>239</v>
       </c>
       <c r="K37" t="s">
-        <v>214</v>
+        <v>16</v>
       </c>
       <c r="L37" t="s">
-        <v>33</v>
+        <v>238</v>
       </c>
       <c r="M37" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="N37" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="B38" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>29</v>
+        <v>242</v>
       </c>
       <c r="G38" t="s">
-        <v>217</v>
+        <v>60</v>
       </c>
       <c r="H38" t="s">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="I38" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J38" t="s">
-        <v>22</v>
+        <v>244</v>
       </c>
       <c r="K38" t="s">
-        <v>218</v>
+        <v>16</v>
       </c>
       <c r="L38" t="s">
-        <v>33</v>
+        <v>243</v>
       </c>
       <c r="M38" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N38" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>221</v>
+        <v>53</v>
       </c>
       <c r="F39" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="G39" t="s">
-        <v>223</v>
+        <v>22</v>
       </c>
       <c r="H39" t="s">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="I39" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J39" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="K39" t="s">
-        <v>225</v>
+        <v>16</v>
       </c>
       <c r="L39" t="s">
-        <v>122</v>
+        <v>248</v>
       </c>
       <c r="M39" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N39" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="B40" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G40" t="s">
-        <v>14</v>
+        <v>252</v>
       </c>
       <c r="H40" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I40" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40" t="s">
+        <v>254</v>
+      </c>
+      <c r="K40" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" t="s">
+        <v>253</v>
+      </c>
+      <c r="M40" t="s">
+        <v>38</v>
+      </c>
+      <c r="N40" t="s">
         <v>68</v>
-      </c>
-      <c r="J40" t="s">
-        <v>46</v>
-      </c>
-      <c r="K40" t="s">
-        <v>229</v>
-      </c>
-      <c r="L40" t="s">
-        <v>58</v>
-      </c>
-      <c r="M40" t="s">
-        <v>59</v>
-      </c>
-      <c r="N40" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="B41" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>257</v>
       </c>
       <c r="F41" t="s">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="G41" t="s">
-        <v>43</v>
+        <v>259</v>
       </c>
       <c r="H41" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="I41" t="s">
-        <v>36</v>
+        <v>261</v>
       </c>
       <c r="J41" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="K41" t="s">
-        <v>232</v>
+        <v>16</v>
       </c>
       <c r="L41" t="s">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="M41" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N41" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B42" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F42" t="s">
-        <v>235</v>
+        <v>54</v>
       </c>
       <c r="G42" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H42" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="I42" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J42" t="s">
-        <v>22</v>
+        <v>266</v>
       </c>
       <c r="K42" t="s">
-        <v>236</v>
+        <v>16</v>
       </c>
       <c r="L42" t="s">
-        <v>45</v>
+        <v>265</v>
       </c>
       <c r="M42" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="N42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="B43" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="F43" t="s">
-        <v>239</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="H43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I43" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J43" t="s">
-        <v>22</v>
+        <v>270</v>
       </c>
       <c r="K43" t="s">
-        <v>240</v>
+        <v>16</v>
       </c>
       <c r="L43" t="s">
-        <v>45</v>
+        <v>269</v>
       </c>
       <c r="M43" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N43" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="B44" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="G44" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="H44" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I44" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="J44" t="s">
-        <v>23</v>
+        <v>275</v>
       </c>
       <c r="K44" t="s">
-        <v>243</v>
+        <v>16</v>
       </c>
       <c r="L44" t="s">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="M44" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="B45" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="F45" t="s">
-        <v>246</v>
+        <v>116</v>
       </c>
       <c r="G45" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="H45" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="I45" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
       <c r="K45" t="s">
-        <v>247</v>
+        <v>16</v>
       </c>
       <c r="L45" t="s">
-        <v>45</v>
+        <v>278</v>
       </c>
       <c r="M45" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N45" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="B46" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>89</v>
+        <v>282</v>
       </c>
       <c r="G46" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="H46" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I46" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J46" t="s">
+        <v>284</v>
+      </c>
+      <c r="K46" t="s">
+        <v>16</v>
+      </c>
+      <c r="L46" t="s">
+        <v>283</v>
+      </c>
+      <c r="M46" t="s">
         <v>24</v>
       </c>
-      <c r="K46" t="s">
-        <v>251</v>
-      </c>
-      <c r="L46" t="s">
-        <v>33</v>
-      </c>
-      <c r="M46" t="s">
-        <v>34</v>
-      </c>
       <c r="N46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="B47" t="s">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>287</v>
       </c>
       <c r="F47" t="s">
-        <v>235</v>
+        <v>45</v>
       </c>
       <c r="G47" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="H47" t="s">
-        <v>254</v>
+        <v>40</v>
       </c>
       <c r="I47" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J47" t="s">
-        <v>22</v>
+        <v>289</v>
       </c>
       <c r="K47" t="s">
-        <v>255</v>
+        <v>16</v>
       </c>
       <c r="L47" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="M47" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="B48" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="C48" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="F48" t="s">
-        <v>95</v>
+        <v>293</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H48" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I48" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J48" t="s">
-        <v>22</v>
+        <v>295</v>
       </c>
       <c r="K48" t="s">
-        <v>259</v>
+        <v>16</v>
       </c>
       <c r="L48" t="s">
-        <v>130</v>
+        <v>294</v>
       </c>
       <c r="M48" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="N48" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="B49" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E49" t="s">
-        <v>262</v>
+        <v>89</v>
       </c>
       <c r="F49" t="s">
-        <v>263</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H49" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="I49" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="J49" t="s">
-        <v>22</v>
+        <v>299</v>
       </c>
       <c r="K49" t="s">
-        <v>264</v>
+        <v>16</v>
       </c>
       <c r="L49" t="s">
-        <v>167</v>
+        <v>298</v>
       </c>
       <c r="M49" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="B50" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="C50" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="F50" t="s">
-        <v>75</v>
+        <v>302</v>
       </c>
       <c r="G50" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="I50" t="s">
-        <v>36</v>
+        <v>261</v>
       </c>
       <c r="J50" t="s">
-        <v>25</v>
+        <v>303</v>
       </c>
       <c r="K50" t="s">
-        <v>267</v>
+        <v>16</v>
       </c>
       <c r="L50" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="M50" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N50" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="B51" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="C51" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E51" t="s">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="F51" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="G51" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="I51" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J51" t="s">
-        <v>226</v>
+        <v>309</v>
       </c>
       <c r="K51" t="s">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c r="L51" t="s">
-        <v>33</v>
+        <v>308</v>
       </c>
       <c r="M51" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="N51" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="B52" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="C52" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>40</v>
+        <v>312</v>
       </c>
       <c r="F52" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="G52" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="H52" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I52" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>46</v>
+        <v>315</v>
       </c>
       <c r="K52" t="s">
-        <v>275</v>
+        <v>16</v>
       </c>
       <c r="L52" t="s">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="M52" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="B53" t="s">
-        <v>277</v>
+        <v>317</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>49</v>
+        <v>318</v>
       </c>
       <c r="F53" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="G53" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H53" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I53" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J53" t="s">
-        <v>22</v>
+        <v>321</v>
       </c>
       <c r="K53" t="s">
-        <v>279</v>
+        <v>16</v>
       </c>
       <c r="L53" t="s">
-        <v>45</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N53" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>280</v>
+        <v>322</v>
       </c>
       <c r="B54" t="s">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E54" t="s">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="F54" t="s">
-        <v>282</v>
+        <v>325</v>
       </c>
       <c r="G54" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="H54" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="I54" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J54" t="s">
-        <v>22</v>
+        <v>327</v>
       </c>
       <c r="K54" t="s">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c r="L54" t="s">
-        <v>122</v>
+        <v>326</v>
       </c>
       <c r="M54" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N54" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="B55" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="F55" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="G55" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="H55" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I55" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J55" t="s">
-        <v>24</v>
+        <v>333</v>
       </c>
       <c r="K55" t="s">
-        <v>287</v>
+        <v>16</v>
       </c>
       <c r="L55" t="s">
-        <v>33</v>
+        <v>332</v>
       </c>
       <c r="M55" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N55" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>288</v>
-      </c>
-      <c r="B56" t="s">
-        <v>289</v>
-      </c>
-      <c r="C56" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" t="s">
-        <v>16</v>
-      </c>
-      <c r="E56" t="s">
-        <v>290</v>
-      </c>
-      <c r="F56" t="s">
-        <v>291</v>
-      </c>
-      <c r="G56" t="s">
-        <v>52</v>
-      </c>
-      <c r="H56" t="s">
-        <v>292</v>
-      </c>
-      <c r="I56" t="s">
-        <v>36</v>
-      </c>
-      <c r="J56" t="s">
-        <v>24</v>
-      </c>
-      <c r="K56" t="s">
-        <v>293</v>
-      </c>
-      <c r="L56" t="s">
-        <v>19</v>
-      </c>
-      <c r="M56" t="s">
-        <v>20</v>
-      </c>
-      <c r="N56" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>294</v>
-      </c>
-      <c r="B57" t="s">
-        <v>295</v>
-      </c>
-      <c r="C57" t="s">
-        <v>39</v>
-      </c>
-      <c r="D57" t="s">
-        <v>56</v>
-      </c>
-      <c r="E57" t="s">
-        <v>296</v>
-      </c>
-      <c r="F57" t="s">
-        <v>297</v>
-      </c>
-      <c r="G57" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" t="s">
-        <v>14</v>
-      </c>
-      <c r="I57" t="s">
-        <v>36</v>
-      </c>
-      <c r="J57" t="s">
-        <v>24</v>
-      </c>
-      <c r="K57" t="s">
-        <v>298</v>
-      </c>
-      <c r="L57" t="s">
-        <v>58</v>
-      </c>
-      <c r="M57" t="s">
-        <v>59</v>
-      </c>
-      <c r="N57" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N57"/>
+  <autoFilter ref="A1:N55"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$R$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$R$39</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="261">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -257,9 +257,6 @@
     <t>1G</t>
   </si>
   <si>
-    <t>100M</t>
-  </si>
-  <si>
     <t>SYTHD220197</t>
   </si>
   <si>
@@ -335,33 +332,9 @@
     <t>06/07/2026 09:05:11</t>
   </si>
   <si>
-    <t>64551757</t>
-  </si>
-  <si>
-    <t>08/06/2026 16:23:11</t>
-  </si>
-  <si>
-    <t>DREAM COSMETICS</t>
-  </si>
-  <si>
-    <t>DREAM COSMETICS/ YOPOUGON</t>
-  </si>
-  <si>
-    <t>YOPOUGON ZONE INDUSTRIELLE.</t>
-  </si>
-  <si>
-    <t>SYTHD130143</t>
-  </si>
-  <si>
     <t>Principale (avec backup)</t>
   </si>
   <si>
-    <t>Saisie ASCOM</t>
-  </si>
-  <si>
-    <t>25/06/2026 13:29:07</t>
-  </si>
-  <si>
     <t>65532924</t>
   </si>
   <si>
@@ -471,30 +444,6 @@
   </si>
   <si>
     <t>06/07/2026 09:46:18</t>
-  </si>
-  <si>
-    <t>65337758</t>
-  </si>
-  <si>
-    <t>23/06/2026 10:55:27</t>
-  </si>
-  <si>
-    <t>PIXAGILITY AFRIQUE</t>
-  </si>
-  <si>
-    <t>PIXAGILITYAFRIQUE</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/2PLATEAUX-VALLONS</t>
-  </si>
-  <si>
-    <t>130M</t>
-  </si>
-  <si>
-    <t>SYTHD180206</t>
-  </si>
-  <si>
-    <t>06/07/2026 09:23:49</t>
   </si>
   <si>
     <t>65394128</t>
@@ -1241,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -1641,13 +1590,13 @@
         <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O7" t="s">
         <v>18</v>
       </c>
       <c r="P7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q7" t="s">
         <v>38</v>
@@ -1658,10 +1607,10 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
         <v>78</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
@@ -1676,16 +1625,16 @@
         <v>20</v>
       </c>
       <c r="G8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" t="s">
         <v>80</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
         <v>81</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>82</v>
       </c>
       <c r="K8" t="s">
         <v>36</v>
@@ -1697,13 +1646,13 @@
         <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O8" t="s">
         <v>18</v>
       </c>
       <c r="P8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q8" t="s">
         <v>38</v>
@@ -1714,10 +1663,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
         <v>85</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
@@ -1732,19 +1681,19 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s">
         <v>46</v>
       </c>
       <c r="J9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" t="s">
         <v>88</v>
-      </c>
-      <c r="K9" t="s">
-        <v>89</v>
       </c>
       <c r="L9" t="s">
         <v>28</v>
@@ -1753,13 +1702,13 @@
         <v>62</v>
       </c>
       <c r="N9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O9" t="s">
         <v>18</v>
       </c>
       <c r="P9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q9" t="s">
         <v>21</v>
@@ -1770,10 +1719,10 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" t="s">
         <v>92</v>
-      </c>
-      <c r="B10" t="s">
-        <v>93</v>
       </c>
       <c r="C10" t="s">
         <v>25</v>
@@ -1797,10 +1746,10 @@
         <v>46</v>
       </c>
       <c r="J10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L10" t="s">
         <v>28</v>
@@ -1809,13 +1758,13 @@
         <v>49</v>
       </c>
       <c r="N10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O10" t="s">
         <v>18</v>
       </c>
       <c r="P10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q10" t="s">
         <v>38</v>
@@ -1826,10 +1775,10 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" t="s">
         <v>97</v>
-      </c>
-      <c r="B11" t="s">
-        <v>98</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
@@ -1865,13 +1814,13 @@
         <v>49</v>
       </c>
       <c r="N11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O11" t="s">
         <v>18</v>
       </c>
       <c r="P11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q11" t="s">
         <v>21</v>
@@ -1888,7 +1837,7 @@
         <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
@@ -1900,75 +1849,75 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="H12" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J12" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="L12" t="s">
         <v>28</v>
       </c>
       <c r="M12" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="O12" t="s">
         <v>18</v>
       </c>
       <c r="P12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q12" t="s">
         <v>38</v>
       </c>
       <c r="R12" t="s">
-        <v>107</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
         <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s">
         <v>46</v>
       </c>
       <c r="J13" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="K13" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="L13" t="s">
         <v>28</v>
@@ -1977,16 +1926,16 @@
         <v>49</v>
       </c>
       <c r="N13" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O13" t="s">
         <v>18</v>
       </c>
       <c r="P13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="R13" t="s">
         <v>22</v>
@@ -1994,10 +1943,10 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
         <v>25</v>
@@ -2012,7 +1961,7 @@
         <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2021,25 +1970,25 @@
         <v>46</v>
       </c>
       <c r="J14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="K14" t="s">
         <v>18</v>
       </c>
       <c r="L14" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M14" t="s">
         <v>49</v>
       </c>
       <c r="N14" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="O14" t="s">
         <v>18</v>
       </c>
       <c r="P14" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="Q14" t="s">
         <v>48</v>
@@ -2050,55 +1999,55 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="I15" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
         <v>117</v>
       </c>
       <c r="K15" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="L15" t="s">
         <v>24</v>
       </c>
       <c r="M15" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O15" t="s">
         <v>18</v>
       </c>
       <c r="P15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q15" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="R15" t="s">
         <v>22</v>
@@ -2106,55 +2055,55 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s">
         <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H16" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J16" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="K16" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N16" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="O16" t="s">
         <v>18</v>
       </c>
       <c r="P16" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="Q16" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="R16" t="s">
         <v>22</v>
@@ -2162,37 +2111,37 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="H17" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="I17" t="s">
         <v>46</v>
       </c>
       <c r="J17" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="K17" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="L17" t="s">
         <v>28</v>
@@ -2201,16 +2150,16 @@
         <v>49</v>
       </c>
       <c r="N17" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="O17" t="s">
         <v>18</v>
       </c>
       <c r="P17" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="Q17" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="R17" t="s">
         <v>22</v>
@@ -2218,37 +2167,37 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B18" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C18" t="s">
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G18" t="s">
         <v>44</v>
       </c>
       <c r="H18" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="I18" t="s">
         <v>46</v>
       </c>
       <c r="J18" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="K18" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="L18" t="s">
         <v>28</v>
@@ -2257,16 +2206,16 @@
         <v>49</v>
       </c>
       <c r="N18" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="O18" t="s">
         <v>18</v>
       </c>
       <c r="P18" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="Q18" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="R18" t="s">
         <v>22</v>
@@ -2274,22 +2223,22 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
         <v>44</v>
@@ -2301,10 +2250,10 @@
         <v>46</v>
       </c>
       <c r="J19" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="K19" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="L19" t="s">
         <v>28</v>
@@ -2313,16 +2262,16 @@
         <v>49</v>
       </c>
       <c r="N19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O19" t="s">
         <v>18</v>
       </c>
       <c r="P19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="Q19" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="R19" t="s">
         <v>22</v>
@@ -2330,22 +2279,22 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G20" t="s">
         <v>44</v>
@@ -2357,28 +2306,28 @@
         <v>46</v>
       </c>
       <c r="J20" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="K20" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="L20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M20" t="s">
         <v>49</v>
       </c>
       <c r="N20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="O20" t="s">
         <v>18</v>
       </c>
       <c r="P20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="Q20" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="R20" t="s">
         <v>22</v>
@@ -2386,10 +2335,10 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C21" t="s">
         <v>31</v>
@@ -2401,107 +2350,107 @@
         <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H21" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I21" t="s">
         <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K21" t="s">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="L21" t="s">
         <v>28</v>
       </c>
       <c r="M21" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="N21" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="O21" t="s">
         <v>18</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="Q21" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="R21" t="s">
-        <v>107</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>151</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="I22" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="K22" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M22" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O22" t="s">
         <v>18</v>
       </c>
       <c r="P22" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q22" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="R22" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C23" t="s">
         <v>31</v>
@@ -2516,19 +2465,19 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" t="s">
+        <v>160</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s">
         <v>161</v>
       </c>
-      <c r="H23" t="s">
-        <v>162</v>
-      </c>
-      <c r="I23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" t="s">
-        <v>163</v>
-      </c>
       <c r="K23" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="L23" t="s">
         <v>28</v>
@@ -2537,16 +2486,16 @@
         <v>23</v>
       </c>
       <c r="N23" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O23" t="s">
         <v>18</v>
       </c>
       <c r="P23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q23" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="R23" t="s">
         <v>22</v>
@@ -2554,13 +2503,13 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
         <v>19</v>
@@ -2572,19 +2521,19 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" t="s">
+        <v>167</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s">
         <v>168</v>
       </c>
-      <c r="H24" t="s">
+      <c r="K24" t="s">
         <v>169</v>
-      </c>
-      <c r="I24" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" t="s">
-        <v>170</v>
-      </c>
-      <c r="K24" t="s">
-        <v>27</v>
       </c>
       <c r="L24" t="s">
         <v>28</v>
@@ -2593,27 +2542,27 @@
         <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O24" t="s">
         <v>18</v>
       </c>
       <c r="P24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q24" t="s">
         <v>38</v>
       </c>
       <c r="R24" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C25" t="s">
         <v>31</v>
@@ -2628,19 +2577,19 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="H25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I25" t="s">
         <v>18</v>
       </c>
       <c r="J25" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L25" t="s">
         <v>28</v>
@@ -2649,13 +2598,13 @@
         <v>23</v>
       </c>
       <c r="N25" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="O25" t="s">
         <v>18</v>
       </c>
       <c r="P25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Q25" t="s">
         <v>21</v>
@@ -2666,10 +2615,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
@@ -2684,19 +2633,19 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H26" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I26" t="s">
         <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K26" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="L26" t="s">
         <v>28</v>
@@ -2705,27 +2654,27 @@
         <v>23</v>
       </c>
       <c r="N26" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="O26" t="s">
         <v>18</v>
       </c>
       <c r="P26" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q26" t="s">
         <v>38</v>
       </c>
       <c r="R26" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C27" t="s">
         <v>31</v>
@@ -2740,19 +2689,19 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="H27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L27" t="s">
         <v>28</v>
@@ -2761,13 +2710,13 @@
         <v>23</v>
       </c>
       <c r="N27" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O27" t="s">
         <v>18</v>
       </c>
       <c r="P27" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="Q27" t="s">
         <v>21</v>
@@ -2778,13 +2727,13 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
         <v>19</v>
@@ -2796,19 +2745,19 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="H28" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="I28" t="s">
         <v>18</v>
       </c>
       <c r="J28" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="K28" t="s">
-        <v>74</v>
+        <v>193</v>
       </c>
       <c r="L28" t="s">
         <v>28</v>
@@ -2817,27 +2766,27 @@
         <v>23</v>
       </c>
       <c r="N28" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="O28" t="s">
         <v>18</v>
       </c>
       <c r="P28" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="Q28" t="s">
         <v>38</v>
       </c>
       <c r="R28" t="s">
-        <v>172</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B29" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C29" t="s">
         <v>31</v>
@@ -2852,19 +2801,19 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="H29" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I29" t="s">
         <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="K29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L29" t="s">
         <v>28</v>
@@ -2873,13 +2822,13 @@
         <v>23</v>
       </c>
       <c r="N29" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="O29" t="s">
         <v>18</v>
       </c>
       <c r="P29" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="Q29" t="s">
         <v>21</v>
@@ -2890,37 +2839,37 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B30" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C30" t="s">
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E30" t="s">
         <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G30" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="H30" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
       </c>
       <c r="J30" t="s">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="K30" t="s">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
@@ -2929,16 +2878,16 @@
         <v>23</v>
       </c>
       <c r="N30" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="O30" t="s">
         <v>18</v>
       </c>
       <c r="P30" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="Q30" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="R30" t="s">
         <v>22</v>
@@ -2946,13 +2895,13 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
         <v>19</v>
@@ -2964,19 +2913,19 @@
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="H31" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I31" t="s">
         <v>18</v>
       </c>
       <c r="J31" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="K31" t="s">
-        <v>89</v>
+        <v>212</v>
       </c>
       <c r="L31" t="s">
         <v>28</v>
@@ -2985,13 +2934,13 @@
         <v>23</v>
       </c>
       <c r="N31" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="O31" t="s">
         <v>18</v>
       </c>
       <c r="P31" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Q31" t="s">
         <v>21</v>
@@ -3002,37 +2951,37 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B32" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
         <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="H32" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I32" t="s">
         <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K32" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="L32" t="s">
         <v>28</v>
@@ -3041,16 +2990,16 @@
         <v>23</v>
       </c>
       <c r="N32" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="O32" t="s">
         <v>18</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="Q32" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="R32" t="s">
         <v>22</v>
@@ -3058,13 +3007,13 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B33" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
         <v>19</v>
@@ -3076,19 +3025,19 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="H33" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I33" t="s">
         <v>18</v>
       </c>
       <c r="J33" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K33" t="s">
-        <v>229</v>
+        <v>88</v>
       </c>
       <c r="L33" t="s">
         <v>28</v>
@@ -3097,13 +3046,13 @@
         <v>23</v>
       </c>
       <c r="N33" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="O33" t="s">
         <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="Q33" t="s">
         <v>21</v>
@@ -3114,10 +3063,10 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
@@ -3132,19 +3081,19 @@
         <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="H34" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I34" t="s">
         <v>18</v>
       </c>
       <c r="J34" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L34" t="s">
         <v>28</v>
@@ -3153,13 +3102,13 @@
         <v>23</v>
       </c>
       <c r="N34" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O34" t="s">
         <v>18</v>
       </c>
       <c r="P34" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="Q34" t="s">
         <v>21</v>
@@ -3170,10 +3119,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C35" t="s">
         <v>31</v>
@@ -3188,19 +3137,19 @@
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="H35" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I35" t="s">
         <v>18</v>
       </c>
       <c r="J35" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="K35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L35" t="s">
         <v>28</v>
@@ -3209,13 +3158,13 @@
         <v>23</v>
       </c>
       <c r="N35" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="O35" t="s">
         <v>18</v>
       </c>
       <c r="P35" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Q35" t="s">
         <v>21</v>
@@ -3226,10 +3175,10 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B36" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C36" t="s">
         <v>31</v>
@@ -3244,19 +3193,19 @@
         <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I36" t="s">
         <v>18</v>
       </c>
       <c r="J36" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L36" t="s">
         <v>28</v>
@@ -3265,13 +3214,13 @@
         <v>23</v>
       </c>
       <c r="N36" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O36" t="s">
         <v>18</v>
       </c>
       <c r="P36" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="Q36" t="s">
         <v>21</v>
@@ -3282,10 +3231,10 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B37" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C37" t="s">
         <v>31</v>
@@ -3300,19 +3249,19 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>176</v>
+        <v>247</v>
       </c>
       <c r="H37" t="s">
-        <v>252</v>
+        <v>181</v>
       </c>
       <c r="I37" t="s">
         <v>18</v>
       </c>
       <c r="J37" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="K37" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="L37" t="s">
         <v>28</v>
@@ -3321,16 +3270,16 @@
         <v>23</v>
       </c>
       <c r="N37" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="O37" t="s">
         <v>18</v>
       </c>
       <c r="P37" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="Q37" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="R37" t="s">
         <v>22</v>
@@ -3338,10 +3287,10 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B38" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C38" t="s">
         <v>31</v>
@@ -3356,19 +3305,19 @@
         <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="H38" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="K38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L38" t="s">
         <v>28</v>
@@ -3377,13 +3326,13 @@
         <v>23</v>
       </c>
       <c r="N38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="O38" t="s">
         <v>18</v>
       </c>
       <c r="P38" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="Q38" t="s">
         <v>21</v>
@@ -3394,10 +3343,10 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C39" t="s">
         <v>31</v>
@@ -3412,19 +3361,19 @@
         <v>20</v>
       </c>
       <c r="G39" t="s">
-        <v>264</v>
+        <v>166</v>
       </c>
       <c r="H39" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="I39" t="s">
         <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>265</v>
+        <v>168</v>
       </c>
       <c r="K39" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="L39" t="s">
         <v>28</v>
@@ -3433,135 +3382,23 @@
         <v>23</v>
       </c>
       <c r="N39" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="O39" t="s">
         <v>18</v>
       </c>
       <c r="P39" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="Q39" t="s">
         <v>38</v>
       </c>
       <c r="R39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>268</v>
-      </c>
-      <c r="B40" t="s">
-        <v>269</v>
-      </c>
-      <c r="C40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D40" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" t="s">
-        <v>18</v>
-      </c>
-      <c r="F40" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" t="s">
-        <v>176</v>
-      </c>
-      <c r="H40" t="s">
-        <v>270</v>
-      </c>
-      <c r="I40" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" t="s">
-        <v>271</v>
-      </c>
-      <c r="K40" t="s">
-        <v>89</v>
-      </c>
-      <c r="L40" t="s">
-        <v>28</v>
-      </c>
-      <c r="M40" t="s">
-        <v>23</v>
-      </c>
-      <c r="N40" t="s">
-        <v>273</v>
-      </c>
-      <c r="O40" t="s">
-        <v>18</v>
-      </c>
-      <c r="P40" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>21</v>
-      </c>
-      <c r="R40" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>274</v>
-      </c>
-      <c r="B41" t="s">
-        <v>275</v>
-      </c>
-      <c r="C41" t="s">
-        <v>31</v>
-      </c>
-      <c r="D41" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" t="s">
-        <v>183</v>
-      </c>
-      <c r="H41" t="s">
-        <v>184</v>
-      </c>
-      <c r="I41" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" t="s">
-        <v>185</v>
-      </c>
-      <c r="K41" t="s">
-        <v>186</v>
-      </c>
-      <c r="L41" t="s">
-        <v>28</v>
-      </c>
-      <c r="M41" t="s">
-        <v>23</v>
-      </c>
-      <c r="N41" t="s">
-        <v>277</v>
-      </c>
-      <c r="O41" t="s">
-        <v>18</v>
-      </c>
-      <c r="P41" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>38</v>
-      </c>
-      <c r="R41" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R41"/>
+  <autoFilter ref="A1:R39"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -9,18 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$R$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$Q$21</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="150">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -65,9 +65,6 @@
     <t>DEBIT INITIAL</t>
   </si>
   <si>
-    <t>ID TACHE</t>
-  </si>
-  <si>
     <t>ETAT TACHE</t>
   </si>
   <si>
@@ -98,21 +95,18 @@
     <t>sur mesure</t>
   </si>
   <si>
-    <t>1G</t>
-  </si>
-  <si>
     <t>100M</t>
   </si>
   <si>
+    <t>VPNLL</t>
+  </si>
+  <si>
     <t>LS</t>
   </si>
   <si>
     <t>Nominale</t>
   </si>
   <si>
-    <t>Support IP: Correction</t>
-  </si>
-  <si>
     <t>En cours</t>
   </si>
   <si>
@@ -122,7 +116,7 @@
     <t>Parametrage facturation</t>
   </si>
   <si>
-    <t>support</t>
+    <t>BO Homologation: Saisie GAIA</t>
   </si>
   <si>
     <t>ftto</t>
@@ -131,9 +125,6 @@
     <t>BUVPN</t>
   </si>
   <si>
-    <t>20M</t>
-  </si>
-  <si>
     <t>catalogue</t>
   </si>
   <si>
@@ -170,9 +161,6 @@
     <t>numerique</t>
   </si>
   <si>
-    <t>65531900</t>
-  </si>
-  <si>
     <t>Ingenieur Projet: Suspension Travaux DOB</t>
   </si>
   <si>
@@ -188,9 +176,6 @@
     <t>2720209900</t>
   </si>
   <si>
-    <t>65533632</t>
-  </si>
-  <si>
     <t>26/06/2026 14:30:26</t>
   </si>
   <si>
@@ -203,9 +188,6 @@
     <t>2720209800</t>
   </si>
   <si>
-    <t>65532878</t>
-  </si>
-  <si>
     <t>26/06/2026 14:21:02</t>
   </si>
   <si>
@@ -230,9 +212,6 @@
     <t>26/06/2026 14:59:53</t>
   </si>
   <si>
-    <t>65536408</t>
-  </si>
-  <si>
     <t>65401420</t>
   </si>
   <si>
@@ -242,9 +221,6 @@
     <t>2720310777</t>
   </si>
   <si>
-    <t>65533279</t>
-  </si>
-  <si>
     <t>26/06/2026 14:26:10</t>
   </si>
   <si>
@@ -257,9 +233,6 @@
     <t>2720312270</t>
   </si>
   <si>
-    <t>65536161</t>
-  </si>
-  <si>
     <t>26/06/2026 14:55:41</t>
   </si>
   <si>
@@ -275,15 +248,9 @@
     <t>2720303000</t>
   </si>
   <si>
-    <t>65534180</t>
-  </si>
-  <si>
     <t>26/06/2026 14:35:28</t>
   </si>
   <si>
-    <t>65442117</t>
-  </si>
-  <si>
     <t>25/06/2026 08:37:15</t>
   </si>
   <si>
@@ -302,69 +269,21 @@
     <t>IP Connect LL</t>
   </si>
   <si>
-    <t>66580530</t>
-  </si>
-  <si>
     <t>BBF : Prerequis Etude</t>
   </si>
   <si>
     <t>15/07/2026 10:11:02</t>
   </si>
   <si>
-    <t>65514648</t>
-  </si>
-  <si>
-    <t>26/06/2026 10:39:13</t>
-  </si>
-  <si>
-    <t>PROSUMA</t>
-  </si>
-  <si>
     <t>ABIDJAN-PLATEAU//VOIE INCONNUE/PLATEAU</t>
   </si>
   <si>
-    <t>5M</t>
-  </si>
-  <si>
-    <t>BUVPN230159</t>
-  </si>
-  <si>
-    <t>66725563</t>
-  </si>
-  <si>
-    <t>17/07/2026 13:37:33</t>
-  </si>
-  <si>
-    <t>65514856</t>
-  </si>
-  <si>
-    <t>26/06/2026 10:42:34</t>
-  </si>
-  <si>
-    <t>GCB COCOA</t>
-  </si>
-  <si>
-    <t>SAN PEDRO</t>
-  </si>
-  <si>
-    <t>SYTHD220197</t>
-  </si>
-  <si>
     <t>SYTRAN</t>
   </si>
   <si>
     <t>LSI</t>
   </si>
   <si>
-    <t>66850290</t>
-  </si>
-  <si>
-    <t>BO Homologation: Saisie BSCS</t>
-  </si>
-  <si>
-    <t>20/07/2026 08:17:51</t>
-  </si>
-  <si>
     <t>65530820</t>
   </si>
   <si>
@@ -380,9 +299,6 @@
     <t>VPNLL060103</t>
   </si>
   <si>
-    <t>66021892</t>
-  </si>
-  <si>
     <t>06/07/2026 09:41:35</t>
   </si>
   <si>
@@ -404,9 +320,6 @@
     <t>06/07/2026 09:46:18</t>
   </si>
   <si>
-    <t>66022272</t>
-  </si>
-  <si>
     <t>65532924</t>
   </si>
   <si>
@@ -419,9 +332,6 @@
     <t>06/07/2026 09:42:13</t>
   </si>
   <si>
-    <t>66021936</t>
-  </si>
-  <si>
     <t>65534223</t>
   </si>
   <si>
@@ -434,9 +344,6 @@
     <t>SYTHD250263</t>
   </si>
   <si>
-    <t>66023299</t>
-  </si>
-  <si>
     <t>06/07/2026 09:58:36</t>
   </si>
   <si>
@@ -452,9 +359,6 @@
     <t>VPNLL100132</t>
   </si>
   <si>
-    <t>66019680</t>
-  </si>
-  <si>
     <t>06/07/2026 09:11:13</t>
   </si>
   <si>
@@ -470,9 +374,6 @@
     <t>06/07/2026 09:03:44</t>
   </si>
   <si>
-    <t>66019321</t>
-  </si>
-  <si>
     <t>65587639</t>
   </si>
   <si>
@@ -485,33 +386,6 @@
     <t>06/07/2026 09:05:11</t>
   </si>
   <si>
-    <t>66019377</t>
-  </si>
-  <si>
-    <t>65811580</t>
-  </si>
-  <si>
-    <t>02/07/2026 12:18:31</t>
-  </si>
-  <si>
-    <t>BAOBAB COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>ABIDJAN-YOPOUGON//VOIE INCONNUE/CARREFOUR LUBAFRIQUE</t>
-  </si>
-  <si>
-    <t>SYTHD210090</t>
-  </si>
-  <si>
-    <t>66850743</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Validation intervention</t>
-  </si>
-  <si>
-    <t>20/07/2026 08:37:47</t>
-  </si>
-  <si>
     <t>66163696</t>
   </si>
   <si>
@@ -530,31 +404,7 @@
     <t>BUVPN200043</t>
   </si>
   <si>
-    <t>66578424</t>
-  </si>
-  <si>
-    <t>15/07/2026 09:47:39</t>
-  </si>
-  <si>
-    <t>66610159</t>
-  </si>
-  <si>
-    <t>15/07/2026 15:36:05</t>
-  </si>
-  <si>
-    <t>ELIZABETH GLASER PEDIATRIC AIDS FOUNDATION</t>
-  </si>
-  <si>
-    <t>COCODY VALLON, IMMEUBLE</t>
-  </si>
-  <si>
-    <t>2722414505</t>
-  </si>
-  <si>
-    <t>66743124</t>
-  </si>
-  <si>
-    <t>17/07/2026 16:56:19</t>
+    <t>21/07/2026 16:49:56</t>
   </si>
   <si>
     <t>66856525</t>
@@ -572,10 +422,67 @@
     <t>2721250972</t>
   </si>
   <si>
-    <t>20/07/2026 10:56:50</t>
-  </si>
-  <si>
-    <t>66861056</t>
+    <t>24/07/2026 14:33:56</t>
+  </si>
+  <si>
+    <t>67108287</t>
+  </si>
+  <si>
+    <t>24/07/2026 09:00:54</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIRIENNE DE GESTION DU PATRIMOINE FERROVIERE</t>
+  </si>
+  <si>
+    <t>BOUAKE COMMERCE</t>
+  </si>
+  <si>
+    <t>SYTHD230247</t>
+  </si>
+  <si>
+    <t>24/07/2026 11:23:53</t>
+  </si>
+  <si>
+    <t>67152246</t>
+  </si>
+  <si>
+    <t>24/07/2026 17:08:58</t>
+  </si>
+  <si>
+    <t>VIPNET</t>
+  </si>
+  <si>
+    <t>TRANSFERT DU LIEN SYTHD 250258
+DEBIT : 20MBPS
+EXT A: DT VIPNET ATTOBAN
+EXT B : GIZ KORHOGO</t>
+  </si>
+  <si>
+    <t>SYTHD250258</t>
+  </si>
+  <si>
+    <t>24/07/2026 18:10:45</t>
+  </si>
+  <si>
+    <t>67249021</t>
+  </si>
+  <si>
+    <t>27/07/2026 10:03:44</t>
+  </si>
+  <si>
+    <t>CI-ENERGIES</t>
+  </si>
+  <si>
+    <t>PLATEAU IMMEUBLE EECI</t>
+  </si>
+  <si>
+    <t>150M</t>
+  </si>
+  <si>
+    <t>SYTHD210210</t>
+  </si>
+  <si>
+    <t>27/07/2026 10:05:26</t>
   </si>
 </sst>
 </file>
@@ -952,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -964,18 +871,17 @@
     <col min="7" max="7" width="59.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="44.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="38.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="29.1640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="25.83203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="69.83203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="35.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="33" style="1" customWidth="1"/>
-    <col min="15" max="15" width="35" style="1" customWidth="1"/>
-    <col min="16" max="16" width="37.9140625" customWidth="1"/>
-    <col min="17" max="17" width="39.9140625" customWidth="1"/>
-    <col min="18" max="18" width="48.58203125" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="69.83203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="33" style="1" customWidth="1"/>
+    <col min="14" max="14" width="35" style="1" customWidth="1"/>
+    <col min="15" max="15" width="37.9140625" customWidth="1"/>
+    <col min="16" max="16" width="39.9140625" customWidth="1"/>
+    <col min="17" max="17" width="48.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1019,1196 +925,1077 @@
         <v>15</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
         <v>40</v>
       </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="O2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" t="s">
+      <c r="P2" t="s">
         <v>42</v>
       </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="Q2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
         <v>46</v>
       </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
         <v>47</v>
       </c>
-      <c r="M2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="O3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
         <v>43</v>
       </c>
-      <c r="P2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="L4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
         <v>25</v>
       </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7" t="s">
+        <v>58</v>
+      </c>
+      <c r="P7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" t="s">
         <v>41</v>
       </c>
-      <c r="G3" t="s">
+      <c r="P8" t="s">
         <v>42</v>
       </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="Q8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>65442117</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" t="s">
-        <v>58</v>
-      </c>
-      <c r="N4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4" t="s">
-        <v>56</v>
-      </c>
-      <c r="P4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M5" t="s">
-        <v>65</v>
-      </c>
-      <c r="N5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" t="s">
-        <v>63</v>
-      </c>
-      <c r="P5" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>45</v>
-      </c>
-      <c r="R5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s">
-        <v>70</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" t="s">
-        <v>71</v>
-      </c>
-      <c r="N6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" t="s">
-        <v>69</v>
-      </c>
-      <c r="P6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>45</v>
-      </c>
-      <c r="R6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" t="s">
         <v>75</v>
       </c>
-      <c r="K7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="H9" t="s">
         <v>76</v>
       </c>
-      <c r="N7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" t="s">
-        <v>74</v>
-      </c>
-      <c r="P7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>45</v>
-      </c>
-      <c r="R7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
         <v>77</v>
       </c>
-      <c r="B8" t="s">
+      <c r="O9" t="s">
         <v>78</v>
       </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8" t="s">
-        <v>82</v>
-      </c>
-      <c r="N8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" t="s">
-        <v>80</v>
-      </c>
-      <c r="P8" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>45</v>
-      </c>
-      <c r="R8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" t="s">
-        <v>91</v>
-      </c>
-      <c r="M9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" t="s">
-        <v>88</v>
-      </c>
       <c r="P9" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="Q9" t="s">
         <v>24</v>
       </c>
-      <c r="R9" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="K10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="M10" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="O10" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="s">
         <v>24</v>
       </c>
-      <c r="R10" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
-        <v>21</v>
-      </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L11" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="M11" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="O11" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="Q11" t="s">
-        <v>107</v>
-      </c>
-      <c r="R11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="K12" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L12" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="M12" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="O12" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="P12" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="Q12" t="s">
         <v>24</v>
       </c>
-      <c r="R12" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="K13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>103</v>
+      </c>
+      <c r="O13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" t="s">
         <v>36</v>
       </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
-      <c r="M13" t="s">
-        <v>123</v>
-      </c>
-      <c r="N13" t="s">
-        <v>18</v>
-      </c>
-      <c r="O13" t="s">
-        <v>122</v>
-      </c>
-      <c r="P13" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" t="s">
         <v>107</v>
       </c>
-      <c r="R13" t="s">
-        <v>25</v>
+      <c r="H14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" t="s">
+        <v>109</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O14" t="s">
+        <v>78</v>
+      </c>
+      <c r="P14" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>125</v>
-      </c>
-      <c r="B14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
         <v>20</v>
       </c>
-      <c r="E14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
-        <v>129</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="F15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" t="s">
+        <v>43</v>
+      </c>
+      <c r="L15" t="s">
+        <v>113</v>
+      </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>112</v>
+      </c>
+      <c r="O15" t="s">
+        <v>78</v>
+      </c>
+      <c r="P15" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="L14" t="s">
-        <v>47</v>
-      </c>
-      <c r="M14" t="s">
-        <v>128</v>
-      </c>
-      <c r="N14" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" t="s">
-        <v>127</v>
-      </c>
-      <c r="P14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
         <v>107</v>
       </c>
-      <c r="R14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" t="s">
-        <v>96</v>
-      </c>
-      <c r="H15" t="s">
-        <v>132</v>
-      </c>
-      <c r="I15" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>134</v>
-      </c>
-      <c r="K15" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" t="s">
-        <v>47</v>
-      </c>
-      <c r="M15" t="s">
-        <v>135</v>
-      </c>
-      <c r="N15" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15" t="s">
-        <v>133</v>
-      </c>
-      <c r="P15" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>107</v>
-      </c>
-      <c r="R15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" t="s">
-        <v>138</v>
-      </c>
       <c r="H16" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J16" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="K16" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L16" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="M16" t="s">
-        <v>141</v>
+        <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="O16" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="P16" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="Q16" t="s">
         <v>24</v>
       </c>
-      <c r="R16" t="s">
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>142</v>
-      </c>
-      <c r="B17" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" t="s">
-        <v>138</v>
-      </c>
-      <c r="H17" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" t="s">
-        <v>146</v>
-      </c>
       <c r="K17" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L17" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="M17" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="O17" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="P17" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="Q17" t="s">
         <v>24</v>
       </c>
-      <c r="R17" t="s">
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>147</v>
-      </c>
-      <c r="B18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" t="s">
-        <v>138</v>
-      </c>
-      <c r="H18" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
-        <v>151</v>
-      </c>
       <c r="K18" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="L18" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="M18" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="O18" t="s">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="P18" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="Q18" t="s">
         <v>24</v>
       </c>
-      <c r="R18" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" t="s">
         <v>20</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" t="s">
         <v>21</v>
       </c>
-      <c r="F19" t="s">
-        <v>154</v>
-      </c>
-      <c r="G19" t="s">
-        <v>155</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" t="s">
         <v>33</v>
       </c>
-      <c r="I19" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s">
-        <v>157</v>
-      </c>
       <c r="K19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>135</v>
+      </c>
+      <c r="O19" t="s">
+        <v>82</v>
+      </c>
+      <c r="P19" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" t="s">
         <v>36</v>
       </c>
-      <c r="L19" t="s">
-        <v>158</v>
-      </c>
-      <c r="M19" t="s">
-        <v>159</v>
-      </c>
-      <c r="N19" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" t="s">
-        <v>156</v>
-      </c>
-      <c r="P19" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>107</v>
-      </c>
-      <c r="R19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>160</v>
-      </c>
-      <c r="B20" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F20" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="G20" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="H20" t="s">
-        <v>164</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J20" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="K20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L20" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="M20" t="s">
-        <v>167</v>
+        <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="O20" t="s">
-        <v>165</v>
+        <v>22</v>
       </c>
       <c r="P20" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="Q20" t="s">
         <v>24</v>
       </c>
-      <c r="R20" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="G21" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="H21" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J21" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="M21" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="O21" t="s">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="Q21" t="s">
-        <v>45</v>
-      </c>
-      <c r="R21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B22" t="s">
-        <v>176</v>
-      </c>
-      <c r="C22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" t="s">
-        <v>177</v>
-      </c>
-      <c r="G22" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s">
-        <v>181</v>
-      </c>
-      <c r="K22" t="s">
-        <v>36</v>
-      </c>
-      <c r="L22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M22" t="s">
-        <v>180</v>
-      </c>
-      <c r="N22" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" t="s">
-        <v>179</v>
-      </c>
-      <c r="P22" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>45</v>
-      </c>
-      <c r="R22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R22"/>
+  <autoFilter ref="A1:Q21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/transfert.xlsx
+++ b/transfert.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Données du dasboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$S$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données du dasboard'!$A$1:$S$30</definedName>
     <definedName name="corbeil">#REF!</definedName>
     <definedName name="corbeilHeader">#REF!</definedName>
     <definedName name="en_tete">#REF!</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="243">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -528,27 +528,6 @@
   </si>
   <si>
     <t>10/08/2026 11:37:58</t>
-  </si>
-  <si>
-    <t>67285588</t>
-  </si>
-  <si>
-    <t>27/07/2026 16:43:17</t>
-  </si>
-  <si>
-    <t>MINIERE  DE LA LOBO</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY BONOUMIN</t>
-  </si>
-  <si>
-    <t>SYTHD230030</t>
-  </si>
-  <si>
-    <t>68061949</t>
-  </si>
-  <si>
-    <t>10/08/2026 11:24:19</t>
   </si>
   <si>
     <t>67525337</t>
@@ -1156,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -2368,10 +2347,10 @@
         <v>167</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
         <v>22</v>
@@ -2386,13 +2365,13 @@
         <v>169</v>
       </c>
       <c r="I21" t="s">
-        <v>156</v>
+        <v>31</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="K21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L21" t="s">
         <v>35</v>
@@ -2401,7 +2380,7 @@
         <v>93</v>
       </c>
       <c r="N21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O21" t="s">
         <v>19</v>
@@ -2410,27 +2389,27 @@
         <v>170</v>
       </c>
       <c r="Q21" t="s">
-        <v>37</v>
+        <v>171</v>
       </c>
       <c r="R21" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="S21" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
         <v>22</v>
@@ -2439,19 +2418,19 @@
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s">
         <v>176</v>
       </c>
       <c r="I22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J22" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="K22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L22" t="s">
         <v>35</v>
@@ -2460,7 +2439,7 @@
         <v>93</v>
       </c>
       <c r="N22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O22" t="s">
         <v>19</v>
@@ -2469,22 +2448,22 @@
         <v>177</v>
       </c>
       <c r="Q22" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="R22" t="s">
         <v>25</v>
       </c>
       <c r="S22" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B23" t="s">
         <v>181</v>
       </c>
-      <c r="B23" t="s">
-        <v>182</v>
-      </c>
       <c r="C23" t="s">
         <v>41</v>
       </c>
@@ -2492,43 +2471,43 @@
         <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
         <v>23</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="H23" t="s">
         <v>183</v>
       </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
       </c>
       <c r="K23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L23" t="s">
         <v>35</v>
       </c>
       <c r="M23" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="N23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O23" t="s">
         <v>19</v>
       </c>
       <c r="P23" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q23" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="R23" t="s">
         <v>25</v>
@@ -2539,37 +2518,37 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F24" t="s">
         <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I24" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s">
         <v>35</v>
@@ -2578,7 +2557,7 @@
         <v>33</v>
       </c>
       <c r="N24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O24" t="s">
         <v>19</v>
@@ -2590,7 +2569,7 @@
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="S24" t="s">
         <v>26</v>
@@ -2622,7 +2601,7 @@
         <v>198</v>
       </c>
       <c r="I25" t="s">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="J25" t="s">
         <v>89</v>
@@ -2634,19 +2613,19 @@
         <v>35</v>
       </c>
       <c r="M25" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="N25" t="s">
+        <v>202</v>
+      </c>
+      <c r="O25" t="s">
+        <v>19</v>
+      </c>
+      <c r="P25" t="s">
         <v>200</v>
       </c>
-      <c r="O25" t="s">
-        <v>19</v>
-      </c>
-      <c r="P25" t="s">
-        <v>199</v>
-      </c>
       <c r="Q25" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="R25" t="s">
         <v>108</v>
@@ -2657,10 +2636,10 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C26" t="s">
         <v>20</v>
@@ -2669,46 +2648,46 @@
         <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J26" t="s">
-        <v>89</v>
+        <v>208</v>
       </c>
       <c r="K26" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L26" t="s">
         <v>35</v>
       </c>
       <c r="M26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N26" t="s">
+        <v>210</v>
+      </c>
+      <c r="O26" t="s">
+        <v>19</v>
+      </c>
+      <c r="P26" t="s">
         <v>209</v>
       </c>
-      <c r="O26" t="s">
-        <v>19</v>
-      </c>
-      <c r="P26" t="s">
-        <v>207</v>
-      </c>
       <c r="Q26" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="R26" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="S26" t="s">
         <v>26</v>
@@ -2716,10 +2695,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
@@ -2728,57 +2707,57 @@
         <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H27" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I27" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J27" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L27" t="s">
         <v>35</v>
       </c>
       <c r="M27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N27" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O27" t="s">
         <v>19</v>
       </c>
       <c r="P27" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q27" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="R27" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="S27" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B28" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C28" t="s">
         <v>20</v>
@@ -2787,22 +2766,22 @@
         <v>30</v>
       </c>
       <c r="E28" t="s">
-        <v>22</v>
+        <v>223</v>
       </c>
       <c r="F28" t="s">
         <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="H28" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="I28" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="J28" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K28" t="s">
         <v>226</v>
@@ -2814,13 +2793,13 @@
         <v>27</v>
       </c>
       <c r="N28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="O28" t="s">
         <v>19</v>
       </c>
       <c r="P28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q28" t="s">
         <v>107</v>
@@ -2829,42 +2808,42 @@
         <v>108</v>
       </c>
       <c r="S28" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>227</v>
+      </c>
+      <c r="B29" t="s">
         <v>228</v>
       </c>
-      <c r="B29" t="s">
-        <v>229</v>
-      </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E29" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
       <c r="F29" t="s">
         <v>23</v>
       </c>
       <c r="G29" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="H29" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="I29" t="s">
-        <v>223</v>
+        <v>34</v>
       </c>
       <c r="J29" t="s">
-        <v>224</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L29" t="s">
         <v>35</v>
@@ -2873,7 +2852,7 @@
         <v>27</v>
       </c>
       <c r="N29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O29" t="s">
         <v>19</v>
@@ -2888,7 +2867,7 @@
         <v>108</v>
       </c>
       <c r="S29" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
@@ -2899,10 +2878,10 @@
         <v>235</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
         <v>22</v>
@@ -2917,13 +2896,13 @@
         <v>237</v>
       </c>
       <c r="I30" t="s">
-        <v>34</v>
+        <v>238</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
       <c r="K30" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L30" t="s">
         <v>35</v>
@@ -2932,85 +2911,26 @@
         <v>27</v>
       </c>
       <c r="N30" t="s">
+        <v>242</v>
+      </c>
+      <c r="O30" t="s">
+        <v>19</v>
+      </c>
+      <c r="P30" t="s">
         <v>240</v>
       </c>
-      <c r="O30" t="s">
-        <v>19</v>
-      </c>
-      <c r="P30" t="s">
-        <v>238</v>
-      </c>
       <c r="Q30" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="R30" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="S30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>241</v>
-      </c>
-      <c r="B31" t="s">
-        <v>242</v>
-      </c>
-      <c r="C31" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" t="s">
-        <v>243</v>
-      </c>
-      <c r="H31" t="s">
-        <v>244</v>
-      </c>
-      <c r="I31" t="s">
-        <v>245</v>
-      </c>
-      <c r="J31" t="s">
-        <v>246</v>
-      </c>
-      <c r="K31" t="s">
-        <v>248</v>
-      </c>
-      <c r="L31" t="s">
-        <v>35</v>
-      </c>
-      <c r="M31" t="s">
-        <v>27</v>
-      </c>
-      <c r="N31" t="s">
-        <v>249</v>
-      </c>
-      <c r="O31" t="s">
-        <v>19</v>
-      </c>
-      <c r="P31" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>24</v>
-      </c>
-      <c r="R31" t="s">
-        <v>25</v>
-      </c>
-      <c r="S31" t="s">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S31"/>
+  <autoFilter ref="A1:S30"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
